--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -41674,19 +41674,19 @@
         </is>
       </c>
       <c r="D1250" t="n">
-        <v>56.9</v>
+        <v>106.3</v>
       </c>
       <c r="E1250" t="n">
-        <v>341.1</v>
+        <v>390.5</v>
       </c>
       <c r="F1250" t="n">
-        <v>11052.2</v>
+        <v>11101.6</v>
       </c>
       <c r="G1250" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H1250" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1250" t="n">
         <v>3</v>
@@ -41707,19 +41707,19 @@
         </is>
       </c>
       <c r="D1251" t="n">
-        <v>55.1</v>
+        <v>133.5</v>
       </c>
       <c r="E1251" t="n">
-        <v>393.2</v>
+        <v>471.6</v>
       </c>
       <c r="F1251" t="n">
-        <v>11084.2</v>
+        <v>11162.6</v>
       </c>
       <c r="G1251" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1251" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1251" t="n">
         <v>2</v>
@@ -41740,19 +41740,19 @@
         </is>
       </c>
       <c r="D1252" t="n">
-        <v>58.8</v>
+        <v>112.9</v>
       </c>
       <c r="E1252" t="n">
-        <v>403.6</v>
+        <v>457.7</v>
       </c>
       <c r="F1252" t="n">
-        <v>10268.7</v>
+        <v>10322.8</v>
       </c>
       <c r="G1252" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H1252" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1252" t="n">
         <v>4</v>
@@ -41773,13 +41773,13 @@
         </is>
       </c>
       <c r="D1253" t="n">
-        <v>86.2</v>
+        <v>167.5</v>
       </c>
       <c r="E1253" t="n">
-        <v>439.5</v>
+        <v>520.8</v>
       </c>
       <c r="F1253" t="n">
-        <v>10104.1</v>
+        <v>10185.4</v>
       </c>
       <c r="G1253" t="n">
         <v>1</v>
@@ -41806,13 +41806,13 @@
         </is>
       </c>
       <c r="D1254" t="n">
-        <v>56.8</v>
+        <v>130.3</v>
       </c>
       <c r="E1254" t="n">
-        <v>428.2</v>
+        <v>501.7</v>
       </c>
       <c r="F1254" t="n">
-        <v>11363</v>
+        <v>11436.5</v>
       </c>
       <c r="G1254" t="n">
         <v>5</v>
@@ -41839,16 +41839,16 @@
         </is>
       </c>
       <c r="D1255" t="n">
-        <v>53.5</v>
+        <v>124.2</v>
       </c>
       <c r="E1255" t="n">
-        <v>314.7</v>
+        <v>385.4</v>
       </c>
       <c r="F1255" t="n">
-        <v>9148.6</v>
+        <v>9219.299999999999</v>
       </c>
       <c r="G1255" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H1255" t="n">
         <v>8</v>
@@ -41872,19 +41872,19 @@
         </is>
       </c>
       <c r="D1256" t="n">
-        <v>44.2</v>
+        <v>137.4</v>
       </c>
       <c r="E1256" t="n">
-        <v>330</v>
+        <v>423.2</v>
       </c>
       <c r="F1256" t="n">
-        <v>9934.1</v>
+        <v>10027.3</v>
       </c>
       <c r="G1256" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H1256" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I1256" t="n">
         <v>6</v>
@@ -41905,16 +41905,16 @@
         </is>
       </c>
       <c r="D1257" t="n">
-        <v>71.5</v>
+        <v>131.3</v>
       </c>
       <c r="E1257" t="n">
-        <v>377</v>
+        <v>436.8</v>
       </c>
       <c r="F1257" t="n">
-        <v>7912</v>
+        <v>7971.8</v>
       </c>
       <c r="G1257" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1257" t="n">
         <v>5</v>
@@ -41941,16 +41941,16 @@
         <v>49.90000000000001</v>
       </c>
       <c r="E1258" t="n">
-        <v>391</v>
+        <v>440.4</v>
       </c>
       <c r="F1258" t="n">
-        <v>11102.1</v>
+        <v>11151.5</v>
       </c>
       <c r="G1258" t="n">
         <v>8</v>
       </c>
       <c r="H1258" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1258" t="n">
         <v>3</v>
@@ -41974,10 +41974,10 @@
         <v>70.40000000000001</v>
       </c>
       <c r="E1259" t="n">
-        <v>463.6</v>
+        <v>542</v>
       </c>
       <c r="F1259" t="n">
-        <v>11154.6</v>
+        <v>11233</v>
       </c>
       <c r="G1259" t="n">
         <v>5</v>
@@ -42007,10 +42007,10 @@
         <v>57.1</v>
       </c>
       <c r="E1260" t="n">
-        <v>460.7</v>
+        <v>514.8</v>
       </c>
       <c r="F1260" t="n">
-        <v>10325.8</v>
+        <v>10379.9</v>
       </c>
       <c r="G1260" t="n">
         <v>6</v>
@@ -42040,10 +42040,10 @@
         <v>82.7</v>
       </c>
       <c r="E1261" t="n">
-        <v>522.2</v>
+        <v>603.5</v>
       </c>
       <c r="F1261" t="n">
-        <v>10186.8</v>
+        <v>10268.1</v>
       </c>
       <c r="G1261" t="n">
         <v>2</v>
@@ -42073,10 +42073,10 @@
         <v>86.5</v>
       </c>
       <c r="E1262" t="n">
-        <v>514.7</v>
+        <v>588.2</v>
       </c>
       <c r="F1262" t="n">
-        <v>11449.5</v>
+        <v>11523</v>
       </c>
       <c r="G1262" t="n">
         <v>1</v>
@@ -42106,16 +42106,16 @@
         <v>75.8</v>
       </c>
       <c r="E1263" t="n">
-        <v>390.5</v>
+        <v>461.2</v>
       </c>
       <c r="F1263" t="n">
-        <v>9224.4</v>
+        <v>9295.1</v>
       </c>
       <c r="G1263" t="n">
         <v>4</v>
       </c>
       <c r="H1263" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I1263" t="n">
         <v>7</v>
@@ -42139,16 +42139,16 @@
         <v>77.7</v>
       </c>
       <c r="E1264" t="n">
-        <v>407.7</v>
+        <v>500.9</v>
       </c>
       <c r="F1264" t="n">
-        <v>10011.8</v>
+        <v>10105</v>
       </c>
       <c r="G1264" t="n">
         <v>3</v>
       </c>
       <c r="H1264" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1264" t="n">
         <v>6</v>
@@ -42172,16 +42172,16 @@
         <v>55.6</v>
       </c>
       <c r="E1265" t="n">
-        <v>432.6</v>
+        <v>492.4</v>
       </c>
       <c r="F1265" t="n">
-        <v>7967.6</v>
+        <v>8027.4</v>
       </c>
       <c r="G1265" t="n">
         <v>7</v>
       </c>
       <c r="H1265" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1265" t="n">
         <v>8</v>
@@ -42205,10 +42205,10 @@
         <v>34.2</v>
       </c>
       <c r="E1266" t="n">
-        <v>425.2</v>
+        <v>474.6</v>
       </c>
       <c r="F1266" t="n">
-        <v>11136.3</v>
+        <v>11185.7</v>
       </c>
       <c r="G1266" t="n">
         <v>6</v>
@@ -42238,16 +42238,16 @@
         <v>45.6</v>
       </c>
       <c r="E1267" t="n">
-        <v>509.2</v>
+        <v>587.6</v>
       </c>
       <c r="F1267" t="n">
-        <v>11200.2</v>
+        <v>11278.6</v>
       </c>
       <c r="G1267" t="n">
         <v>5</v>
       </c>
       <c r="H1267" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1267" t="n">
         <v>2</v>
@@ -42271,16 +42271,16 @@
         <v>56.1</v>
       </c>
       <c r="E1268" t="n">
-        <v>516.8</v>
+        <v>570.9</v>
       </c>
       <c r="F1268" t="n">
-        <v>10381.9</v>
+        <v>10436</v>
       </c>
       <c r="G1268" t="n">
         <v>3</v>
       </c>
       <c r="H1268" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1268" t="n">
         <v>4</v>
@@ -42304,10 +42304,10 @@
         <v>61.7</v>
       </c>
       <c r="E1269" t="n">
-        <v>583.9</v>
+        <v>665.2</v>
       </c>
       <c r="F1269" t="n">
-        <v>10248.5</v>
+        <v>10329.8</v>
       </c>
       <c r="G1269" t="n">
         <v>1</v>
@@ -42337,10 +42337,10 @@
         <v>58.3</v>
       </c>
       <c r="E1270" t="n">
-        <v>573</v>
+        <v>646.5</v>
       </c>
       <c r="F1270" t="n">
-        <v>11507.8</v>
+        <v>11581.3</v>
       </c>
       <c r="G1270" t="n">
         <v>2</v>
@@ -42370,10 +42370,10 @@
         <v>47.9</v>
       </c>
       <c r="E1271" t="n">
-        <v>438.4</v>
+        <v>509.1</v>
       </c>
       <c r="F1271" t="n">
-        <v>9272.299999999999</v>
+        <v>9343</v>
       </c>
       <c r="G1271" t="n">
         <v>4</v>
@@ -42403,16 +42403,16 @@
         <v>32.4</v>
       </c>
       <c r="E1272" t="n">
-        <v>440.1</v>
+        <v>533.3</v>
       </c>
       <c r="F1272" t="n">
-        <v>10044.2</v>
+        <v>10137.4</v>
       </c>
       <c r="G1272" t="n">
         <v>8</v>
       </c>
       <c r="H1272" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1272" t="n">
         <v>6</v>
@@ -42436,16 +42436,16 @@
         <v>34.2</v>
       </c>
       <c r="E1273" t="n">
-        <v>466.8</v>
+        <v>526.6</v>
       </c>
       <c r="F1273" t="n">
-        <v>8001.8</v>
+        <v>8061.6</v>
       </c>
       <c r="G1273" t="n">
         <v>6</v>
       </c>
       <c r="H1273" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1273" t="n">
         <v>8</v>
@@ -42469,16 +42469,16 @@
         <v>73.59999999999999</v>
       </c>
       <c r="E1274" t="n">
-        <v>498.8</v>
+        <v>548.2</v>
       </c>
       <c r="F1274" t="n">
-        <v>11209.9</v>
+        <v>11259.3</v>
       </c>
       <c r="G1274" t="n">
         <v>3</v>
       </c>
       <c r="H1274" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1274" t="n">
         <v>3</v>
@@ -42502,10 +42502,10 @@
         <v>59.40000000000001</v>
       </c>
       <c r="E1275" t="n">
-        <v>568.6</v>
+        <v>647</v>
       </c>
       <c r="F1275" t="n">
-        <v>11259.6</v>
+        <v>11338</v>
       </c>
       <c r="G1275" t="n">
         <v>5</v>
@@ -42535,10 +42535,10 @@
         <v>78.59999999999999</v>
       </c>
       <c r="E1276" t="n">
-        <v>595.4</v>
+        <v>649.5</v>
       </c>
       <c r="F1276" t="n">
-        <v>10460.5</v>
+        <v>10514.6</v>
       </c>
       <c r="G1276" t="n">
         <v>1</v>
@@ -42568,10 +42568,10 @@
         <v>46</v>
       </c>
       <c r="E1277" t="n">
-        <v>629.9</v>
+        <v>711.2</v>
       </c>
       <c r="F1277" t="n">
-        <v>10294.5</v>
+        <v>10375.8</v>
       </c>
       <c r="G1277" t="n">
         <v>8</v>
@@ -42601,10 +42601,10 @@
         <v>70.09999999999999</v>
       </c>
       <c r="E1278" t="n">
-        <v>643.1</v>
+        <v>716.6</v>
       </c>
       <c r="F1278" t="n">
-        <v>11577.9</v>
+        <v>11651.4</v>
       </c>
       <c r="G1278" t="n">
         <v>4</v>
@@ -42634,16 +42634,16 @@
         <v>52.5</v>
       </c>
       <c r="E1279" t="n">
-        <v>490.9</v>
+        <v>561.6</v>
       </c>
       <c r="F1279" t="n">
-        <v>9324.799999999999</v>
+        <v>9395.5</v>
       </c>
       <c r="G1279" t="n">
         <v>7</v>
       </c>
       <c r="H1279" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I1279" t="n">
         <v>7</v>
@@ -42667,16 +42667,16 @@
         <v>74.90000000000001</v>
       </c>
       <c r="E1280" t="n">
-        <v>515</v>
+        <v>608.2</v>
       </c>
       <c r="F1280" t="n">
-        <v>10119.1</v>
+        <v>10212.3</v>
       </c>
       <c r="G1280" t="n">
         <v>2</v>
       </c>
       <c r="H1280" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1280" t="n">
         <v>6</v>
@@ -42700,16 +42700,16 @@
         <v>58.2</v>
       </c>
       <c r="E1281" t="n">
-        <v>525</v>
+        <v>584.8000000000001</v>
       </c>
       <c r="F1281" t="n">
-        <v>8060</v>
+        <v>8119.8</v>
       </c>
       <c r="G1281" t="n">
         <v>6</v>
       </c>
       <c r="H1281" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1281" t="n">
         <v>8</v>
@@ -42733,16 +42733,16 @@
         <v>53.8</v>
       </c>
       <c r="E1282" t="n">
-        <v>552.6</v>
+        <v>602</v>
       </c>
       <c r="F1282" t="n">
-        <v>11263.7</v>
+        <v>11313.1</v>
       </c>
       <c r="G1282" t="n">
         <v>7</v>
       </c>
       <c r="H1282" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1282" t="n">
         <v>3</v>
@@ -42766,10 +42766,10 @@
         <v>51.1</v>
       </c>
       <c r="E1283" t="n">
-        <v>619.7</v>
+        <v>698.1</v>
       </c>
       <c r="F1283" t="n">
-        <v>11310.7</v>
+        <v>11389.1</v>
       </c>
       <c r="G1283" t="n">
         <v>8</v>
@@ -42799,10 +42799,10 @@
         <v>62.1</v>
       </c>
       <c r="E1284" t="n">
-        <v>657.5</v>
+        <v>711.6</v>
       </c>
       <c r="F1284" t="n">
-        <v>10522.6</v>
+        <v>10576.7</v>
       </c>
       <c r="G1284" t="n">
         <v>3</v>
@@ -42832,16 +42832,16 @@
         <v>69.5</v>
       </c>
       <c r="E1285" t="n">
-        <v>699.4</v>
+        <v>780.7</v>
       </c>
       <c r="F1285" t="n">
-        <v>10364</v>
+        <v>10445.3</v>
       </c>
       <c r="G1285" t="n">
         <v>1</v>
       </c>
       <c r="H1285" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1285" t="n">
         <v>5</v>
@@ -42865,16 +42865,16 @@
         <v>59.5</v>
       </c>
       <c r="E1286" t="n">
-        <v>702.6</v>
+        <v>776.1</v>
       </c>
       <c r="F1286" t="n">
-        <v>11637.4</v>
+        <v>11710.9</v>
       </c>
       <c r="G1286" t="n">
         <v>5</v>
       </c>
       <c r="H1286" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1286" t="n">
         <v>1</v>
@@ -42898,16 +42898,16 @@
         <v>54.1</v>
       </c>
       <c r="E1287" t="n">
-        <v>545</v>
+        <v>615.7</v>
       </c>
       <c r="F1287" t="n">
-        <v>9378.9</v>
+        <v>9449.6</v>
       </c>
       <c r="G1287" t="n">
         <v>6</v>
       </c>
       <c r="H1287" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I1287" t="n">
         <v>7</v>
@@ -42931,16 +42931,16 @@
         <v>69.2</v>
       </c>
       <c r="E1288" t="n">
-        <v>584.2</v>
+        <v>677.4</v>
       </c>
       <c r="F1288" t="n">
-        <v>10188.3</v>
+        <v>10281.5</v>
       </c>
       <c r="G1288" t="n">
         <v>2</v>
       </c>
       <c r="H1288" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1288" t="n">
         <v>6</v>
@@ -42964,16 +42964,16 @@
         <v>60</v>
       </c>
       <c r="E1289" t="n">
-        <v>585</v>
+        <v>644.8000000000001</v>
       </c>
       <c r="F1289" t="n">
-        <v>8120</v>
+        <v>8179.8</v>
       </c>
       <c r="G1289" t="n">
         <v>4</v>
       </c>
       <c r="H1289" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1289" t="n">
         <v>8</v>
@@ -42997,10 +42997,10 @@
         <v>87.8</v>
       </c>
       <c r="E1290" t="n">
-        <v>640.4</v>
+        <v>689.8</v>
       </c>
       <c r="F1290" t="n">
-        <v>11351.5</v>
+        <v>11400.9</v>
       </c>
       <c r="G1290" t="n">
         <v>1</v>
@@ -43030,10 +43030,10 @@
         <v>67</v>
       </c>
       <c r="E1291" t="n">
-        <v>686.7</v>
+        <v>765.1</v>
       </c>
       <c r="F1291" t="n">
-        <v>11377.7</v>
+        <v>11456.1</v>
       </c>
       <c r="G1291" t="n">
         <v>4</v>
@@ -43063,10 +43063,10 @@
         <v>55.4</v>
       </c>
       <c r="E1292" t="n">
-        <v>712.9</v>
+        <v>767</v>
       </c>
       <c r="F1292" t="n">
-        <v>10578</v>
+        <v>10632.1</v>
       </c>
       <c r="G1292" t="n">
         <v>7</v>
@@ -43096,10 +43096,10 @@
         <v>57.6</v>
       </c>
       <c r="E1293" t="n">
-        <v>757</v>
+        <v>838.3000000000001</v>
       </c>
       <c r="F1293" t="n">
-        <v>10421.6</v>
+        <v>10502.9</v>
       </c>
       <c r="G1293" t="n">
         <v>6</v>
@@ -43129,10 +43129,10 @@
         <v>66.3</v>
       </c>
       <c r="E1294" t="n">
-        <v>768.9</v>
+        <v>842.4</v>
       </c>
       <c r="F1294" t="n">
-        <v>11703.7</v>
+        <v>11777.2</v>
       </c>
       <c r="G1294" t="n">
         <v>5</v>
@@ -43162,10 +43162,10 @@
         <v>52.1</v>
       </c>
       <c r="E1295" t="n">
-        <v>597.1</v>
+        <v>667.8</v>
       </c>
       <c r="F1295" t="n">
-        <v>9431</v>
+        <v>9501.700000000001</v>
       </c>
       <c r="G1295" t="n">
         <v>8</v>
@@ -43195,10 +43195,10 @@
         <v>81.09999999999999</v>
       </c>
       <c r="E1296" t="n">
-        <v>665.3</v>
+        <v>758.5</v>
       </c>
       <c r="F1296" t="n">
-        <v>10269.4</v>
+        <v>10362.6</v>
       </c>
       <c r="G1296" t="n">
         <v>2</v>
@@ -43228,10 +43228,10 @@
         <v>76.89999999999999</v>
       </c>
       <c r="E1297" t="n">
-        <v>661.9</v>
+        <v>721.7</v>
       </c>
       <c r="F1297" t="n">
-        <v>8196.9</v>
+        <v>8256.700000000001</v>
       </c>
       <c r="G1297" t="n">
         <v>3</v>
@@ -43261,10 +43261,10 @@
         <v>77.90000000000001</v>
       </c>
       <c r="E1298" t="n">
-        <v>718.3</v>
+        <v>767.7</v>
       </c>
       <c r="F1298" t="n">
-        <v>11429.4</v>
+        <v>11478.8</v>
       </c>
       <c r="G1298" t="n">
         <v>1</v>
@@ -43294,16 +43294,16 @@
         <v>54.8</v>
       </c>
       <c r="E1299" t="n">
-        <v>741.5</v>
+        <v>819.9</v>
       </c>
       <c r="F1299" t="n">
-        <v>11432.5</v>
+        <v>11510.9</v>
       </c>
       <c r="G1299" t="n">
         <v>7</v>
       </c>
       <c r="H1299" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1299" t="n">
         <v>2</v>
@@ -43327,10 +43327,10 @@
         <v>68.8</v>
       </c>
       <c r="E1300" t="n">
-        <v>781.7</v>
+        <v>835.8</v>
       </c>
       <c r="F1300" t="n">
-        <v>10646.8</v>
+        <v>10700.9</v>
       </c>
       <c r="G1300" t="n">
         <v>3</v>
@@ -43360,10 +43360,10 @@
         <v>60.2</v>
       </c>
       <c r="E1301" t="n">
-        <v>817.2</v>
+        <v>898.5</v>
       </c>
       <c r="F1301" t="n">
-        <v>10481.8</v>
+        <v>10563.1</v>
       </c>
       <c r="G1301" t="n">
         <v>6</v>
@@ -43393,10 +43393,10 @@
         <v>62.8</v>
       </c>
       <c r="E1302" t="n">
-        <v>831.7</v>
+        <v>905.2</v>
       </c>
       <c r="F1302" t="n">
-        <v>11766.5</v>
+        <v>11840</v>
       </c>
       <c r="G1302" t="n">
         <v>5</v>
@@ -43426,10 +43426,10 @@
         <v>50.9</v>
       </c>
       <c r="E1303" t="n">
-        <v>648</v>
+        <v>718.7</v>
       </c>
       <c r="F1303" t="n">
-        <v>9481.9</v>
+        <v>9552.6</v>
       </c>
       <c r="G1303" t="n">
         <v>8</v>
@@ -43459,16 +43459,16 @@
         <v>69.40000000000001</v>
       </c>
       <c r="E1304" t="n">
-        <v>734.7</v>
+        <v>827.9</v>
       </c>
       <c r="F1304" t="n">
-        <v>10338.8</v>
+        <v>10432</v>
       </c>
       <c r="G1304" t="n">
         <v>2</v>
       </c>
       <c r="H1304" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1304" t="n">
         <v>6</v>
@@ -43492,10 +43492,10 @@
         <v>66.3</v>
       </c>
       <c r="E1305" t="n">
-        <v>728.2</v>
+        <v>788</v>
       </c>
       <c r="F1305" t="n">
-        <v>8263.200000000001</v>
+        <v>8323</v>
       </c>
       <c r="G1305" t="n">
         <v>4</v>
@@ -43525,10 +43525,10 @@
         <v>68</v>
       </c>
       <c r="E1306" t="n">
-        <v>786.3</v>
+        <v>835.7</v>
       </c>
       <c r="F1306" t="n">
-        <v>11497.4</v>
+        <v>11546.8</v>
       </c>
       <c r="G1306" t="n">
         <v>5</v>
@@ -43558,10 +43558,10 @@
         <v>89.2</v>
       </c>
       <c r="E1307" t="n">
-        <v>830.7</v>
+        <v>909.1</v>
       </c>
       <c r="F1307" t="n">
-        <v>11521.7</v>
+        <v>11600.1</v>
       </c>
       <c r="G1307" t="n">
         <v>2</v>
@@ -43591,10 +43591,10 @@
         <v>79.3</v>
       </c>
       <c r="E1308" t="n">
-        <v>861</v>
+        <v>915.1</v>
       </c>
       <c r="F1308" t="n">
-        <v>10726.1</v>
+        <v>10780.2</v>
       </c>
       <c r="G1308" t="n">
         <v>3</v>
@@ -43624,10 +43624,10 @@
         <v>61</v>
       </c>
       <c r="E1309" t="n">
-        <v>878.2</v>
+        <v>959.5</v>
       </c>
       <c r="F1309" t="n">
-        <v>10542.8</v>
+        <v>10624.1</v>
       </c>
       <c r="G1309" t="n">
         <v>6</v>
@@ -43657,10 +43657,10 @@
         <v>57.4</v>
       </c>
       <c r="E1310" t="n">
-        <v>889.1</v>
+        <v>962.6</v>
       </c>
       <c r="F1310" t="n">
-        <v>11823.9</v>
+        <v>11897.4</v>
       </c>
       <c r="G1310" t="n">
         <v>7</v>
@@ -43690,10 +43690,10 @@
         <v>46.4</v>
       </c>
       <c r="E1311" t="n">
-        <v>694.4</v>
+        <v>765.1</v>
       </c>
       <c r="F1311" t="n">
-        <v>9528.299999999999</v>
+        <v>9599</v>
       </c>
       <c r="G1311" t="n">
         <v>8</v>
@@ -43723,16 +43723,16 @@
         <v>77.2</v>
       </c>
       <c r="E1312" t="n">
-        <v>811.9</v>
+        <v>905.1</v>
       </c>
       <c r="F1312" t="n">
-        <v>10416</v>
+        <v>10509.2</v>
       </c>
       <c r="G1312" t="n">
         <v>4</v>
       </c>
       <c r="H1312" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1312" t="n">
         <v>6</v>
@@ -43756,16 +43756,16 @@
         <v>95.2</v>
       </c>
       <c r="E1313" t="n">
-        <v>823.4</v>
+        <v>883.2</v>
       </c>
       <c r="F1313" t="n">
-        <v>8358.4</v>
+        <v>8418.200000000001</v>
       </c>
       <c r="G1313" t="n">
         <v>1</v>
       </c>
       <c r="H1313" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1313" t="n">
         <v>8</v>
@@ -43789,10 +43789,10 @@
         <v>78</v>
       </c>
       <c r="E1314" t="n">
-        <v>864.3</v>
+        <v>913.7</v>
       </c>
       <c r="F1314" t="n">
-        <v>11575.4</v>
+        <v>11624.8</v>
       </c>
       <c r="G1314" t="n">
         <v>3</v>
@@ -43822,10 +43822,10 @@
         <v>78.59999999999999</v>
       </c>
       <c r="E1315" t="n">
-        <v>909.3</v>
+        <v>987.7</v>
       </c>
       <c r="F1315" t="n">
-        <v>11600.3</v>
+        <v>11678.7</v>
       </c>
       <c r="G1315" t="n">
         <v>2</v>
@@ -43855,16 +43855,16 @@
         <v>76.90000000000001</v>
       </c>
       <c r="E1316" t="n">
-        <v>937.9</v>
+        <v>992</v>
       </c>
       <c r="F1316" t="n">
-        <v>10803</v>
+        <v>10857.1</v>
       </c>
       <c r="G1316" t="n">
         <v>4</v>
       </c>
       <c r="H1316" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1316" t="n">
         <v>4</v>
@@ -43888,16 +43888,16 @@
         <v>48.4</v>
       </c>
       <c r="E1317" t="n">
-        <v>926.6</v>
+        <v>1007.9</v>
       </c>
       <c r="F1317" t="n">
-        <v>10591.2</v>
+        <v>10672.5</v>
       </c>
       <c r="G1317" t="n">
         <v>8</v>
       </c>
       <c r="H1317" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1317" t="n">
         <v>5</v>
@@ -43921,10 +43921,10 @@
         <v>67.59999999999999</v>
       </c>
       <c r="E1318" t="n">
-        <v>956.7</v>
+        <v>1030.2</v>
       </c>
       <c r="F1318" t="n">
-        <v>11891.5</v>
+        <v>11965</v>
       </c>
       <c r="G1318" t="n">
         <v>5</v>
@@ -43954,10 +43954,10 @@
         <v>58.1</v>
       </c>
       <c r="E1319" t="n">
-        <v>752.5</v>
+        <v>823.2</v>
       </c>
       <c r="F1319" t="n">
-        <v>9586.4</v>
+        <v>9657.1</v>
       </c>
       <c r="G1319" t="n">
         <v>7</v>
@@ -43987,16 +43987,16 @@
         <v>61.4</v>
       </c>
       <c r="E1320" t="n">
-        <v>873.3</v>
+        <v>966.5</v>
       </c>
       <c r="F1320" t="n">
-        <v>10477.4</v>
+        <v>10570.6</v>
       </c>
       <c r="G1320" t="n">
         <v>6</v>
       </c>
       <c r="H1320" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1320" t="n">
         <v>6</v>
@@ -44020,16 +44020,16 @@
         <v>81.59999999999999</v>
       </c>
       <c r="E1321" t="n">
-        <v>905</v>
+        <v>964.8</v>
       </c>
       <c r="F1321" t="n">
-        <v>8440</v>
+        <v>8499.799999999999</v>
       </c>
       <c r="G1321" t="n">
         <v>1</v>
       </c>
       <c r="H1321" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1321" t="n">
         <v>8</v>
@@ -44053,10 +44053,10 @@
         <v>67.5</v>
       </c>
       <c r="E1322" t="n">
-        <v>931.8</v>
+        <v>981.2</v>
       </c>
       <c r="F1322" t="n">
-        <v>11642.9</v>
+        <v>11692.3</v>
       </c>
       <c r="G1322" t="n">
         <v>5</v>
@@ -44086,16 +44086,16 @@
         <v>69.8</v>
       </c>
       <c r="E1323" t="n">
-        <v>979.1</v>
+        <v>1057.5</v>
       </c>
       <c r="F1323" t="n">
-        <v>11670.1</v>
+        <v>11748.5</v>
       </c>
       <c r="G1323" t="n">
         <v>2</v>
       </c>
       <c r="H1323" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1323" t="n">
         <v>2</v>
@@ -44119,10 +44119,10 @@
         <v>68.3</v>
       </c>
       <c r="E1324" t="n">
-        <v>1006.2</v>
+        <v>1060.3</v>
       </c>
       <c r="F1324" t="n">
-        <v>10871.3</v>
+        <v>10925.4</v>
       </c>
       <c r="G1324" t="n">
         <v>3</v>
@@ -44152,16 +44152,16 @@
         <v>52.1</v>
       </c>
       <c r="E1325" t="n">
-        <v>978.7</v>
+        <v>1060</v>
       </c>
       <c r="F1325" t="n">
-        <v>10643.3</v>
+        <v>10724.6</v>
       </c>
       <c r="G1325" t="n">
         <v>8</v>
       </c>
       <c r="H1325" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1325" t="n">
         <v>5</v>
@@ -44185,10 +44185,10 @@
         <v>79.7</v>
       </c>
       <c r="E1326" t="n">
-        <v>1036.4</v>
+        <v>1109.9</v>
       </c>
       <c r="F1326" t="n">
-        <v>11971.2</v>
+        <v>12044.7</v>
       </c>
       <c r="G1326" t="n">
         <v>1</v>
@@ -44218,10 +44218,10 @@
         <v>58</v>
       </c>
       <c r="E1327" t="n">
-        <v>810.5</v>
+        <v>881.2</v>
       </c>
       <c r="F1327" t="n">
-        <v>9644.4</v>
+        <v>9715.1</v>
       </c>
       <c r="G1327" t="n">
         <v>7</v>
@@ -44251,10 +44251,10 @@
         <v>59.5</v>
       </c>
       <c r="E1328" t="n">
-        <v>932.8</v>
+        <v>1026</v>
       </c>
       <c r="F1328" t="n">
-        <v>10536.9</v>
+        <v>10630.1</v>
       </c>
       <c r="G1328" t="n">
         <v>6</v>
@@ -44284,10 +44284,10 @@
         <v>68.10000000000001</v>
       </c>
       <c r="E1329" t="n">
-        <v>973.1</v>
+        <v>1032.9</v>
       </c>
       <c r="F1329" t="n">
-        <v>8508.1</v>
+        <v>8567.9</v>
       </c>
       <c r="G1329" t="n">
         <v>4</v>
@@ -44317,10 +44317,10 @@
         <v>58.6</v>
       </c>
       <c r="E1330" t="n">
-        <v>990.4</v>
+        <v>1039.8</v>
       </c>
       <c r="F1330" t="n">
-        <v>11701.5</v>
+        <v>11750.9</v>
       </c>
       <c r="G1330" t="n">
         <v>6</v>
@@ -44350,10 +44350,10 @@
         <v>105.7</v>
       </c>
       <c r="E1331" t="n">
-        <v>1084.8</v>
+        <v>1163.2</v>
       </c>
       <c r="F1331" t="n">
-        <v>11775.8</v>
+        <v>11854.2</v>
       </c>
       <c r="G1331" t="n">
         <v>1</v>
@@ -44383,16 +44383,16 @@
         <v>58.4</v>
       </c>
       <c r="E1332" t="n">
-        <v>1064.6</v>
+        <v>1118.7</v>
       </c>
       <c r="F1332" t="n">
-        <v>10929.7</v>
+        <v>10983.8</v>
       </c>
       <c r="G1332" t="n">
         <v>7</v>
       </c>
       <c r="H1332" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1332" t="n">
         <v>4</v>
@@ -44416,10 +44416,10 @@
         <v>57.4</v>
       </c>
       <c r="E1333" t="n">
-        <v>1036.1</v>
+        <v>1117.4</v>
       </c>
       <c r="F1333" t="n">
-        <v>10700.7</v>
+        <v>10782</v>
       </c>
       <c r="G1333" t="n">
         <v>8</v>
@@ -44449,10 +44449,10 @@
         <v>83.40000000000001</v>
       </c>
       <c r="E1334" t="n">
-        <v>1119.8</v>
+        <v>1193.3</v>
       </c>
       <c r="F1334" t="n">
-        <v>12054.6</v>
+        <v>12128.1</v>
       </c>
       <c r="G1334" t="n">
         <v>3</v>
@@ -44482,10 +44482,10 @@
         <v>74.3</v>
       </c>
       <c r="E1335" t="n">
-        <v>884.8</v>
+        <v>955.5</v>
       </c>
       <c r="F1335" t="n">
-        <v>9718.700000000001</v>
+        <v>9789.4</v>
       </c>
       <c r="G1335" t="n">
         <v>4</v>
@@ -44515,10 +44515,10 @@
         <v>72</v>
       </c>
       <c r="E1336" t="n">
-        <v>1004.8</v>
+        <v>1098</v>
       </c>
       <c r="F1336" t="n">
-        <v>10608.9</v>
+        <v>10702.1</v>
       </c>
       <c r="G1336" t="n">
         <v>5</v>
@@ -44548,16 +44548,16 @@
         <v>87.09999999999999</v>
       </c>
       <c r="E1337" t="n">
-        <v>1060.2</v>
+        <v>1120</v>
       </c>
       <c r="F1337" t="n">
-        <v>8595.200000000001</v>
+        <v>8655</v>
       </c>
       <c r="G1337" t="n">
         <v>2</v>
       </c>
       <c r="H1337" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1337" t="n">
         <v>8</v>
@@ -44581,10 +44581,10 @@
         <v>61.2</v>
       </c>
       <c r="E1338" t="n">
-        <v>1051.6</v>
+        <v>1101</v>
       </c>
       <c r="F1338" t="n">
-        <v>11762.7</v>
+        <v>11812.1</v>
       </c>
       <c r="G1338" t="n">
         <v>5</v>
@@ -44614,10 +44614,10 @@
         <v>55.59999999999999</v>
       </c>
       <c r="E1339" t="n">
-        <v>1140.4</v>
+        <v>1218.8</v>
       </c>
       <c r="F1339" t="n">
-        <v>11831.4</v>
+        <v>11909.8</v>
       </c>
       <c r="G1339" t="n">
         <v>7</v>
@@ -44647,16 +44647,16 @@
         <v>50.59999999999999</v>
       </c>
       <c r="E1340" t="n">
-        <v>1115.2</v>
+        <v>1169.3</v>
       </c>
       <c r="F1340" t="n">
-        <v>10980.3</v>
+        <v>11034.4</v>
       </c>
       <c r="G1340" t="n">
         <v>8</v>
       </c>
       <c r="H1340" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I1340" t="n">
         <v>4</v>
@@ -44680,16 +44680,16 @@
         <v>62.40000000000001</v>
       </c>
       <c r="E1341" t="n">
-        <v>1098.5</v>
+        <v>1179.8</v>
       </c>
       <c r="F1341" t="n">
-        <v>10763.1</v>
+        <v>10844.4</v>
       </c>
       <c r="G1341" t="n">
         <v>4</v>
       </c>
       <c r="H1341" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1341" t="n">
         <v>5</v>
@@ -44713,10 +44713,10 @@
         <v>81.90000000000001</v>
       </c>
       <c r="E1342" t="n">
-        <v>1201.7</v>
+        <v>1275.2</v>
       </c>
       <c r="F1342" t="n">
-        <v>12136.5</v>
+        <v>12210</v>
       </c>
       <c r="G1342" t="n">
         <v>2</v>
@@ -44746,10 +44746,10 @@
         <v>63.3</v>
       </c>
       <c r="E1343" t="n">
-        <v>948.1</v>
+        <v>1018.8</v>
       </c>
       <c r="F1343" t="n">
-        <v>9782</v>
+        <v>9852.700000000001</v>
       </c>
       <c r="G1343" t="n">
         <v>3</v>
@@ -44779,16 +44779,16 @@
         <v>86</v>
       </c>
       <c r="E1344" t="n">
-        <v>1090.8</v>
+        <v>1184</v>
       </c>
       <c r="F1344" t="n">
-        <v>10694.9</v>
+        <v>10788.1</v>
       </c>
       <c r="G1344" t="n">
         <v>1</v>
       </c>
       <c r="H1344" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I1344" t="n">
         <v>6</v>
@@ -44812,16 +44812,16 @@
         <v>58.1</v>
       </c>
       <c r="E1345" t="n">
-        <v>1118.3</v>
+        <v>1178.1</v>
       </c>
       <c r="F1345" t="n">
-        <v>8653.299999999999</v>
+        <v>8713.1</v>
       </c>
       <c r="G1345" t="n">
         <v>6</v>
       </c>
       <c r="H1345" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I1345" t="n">
         <v>8</v>
@@ -44845,10 +44845,10 @@
         <v>64.2</v>
       </c>
       <c r="E1346" t="n">
-        <v>1115.8</v>
+        <v>1165.2</v>
       </c>
       <c r="F1346" t="n">
-        <v>11826.9</v>
+        <v>11876.3</v>
       </c>
       <c r="G1346" t="n">
         <v>5</v>
@@ -44878,10 +44878,10 @@
         <v>88.7</v>
       </c>
       <c r="E1347" t="n">
-        <v>1229.1</v>
+        <v>1307.5</v>
       </c>
       <c r="F1347" t="n">
-        <v>11920.1</v>
+        <v>11998.5</v>
       </c>
       <c r="G1347" t="n">
         <v>1</v>
@@ -44911,16 +44911,16 @@
         <v>76.8</v>
       </c>
       <c r="E1348" t="n">
-        <v>1192</v>
+        <v>1246.1</v>
       </c>
       <c r="F1348" t="n">
-        <v>11057.1</v>
+        <v>11111.2</v>
       </c>
       <c r="G1348" t="n">
         <v>3</v>
       </c>
       <c r="H1348" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1348" t="n">
         <v>4</v>
@@ -44944,10 +44944,10 @@
         <v>45</v>
       </c>
       <c r="E1349" t="n">
-        <v>1143.5</v>
+        <v>1224.8</v>
       </c>
       <c r="F1349" t="n">
-        <v>10808.1</v>
+        <v>10889.4</v>
       </c>
       <c r="G1349" t="n">
         <v>8</v>
@@ -44977,10 +44977,10 @@
         <v>81.2</v>
       </c>
       <c r="E1350" t="n">
-        <v>1282.9</v>
+        <v>1356.4</v>
       </c>
       <c r="F1350" t="n">
-        <v>12217.7</v>
+        <v>12291.2</v>
       </c>
       <c r="G1350" t="n">
         <v>2</v>
@@ -45010,10 +45010,10 @@
         <v>63.7</v>
       </c>
       <c r="E1351" t="n">
-        <v>1011.8</v>
+        <v>1082.5</v>
       </c>
       <c r="F1351" t="n">
-        <v>9845.700000000001</v>
+        <v>9916.4</v>
       </c>
       <c r="G1351" t="n">
         <v>6</v>
@@ -45043,16 +45043,16 @@
         <v>67.7</v>
       </c>
       <c r="E1352" t="n">
-        <v>1158.5</v>
+        <v>1251.7</v>
       </c>
       <c r="F1352" t="n">
-        <v>10762.6</v>
+        <v>10855.8</v>
       </c>
       <c r="G1352" t="n">
         <v>4</v>
       </c>
       <c r="H1352" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I1352" t="n">
         <v>6</v>
@@ -45076,16 +45076,16 @@
         <v>60.2</v>
       </c>
       <c r="E1353" t="n">
-        <v>1178.5</v>
+        <v>1238.3</v>
       </c>
       <c r="F1353" t="n">
-        <v>8713.5</v>
+        <v>8773.299999999999</v>
       </c>
       <c r="G1353" t="n">
         <v>7</v>
       </c>
       <c r="H1353" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1353" t="n">
         <v>8</v>
@@ -45109,10 +45109,10 @@
         <v>88.09999999999999</v>
       </c>
       <c r="E1354" t="n">
-        <v>1203.9</v>
+        <v>1253.3</v>
       </c>
       <c r="F1354" t="n">
-        <v>11915</v>
+        <v>11964.4</v>
       </c>
       <c r="G1354" t="n">
         <v>3</v>
@@ -45142,10 +45142,10 @@
         <v>59.9</v>
       </c>
       <c r="E1355" t="n">
-        <v>1289</v>
+        <v>1367.4</v>
       </c>
       <c r="F1355" t="n">
-        <v>11980</v>
+        <v>12058.4</v>
       </c>
       <c r="G1355" t="n">
         <v>6</v>
@@ -45175,10 +45175,10 @@
         <v>70.2</v>
       </c>
       <c r="E1356" t="n">
-        <v>1262.2</v>
+        <v>1316.3</v>
       </c>
       <c r="F1356" t="n">
-        <v>11127.3</v>
+        <v>11181.4</v>
       </c>
       <c r="G1356" t="n">
         <v>4</v>
@@ -45208,10 +45208,10 @@
         <v>0</v>
       </c>
       <c r="E1357" t="n">
-        <v>1143.5</v>
+        <v>1224.8</v>
       </c>
       <c r="F1357" t="n">
-        <v>10808.1</v>
+        <v>10889.4</v>
       </c>
       <c r="G1357" t="n">
         <v>8</v>
@@ -45241,10 +45241,10 @@
         <v>94</v>
       </c>
       <c r="E1358" t="n">
-        <v>1376.9</v>
+        <v>1450.4</v>
       </c>
       <c r="F1358" t="n">
-        <v>12311.7</v>
+        <v>12385.2</v>
       </c>
       <c r="G1358" t="n">
         <v>1</v>
@@ -45274,10 +45274,10 @@
         <v>61.6</v>
       </c>
       <c r="E1359" t="n">
-        <v>1073.4</v>
+        <v>1144.1</v>
       </c>
       <c r="F1359" t="n">
-        <v>9907.299999999999</v>
+        <v>9978</v>
       </c>
       <c r="G1359" t="n">
         <v>5</v>
@@ -45307,10 +45307,10 @@
         <v>58.6</v>
       </c>
       <c r="E1360" t="n">
-        <v>1217.1</v>
+        <v>1310.3</v>
       </c>
       <c r="F1360" t="n">
-        <v>10821.2</v>
+        <v>10914.4</v>
       </c>
       <c r="G1360" t="n">
         <v>7</v>
@@ -45340,10 +45340,10 @@
         <v>89.5</v>
       </c>
       <c r="E1361" t="n">
-        <v>1268</v>
+        <v>1327.8</v>
       </c>
       <c r="F1361" t="n">
-        <v>8803</v>
+        <v>8862.799999999999</v>
       </c>
       <c r="G1361" t="n">
         <v>2</v>
@@ -45373,10 +45373,10 @@
         <v>66.7</v>
       </c>
       <c r="E1362" t="n">
-        <v>1270.6</v>
+        <v>1320</v>
       </c>
       <c r="F1362" t="n">
-        <v>11981.7</v>
+        <v>12031.1</v>
       </c>
       <c r="G1362" t="n">
         <v>4</v>
@@ -45406,10 +45406,10 @@
         <v>35.8</v>
       </c>
       <c r="E1363" t="n">
-        <v>1324.8</v>
+        <v>1403.2</v>
       </c>
       <c r="F1363" t="n">
-        <v>12015.8</v>
+        <v>12094.2</v>
       </c>
       <c r="G1363" t="n">
         <v>8</v>
@@ -45439,16 +45439,16 @@
         <v>59.2</v>
       </c>
       <c r="E1364" t="n">
-        <v>1321.4</v>
+        <v>1375.5</v>
       </c>
       <c r="F1364" t="n">
-        <v>11186.5</v>
+        <v>11240.6</v>
       </c>
       <c r="G1364" t="n">
         <v>6</v>
       </c>
       <c r="H1364" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1364" t="n">
         <v>4</v>
@@ -45472,10 +45472,10 @@
         <v>82.2</v>
       </c>
       <c r="E1365" t="n">
-        <v>1225.7</v>
+        <v>1307</v>
       </c>
       <c r="F1365" t="n">
-        <v>10890.3</v>
+        <v>10971.6</v>
       </c>
       <c r="G1365" t="n">
         <v>2</v>
@@ -45505,10 +45505,10 @@
         <v>63</v>
       </c>
       <c r="E1366" t="n">
-        <v>1439.9</v>
+        <v>1513.4</v>
       </c>
       <c r="F1366" t="n">
-        <v>12374.7</v>
+        <v>12448.2</v>
       </c>
       <c r="G1366" t="n">
         <v>5</v>
@@ -45538,10 +45538,10 @@
         <v>56.6</v>
       </c>
       <c r="E1367" t="n">
-        <v>1130</v>
+        <v>1200.7</v>
       </c>
       <c r="F1367" t="n">
-        <v>9963.9</v>
+        <v>10034.6</v>
       </c>
       <c r="G1367" t="n">
         <v>7</v>
@@ -45571,16 +45571,16 @@
         <v>78.59999999999999</v>
       </c>
       <c r="E1368" t="n">
-        <v>1295.7</v>
+        <v>1388.9</v>
       </c>
       <c r="F1368" t="n">
-        <v>10899.8</v>
+        <v>10993</v>
       </c>
       <c r="G1368" t="n">
         <v>3</v>
       </c>
       <c r="H1368" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1368" t="n">
         <v>5</v>
@@ -45604,10 +45604,10 @@
         <v>87.3</v>
       </c>
       <c r="E1369" t="n">
-        <v>1355.3</v>
+        <v>1415.1</v>
       </c>
       <c r="F1369" t="n">
-        <v>8890.299999999999</v>
+        <v>8950.1</v>
       </c>
       <c r="G1369" t="n">
         <v>1</v>
@@ -45637,10 +45637,10 @@
         <v>70.8</v>
       </c>
       <c r="E1370" t="n">
-        <v>1341.4</v>
+        <v>1390.8</v>
       </c>
       <c r="F1370" t="n">
-        <v>12052.5</v>
+        <v>12101.9</v>
       </c>
       <c r="G1370" t="n">
         <v>4</v>
@@ -45670,16 +45670,16 @@
         <v>76.5</v>
       </c>
       <c r="E1371" t="n">
-        <v>1401.3</v>
+        <v>1479.7</v>
       </c>
       <c r="F1371" t="n">
-        <v>12092.3</v>
+        <v>12170.7</v>
       </c>
       <c r="G1371" t="n">
         <v>2</v>
       </c>
       <c r="H1371" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1371" t="n">
         <v>2</v>
@@ -45703,16 +45703,16 @@
         <v>75.2</v>
       </c>
       <c r="E1372" t="n">
-        <v>1396.6</v>
+        <v>1450.7</v>
       </c>
       <c r="F1372" t="n">
-        <v>11261.7</v>
+        <v>11315.8</v>
       </c>
       <c r="G1372" t="n">
         <v>3</v>
       </c>
       <c r="H1372" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1372" t="n">
         <v>4</v>
@@ -45736,10 +45736,10 @@
         <v>46.7</v>
       </c>
       <c r="E1373" t="n">
-        <v>1272.4</v>
+        <v>1353.7</v>
       </c>
       <c r="F1373" t="n">
-        <v>10937</v>
+        <v>11018.3</v>
       </c>
       <c r="G1373" t="n">
         <v>8</v>
@@ -45769,10 +45769,10 @@
         <v>79.40000000000001</v>
       </c>
       <c r="E1374" t="n">
-        <v>1519.3</v>
+        <v>1592.8</v>
       </c>
       <c r="F1374" t="n">
-        <v>12454.1</v>
+        <v>12527.6</v>
       </c>
       <c r="G1374" t="n">
         <v>1</v>
@@ -45802,10 +45802,10 @@
         <v>56.59999999999999</v>
       </c>
       <c r="E1375" t="n">
-        <v>1186.6</v>
+        <v>1257.3</v>
       </c>
       <c r="F1375" t="n">
-        <v>10020.5</v>
+        <v>10091.2</v>
       </c>
       <c r="G1375" t="n">
         <v>6</v>
@@ -45835,16 +45835,16 @@
         <v>65.2</v>
       </c>
       <c r="E1376" t="n">
-        <v>1360.9</v>
+        <v>1454.1</v>
       </c>
       <c r="F1376" t="n">
-        <v>10965</v>
+        <v>11058.2</v>
       </c>
       <c r="G1376" t="n">
         <v>5</v>
       </c>
       <c r="H1376" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1376" t="n">
         <v>5</v>
@@ -45868,16 +45868,16 @@
         <v>54.8</v>
       </c>
       <c r="E1377" t="n">
-        <v>1410.1</v>
+        <v>1469.9</v>
       </c>
       <c r="F1377" t="n">
-        <v>8945.1</v>
+        <v>9004.9</v>
       </c>
       <c r="G1377" t="n">
         <v>7</v>
       </c>
       <c r="H1377" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1377" t="n">
         <v>8</v>
@@ -45901,16 +45901,16 @@
         <v>93.8</v>
       </c>
       <c r="E1378" t="n">
-        <v>1435.2</v>
+        <v>1484.6</v>
       </c>
       <c r="F1378" t="n">
-        <v>12146.3</v>
+        <v>12195.7</v>
       </c>
       <c r="G1378" t="n">
         <v>2</v>
       </c>
       <c r="H1378" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1378" t="n">
         <v>3</v>
@@ -45934,10 +45934,10 @@
         <v>65.2</v>
       </c>
       <c r="E1379" t="n">
-        <v>1466.5</v>
+        <v>1544.9</v>
       </c>
       <c r="F1379" t="n">
-        <v>12157.5</v>
+        <v>12235.9</v>
       </c>
       <c r="G1379" t="n">
         <v>7</v>
@@ -45967,16 +45967,16 @@
         <v>97.59999999999999</v>
       </c>
       <c r="E1380" t="n">
-        <v>1494.2</v>
+        <v>1548.3</v>
       </c>
       <c r="F1380" t="n">
-        <v>11359.3</v>
+        <v>11413.4</v>
       </c>
       <c r="G1380" t="n">
         <v>1</v>
       </c>
       <c r="H1380" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1380" t="n">
         <v>4</v>
@@ -46000,10 +46000,10 @@
         <v>63.3</v>
       </c>
       <c r="E1381" t="n">
-        <v>1335.7</v>
+        <v>1417</v>
       </c>
       <c r="F1381" t="n">
-        <v>11000.3</v>
+        <v>11081.6</v>
       </c>
       <c r="G1381" t="n">
         <v>8</v>
@@ -46033,10 +46033,10 @@
         <v>79.3</v>
       </c>
       <c r="E1382" t="n">
-        <v>1598.6</v>
+        <v>1672.1</v>
       </c>
       <c r="F1382" t="n">
-        <v>12533.4</v>
+        <v>12606.9</v>
       </c>
       <c r="G1382" t="n">
         <v>5</v>
@@ -46066,10 +46066,10 @@
         <v>81.7</v>
       </c>
       <c r="E1383" t="n">
-        <v>1268.3</v>
+        <v>1339</v>
       </c>
       <c r="F1383" t="n">
-        <v>10102.2</v>
+        <v>10172.9</v>
       </c>
       <c r="G1383" t="n">
         <v>4</v>
@@ -46099,16 +46099,16 @@
         <v>67.40000000000001</v>
       </c>
       <c r="E1384" t="n">
-        <v>1428.3</v>
+        <v>1521.5</v>
       </c>
       <c r="F1384" t="n">
-        <v>11032.4</v>
+        <v>11125.6</v>
       </c>
       <c r="G1384" t="n">
         <v>6</v>
       </c>
       <c r="H1384" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1384" t="n">
         <v>5</v>
@@ -46132,16 +46132,16 @@
         <v>82.59999999999999</v>
       </c>
       <c r="E1385" t="n">
-        <v>1492.7</v>
+        <v>1552.5</v>
       </c>
       <c r="F1385" t="n">
-        <v>9027.700000000001</v>
+        <v>9087.5</v>
       </c>
       <c r="G1385" t="n">
         <v>3</v>
       </c>
       <c r="H1385" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1385" t="n">
         <v>8</v>
@@ -46165,10 +46165,10 @@
         <v>100.5</v>
       </c>
       <c r="E1386" t="n">
-        <v>1535.7</v>
+        <v>1585.1</v>
       </c>
       <c r="F1386" t="n">
-        <v>12246.8</v>
+        <v>12296.2</v>
       </c>
       <c r="G1386" t="n">
         <v>1</v>
@@ -46177,7 +46177,7 @@
         <v>5</v>
       </c>
       <c r="I1386" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1387">
@@ -46198,19 +46198,19 @@
         <v>80.3</v>
       </c>
       <c r="E1387" t="n">
-        <v>1546.8</v>
+        <v>1625.2</v>
       </c>
       <c r="F1387" t="n">
-        <v>12237.8</v>
+        <v>12316.2</v>
       </c>
       <c r="G1387" t="n">
         <v>2</v>
       </c>
       <c r="H1387" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I1387" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1388">
@@ -46231,16 +46231,16 @@
         <v>60.3</v>
       </c>
       <c r="E1388" t="n">
-        <v>1554.5</v>
+        <v>1608.6</v>
       </c>
       <c r="F1388" t="n">
-        <v>11419.6</v>
+        <v>11473.7</v>
       </c>
       <c r="G1388" t="n">
         <v>6</v>
       </c>
       <c r="H1388" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1388" t="n">
         <v>4</v>
@@ -46264,10 +46264,10 @@
         <v>67.59999999999999</v>
       </c>
       <c r="E1389" t="n">
-        <v>1403.3</v>
+        <v>1484.6</v>
       </c>
       <c r="F1389" t="n">
-        <v>11067.9</v>
+        <v>11149.2</v>
       </c>
       <c r="G1389" t="n">
         <v>4</v>
@@ -46297,10 +46297,10 @@
         <v>70.2</v>
       </c>
       <c r="E1390" t="n">
-        <v>1668.8</v>
+        <v>1742.3</v>
       </c>
       <c r="F1390" t="n">
-        <v>12603.6</v>
+        <v>12677.1</v>
       </c>
       <c r="G1390" t="n">
         <v>3</v>
@@ -46330,10 +46330,10 @@
         <v>61.2</v>
       </c>
       <c r="E1391" t="n">
-        <v>1329.5</v>
+        <v>1400.2</v>
       </c>
       <c r="F1391" t="n">
-        <v>10163.4</v>
+        <v>10234.1</v>
       </c>
       <c r="G1391" t="n">
         <v>5</v>
@@ -46363,10 +46363,10 @@
         <v>50.8</v>
       </c>
       <c r="E1392" t="n">
-        <v>1479.1</v>
+        <v>1572.3</v>
       </c>
       <c r="F1392" t="n">
-        <v>11083.2</v>
+        <v>11176.4</v>
       </c>
       <c r="G1392" t="n">
         <v>8</v>
@@ -46396,10 +46396,10 @@
         <v>58.9</v>
       </c>
       <c r="E1393" t="n">
-        <v>1551.6</v>
+        <v>1611.4</v>
       </c>
       <c r="F1393" t="n">
-        <v>9086.6</v>
+        <v>9146.4</v>
       </c>
       <c r="G1393" t="n">
         <v>7</v>
@@ -46429,19 +46429,19 @@
         <v>92</v>
       </c>
       <c r="E1394" t="n">
-        <v>1627.7</v>
+        <v>1677.1</v>
       </c>
       <c r="F1394" t="n">
-        <v>12338.8</v>
+        <v>12388.2</v>
       </c>
       <c r="G1394" t="n">
         <v>2</v>
       </c>
       <c r="H1394" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I1394" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1395">
@@ -46462,19 +46462,19 @@
         <v>77.2</v>
       </c>
       <c r="E1395" t="n">
-        <v>1624</v>
+        <v>1702.4</v>
       </c>
       <c r="F1395" t="n">
-        <v>12315</v>
+        <v>12393.4</v>
       </c>
       <c r="G1395" t="n">
         <v>4</v>
       </c>
       <c r="H1395" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I1395" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1396">
@@ -46495,16 +46495,16 @@
         <v>80.3</v>
       </c>
       <c r="E1396" t="n">
-        <v>1634.8</v>
+        <v>1688.9</v>
       </c>
       <c r="F1396" t="n">
-        <v>11499.9</v>
+        <v>11554</v>
       </c>
       <c r="G1396" t="n">
         <v>3</v>
       </c>
       <c r="H1396" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1396" t="n">
         <v>4</v>
@@ -46528,10 +46528,10 @@
         <v>50.6</v>
       </c>
       <c r="E1397" t="n">
-        <v>1453.9</v>
+        <v>1535.2</v>
       </c>
       <c r="F1397" t="n">
-        <v>11118.5</v>
+        <v>11199.8</v>
       </c>
       <c r="G1397" t="n">
         <v>7</v>
@@ -46561,10 +46561,10 @@
         <v>76.7</v>
       </c>
       <c r="E1398" t="n">
-        <v>1745.5</v>
+        <v>1819</v>
       </c>
       <c r="F1398" t="n">
-        <v>12680.3</v>
+        <v>12753.8</v>
       </c>
       <c r="G1398" t="n">
         <v>5</v>
@@ -46594,10 +46594,10 @@
         <v>48.7</v>
       </c>
       <c r="E1399" t="n">
-        <v>1378.2</v>
+        <v>1448.9</v>
       </c>
       <c r="F1399" t="n">
-        <v>10212.1</v>
+        <v>10282.8</v>
       </c>
       <c r="G1399" t="n">
         <v>8</v>
@@ -46627,10 +46627,10 @@
         <v>92.5</v>
       </c>
       <c r="E1400" t="n">
-        <v>1571.6</v>
+        <v>1664.8</v>
       </c>
       <c r="F1400" t="n">
-        <v>11175.7</v>
+        <v>11268.9</v>
       </c>
       <c r="G1400" t="n">
         <v>1</v>
@@ -46660,10 +46660,10 @@
         <v>73.10000000000001</v>
       </c>
       <c r="E1401" t="n">
-        <v>1624.7</v>
+        <v>1684.5</v>
       </c>
       <c r="F1401" t="n">
-        <v>9159.700000000001</v>
+        <v>9219.5</v>
       </c>
       <c r="G1401" t="n">
         <v>6</v>
@@ -46693,10 +46693,10 @@
         <v>75.59999999999999</v>
       </c>
       <c r="E1402" t="n">
-        <v>1703.3</v>
+        <v>1752.7</v>
       </c>
       <c r="F1402" t="n">
-        <v>12414.4</v>
+        <v>12463.8</v>
       </c>
       <c r="G1402" t="n">
         <v>3</v>
@@ -46705,7 +46705,7 @@
         <v>4</v>
       </c>
       <c r="I1402" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1403">
@@ -46726,10 +46726,10 @@
         <v>84.09999999999999</v>
       </c>
       <c r="E1403" t="n">
-        <v>1708.1</v>
+        <v>1786.5</v>
       </c>
       <c r="F1403" t="n">
-        <v>12399.1</v>
+        <v>12477.5</v>
       </c>
       <c r="G1403" t="n">
         <v>1</v>
@@ -46738,7 +46738,7 @@
         <v>2</v>
       </c>
       <c r="I1403" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1404">
@@ -46759,10 +46759,10 @@
         <v>59.3</v>
       </c>
       <c r="E1404" t="n">
-        <v>1694.1</v>
+        <v>1748.2</v>
       </c>
       <c r="F1404" t="n">
-        <v>11559.2</v>
+        <v>11613.3</v>
       </c>
       <c r="G1404" t="n">
         <v>8</v>
@@ -46792,10 +46792,10 @@
         <v>71.5</v>
       </c>
       <c r="E1405" t="n">
-        <v>1525.4</v>
+        <v>1606.7</v>
       </c>
       <c r="F1405" t="n">
-        <v>11190</v>
+        <v>11271.3</v>
       </c>
       <c r="G1405" t="n">
         <v>6</v>
@@ -46825,10 +46825,10 @@
         <v>75.39999999999999</v>
       </c>
       <c r="E1406" t="n">
-        <v>1820.9</v>
+        <v>1894.4</v>
       </c>
       <c r="F1406" t="n">
-        <v>12755.7</v>
+        <v>12829.2</v>
       </c>
       <c r="G1406" t="n">
         <v>4</v>
@@ -46858,10 +46858,10 @@
         <v>62.7</v>
       </c>
       <c r="E1407" t="n">
-        <v>1440.9</v>
+        <v>1511.6</v>
       </c>
       <c r="F1407" t="n">
-        <v>10274.8</v>
+        <v>10345.5</v>
       </c>
       <c r="G1407" t="n">
         <v>7</v>
@@ -46891,10 +46891,10 @@
         <v>72</v>
       </c>
       <c r="E1408" t="n">
-        <v>1643.6</v>
+        <v>1736.8</v>
       </c>
       <c r="F1408" t="n">
-        <v>11247.7</v>
+        <v>11340.9</v>
       </c>
       <c r="G1408" t="n">
         <v>5</v>
@@ -46924,10 +46924,10 @@
         <v>79.09999999999999</v>
       </c>
       <c r="E1409" t="n">
-        <v>1703.8</v>
+        <v>1763.6</v>
       </c>
       <c r="F1409" t="n">
-        <v>9238.799999999999</v>
+        <v>9298.6</v>
       </c>
       <c r="G1409" t="n">
         <v>2</v>
@@ -46957,19 +46957,19 @@
         <v>73.2</v>
       </c>
       <c r="E1410" t="n">
-        <v>1776.5</v>
+        <v>1825.9</v>
       </c>
       <c r="F1410" t="n">
-        <v>12487.6</v>
+        <v>12537</v>
       </c>
       <c r="G1410" t="n">
         <v>2</v>
       </c>
       <c r="H1410" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1410" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1411">
@@ -46990,19 +46990,19 @@
         <v>62.7</v>
       </c>
       <c r="E1411" t="n">
-        <v>1770.8</v>
+        <v>1849.2</v>
       </c>
       <c r="F1411" t="n">
-        <v>12461.8</v>
+        <v>12540.2</v>
       </c>
       <c r="G1411" t="n">
         <v>5</v>
       </c>
       <c r="H1411" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I1411" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1412">
@@ -47023,10 +47023,10 @@
         <v>49.2</v>
       </c>
       <c r="E1412" t="n">
-        <v>1743.3</v>
+        <v>1797.4</v>
       </c>
       <c r="F1412" t="n">
-        <v>11608.4</v>
+        <v>11662.5</v>
       </c>
       <c r="G1412" t="n">
         <v>6</v>
@@ -47056,10 +47056,10 @@
         <v>43.9</v>
       </c>
       <c r="E1413" t="n">
-        <v>1569.3</v>
+        <v>1650.6</v>
       </c>
       <c r="F1413" t="n">
-        <v>11233.9</v>
+        <v>11315.2</v>
       </c>
       <c r="G1413" t="n">
         <v>7</v>
@@ -47089,10 +47089,10 @@
         <v>71.2</v>
       </c>
       <c r="E1414" t="n">
-        <v>1892.1</v>
+        <v>1965.6</v>
       </c>
       <c r="F1414" t="n">
-        <v>12826.9</v>
+        <v>12900.4</v>
       </c>
       <c r="G1414" t="n">
         <v>3</v>
@@ -47122,10 +47122,10 @@
         <v>64.09999999999999</v>
       </c>
       <c r="E1415" t="n">
-        <v>1505</v>
+        <v>1575.7</v>
       </c>
       <c r="F1415" t="n">
-        <v>10338.9</v>
+        <v>10409.6</v>
       </c>
       <c r="G1415" t="n">
         <v>4</v>
@@ -47155,10 +47155,10 @@
         <v>42.9</v>
       </c>
       <c r="E1416" t="n">
-        <v>1686.5</v>
+        <v>1779.7</v>
       </c>
       <c r="F1416" t="n">
-        <v>11290.6</v>
+        <v>11383.8</v>
       </c>
       <c r="G1416" t="n">
         <v>8</v>
@@ -47188,16 +47188,16 @@
         <v>73.8</v>
       </c>
       <c r="E1417" t="n">
-        <v>1777.6</v>
+        <v>1837.4</v>
       </c>
       <c r="F1417" t="n">
-        <v>9312.6</v>
+        <v>9372.4</v>
       </c>
       <c r="G1417" t="n">
         <v>1</v>
       </c>
       <c r="H1417" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1417" t="n">
         <v>8</v>
@@ -47221,16 +47221,16 @@
         <v>79.3</v>
       </c>
       <c r="E1418" t="n">
-        <v>1855.8</v>
+        <v>1905.2</v>
       </c>
       <c r="F1418" t="n">
-        <v>12566.9</v>
+        <v>12616.3</v>
       </c>
       <c r="G1418" t="n">
         <v>1</v>
       </c>
       <c r="H1418" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1418" t="n">
         <v>2</v>
@@ -47254,16 +47254,16 @@
         <v>62.3</v>
       </c>
       <c r="E1419" t="n">
-        <v>1833.1</v>
+        <v>1911.5</v>
       </c>
       <c r="F1419" t="n">
-        <v>12524.1</v>
+        <v>12602.5</v>
       </c>
       <c r="G1419" t="n">
         <v>4</v>
       </c>
       <c r="H1419" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I1419" t="n">
         <v>3</v>
@@ -47287,10 +47287,10 @@
         <v>50.4</v>
       </c>
       <c r="E1420" t="n">
-        <v>1793.7</v>
+        <v>1847.8</v>
       </c>
       <c r="F1420" t="n">
-        <v>11658.8</v>
+        <v>11712.9</v>
       </c>
       <c r="G1420" t="n">
         <v>7</v>
@@ -47320,10 +47320,10 @@
         <v>48.8</v>
       </c>
       <c r="E1421" t="n">
-        <v>1618.1</v>
+        <v>1699.4</v>
       </c>
       <c r="F1421" t="n">
-        <v>11282.7</v>
+        <v>11364</v>
       </c>
       <c r="G1421" t="n">
         <v>8</v>
@@ -47353,10 +47353,10 @@
         <v>75</v>
       </c>
       <c r="E1422" t="n">
-        <v>1967.1</v>
+        <v>2040.6</v>
       </c>
       <c r="F1422" t="n">
-        <v>12901.9</v>
+        <v>12975.4</v>
       </c>
       <c r="G1422" t="n">
         <v>2</v>
@@ -47386,10 +47386,10 @@
         <v>64.5</v>
       </c>
       <c r="E1423" t="n">
-        <v>1569.5</v>
+        <v>1640.2</v>
       </c>
       <c r="F1423" t="n">
-        <v>10403.4</v>
+        <v>10474.1</v>
       </c>
       <c r="G1423" t="n">
         <v>3</v>
@@ -47419,10 +47419,10 @@
         <v>59.7</v>
       </c>
       <c r="E1424" t="n">
-        <v>1746.2</v>
+        <v>1839.4</v>
       </c>
       <c r="F1424" t="n">
-        <v>11350.3</v>
+        <v>11443.5</v>
       </c>
       <c r="G1424" t="n">
         <v>5</v>
@@ -47452,16 +47452,16 @@
         <v>57.7</v>
       </c>
       <c r="E1425" t="n">
-        <v>1835.3</v>
+        <v>1895.1</v>
       </c>
       <c r="F1425" t="n">
-        <v>9370.299999999999</v>
+        <v>9430.1</v>
       </c>
       <c r="G1425" t="n">
         <v>6</v>
       </c>
       <c r="H1425" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1425" t="n">
         <v>8</v>
@@ -47485,10 +47485,10 @@
         <v>86.3</v>
       </c>
       <c r="E1426" t="n">
-        <v>1942.1</v>
+        <v>1991.5</v>
       </c>
       <c r="F1426" t="n">
-        <v>12653.2</v>
+        <v>12702.6</v>
       </c>
       <c r="G1426" t="n">
         <v>2</v>
@@ -47518,10 +47518,10 @@
         <v>75.59999999999999</v>
       </c>
       <c r="E1427" t="n">
-        <v>1908.7</v>
+        <v>1987.1</v>
       </c>
       <c r="F1427" t="n">
-        <v>12599.7</v>
+        <v>12678.1</v>
       </c>
       <c r="G1427" t="n">
         <v>3</v>
@@ -47551,10 +47551,10 @@
         <v>50.9</v>
       </c>
       <c r="E1428" t="n">
-        <v>1844.6</v>
+        <v>1898.7</v>
       </c>
       <c r="F1428" t="n">
-        <v>11709.7</v>
+        <v>11763.8</v>
       </c>
       <c r="G1428" t="n">
         <v>8</v>
@@ -47584,10 +47584,10 @@
         <v>65.3</v>
       </c>
       <c r="E1429" t="n">
-        <v>1683.4</v>
+        <v>1764.7</v>
       </c>
       <c r="F1429" t="n">
-        <v>11348</v>
+        <v>11429.3</v>
       </c>
       <c r="G1429" t="n">
         <v>4</v>
@@ -47617,10 +47617,10 @@
         <v>58.4</v>
       </c>
       <c r="E1430" t="n">
-        <v>2025.5</v>
+        <v>2099</v>
       </c>
       <c r="F1430" t="n">
-        <v>12960.3</v>
+        <v>13033.8</v>
       </c>
       <c r="G1430" t="n">
         <v>6</v>
@@ -47650,10 +47650,10 @@
         <v>58.6</v>
       </c>
       <c r="E1431" t="n">
-        <v>1628.1</v>
+        <v>1698.8</v>
       </c>
       <c r="F1431" t="n">
-        <v>10462</v>
+        <v>10532.7</v>
       </c>
       <c r="G1431" t="n">
         <v>5</v>
@@ -47683,10 +47683,10 @@
         <v>55.3</v>
       </c>
       <c r="E1432" t="n">
-        <v>1801.5</v>
+        <v>1894.7</v>
       </c>
       <c r="F1432" t="n">
-        <v>11405.6</v>
+        <v>11498.8</v>
       </c>
       <c r="G1432" t="n">
         <v>7</v>
@@ -47716,10 +47716,10 @@
         <v>96</v>
       </c>
       <c r="E1433" t="n">
-        <v>1931.3</v>
+        <v>1991.1</v>
       </c>
       <c r="F1433" t="n">
-        <v>9466.299999999999</v>
+        <v>9526.1</v>
       </c>
       <c r="G1433" t="n">
         <v>1</v>
@@ -47749,10 +47749,10 @@
         <v>84.5</v>
       </c>
       <c r="E1434" t="n">
-        <v>2026.6</v>
+        <v>2076</v>
       </c>
       <c r="F1434" t="n">
-        <v>12737.7</v>
+        <v>12787.1</v>
       </c>
       <c r="G1434" t="n">
         <v>1</v>
@@ -47782,10 +47782,10 @@
         <v>66.59999999999999</v>
       </c>
       <c r="E1435" t="n">
-        <v>1975.3</v>
+        <v>2053.7</v>
       </c>
       <c r="F1435" t="n">
-        <v>12666.3</v>
+        <v>12744.7</v>
       </c>
       <c r="G1435" t="n">
         <v>4</v>
@@ -47815,16 +47815,16 @@
         <v>60.1</v>
       </c>
       <c r="E1436" t="n">
-        <v>1904.7</v>
+        <v>1958.8</v>
       </c>
       <c r="F1436" t="n">
-        <v>11769.8</v>
+        <v>11823.9</v>
       </c>
       <c r="G1436" t="n">
         <v>6</v>
       </c>
       <c r="H1436" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1436" t="n">
         <v>4</v>
@@ -47848,10 +47848,10 @@
         <v>74.09999999999999</v>
       </c>
       <c r="E1437" t="n">
-        <v>1757.5</v>
+        <v>1838.8</v>
       </c>
       <c r="F1437" t="n">
-        <v>11422.1</v>
+        <v>11503.4</v>
       </c>
       <c r="G1437" t="n">
         <v>3</v>
@@ -47881,10 +47881,10 @@
         <v>57.4</v>
       </c>
       <c r="E1438" t="n">
-        <v>2082.9</v>
+        <v>2156.4</v>
       </c>
       <c r="F1438" t="n">
-        <v>13017.7</v>
+        <v>13091.2</v>
       </c>
       <c r="G1438" t="n">
         <v>7</v>
@@ -47914,10 +47914,10 @@
         <v>0</v>
       </c>
       <c r="E1439" t="n">
-        <v>1628.1</v>
+        <v>1698.8</v>
       </c>
       <c r="F1439" t="n">
-        <v>10462</v>
+        <v>10532.7</v>
       </c>
       <c r="G1439" t="n">
         <v>8</v>
@@ -47947,16 +47947,16 @@
         <v>65.90000000000001</v>
       </c>
       <c r="E1440" t="n">
-        <v>1867.4</v>
+        <v>1960.6</v>
       </c>
       <c r="F1440" t="n">
-        <v>11471.5</v>
+        <v>11564.7</v>
       </c>
       <c r="G1440" t="n">
         <v>5</v>
       </c>
       <c r="H1440" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1440" t="n">
         <v>5</v>
@@ -47980,10 +47980,10 @@
         <v>76</v>
       </c>
       <c r="E1441" t="n">
-        <v>2007.3</v>
+        <v>2067.1</v>
       </c>
       <c r="F1441" t="n">
-        <v>9542.299999999999</v>
+        <v>9602.1</v>
       </c>
       <c r="G1441" t="n">
         <v>2</v>
@@ -48013,10 +48013,10 @@
         <v>73.09999999999999</v>
       </c>
       <c r="E1442" t="n">
-        <v>2099.7</v>
+        <v>2149.1</v>
       </c>
       <c r="F1442" t="n">
-        <v>12810.8</v>
+        <v>12860.2</v>
       </c>
       <c r="G1442" t="n">
         <v>6</v>
@@ -48046,10 +48046,10 @@
         <v>92.90000000000001</v>
       </c>
       <c r="E1443" t="n">
-        <v>2068.2</v>
+        <v>2146.6</v>
       </c>
       <c r="F1443" t="n">
-        <v>12759.2</v>
+        <v>12837.6</v>
       </c>
       <c r="G1443" t="n">
         <v>2</v>
@@ -48079,16 +48079,16 @@
         <v>51.6</v>
       </c>
       <c r="E1444" t="n">
-        <v>1956.3</v>
+        <v>2010.4</v>
       </c>
       <c r="F1444" t="n">
-        <v>11821.4</v>
+        <v>11875.5</v>
       </c>
       <c r="G1444" t="n">
         <v>8</v>
       </c>
       <c r="H1444" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1444" t="n">
         <v>4</v>
@@ -48112,10 +48112,10 @@
         <v>62.1</v>
       </c>
       <c r="E1445" t="n">
-        <v>1819.6</v>
+        <v>1900.9</v>
       </c>
       <c r="F1445" t="n">
-        <v>11484.2</v>
+        <v>11565.5</v>
       </c>
       <c r="G1445" t="n">
         <v>7</v>
@@ -48145,10 +48145,10 @@
         <v>86.7</v>
       </c>
       <c r="E1446" t="n">
-        <v>2169.6</v>
+        <v>2243.1</v>
       </c>
       <c r="F1446" t="n">
-        <v>13104.4</v>
+        <v>13177.9</v>
       </c>
       <c r="G1446" t="n">
         <v>4</v>
@@ -48178,10 +48178,10 @@
         <v>88.2</v>
       </c>
       <c r="E1447" t="n">
-        <v>1716.3</v>
+        <v>1787</v>
       </c>
       <c r="F1447" t="n">
-        <v>10550.2</v>
+        <v>10620.9</v>
       </c>
       <c r="G1447" t="n">
         <v>3</v>
@@ -48211,16 +48211,16 @@
         <v>73.3</v>
       </c>
       <c r="E1448" t="n">
-        <v>1940.7</v>
+        <v>2033.9</v>
       </c>
       <c r="F1448" t="n">
-        <v>11544.8</v>
+        <v>11638</v>
       </c>
       <c r="G1448" t="n">
         <v>5</v>
       </c>
       <c r="H1448" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1448" t="n">
         <v>5</v>
@@ -48244,10 +48244,10 @@
         <v>100.9</v>
       </c>
       <c r="E1449" t="n">
-        <v>2108.2</v>
+        <v>2168</v>
       </c>
       <c r="F1449" t="n">
-        <v>9643.200000000001</v>
+        <v>9703</v>
       </c>
       <c r="G1449" t="n">
         <v>1</v>
@@ -48277,10 +48277,10 @@
         <v>82.5</v>
       </c>
       <c r="E1450" t="n">
-        <v>2182.2</v>
+        <v>2231.6</v>
       </c>
       <c r="F1450" t="n">
-        <v>12893.3</v>
+        <v>12942.7</v>
       </c>
       <c r="G1450" t="n">
         <v>3</v>
@@ -48310,16 +48310,16 @@
         <v>73.5</v>
       </c>
       <c r="E1451" t="n">
-        <v>2141.7</v>
+        <v>2220.1</v>
       </c>
       <c r="F1451" t="n">
-        <v>12832.7</v>
+        <v>12911.1</v>
       </c>
       <c r="G1451" t="n">
         <v>4</v>
       </c>
       <c r="H1451" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1451" t="n">
         <v>3</v>
@@ -48343,10 +48343,10 @@
         <v>114.5</v>
       </c>
       <c r="E1452" t="n">
-        <v>2070.8</v>
+        <v>2124.9</v>
       </c>
       <c r="F1452" t="n">
-        <v>11935.9</v>
+        <v>11990</v>
       </c>
       <c r="G1452" t="n">
         <v>1</v>
@@ -48376,10 +48376,10 @@
         <v>85.90000000000001</v>
       </c>
       <c r="E1453" t="n">
-        <v>1905.5</v>
+        <v>1986.8</v>
       </c>
       <c r="F1453" t="n">
-        <v>11570.1</v>
+        <v>11651.4</v>
       </c>
       <c r="G1453" t="n">
         <v>2</v>
@@ -48409,10 +48409,10 @@
         <v>48.6</v>
       </c>
       <c r="E1454" t="n">
-        <v>2218.2</v>
+        <v>2291.7</v>
       </c>
       <c r="F1454" t="n">
-        <v>13153</v>
+        <v>13226.5</v>
       </c>
       <c r="G1454" t="n">
         <v>6</v>
@@ -48442,10 +48442,10 @@
         <v>52.8</v>
       </c>
       <c r="E1455" t="n">
-        <v>1769.1</v>
+        <v>1839.8</v>
       </c>
       <c r="F1455" t="n">
-        <v>10603</v>
+        <v>10673.7</v>
       </c>
       <c r="G1455" t="n">
         <v>5</v>
@@ -48475,10 +48475,10 @@
         <v>47.9</v>
       </c>
       <c r="E1456" t="n">
-        <v>1988.6</v>
+        <v>2081.8</v>
       </c>
       <c r="F1456" t="n">
-        <v>11592.7</v>
+        <v>11685.9</v>
       </c>
       <c r="G1456" t="n">
         <v>7</v>
@@ -48508,16 +48508,16 @@
         <v>43.3</v>
       </c>
       <c r="E1457" t="n">
-        <v>2151.5</v>
+        <v>2211.3</v>
       </c>
       <c r="F1457" t="n">
-        <v>9686.5</v>
+        <v>9746.299999999999</v>
       </c>
       <c r="G1457" t="n">
         <v>8</v>
       </c>
       <c r="H1457" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1457" t="n">
         <v>8</v>
@@ -48541,10 +48541,10 @@
         <v>66.5</v>
       </c>
       <c r="E1458" t="n">
-        <v>2248.7</v>
+        <v>2298.1</v>
       </c>
       <c r="F1458" t="n">
-        <v>12959.8</v>
+        <v>13009.2</v>
       </c>
       <c r="G1458" t="n">
         <v>5</v>
@@ -48574,10 +48574,10 @@
         <v>65.5</v>
       </c>
       <c r="E1459" t="n">
-        <v>2207.2</v>
+        <v>2285.6</v>
       </c>
       <c r="F1459" t="n">
-        <v>12898.2</v>
+        <v>12976.6</v>
       </c>
       <c r="G1459" t="n">
         <v>7</v>
@@ -48607,10 +48607,10 @@
         <v>83.90000000000001</v>
       </c>
       <c r="E1460" t="n">
-        <v>2154.7</v>
+        <v>2208.8</v>
       </c>
       <c r="F1460" t="n">
-        <v>12019.8</v>
+        <v>12073.9</v>
       </c>
       <c r="G1460" t="n">
         <v>3</v>
@@ -48640,10 +48640,10 @@
         <v>66.40000000000001</v>
       </c>
       <c r="E1461" t="n">
-        <v>1971.9</v>
+        <v>2053.2</v>
       </c>
       <c r="F1461" t="n">
-        <v>11636.5</v>
+        <v>11717.8</v>
       </c>
       <c r="G1461" t="n">
         <v>6</v>
@@ -48673,10 +48673,10 @@
         <v>107</v>
       </c>
       <c r="E1462" t="n">
-        <v>2325.2</v>
+        <v>2398.7</v>
       </c>
       <c r="F1462" t="n">
-        <v>13260</v>
+        <v>13333.5</v>
       </c>
       <c r="G1462" t="n">
         <v>1</v>
@@ -48706,10 +48706,10 @@
         <v>46.5</v>
       </c>
       <c r="E1463" t="n">
-        <v>1815.6</v>
+        <v>1886.3</v>
       </c>
       <c r="F1463" t="n">
-        <v>10649.5</v>
+        <v>10720.2</v>
       </c>
       <c r="G1463" t="n">
         <v>8</v>
@@ -48739,10 +48739,10 @@
         <v>67.40000000000001</v>
       </c>
       <c r="E1464" t="n">
-        <v>2056</v>
+        <v>2149.2</v>
       </c>
       <c r="F1464" t="n">
-        <v>11660.1</v>
+        <v>11753.3</v>
       </c>
       <c r="G1464" t="n">
         <v>4</v>
@@ -48772,10 +48772,10 @@
         <v>85.59999999999999</v>
       </c>
       <c r="E1465" t="n">
-        <v>2237.1</v>
+        <v>2296.9</v>
       </c>
       <c r="F1465" t="n">
-        <v>9772.1</v>
+        <v>9831.9</v>
       </c>
       <c r="G1465" t="n">
         <v>2</v>
@@ -48805,10 +48805,10 @@
         <v>100.6</v>
       </c>
       <c r="E1466" t="n">
-        <v>2349.3</v>
+        <v>2398.7</v>
       </c>
       <c r="F1466" t="n">
-        <v>13060.4</v>
+        <v>13109.8</v>
       </c>
       <c r="G1466" t="n">
         <v>1</v>
@@ -48838,10 +48838,10 @@
         <v>65.90000000000001</v>
       </c>
       <c r="E1467" t="n">
-        <v>2273.1</v>
+        <v>2351.5</v>
       </c>
       <c r="F1467" t="n">
-        <v>12964.1</v>
+        <v>13042.5</v>
       </c>
       <c r="G1467" t="n">
         <v>5</v>
@@ -48871,10 +48871,10 @@
         <v>70.8</v>
       </c>
       <c r="E1468" t="n">
-        <v>2225.5</v>
+        <v>2279.6</v>
       </c>
       <c r="F1468" t="n">
-        <v>12090.6</v>
+        <v>12144.7</v>
       </c>
       <c r="G1468" t="n">
         <v>4</v>
@@ -48904,10 +48904,10 @@
         <v>60.5</v>
       </c>
       <c r="E1469" t="n">
-        <v>2032.4</v>
+        <v>2113.7</v>
       </c>
       <c r="F1469" t="n">
-        <v>11697</v>
+        <v>11778.3</v>
       </c>
       <c r="G1469" t="n">
         <v>7</v>
@@ -48937,10 +48937,10 @@
         <v>64.59999999999999</v>
       </c>
       <c r="E1470" t="n">
-        <v>2389.8</v>
+        <v>2463.3</v>
       </c>
       <c r="F1470" t="n">
-        <v>13324.6</v>
+        <v>13398.1</v>
       </c>
       <c r="G1470" t="n">
         <v>6</v>
@@ -48970,10 +48970,10 @@
         <v>73.7</v>
       </c>
       <c r="E1471" t="n">
-        <v>1889.3</v>
+        <v>1960</v>
       </c>
       <c r="F1471" t="n">
-        <v>10723.2</v>
+        <v>10793.9</v>
       </c>
       <c r="G1471" t="n">
         <v>3</v>
@@ -49003,10 +49003,10 @@
         <v>55.2</v>
       </c>
       <c r="E1472" t="n">
-        <v>2111.2</v>
+        <v>2204.4</v>
       </c>
       <c r="F1472" t="n">
-        <v>11715.3</v>
+        <v>11808.5</v>
       </c>
       <c r="G1472" t="n">
         <v>8</v>
@@ -49036,10 +49036,10 @@
         <v>88</v>
       </c>
       <c r="E1473" t="n">
-        <v>2325.1</v>
+        <v>2384.9</v>
       </c>
       <c r="F1473" t="n">
-        <v>9860.1</v>
+        <v>9919.9</v>
       </c>
       <c r="G1473" t="n">
         <v>2</v>
@@ -49069,10 +49069,10 @@
         <v>70.09999999999999</v>
       </c>
       <c r="E1474" t="n">
-        <v>2419.4</v>
+        <v>2468.8</v>
       </c>
       <c r="F1474" t="n">
-        <v>13130.5</v>
+        <v>13179.9</v>
       </c>
       <c r="G1474" t="n">
         <v>4</v>
@@ -49102,10 +49102,10 @@
         <v>77.90000000000001</v>
       </c>
       <c r="E1475" t="n">
-        <v>2351</v>
+        <v>2429.4</v>
       </c>
       <c r="F1475" t="n">
-        <v>13042</v>
+        <v>13120.4</v>
       </c>
       <c r="G1475" t="n">
         <v>3</v>
@@ -49135,10 +49135,10 @@
         <v>80.8</v>
       </c>
       <c r="E1476" t="n">
-        <v>2306.3</v>
+        <v>2360.4</v>
       </c>
       <c r="F1476" t="n">
-        <v>12171.4</v>
+        <v>12225.5</v>
       </c>
       <c r="G1476" t="n">
         <v>2</v>
@@ -49168,10 +49168,10 @@
         <v>53</v>
       </c>
       <c r="E1477" t="n">
-        <v>2085.4</v>
+        <v>2166.7</v>
       </c>
       <c r="F1477" t="n">
-        <v>11750</v>
+        <v>11831.3</v>
       </c>
       <c r="G1477" t="n">
         <v>7</v>
@@ -49201,10 +49201,10 @@
         <v>59.8</v>
       </c>
       <c r="E1478" t="n">
-        <v>2449.6</v>
+        <v>2523.1</v>
       </c>
       <c r="F1478" t="n">
-        <v>13384.4</v>
+        <v>13457.9</v>
       </c>
       <c r="G1478" t="n">
         <v>6</v>
@@ -49234,10 +49234,10 @@
         <v>68.39999999999999</v>
       </c>
       <c r="E1479" t="n">
-        <v>1957.7</v>
+        <v>2028.4</v>
       </c>
       <c r="F1479" t="n">
-        <v>10791.6</v>
+        <v>10862.3</v>
       </c>
       <c r="G1479" t="n">
         <v>5</v>
@@ -49267,10 +49267,10 @@
         <v>48.4</v>
       </c>
       <c r="E1480" t="n">
-        <v>2159.6</v>
+        <v>2252.8</v>
       </c>
       <c r="F1480" t="n">
-        <v>11763.7</v>
+        <v>11856.9</v>
       </c>
       <c r="G1480" t="n">
         <v>8</v>
@@ -49300,10 +49300,10 @@
         <v>104.8</v>
       </c>
       <c r="E1481" t="n">
-        <v>2429.9</v>
+        <v>2489.7</v>
       </c>
       <c r="F1481" t="n">
-        <v>9964.9</v>
+        <v>10024.7</v>
       </c>
       <c r="G1481" t="n">
         <v>1</v>
@@ -49333,10 +49333,10 @@
         <v>76.3</v>
       </c>
       <c r="E1482" t="n">
-        <v>2495.7</v>
+        <v>2545.1</v>
       </c>
       <c r="F1482" t="n">
-        <v>13206.8</v>
+        <v>13256.2</v>
       </c>
       <c r="G1482" t="n">
         <v>3</v>
@@ -49366,10 +49366,10 @@
         <v>73.3</v>
       </c>
       <c r="E1483" t="n">
-        <v>2424.3</v>
+        <v>2502.7</v>
       </c>
       <c r="F1483" t="n">
-        <v>13115.3</v>
+        <v>13193.7</v>
       </c>
       <c r="G1483" t="n">
         <v>5</v>
@@ -49399,10 +49399,10 @@
         <v>56.5</v>
       </c>
       <c r="E1484" t="n">
-        <v>2362.8</v>
+        <v>2416.9</v>
       </c>
       <c r="F1484" t="n">
-        <v>12227.9</v>
+        <v>12282</v>
       </c>
       <c r="G1484" t="n">
         <v>7</v>
@@ -49432,10 +49432,10 @@
         <v>75.09999999999999</v>
       </c>
       <c r="E1485" t="n">
-        <v>2160.5</v>
+        <v>2241.8</v>
       </c>
       <c r="F1485" t="n">
-        <v>11825.1</v>
+        <v>11906.4</v>
       </c>
       <c r="G1485" t="n">
         <v>4</v>
@@ -49465,10 +49465,10 @@
         <v>69.7</v>
       </c>
       <c r="E1486" t="n">
-        <v>2519.3</v>
+        <v>2592.8</v>
       </c>
       <c r="F1486" t="n">
-        <v>13454.1</v>
+        <v>13527.6</v>
       </c>
       <c r="G1486" t="n">
         <v>6</v>
@@ -49498,10 +49498,10 @@
         <v>80.09999999999999</v>
       </c>
       <c r="E1487" t="n">
-        <v>2037.8</v>
+        <v>2108.5</v>
       </c>
       <c r="F1487" t="n">
-        <v>10871.7</v>
+        <v>10942.4</v>
       </c>
       <c r="G1487" t="n">
         <v>2</v>
@@ -49531,10 +49531,10 @@
         <v>44.90000000000001</v>
       </c>
       <c r="E1488" t="n">
-        <v>2204.5</v>
+        <v>2297.7</v>
       </c>
       <c r="F1488" t="n">
-        <v>11808.6</v>
+        <v>11901.8</v>
       </c>
       <c r="G1488" t="n">
         <v>8</v>
@@ -49564,10 +49564,10 @@
         <v>82.40000000000001</v>
       </c>
       <c r="E1489" t="n">
-        <v>2512.3</v>
+        <v>2572.1</v>
       </c>
       <c r="F1489" t="n">
-        <v>10047.3</v>
+        <v>10107.1</v>
       </c>
       <c r="G1489" t="n">
         <v>1</v>
@@ -49597,16 +49597,16 @@
         <v>94.09999999999999</v>
       </c>
       <c r="E1490" t="n">
-        <v>2589.8</v>
+        <v>2639.2</v>
       </c>
       <c r="F1490" t="n">
-        <v>13300.9</v>
+        <v>13350.3</v>
       </c>
       <c r="G1490" t="n">
         <v>3</v>
       </c>
       <c r="H1490" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1490" t="n">
         <v>2</v>
@@ -49630,10 +49630,10 @@
         <v>94.90000000000001</v>
       </c>
       <c r="E1491" t="n">
-        <v>2519.2</v>
+        <v>2597.6</v>
       </c>
       <c r="F1491" t="n">
-        <v>13210.2</v>
+        <v>13288.6</v>
       </c>
       <c r="G1491" t="n">
         <v>2</v>
@@ -49663,10 +49663,10 @@
         <v>75.2</v>
       </c>
       <c r="E1492" t="n">
-        <v>2438</v>
+        <v>2492.1</v>
       </c>
       <c r="F1492" t="n">
-        <v>12303.1</v>
+        <v>12357.2</v>
       </c>
       <c r="G1492" t="n">
         <v>5</v>
@@ -49696,10 +49696,10 @@
         <v>38.3</v>
       </c>
       <c r="E1493" t="n">
-        <v>2198.8</v>
+        <v>2280.1</v>
       </c>
       <c r="F1493" t="n">
-        <v>11863.4</v>
+        <v>11944.7</v>
       </c>
       <c r="G1493" t="n">
         <v>8</v>
@@ -49708,7 +49708,7 @@
         <v>7</v>
       </c>
       <c r="I1493" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1494">
@@ -49729,16 +49729,16 @@
         <v>52.9</v>
       </c>
       <c r="E1494" t="n">
-        <v>2572.2</v>
+        <v>2645.7</v>
       </c>
       <c r="F1494" t="n">
-        <v>13507</v>
+        <v>13580.5</v>
       </c>
       <c r="G1494" t="n">
         <v>6</v>
       </c>
       <c r="H1494" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1494" t="n">
         <v>1</v>
@@ -49762,10 +49762,10 @@
         <v>78.7</v>
       </c>
       <c r="E1495" t="n">
-        <v>2116.5</v>
+        <v>2187.2</v>
       </c>
       <c r="F1495" t="n">
-        <v>10950.4</v>
+        <v>11021.1</v>
       </c>
       <c r="G1495" t="n">
         <v>4</v>
@@ -49795,10 +49795,10 @@
         <v>44.4</v>
       </c>
       <c r="E1496" t="n">
-        <v>2248.9</v>
+        <v>2342.1</v>
       </c>
       <c r="F1496" t="n">
-        <v>11853</v>
+        <v>11946.2</v>
       </c>
       <c r="G1496" t="n">
         <v>7</v>
@@ -49807,7 +49807,7 @@
         <v>6</v>
       </c>
       <c r="I1496" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1497">
@@ -49828,10 +49828,10 @@
         <v>95.3</v>
       </c>
       <c r="E1497" t="n">
-        <v>2607.6</v>
+        <v>2667.4</v>
       </c>
       <c r="F1497" t="n">
-        <v>10142.6</v>
+        <v>10202.4</v>
       </c>
       <c r="G1497" t="n">
         <v>1</v>
@@ -49861,10 +49861,10 @@
         <v>72.8</v>
       </c>
       <c r="E1498" t="n">
-        <v>2662.6</v>
+        <v>2712</v>
       </c>
       <c r="F1498" t="n">
-        <v>13373.7</v>
+        <v>13423.1</v>
       </c>
       <c r="G1498" t="n">
         <v>2</v>
@@ -49894,10 +49894,10 @@
         <v>42</v>
       </c>
       <c r="E1499" t="n">
-        <v>2561.2</v>
+        <v>2639.6</v>
       </c>
       <c r="F1499" t="n">
-        <v>13252.2</v>
+        <v>13330.6</v>
       </c>
       <c r="G1499" t="n">
         <v>7</v>
@@ -49927,10 +49927,10 @@
         <v>65.10000000000001</v>
       </c>
       <c r="E1500" t="n">
-        <v>2503.1</v>
+        <v>2557.2</v>
       </c>
       <c r="F1500" t="n">
-        <v>12368.2</v>
+        <v>12422.3</v>
       </c>
       <c r="G1500" t="n">
         <v>5</v>
@@ -49960,10 +49960,10 @@
         <v>39.8</v>
       </c>
       <c r="E1501" t="n">
-        <v>2238.6</v>
+        <v>2319.9</v>
       </c>
       <c r="F1501" t="n">
-        <v>11903.2</v>
+        <v>11984.5</v>
       </c>
       <c r="G1501" t="n">
         <v>8</v>
@@ -49993,10 +49993,10 @@
         <v>65.8</v>
       </c>
       <c r="E1502" t="n">
-        <v>2638</v>
+        <v>2711.5</v>
       </c>
       <c r="F1502" t="n">
-        <v>13572.8</v>
+        <v>13646.3</v>
       </c>
       <c r="G1502" t="n">
         <v>4</v>
@@ -50026,10 +50026,10 @@
         <v>66.40000000000001</v>
       </c>
       <c r="E1503" t="n">
-        <v>2182.9</v>
+        <v>2253.6</v>
       </c>
       <c r="F1503" t="n">
-        <v>11016.8</v>
+        <v>11087.5</v>
       </c>
       <c r="G1503" t="n">
         <v>3</v>
@@ -50059,10 +50059,10 @@
         <v>52.7</v>
       </c>
       <c r="E1504" t="n">
-        <v>2301.6</v>
+        <v>2394.8</v>
       </c>
       <c r="F1504" t="n">
-        <v>11905.7</v>
+        <v>11998.9</v>
       </c>
       <c r="G1504" t="n">
         <v>6</v>
@@ -50092,10 +50092,10 @@
         <v>81.3</v>
       </c>
       <c r="E1505" t="n">
-        <v>2688.9</v>
+        <v>2748.7</v>
       </c>
       <c r="F1505" t="n">
-        <v>10223.9</v>
+        <v>10283.7</v>
       </c>
       <c r="G1505" t="n">
         <v>1</v>
@@ -50125,10 +50125,10 @@
         <v>70.59999999999999</v>
       </c>
       <c r="E1506" t="n">
-        <v>2733.2</v>
+        <v>2782.6</v>
       </c>
       <c r="F1506" t="n">
-        <v>13444.3</v>
+        <v>13493.7</v>
       </c>
       <c r="G1506" t="n">
         <v>4</v>
@@ -50158,10 +50158,10 @@
         <v>76.40000000000001</v>
       </c>
       <c r="E1507" t="n">
-        <v>2637.6</v>
+        <v>2716</v>
       </c>
       <c r="F1507" t="n">
-        <v>13328.6</v>
+        <v>13407</v>
       </c>
       <c r="G1507" t="n">
         <v>2</v>
@@ -50191,10 +50191,10 @@
         <v>60.3</v>
       </c>
       <c r="E1508" t="n">
-        <v>2563.4</v>
+        <v>2617.5</v>
       </c>
       <c r="F1508" t="n">
-        <v>12428.5</v>
+        <v>12482.6</v>
       </c>
       <c r="G1508" t="n">
         <v>6</v>
@@ -50224,10 +50224,10 @@
         <v>60.4</v>
       </c>
       <c r="E1509" t="n">
-        <v>2299</v>
+        <v>2380.3</v>
       </c>
       <c r="F1509" t="n">
-        <v>11963.6</v>
+        <v>12044.9</v>
       </c>
       <c r="G1509" t="n">
         <v>5</v>
@@ -50236,7 +50236,7 @@
         <v>7</v>
       </c>
       <c r="I1509" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1510">
@@ -50257,10 +50257,10 @@
         <v>53.9</v>
       </c>
       <c r="E1510" t="n">
-        <v>2691.9</v>
+        <v>2765.4</v>
       </c>
       <c r="F1510" t="n">
-        <v>13626.7</v>
+        <v>13700.2</v>
       </c>
       <c r="G1510" t="n">
         <v>7</v>
@@ -50290,10 +50290,10 @@
         <v>75.80000000000001</v>
       </c>
       <c r="E1511" t="n">
-        <v>2258.7</v>
+        <v>2329.4</v>
       </c>
       <c r="F1511" t="n">
-        <v>11092.6</v>
+        <v>11163.3</v>
       </c>
       <c r="G1511" t="n">
         <v>3</v>
@@ -50323,10 +50323,10 @@
         <v>53.2</v>
       </c>
       <c r="E1512" t="n">
-        <v>2354.8</v>
+        <v>2448</v>
       </c>
       <c r="F1512" t="n">
-        <v>11958.9</v>
+        <v>12052.1</v>
       </c>
       <c r="G1512" t="n">
         <v>8</v>
@@ -50335,7 +50335,7 @@
         <v>6</v>
       </c>
       <c r="I1512" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1513">
@@ -50356,10 +50356,10 @@
         <v>87.59999999999999</v>
       </c>
       <c r="E1513" t="n">
-        <v>2776.5</v>
+        <v>2836.3</v>
       </c>
       <c r="F1513" t="n">
-        <v>10311.5</v>
+        <v>10371.3</v>
       </c>
       <c r="G1513" t="n">
         <v>1</v>
@@ -50389,10 +50389,10 @@
         <v>58.2</v>
       </c>
       <c r="E1514" t="n">
-        <v>2791.4</v>
+        <v>2840.8</v>
       </c>
       <c r="F1514" t="n">
-        <v>13502.5</v>
+        <v>13551.9</v>
       </c>
       <c r="G1514" t="n">
         <v>4</v>
@@ -50422,10 +50422,10 @@
         <v>49.3</v>
       </c>
       <c r="E1515" t="n">
-        <v>2686.9</v>
+        <v>2765.3</v>
       </c>
       <c r="F1515" t="n">
-        <v>13377.9</v>
+        <v>13456.3</v>
       </c>
       <c r="G1515" t="n">
         <v>5</v>
@@ -50455,10 +50455,10 @@
         <v>69.09999999999999</v>
       </c>
       <c r="E1516" t="n">
-        <v>2632.5</v>
+        <v>2686.6</v>
       </c>
       <c r="F1516" t="n">
-        <v>12497.6</v>
+        <v>12551.7</v>
       </c>
       <c r="G1516" t="n">
         <v>3</v>
@@ -50488,10 +50488,10 @@
         <v>48.4</v>
       </c>
       <c r="E1517" t="n">
-        <v>2347.4</v>
+        <v>2428.7</v>
       </c>
       <c r="F1517" t="n">
-        <v>12012</v>
+        <v>12093.3</v>
       </c>
       <c r="G1517" t="n">
         <v>6</v>
@@ -50521,10 +50521,10 @@
         <v>47.6</v>
       </c>
       <c r="E1518" t="n">
-        <v>2739.5</v>
+        <v>2813</v>
       </c>
       <c r="F1518" t="n">
-        <v>13674.3</v>
+        <v>13747.8</v>
       </c>
       <c r="G1518" t="n">
         <v>7</v>
@@ -50554,10 +50554,10 @@
         <v>34.8</v>
       </c>
       <c r="E1519" t="n">
-        <v>2293.5</v>
+        <v>2364.2</v>
       </c>
       <c r="F1519" t="n">
-        <v>11127.4</v>
+        <v>11198.1</v>
       </c>
       <c r="G1519" t="n">
         <v>8</v>
@@ -50587,10 +50587,10 @@
         <v>73.3</v>
       </c>
       <c r="E1520" t="n">
-        <v>2428.1</v>
+        <v>2521.3</v>
       </c>
       <c r="F1520" t="n">
-        <v>12032.2</v>
+        <v>12125.4</v>
       </c>
       <c r="G1520" t="n">
         <v>2</v>
@@ -50620,10 +50620,10 @@
         <v>97.7</v>
       </c>
       <c r="E1521" t="n">
-        <v>2874.2</v>
+        <v>2934</v>
       </c>
       <c r="F1521" t="n">
-        <v>10409.2</v>
+        <v>10469</v>
       </c>
       <c r="G1521" t="n">
         <v>1</v>
@@ -50653,10 +50653,10 @@
         <v>95.7</v>
       </c>
       <c r="E1522" t="n">
-        <v>2887.1</v>
+        <v>2936.5</v>
       </c>
       <c r="F1522" t="n">
-        <v>13598.2</v>
+        <v>13647.6</v>
       </c>
       <c r="G1522" t="n">
         <v>1</v>
@@ -50686,10 +50686,10 @@
         <v>0</v>
       </c>
       <c r="E1523" t="n">
-        <v>2686.9</v>
+        <v>2765.3</v>
       </c>
       <c r="F1523" t="n">
-        <v>13377.9</v>
+        <v>13456.3</v>
       </c>
       <c r="G1523" t="n">
         <v>8</v>
@@ -50719,10 +50719,10 @@
         <v>40.7</v>
       </c>
       <c r="E1524" t="n">
-        <v>2673.2</v>
+        <v>2727.3</v>
       </c>
       <c r="F1524" t="n">
-        <v>12538.3</v>
+        <v>12592.4</v>
       </c>
       <c r="G1524" t="n">
         <v>7</v>
@@ -50752,10 +50752,10 @@
         <v>68.2</v>
       </c>
       <c r="E1525" t="n">
-        <v>2415.6</v>
+        <v>2496.9</v>
       </c>
       <c r="F1525" t="n">
-        <v>12080.2</v>
+        <v>12161.5</v>
       </c>
       <c r="G1525" t="n">
         <v>4</v>
@@ -50764,7 +50764,7 @@
         <v>7</v>
       </c>
       <c r="I1525" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1526">
@@ -50785,10 +50785,10 @@
         <v>66.59999999999999</v>
       </c>
       <c r="E1526" t="n">
-        <v>2806.1</v>
+        <v>2879.6</v>
       </c>
       <c r="F1526" t="n">
-        <v>13740.9</v>
+        <v>13814.4</v>
       </c>
       <c r="G1526" t="n">
         <v>5</v>
@@ -50818,10 +50818,10 @@
         <v>80.59999999999999</v>
       </c>
       <c r="E1527" t="n">
-        <v>2374.1</v>
+        <v>2444.8</v>
       </c>
       <c r="F1527" t="n">
-        <v>11208</v>
+        <v>11278.7</v>
       </c>
       <c r="G1527" t="n">
         <v>2</v>
@@ -50851,10 +50851,10 @@
         <v>46.4</v>
       </c>
       <c r="E1528" t="n">
-        <v>2474.5</v>
+        <v>2567.7</v>
       </c>
       <c r="F1528" t="n">
-        <v>12078.6</v>
+        <v>12171.8</v>
       </c>
       <c r="G1528" t="n">
         <v>6</v>
@@ -50863,7 +50863,7 @@
         <v>6</v>
       </c>
       <c r="I1528" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1529">
@@ -50884,10 +50884,10 @@
         <v>80.40000000000001</v>
       </c>
       <c r="E1529" t="n">
-        <v>2954.6</v>
+        <v>3014.4</v>
       </c>
       <c r="F1529" t="n">
-        <v>10489.6</v>
+        <v>10549.4</v>
       </c>
       <c r="G1529" t="n">
         <v>3</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -42700,7 +42700,7 @@
         <v>58.2</v>
       </c>
       <c r="E1281" t="n">
-        <v>584.8000000000001</v>
+        <v>584.8</v>
       </c>
       <c r="F1281" t="n">
         <v>8119.8</v>
@@ -42964,7 +42964,7 @@
         <v>60</v>
       </c>
       <c r="E1289" t="n">
-        <v>644.8000000000001</v>
+        <v>644.8</v>
       </c>
       <c r="F1289" t="n">
         <v>8179.8</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -42436,7 +42436,7 @@
         <v>34.2</v>
       </c>
       <c r="E1273" t="n">
-        <v>526.6</v>
+        <v>526.5999999999999</v>
       </c>
       <c r="F1273" t="n">
         <v>8061.6</v>
@@ -43228,7 +43228,7 @@
         <v>76.89999999999999</v>
       </c>
       <c r="E1297" t="n">
-        <v>721.7</v>
+        <v>721.6999999999999</v>
       </c>
       <c r="F1297" t="n">
         <v>8256.700000000001</v>
@@ -43756,7 +43756,7 @@
         <v>95.2</v>
       </c>
       <c r="E1313" t="n">
-        <v>883.2</v>
+        <v>883.1999999999999</v>
       </c>
       <c r="F1313" t="n">
         <v>8418.200000000001</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -42436,7 +42436,7 @@
         <v>34.2</v>
       </c>
       <c r="E1273" t="n">
-        <v>526.5999999999999</v>
+        <v>526.6</v>
       </c>
       <c r="F1273" t="n">
         <v>8061.6</v>
@@ -43228,7 +43228,7 @@
         <v>76.89999999999999</v>
       </c>
       <c r="E1297" t="n">
-        <v>721.6999999999999</v>
+        <v>721.7</v>
       </c>
       <c r="F1297" t="n">
         <v>8256.700000000001</v>
@@ -43756,7 +43756,7 @@
         <v>95.2</v>
       </c>
       <c r="E1313" t="n">
-        <v>883.1999999999999</v>
+        <v>883.2</v>
       </c>
       <c r="F1313" t="n">
         <v>8418.200000000001</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -42700,7 +42700,7 @@
         <v>58.2</v>
       </c>
       <c r="E1281" t="n">
-        <v>584.8</v>
+        <v>584.8000000000001</v>
       </c>
       <c r="F1281" t="n">
         <v>8119.8</v>
@@ -42964,7 +42964,7 @@
         <v>60</v>
       </c>
       <c r="E1289" t="n">
-        <v>644.8</v>
+        <v>644.8000000000001</v>
       </c>
       <c r="F1289" t="n">
         <v>8179.8</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -41938,13 +41938,13 @@
         </is>
       </c>
       <c r="D1258" t="n">
-        <v>49.90000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="E1258" t="n">
-        <v>440.4</v>
+        <v>484.1</v>
       </c>
       <c r="F1258" t="n">
-        <v>11151.5</v>
+        <v>11195.2</v>
       </c>
       <c r="G1258" t="n">
         <v>8</v>
@@ -41971,16 +41971,16 @@
         </is>
       </c>
       <c r="D1259" t="n">
-        <v>70.40000000000001</v>
+        <v>136.4</v>
       </c>
       <c r="E1259" t="n">
-        <v>542</v>
+        <v>608</v>
       </c>
       <c r="F1259" t="n">
-        <v>11233</v>
+        <v>11299</v>
       </c>
       <c r="G1259" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1259" t="n">
         <v>3</v>
@@ -42004,16 +42004,16 @@
         </is>
       </c>
       <c r="D1260" t="n">
-        <v>57.1</v>
+        <v>131.8</v>
       </c>
       <c r="E1260" t="n">
-        <v>514.8</v>
+        <v>589.5</v>
       </c>
       <c r="F1260" t="n">
-        <v>10379.9</v>
+        <v>10454.6</v>
       </c>
       <c r="G1260" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1260" t="n">
         <v>4</v>
@@ -42037,19 +42037,19 @@
         </is>
       </c>
       <c r="D1261" t="n">
-        <v>82.7</v>
+        <v>136.3</v>
       </c>
       <c r="E1261" t="n">
-        <v>603.5</v>
+        <v>657.1</v>
       </c>
       <c r="F1261" t="n">
-        <v>10268.1</v>
+        <v>10321.7</v>
       </c>
       <c r="G1261" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1261" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1261" t="n">
         <v>5</v>
@@ -42070,19 +42070,19 @@
         </is>
       </c>
       <c r="D1262" t="n">
-        <v>86.5</v>
+        <v>167.2</v>
       </c>
       <c r="E1262" t="n">
-        <v>588.2</v>
+        <v>668.9</v>
       </c>
       <c r="F1262" t="n">
-        <v>11523</v>
+        <v>11603.7</v>
       </c>
       <c r="G1262" t="n">
         <v>1</v>
       </c>
       <c r="H1262" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1262" t="n">
         <v>1</v>
@@ -42103,16 +42103,16 @@
         </is>
       </c>
       <c r="D1263" t="n">
-        <v>75.8</v>
+        <v>128.7</v>
       </c>
       <c r="E1263" t="n">
-        <v>461.2</v>
+        <v>514.1</v>
       </c>
       <c r="F1263" t="n">
-        <v>9295.1</v>
+        <v>9348</v>
       </c>
       <c r="G1263" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1263" t="n">
         <v>7</v>
@@ -42136,16 +42136,16 @@
         </is>
       </c>
       <c r="D1264" t="n">
-        <v>77.7</v>
+        <v>147.6</v>
       </c>
       <c r="E1264" t="n">
-        <v>500.9</v>
+        <v>570.8</v>
       </c>
       <c r="F1264" t="n">
-        <v>10105</v>
+        <v>10174.9</v>
       </c>
       <c r="G1264" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1264" t="n">
         <v>5</v>
@@ -42169,13 +42169,13 @@
         </is>
       </c>
       <c r="D1265" t="n">
-        <v>55.6</v>
+        <v>114.8</v>
       </c>
       <c r="E1265" t="n">
-        <v>492.4</v>
+        <v>551.5999999999999</v>
       </c>
       <c r="F1265" t="n">
-        <v>8027.4</v>
+        <v>8086.6</v>
       </c>
       <c r="G1265" t="n">
         <v>7</v>
@@ -42205,10 +42205,10 @@
         <v>34.2</v>
       </c>
       <c r="E1266" t="n">
-        <v>474.6</v>
+        <v>518.3</v>
       </c>
       <c r="F1266" t="n">
-        <v>11185.7</v>
+        <v>11229.4</v>
       </c>
       <c r="G1266" t="n">
         <v>6</v>
@@ -42238,10 +42238,10 @@
         <v>45.6</v>
       </c>
       <c r="E1267" t="n">
-        <v>587.6</v>
+        <v>653.6</v>
       </c>
       <c r="F1267" t="n">
-        <v>11278.6</v>
+        <v>11344.6</v>
       </c>
       <c r="G1267" t="n">
         <v>5</v>
@@ -42271,10 +42271,10 @@
         <v>56.1</v>
       </c>
       <c r="E1268" t="n">
-        <v>570.9</v>
+        <v>645.6</v>
       </c>
       <c r="F1268" t="n">
-        <v>10436</v>
+        <v>10510.7</v>
       </c>
       <c r="G1268" t="n">
         <v>3</v>
@@ -42304,16 +42304,16 @@
         <v>61.7</v>
       </c>
       <c r="E1269" t="n">
-        <v>665.2</v>
+        <v>718.8000000000001</v>
       </c>
       <c r="F1269" t="n">
-        <v>10329.8</v>
+        <v>10383.4</v>
       </c>
       <c r="G1269" t="n">
         <v>1</v>
       </c>
       <c r="H1269" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1269" t="n">
         <v>5</v>
@@ -42337,16 +42337,16 @@
         <v>58.3</v>
       </c>
       <c r="E1270" t="n">
-        <v>646.5</v>
+        <v>727.1999999999999</v>
       </c>
       <c r="F1270" t="n">
-        <v>11581.3</v>
+        <v>11662</v>
       </c>
       <c r="G1270" t="n">
         <v>2</v>
       </c>
       <c r="H1270" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1270" t="n">
         <v>1</v>
@@ -42370,10 +42370,10 @@
         <v>47.9</v>
       </c>
       <c r="E1271" t="n">
-        <v>509.1</v>
+        <v>562</v>
       </c>
       <c r="F1271" t="n">
-        <v>9343</v>
+        <v>9395.9</v>
       </c>
       <c r="G1271" t="n">
         <v>4</v>
@@ -42403,10 +42403,10 @@
         <v>32.4</v>
       </c>
       <c r="E1272" t="n">
-        <v>533.3</v>
+        <v>603.1999999999999</v>
       </c>
       <c r="F1272" t="n">
-        <v>10137.4</v>
+        <v>10207.3</v>
       </c>
       <c r="G1272" t="n">
         <v>8</v>
@@ -42436,10 +42436,10 @@
         <v>34.2</v>
       </c>
       <c r="E1273" t="n">
-        <v>526.6</v>
+        <v>585.8</v>
       </c>
       <c r="F1273" t="n">
-        <v>8061.6</v>
+        <v>8120.8</v>
       </c>
       <c r="G1273" t="n">
         <v>6</v>
@@ -42469,10 +42469,10 @@
         <v>73.59999999999999</v>
       </c>
       <c r="E1274" t="n">
-        <v>548.2</v>
+        <v>591.9</v>
       </c>
       <c r="F1274" t="n">
-        <v>11259.3</v>
+        <v>11303</v>
       </c>
       <c r="G1274" t="n">
         <v>3</v>
@@ -42502,10 +42502,10 @@
         <v>59.40000000000001</v>
       </c>
       <c r="E1275" t="n">
-        <v>647</v>
+        <v>713</v>
       </c>
       <c r="F1275" t="n">
-        <v>11338</v>
+        <v>11404</v>
       </c>
       <c r="G1275" t="n">
         <v>5</v>
@@ -42535,10 +42535,10 @@
         <v>78.59999999999999</v>
       </c>
       <c r="E1276" t="n">
-        <v>649.5</v>
+        <v>724.2</v>
       </c>
       <c r="F1276" t="n">
-        <v>10514.6</v>
+        <v>10589.3</v>
       </c>
       <c r="G1276" t="n">
         <v>1</v>
@@ -42568,10 +42568,10 @@
         <v>46</v>
       </c>
       <c r="E1277" t="n">
-        <v>711.2</v>
+        <v>764.8000000000001</v>
       </c>
       <c r="F1277" t="n">
-        <v>10375.8</v>
+        <v>10429.4</v>
       </c>
       <c r="G1277" t="n">
         <v>8</v>
@@ -42601,10 +42601,10 @@
         <v>70.09999999999999</v>
       </c>
       <c r="E1278" t="n">
-        <v>716.6</v>
+        <v>797.3</v>
       </c>
       <c r="F1278" t="n">
-        <v>11651.4</v>
+        <v>11732.1</v>
       </c>
       <c r="G1278" t="n">
         <v>4</v>
@@ -42634,10 +42634,10 @@
         <v>52.5</v>
       </c>
       <c r="E1279" t="n">
-        <v>561.6</v>
+        <v>614.5</v>
       </c>
       <c r="F1279" t="n">
-        <v>9395.5</v>
+        <v>9448.4</v>
       </c>
       <c r="G1279" t="n">
         <v>7</v>
@@ -42667,10 +42667,10 @@
         <v>74.90000000000001</v>
       </c>
       <c r="E1280" t="n">
-        <v>608.2</v>
+        <v>678.1</v>
       </c>
       <c r="F1280" t="n">
-        <v>10212.3</v>
+        <v>10282.2</v>
       </c>
       <c r="G1280" t="n">
         <v>2</v>
@@ -42700,10 +42700,10 @@
         <v>58.2</v>
       </c>
       <c r="E1281" t="n">
-        <v>584.8000000000001</v>
+        <v>644</v>
       </c>
       <c r="F1281" t="n">
-        <v>8119.8</v>
+        <v>8179</v>
       </c>
       <c r="G1281" t="n">
         <v>6</v>
@@ -42733,10 +42733,10 @@
         <v>53.8</v>
       </c>
       <c r="E1282" t="n">
-        <v>602</v>
+        <v>645.6999999999999</v>
       </c>
       <c r="F1282" t="n">
-        <v>11313.1</v>
+        <v>11356.8</v>
       </c>
       <c r="G1282" t="n">
         <v>7</v>
@@ -42766,10 +42766,10 @@
         <v>51.1</v>
       </c>
       <c r="E1283" t="n">
-        <v>698.1</v>
+        <v>764.1</v>
       </c>
       <c r="F1283" t="n">
-        <v>11389.1</v>
+        <v>11455.1</v>
       </c>
       <c r="G1283" t="n">
         <v>8</v>
@@ -42799,10 +42799,10 @@
         <v>62.1</v>
       </c>
       <c r="E1284" t="n">
-        <v>711.6</v>
+        <v>786.3</v>
       </c>
       <c r="F1284" t="n">
-        <v>10576.7</v>
+        <v>10651.4</v>
       </c>
       <c r="G1284" t="n">
         <v>3</v>
@@ -42832,16 +42832,16 @@
         <v>69.5</v>
       </c>
       <c r="E1285" t="n">
-        <v>780.7</v>
+        <v>834.3000000000001</v>
       </c>
       <c r="F1285" t="n">
-        <v>10445.3</v>
+        <v>10498.9</v>
       </c>
       <c r="G1285" t="n">
         <v>1</v>
       </c>
       <c r="H1285" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1285" t="n">
         <v>5</v>
@@ -42865,16 +42865,16 @@
         <v>59.5</v>
       </c>
       <c r="E1286" t="n">
-        <v>776.1</v>
+        <v>856.8</v>
       </c>
       <c r="F1286" t="n">
-        <v>11710.9</v>
+        <v>11791.6</v>
       </c>
       <c r="G1286" t="n">
         <v>5</v>
       </c>
       <c r="H1286" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1286" t="n">
         <v>1</v>
@@ -42898,10 +42898,10 @@
         <v>54.1</v>
       </c>
       <c r="E1287" t="n">
-        <v>615.7</v>
+        <v>668.6</v>
       </c>
       <c r="F1287" t="n">
-        <v>9449.6</v>
+        <v>9502.5</v>
       </c>
       <c r="G1287" t="n">
         <v>6</v>
@@ -42931,10 +42931,10 @@
         <v>69.2</v>
       </c>
       <c r="E1288" t="n">
-        <v>677.4</v>
+        <v>747.3</v>
       </c>
       <c r="F1288" t="n">
-        <v>10281.5</v>
+        <v>10351.4</v>
       </c>
       <c r="G1288" t="n">
         <v>2</v>
@@ -42964,10 +42964,10 @@
         <v>60</v>
       </c>
       <c r="E1289" t="n">
-        <v>644.8000000000001</v>
+        <v>704</v>
       </c>
       <c r="F1289" t="n">
-        <v>8179.8</v>
+        <v>8239</v>
       </c>
       <c r="G1289" t="n">
         <v>4</v>
@@ -42997,10 +42997,10 @@
         <v>87.8</v>
       </c>
       <c r="E1290" t="n">
-        <v>689.8</v>
+        <v>733.5</v>
       </c>
       <c r="F1290" t="n">
-        <v>11400.9</v>
+        <v>11444.6</v>
       </c>
       <c r="G1290" t="n">
         <v>1</v>
@@ -43030,10 +43030,10 @@
         <v>67</v>
       </c>
       <c r="E1291" t="n">
-        <v>765.1</v>
+        <v>831.1</v>
       </c>
       <c r="F1291" t="n">
-        <v>11456.1</v>
+        <v>11522.1</v>
       </c>
       <c r="G1291" t="n">
         <v>4</v>
@@ -43063,10 +43063,10 @@
         <v>55.4</v>
       </c>
       <c r="E1292" t="n">
-        <v>767</v>
+        <v>841.7</v>
       </c>
       <c r="F1292" t="n">
-        <v>10632.1</v>
+        <v>10706.8</v>
       </c>
       <c r="G1292" t="n">
         <v>7</v>
@@ -43096,10 +43096,10 @@
         <v>57.6</v>
       </c>
       <c r="E1293" t="n">
-        <v>838.3000000000001</v>
+        <v>891.9</v>
       </c>
       <c r="F1293" t="n">
-        <v>10502.9</v>
+        <v>10556.5</v>
       </c>
       <c r="G1293" t="n">
         <v>6</v>
@@ -43129,10 +43129,10 @@
         <v>66.3</v>
       </c>
       <c r="E1294" t="n">
-        <v>842.4</v>
+        <v>923.1</v>
       </c>
       <c r="F1294" t="n">
-        <v>11777.2</v>
+        <v>11857.9</v>
       </c>
       <c r="G1294" t="n">
         <v>5</v>
@@ -43162,10 +43162,10 @@
         <v>52.1</v>
       </c>
       <c r="E1295" t="n">
-        <v>667.8</v>
+        <v>720.7</v>
       </c>
       <c r="F1295" t="n">
-        <v>9501.700000000001</v>
+        <v>9554.6</v>
       </c>
       <c r="G1295" t="n">
         <v>8</v>
@@ -43195,10 +43195,10 @@
         <v>81.09999999999999</v>
       </c>
       <c r="E1296" t="n">
-        <v>758.5</v>
+        <v>828.4</v>
       </c>
       <c r="F1296" t="n">
-        <v>10362.6</v>
+        <v>10432.5</v>
       </c>
       <c r="G1296" t="n">
         <v>2</v>
@@ -43228,10 +43228,10 @@
         <v>76.89999999999999</v>
       </c>
       <c r="E1297" t="n">
-        <v>721.7</v>
+        <v>780.9</v>
       </c>
       <c r="F1297" t="n">
-        <v>8256.700000000001</v>
+        <v>8315.9</v>
       </c>
       <c r="G1297" t="n">
         <v>3</v>
@@ -43261,10 +43261,10 @@
         <v>77.90000000000001</v>
       </c>
       <c r="E1298" t="n">
-        <v>767.7</v>
+        <v>811.4</v>
       </c>
       <c r="F1298" t="n">
-        <v>11478.8</v>
+        <v>11522.5</v>
       </c>
       <c r="G1298" t="n">
         <v>1</v>
@@ -43294,10 +43294,10 @@
         <v>54.8</v>
       </c>
       <c r="E1299" t="n">
-        <v>819.9</v>
+        <v>885.9</v>
       </c>
       <c r="F1299" t="n">
-        <v>11510.9</v>
+        <v>11576.9</v>
       </c>
       <c r="G1299" t="n">
         <v>7</v>
@@ -43327,10 +43327,10 @@
         <v>68.8</v>
       </c>
       <c r="E1300" t="n">
-        <v>835.8</v>
+        <v>910.5</v>
       </c>
       <c r="F1300" t="n">
-        <v>10700.9</v>
+        <v>10775.6</v>
       </c>
       <c r="G1300" t="n">
         <v>3</v>
@@ -43360,10 +43360,10 @@
         <v>60.2</v>
       </c>
       <c r="E1301" t="n">
-        <v>898.5</v>
+        <v>952.1</v>
       </c>
       <c r="F1301" t="n">
-        <v>10563.1</v>
+        <v>10616.7</v>
       </c>
       <c r="G1301" t="n">
         <v>6</v>
@@ -43393,10 +43393,10 @@
         <v>62.8</v>
       </c>
       <c r="E1302" t="n">
-        <v>905.2</v>
+        <v>985.9</v>
       </c>
       <c r="F1302" t="n">
-        <v>11840</v>
+        <v>11920.7</v>
       </c>
       <c r="G1302" t="n">
         <v>5</v>
@@ -43426,10 +43426,10 @@
         <v>50.9</v>
       </c>
       <c r="E1303" t="n">
-        <v>718.7</v>
+        <v>771.6</v>
       </c>
       <c r="F1303" t="n">
-        <v>9552.6</v>
+        <v>9605.5</v>
       </c>
       <c r="G1303" t="n">
         <v>8</v>
@@ -43459,10 +43459,10 @@
         <v>69.40000000000001</v>
       </c>
       <c r="E1304" t="n">
-        <v>827.9</v>
+        <v>897.8</v>
       </c>
       <c r="F1304" t="n">
-        <v>10432</v>
+        <v>10501.9</v>
       </c>
       <c r="G1304" t="n">
         <v>2</v>
@@ -43492,10 +43492,10 @@
         <v>66.3</v>
       </c>
       <c r="E1305" t="n">
-        <v>788</v>
+        <v>847.1999999999999</v>
       </c>
       <c r="F1305" t="n">
-        <v>8323</v>
+        <v>8382.200000000001</v>
       </c>
       <c r="G1305" t="n">
         <v>4</v>
@@ -43525,10 +43525,10 @@
         <v>68</v>
       </c>
       <c r="E1306" t="n">
-        <v>835.7</v>
+        <v>879.4</v>
       </c>
       <c r="F1306" t="n">
-        <v>11546.8</v>
+        <v>11590.5</v>
       </c>
       <c r="G1306" t="n">
         <v>5</v>
@@ -43558,10 +43558,10 @@
         <v>89.2</v>
       </c>
       <c r="E1307" t="n">
-        <v>909.1</v>
+        <v>975.1</v>
       </c>
       <c r="F1307" t="n">
-        <v>11600.1</v>
+        <v>11666.1</v>
       </c>
       <c r="G1307" t="n">
         <v>2</v>
@@ -43591,10 +43591,10 @@
         <v>79.3</v>
       </c>
       <c r="E1308" t="n">
-        <v>915.1</v>
+        <v>989.8</v>
       </c>
       <c r="F1308" t="n">
-        <v>10780.2</v>
+        <v>10854.9</v>
       </c>
       <c r="G1308" t="n">
         <v>3</v>
@@ -43624,10 +43624,10 @@
         <v>61</v>
       </c>
       <c r="E1309" t="n">
-        <v>959.5</v>
+        <v>1013.1</v>
       </c>
       <c r="F1309" t="n">
-        <v>10624.1</v>
+        <v>10677.7</v>
       </c>
       <c r="G1309" t="n">
         <v>6</v>
@@ -43657,10 +43657,10 @@
         <v>57.4</v>
       </c>
       <c r="E1310" t="n">
-        <v>962.6</v>
+        <v>1043.3</v>
       </c>
       <c r="F1310" t="n">
-        <v>11897.4</v>
+        <v>11978.1</v>
       </c>
       <c r="G1310" t="n">
         <v>7</v>
@@ -43690,10 +43690,10 @@
         <v>46.4</v>
       </c>
       <c r="E1311" t="n">
-        <v>765.1</v>
+        <v>818</v>
       </c>
       <c r="F1311" t="n">
-        <v>9599</v>
+        <v>9651.9</v>
       </c>
       <c r="G1311" t="n">
         <v>8</v>
@@ -43723,10 +43723,10 @@
         <v>77.2</v>
       </c>
       <c r="E1312" t="n">
-        <v>905.1</v>
+        <v>975</v>
       </c>
       <c r="F1312" t="n">
-        <v>10509.2</v>
+        <v>10579.1</v>
       </c>
       <c r="G1312" t="n">
         <v>4</v>
@@ -43756,10 +43756,10 @@
         <v>95.2</v>
       </c>
       <c r="E1313" t="n">
-        <v>883.2</v>
+        <v>942.4</v>
       </c>
       <c r="F1313" t="n">
-        <v>8418.200000000001</v>
+        <v>8477.4</v>
       </c>
       <c r="G1313" t="n">
         <v>1</v>
@@ -43789,10 +43789,10 @@
         <v>78</v>
       </c>
       <c r="E1314" t="n">
-        <v>913.7</v>
+        <v>957.4</v>
       </c>
       <c r="F1314" t="n">
-        <v>11624.8</v>
+        <v>11668.5</v>
       </c>
       <c r="G1314" t="n">
         <v>3</v>
@@ -43822,10 +43822,10 @@
         <v>78.59999999999999</v>
       </c>
       <c r="E1315" t="n">
-        <v>987.7</v>
+        <v>1053.7</v>
       </c>
       <c r="F1315" t="n">
-        <v>11678.7</v>
+        <v>11744.7</v>
       </c>
       <c r="G1315" t="n">
         <v>2</v>
@@ -43855,16 +43855,16 @@
         <v>76.90000000000001</v>
       </c>
       <c r="E1316" t="n">
-        <v>992</v>
+        <v>1066.7</v>
       </c>
       <c r="F1316" t="n">
-        <v>10857.1</v>
+        <v>10931.8</v>
       </c>
       <c r="G1316" t="n">
         <v>4</v>
       </c>
       <c r="H1316" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1316" t="n">
         <v>4</v>
@@ -43888,16 +43888,16 @@
         <v>48.4</v>
       </c>
       <c r="E1317" t="n">
-        <v>1007.9</v>
+        <v>1061.5</v>
       </c>
       <c r="F1317" t="n">
-        <v>10672.5</v>
+        <v>10726.1</v>
       </c>
       <c r="G1317" t="n">
         <v>8</v>
       </c>
       <c r="H1317" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1317" t="n">
         <v>5</v>
@@ -43921,10 +43921,10 @@
         <v>67.59999999999999</v>
       </c>
       <c r="E1318" t="n">
-        <v>1030.2</v>
+        <v>1110.9</v>
       </c>
       <c r="F1318" t="n">
-        <v>11965</v>
+        <v>12045.7</v>
       </c>
       <c r="G1318" t="n">
         <v>5</v>
@@ -43954,10 +43954,10 @@
         <v>58.1</v>
       </c>
       <c r="E1319" t="n">
-        <v>823.2</v>
+        <v>876.1</v>
       </c>
       <c r="F1319" t="n">
-        <v>9657.1</v>
+        <v>9710</v>
       </c>
       <c r="G1319" t="n">
         <v>7</v>
@@ -43987,10 +43987,10 @@
         <v>61.4</v>
       </c>
       <c r="E1320" t="n">
-        <v>966.5</v>
+        <v>1036.4</v>
       </c>
       <c r="F1320" t="n">
-        <v>10570.6</v>
+        <v>10640.5</v>
       </c>
       <c r="G1320" t="n">
         <v>6</v>
@@ -44020,10 +44020,10 @@
         <v>81.59999999999999</v>
       </c>
       <c r="E1321" t="n">
-        <v>964.8</v>
+        <v>1024</v>
       </c>
       <c r="F1321" t="n">
-        <v>8499.799999999999</v>
+        <v>8559</v>
       </c>
       <c r="G1321" t="n">
         <v>1</v>
@@ -44053,10 +44053,10 @@
         <v>67.5</v>
       </c>
       <c r="E1322" t="n">
-        <v>981.2</v>
+        <v>1024.9</v>
       </c>
       <c r="F1322" t="n">
-        <v>11692.3</v>
+        <v>11736</v>
       </c>
       <c r="G1322" t="n">
         <v>5</v>
@@ -44086,16 +44086,16 @@
         <v>69.8</v>
       </c>
       <c r="E1323" t="n">
-        <v>1057.5</v>
+        <v>1123.5</v>
       </c>
       <c r="F1323" t="n">
-        <v>11748.5</v>
+        <v>11814.5</v>
       </c>
       <c r="G1323" t="n">
         <v>2</v>
       </c>
       <c r="H1323" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1323" t="n">
         <v>2</v>
@@ -44119,10 +44119,10 @@
         <v>68.3</v>
       </c>
       <c r="E1324" t="n">
-        <v>1060.3</v>
+        <v>1135</v>
       </c>
       <c r="F1324" t="n">
-        <v>10925.4</v>
+        <v>11000.1</v>
       </c>
       <c r="G1324" t="n">
         <v>3</v>
@@ -44152,16 +44152,16 @@
         <v>52.1</v>
       </c>
       <c r="E1325" t="n">
-        <v>1060</v>
+        <v>1113.6</v>
       </c>
       <c r="F1325" t="n">
-        <v>10724.6</v>
+        <v>10778.2</v>
       </c>
       <c r="G1325" t="n">
         <v>8</v>
       </c>
       <c r="H1325" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1325" t="n">
         <v>5</v>
@@ -44185,10 +44185,10 @@
         <v>79.7</v>
       </c>
       <c r="E1326" t="n">
-        <v>1109.9</v>
+        <v>1190.6</v>
       </c>
       <c r="F1326" t="n">
-        <v>12044.7</v>
+        <v>12125.4</v>
       </c>
       <c r="G1326" t="n">
         <v>1</v>
@@ -44218,10 +44218,10 @@
         <v>58</v>
       </c>
       <c r="E1327" t="n">
-        <v>881.2</v>
+        <v>934.1</v>
       </c>
       <c r="F1327" t="n">
-        <v>9715.1</v>
+        <v>9768</v>
       </c>
       <c r="G1327" t="n">
         <v>7</v>
@@ -44251,16 +44251,16 @@
         <v>59.5</v>
       </c>
       <c r="E1328" t="n">
-        <v>1026</v>
+        <v>1095.9</v>
       </c>
       <c r="F1328" t="n">
-        <v>10630.1</v>
+        <v>10700</v>
       </c>
       <c r="G1328" t="n">
         <v>6</v>
       </c>
       <c r="H1328" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1328" t="n">
         <v>6</v>
@@ -44284,16 +44284,16 @@
         <v>68.10000000000001</v>
       </c>
       <c r="E1329" t="n">
-        <v>1032.9</v>
+        <v>1092.1</v>
       </c>
       <c r="F1329" t="n">
-        <v>8567.9</v>
+        <v>8627.1</v>
       </c>
       <c r="G1329" t="n">
         <v>4</v>
       </c>
       <c r="H1329" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1329" t="n">
         <v>8</v>
@@ -44317,10 +44317,10 @@
         <v>58.6</v>
       </c>
       <c r="E1330" t="n">
-        <v>1039.8</v>
+        <v>1083.5</v>
       </c>
       <c r="F1330" t="n">
-        <v>11750.9</v>
+        <v>11794.6</v>
       </c>
       <c r="G1330" t="n">
         <v>6</v>
@@ -44350,10 +44350,10 @@
         <v>105.7</v>
       </c>
       <c r="E1331" t="n">
-        <v>1163.2</v>
+        <v>1229.2</v>
       </c>
       <c r="F1331" t="n">
-        <v>11854.2</v>
+        <v>11920.2</v>
       </c>
       <c r="G1331" t="n">
         <v>1</v>
@@ -44383,16 +44383,16 @@
         <v>58.4</v>
       </c>
       <c r="E1332" t="n">
-        <v>1118.7</v>
+        <v>1193.4</v>
       </c>
       <c r="F1332" t="n">
-        <v>10983.8</v>
+        <v>11058.5</v>
       </c>
       <c r="G1332" t="n">
         <v>7</v>
       </c>
       <c r="H1332" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1332" t="n">
         <v>4</v>
@@ -44416,10 +44416,10 @@
         <v>57.4</v>
       </c>
       <c r="E1333" t="n">
-        <v>1117.4</v>
+        <v>1171</v>
       </c>
       <c r="F1333" t="n">
-        <v>10782</v>
+        <v>10835.6</v>
       </c>
       <c r="G1333" t="n">
         <v>8</v>
@@ -44449,10 +44449,10 @@
         <v>83.40000000000001</v>
       </c>
       <c r="E1334" t="n">
-        <v>1193.3</v>
+        <v>1274</v>
       </c>
       <c r="F1334" t="n">
-        <v>12128.1</v>
+        <v>12208.8</v>
       </c>
       <c r="G1334" t="n">
         <v>3</v>
@@ -44482,10 +44482,10 @@
         <v>74.3</v>
       </c>
       <c r="E1335" t="n">
-        <v>955.5</v>
+        <v>1008.4</v>
       </c>
       <c r="F1335" t="n">
-        <v>9789.4</v>
+        <v>9842.299999999999</v>
       </c>
       <c r="G1335" t="n">
         <v>4</v>
@@ -44515,10 +44515,10 @@
         <v>72</v>
       </c>
       <c r="E1336" t="n">
-        <v>1098</v>
+        <v>1167.9</v>
       </c>
       <c r="F1336" t="n">
-        <v>10702.1</v>
+        <v>10772</v>
       </c>
       <c r="G1336" t="n">
         <v>5</v>
@@ -44548,16 +44548,16 @@
         <v>87.09999999999999</v>
       </c>
       <c r="E1337" t="n">
-        <v>1120</v>
+        <v>1179.2</v>
       </c>
       <c r="F1337" t="n">
-        <v>8655</v>
+        <v>8714.200000000001</v>
       </c>
       <c r="G1337" t="n">
         <v>2</v>
       </c>
       <c r="H1337" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1337" t="n">
         <v>8</v>
@@ -44581,10 +44581,10 @@
         <v>61.2</v>
       </c>
       <c r="E1338" t="n">
-        <v>1101</v>
+        <v>1144.7</v>
       </c>
       <c r="F1338" t="n">
-        <v>11812.1</v>
+        <v>11855.8</v>
       </c>
       <c r="G1338" t="n">
         <v>5</v>
@@ -44614,10 +44614,10 @@
         <v>55.59999999999999</v>
       </c>
       <c r="E1339" t="n">
-        <v>1218.8</v>
+        <v>1284.8</v>
       </c>
       <c r="F1339" t="n">
-        <v>11909.8</v>
+        <v>11975.8</v>
       </c>
       <c r="G1339" t="n">
         <v>7</v>
@@ -44647,16 +44647,16 @@
         <v>50.59999999999999</v>
       </c>
       <c r="E1340" t="n">
-        <v>1169.3</v>
+        <v>1244</v>
       </c>
       <c r="F1340" t="n">
-        <v>11034.4</v>
+        <v>11109.1</v>
       </c>
       <c r="G1340" t="n">
         <v>8</v>
       </c>
       <c r="H1340" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I1340" t="n">
         <v>4</v>
@@ -44680,16 +44680,16 @@
         <v>62.40000000000001</v>
       </c>
       <c r="E1341" t="n">
-        <v>1179.8</v>
+        <v>1233.4</v>
       </c>
       <c r="F1341" t="n">
-        <v>10844.4</v>
+        <v>10898</v>
       </c>
       <c r="G1341" t="n">
         <v>4</v>
       </c>
       <c r="H1341" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I1341" t="n">
         <v>5</v>
@@ -44713,10 +44713,10 @@
         <v>81.90000000000001</v>
       </c>
       <c r="E1342" t="n">
-        <v>1275.2</v>
+        <v>1355.9</v>
       </c>
       <c r="F1342" t="n">
-        <v>12210</v>
+        <v>12290.7</v>
       </c>
       <c r="G1342" t="n">
         <v>2</v>
@@ -44746,10 +44746,10 @@
         <v>63.3</v>
       </c>
       <c r="E1343" t="n">
-        <v>1018.8</v>
+        <v>1071.7</v>
       </c>
       <c r="F1343" t="n">
-        <v>9852.700000000001</v>
+        <v>9905.6</v>
       </c>
       <c r="G1343" t="n">
         <v>3</v>
@@ -44779,10 +44779,10 @@
         <v>86</v>
       </c>
       <c r="E1344" t="n">
-        <v>1184</v>
+        <v>1253.9</v>
       </c>
       <c r="F1344" t="n">
-        <v>10788.1</v>
+        <v>10858</v>
       </c>
       <c r="G1344" t="n">
         <v>1</v>
@@ -44812,10 +44812,10 @@
         <v>58.1</v>
       </c>
       <c r="E1345" t="n">
-        <v>1178.1</v>
+        <v>1237.3</v>
       </c>
       <c r="F1345" t="n">
-        <v>8713.1</v>
+        <v>8772.299999999999</v>
       </c>
       <c r="G1345" t="n">
         <v>6</v>
@@ -44845,10 +44845,10 @@
         <v>64.2</v>
       </c>
       <c r="E1346" t="n">
-        <v>1165.2</v>
+        <v>1208.9</v>
       </c>
       <c r="F1346" t="n">
-        <v>11876.3</v>
+        <v>11920</v>
       </c>
       <c r="G1346" t="n">
         <v>5</v>
@@ -44878,10 +44878,10 @@
         <v>88.7</v>
       </c>
       <c r="E1347" t="n">
-        <v>1307.5</v>
+        <v>1373.5</v>
       </c>
       <c r="F1347" t="n">
-        <v>11998.5</v>
+        <v>12064.5</v>
       </c>
       <c r="G1347" t="n">
         <v>1</v>
@@ -44911,10 +44911,10 @@
         <v>76.8</v>
       </c>
       <c r="E1348" t="n">
-        <v>1246.1</v>
+        <v>1320.8</v>
       </c>
       <c r="F1348" t="n">
-        <v>11111.2</v>
+        <v>11185.9</v>
       </c>
       <c r="G1348" t="n">
         <v>3</v>
@@ -44944,10 +44944,10 @@
         <v>45</v>
       </c>
       <c r="E1349" t="n">
-        <v>1224.8</v>
+        <v>1278.4</v>
       </c>
       <c r="F1349" t="n">
-        <v>10889.4</v>
+        <v>10943</v>
       </c>
       <c r="G1349" t="n">
         <v>8</v>
@@ -44977,10 +44977,10 @@
         <v>81.2</v>
       </c>
       <c r="E1350" t="n">
-        <v>1356.4</v>
+        <v>1437.1</v>
       </c>
       <c r="F1350" t="n">
-        <v>12291.2</v>
+        <v>12371.9</v>
       </c>
       <c r="G1350" t="n">
         <v>2</v>
@@ -45010,10 +45010,10 @@
         <v>63.7</v>
       </c>
       <c r="E1351" t="n">
-        <v>1082.5</v>
+        <v>1135.4</v>
       </c>
       <c r="F1351" t="n">
-        <v>9916.4</v>
+        <v>9969.299999999999</v>
       </c>
       <c r="G1351" t="n">
         <v>6</v>
@@ -45043,10 +45043,10 @@
         <v>67.7</v>
       </c>
       <c r="E1352" t="n">
-        <v>1251.7</v>
+        <v>1321.6</v>
       </c>
       <c r="F1352" t="n">
-        <v>10855.8</v>
+        <v>10925.7</v>
       </c>
       <c r="G1352" t="n">
         <v>4</v>
@@ -45076,10 +45076,10 @@
         <v>60.2</v>
       </c>
       <c r="E1353" t="n">
-        <v>1238.3</v>
+        <v>1297.5</v>
       </c>
       <c r="F1353" t="n">
-        <v>8773.299999999999</v>
+        <v>8832.5</v>
       </c>
       <c r="G1353" t="n">
         <v>7</v>
@@ -45109,10 +45109,10 @@
         <v>88.09999999999999</v>
       </c>
       <c r="E1354" t="n">
-        <v>1253.3</v>
+        <v>1297</v>
       </c>
       <c r="F1354" t="n">
-        <v>11964.4</v>
+        <v>12008.1</v>
       </c>
       <c r="G1354" t="n">
         <v>3</v>
@@ -45142,10 +45142,10 @@
         <v>59.9</v>
       </c>
       <c r="E1355" t="n">
-        <v>1367.4</v>
+        <v>1433.4</v>
       </c>
       <c r="F1355" t="n">
-        <v>12058.4</v>
+        <v>12124.4</v>
       </c>
       <c r="G1355" t="n">
         <v>6</v>
@@ -45175,16 +45175,16 @@
         <v>70.2</v>
       </c>
       <c r="E1356" t="n">
-        <v>1316.3</v>
+        <v>1391</v>
       </c>
       <c r="F1356" t="n">
-        <v>11181.4</v>
+        <v>11256.1</v>
       </c>
       <c r="G1356" t="n">
         <v>4</v>
       </c>
       <c r="H1356" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1356" t="n">
         <v>4</v>
@@ -45208,10 +45208,10 @@
         <v>0</v>
       </c>
       <c r="E1357" t="n">
-        <v>1224.8</v>
+        <v>1278.4</v>
       </c>
       <c r="F1357" t="n">
-        <v>10889.4</v>
+        <v>10943</v>
       </c>
       <c r="G1357" t="n">
         <v>8</v>
@@ -45241,10 +45241,10 @@
         <v>94</v>
       </c>
       <c r="E1358" t="n">
-        <v>1450.4</v>
+        <v>1531.1</v>
       </c>
       <c r="F1358" t="n">
-        <v>12385.2</v>
+        <v>12465.9</v>
       </c>
       <c r="G1358" t="n">
         <v>1</v>
@@ -45274,10 +45274,10 @@
         <v>61.6</v>
       </c>
       <c r="E1359" t="n">
-        <v>1144.1</v>
+        <v>1197</v>
       </c>
       <c r="F1359" t="n">
-        <v>9978</v>
+        <v>10030.9</v>
       </c>
       <c r="G1359" t="n">
         <v>5</v>
@@ -45307,10 +45307,10 @@
         <v>58.6</v>
       </c>
       <c r="E1360" t="n">
-        <v>1310.3</v>
+        <v>1380.2</v>
       </c>
       <c r="F1360" t="n">
-        <v>10914.4</v>
+        <v>10984.3</v>
       </c>
       <c r="G1360" t="n">
         <v>7</v>
@@ -45340,16 +45340,16 @@
         <v>89.5</v>
       </c>
       <c r="E1361" t="n">
-        <v>1327.8</v>
+        <v>1387</v>
       </c>
       <c r="F1361" t="n">
-        <v>8862.799999999999</v>
+        <v>8922</v>
       </c>
       <c r="G1361" t="n">
         <v>2</v>
       </c>
       <c r="H1361" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1361" t="n">
         <v>8</v>
@@ -45373,10 +45373,10 @@
         <v>66.7</v>
       </c>
       <c r="E1362" t="n">
-        <v>1320</v>
+        <v>1363.7</v>
       </c>
       <c r="F1362" t="n">
-        <v>12031.1</v>
+        <v>12074.8</v>
       </c>
       <c r="G1362" t="n">
         <v>4</v>
@@ -45406,10 +45406,10 @@
         <v>35.8</v>
       </c>
       <c r="E1363" t="n">
-        <v>1403.2</v>
+        <v>1469.2</v>
       </c>
       <c r="F1363" t="n">
-        <v>12094.2</v>
+        <v>12160.2</v>
       </c>
       <c r="G1363" t="n">
         <v>8</v>
@@ -45439,10 +45439,10 @@
         <v>59.2</v>
       </c>
       <c r="E1364" t="n">
-        <v>1375.5</v>
+        <v>1450.2</v>
       </c>
       <c r="F1364" t="n">
-        <v>11240.6</v>
+        <v>11315.3</v>
       </c>
       <c r="G1364" t="n">
         <v>6</v>
@@ -45472,10 +45472,10 @@
         <v>82.2</v>
       </c>
       <c r="E1365" t="n">
-        <v>1307</v>
+        <v>1360.6</v>
       </c>
       <c r="F1365" t="n">
-        <v>10971.6</v>
+        <v>11025.2</v>
       </c>
       <c r="G1365" t="n">
         <v>2</v>
@@ -45505,10 +45505,10 @@
         <v>63</v>
       </c>
       <c r="E1366" t="n">
-        <v>1513.4</v>
+        <v>1594.1</v>
       </c>
       <c r="F1366" t="n">
-        <v>12448.2</v>
+        <v>12528.9</v>
       </c>
       <c r="G1366" t="n">
         <v>5</v>
@@ -45538,10 +45538,10 @@
         <v>56.6</v>
       </c>
       <c r="E1367" t="n">
-        <v>1200.7</v>
+        <v>1253.6</v>
       </c>
       <c r="F1367" t="n">
-        <v>10034.6</v>
+        <v>10087.5</v>
       </c>
       <c r="G1367" t="n">
         <v>7</v>
@@ -45571,10 +45571,10 @@
         <v>78.59999999999999</v>
       </c>
       <c r="E1368" t="n">
-        <v>1388.9</v>
+        <v>1458.8</v>
       </c>
       <c r="F1368" t="n">
-        <v>10993</v>
+        <v>11062.9</v>
       </c>
       <c r="G1368" t="n">
         <v>3</v>
@@ -45604,10 +45604,10 @@
         <v>87.3</v>
       </c>
       <c r="E1369" t="n">
-        <v>1415.1</v>
+        <v>1474.3</v>
       </c>
       <c r="F1369" t="n">
-        <v>8950.1</v>
+        <v>9009.299999999999</v>
       </c>
       <c r="G1369" t="n">
         <v>1</v>
@@ -45637,10 +45637,10 @@
         <v>70.8</v>
       </c>
       <c r="E1370" t="n">
-        <v>1390.8</v>
+        <v>1434.5</v>
       </c>
       <c r="F1370" t="n">
-        <v>12101.9</v>
+        <v>12145.6</v>
       </c>
       <c r="G1370" t="n">
         <v>4</v>
@@ -45670,10 +45670,10 @@
         <v>76.5</v>
       </c>
       <c r="E1371" t="n">
-        <v>1479.7</v>
+        <v>1545.7</v>
       </c>
       <c r="F1371" t="n">
-        <v>12170.7</v>
+        <v>12236.7</v>
       </c>
       <c r="G1371" t="n">
         <v>2</v>
@@ -45703,16 +45703,16 @@
         <v>75.2</v>
       </c>
       <c r="E1372" t="n">
-        <v>1450.7</v>
+        <v>1525.4</v>
       </c>
       <c r="F1372" t="n">
-        <v>11315.8</v>
+        <v>11390.5</v>
       </c>
       <c r="G1372" t="n">
         <v>3</v>
       </c>
       <c r="H1372" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1372" t="n">
         <v>4</v>
@@ -45736,10 +45736,10 @@
         <v>46.7</v>
       </c>
       <c r="E1373" t="n">
-        <v>1353.7</v>
+        <v>1407.3</v>
       </c>
       <c r="F1373" t="n">
-        <v>11018.3</v>
+        <v>11071.9</v>
       </c>
       <c r="G1373" t="n">
         <v>8</v>
@@ -45769,10 +45769,10 @@
         <v>79.40000000000001</v>
       </c>
       <c r="E1374" t="n">
-        <v>1592.8</v>
+        <v>1673.5</v>
       </c>
       <c r="F1374" t="n">
-        <v>12527.6</v>
+        <v>12608.3</v>
       </c>
       <c r="G1374" t="n">
         <v>1</v>
@@ -45802,10 +45802,10 @@
         <v>56.59999999999999</v>
       </c>
       <c r="E1375" t="n">
-        <v>1257.3</v>
+        <v>1310.2</v>
       </c>
       <c r="F1375" t="n">
-        <v>10091.2</v>
+        <v>10144.1</v>
       </c>
       <c r="G1375" t="n">
         <v>6</v>
@@ -45835,16 +45835,16 @@
         <v>65.2</v>
       </c>
       <c r="E1376" t="n">
-        <v>1454.1</v>
+        <v>1524</v>
       </c>
       <c r="F1376" t="n">
-        <v>11058.2</v>
+        <v>11128.1</v>
       </c>
       <c r="G1376" t="n">
         <v>5</v>
       </c>
       <c r="H1376" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1376" t="n">
         <v>5</v>
@@ -45868,10 +45868,10 @@
         <v>54.8</v>
       </c>
       <c r="E1377" t="n">
-        <v>1469.9</v>
+        <v>1529.1</v>
       </c>
       <c r="F1377" t="n">
-        <v>9004.9</v>
+        <v>9064.1</v>
       </c>
       <c r="G1377" t="n">
         <v>7</v>
@@ -45901,10 +45901,10 @@
         <v>93.8</v>
       </c>
       <c r="E1378" t="n">
-        <v>1484.6</v>
+        <v>1528.3</v>
       </c>
       <c r="F1378" t="n">
-        <v>12195.7</v>
+        <v>12239.4</v>
       </c>
       <c r="G1378" t="n">
         <v>2</v>
@@ -45934,10 +45934,10 @@
         <v>65.2</v>
       </c>
       <c r="E1379" t="n">
-        <v>1544.9</v>
+        <v>1610.9</v>
       </c>
       <c r="F1379" t="n">
-        <v>12235.9</v>
+        <v>12301.9</v>
       </c>
       <c r="G1379" t="n">
         <v>7</v>
@@ -45967,16 +45967,16 @@
         <v>97.59999999999999</v>
       </c>
       <c r="E1380" t="n">
-        <v>1548.3</v>
+        <v>1623</v>
       </c>
       <c r="F1380" t="n">
-        <v>11413.4</v>
+        <v>11488.1</v>
       </c>
       <c r="G1380" t="n">
         <v>1</v>
       </c>
       <c r="H1380" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1380" t="n">
         <v>4</v>
@@ -46000,10 +46000,10 @@
         <v>63.3</v>
       </c>
       <c r="E1381" t="n">
-        <v>1417</v>
+        <v>1470.6</v>
       </c>
       <c r="F1381" t="n">
-        <v>11081.6</v>
+        <v>11135.2</v>
       </c>
       <c r="G1381" t="n">
         <v>8</v>
@@ -46033,10 +46033,10 @@
         <v>79.3</v>
       </c>
       <c r="E1382" t="n">
-        <v>1672.1</v>
+        <v>1752.8</v>
       </c>
       <c r="F1382" t="n">
-        <v>12606.9</v>
+        <v>12687.6</v>
       </c>
       <c r="G1382" t="n">
         <v>5</v>
@@ -46066,10 +46066,10 @@
         <v>81.7</v>
       </c>
       <c r="E1383" t="n">
-        <v>1339</v>
+        <v>1391.9</v>
       </c>
       <c r="F1383" t="n">
-        <v>10172.9</v>
+        <v>10225.8</v>
       </c>
       <c r="G1383" t="n">
         <v>4</v>
@@ -46099,10 +46099,10 @@
         <v>67.40000000000001</v>
       </c>
       <c r="E1384" t="n">
-        <v>1521.5</v>
+        <v>1591.4</v>
       </c>
       <c r="F1384" t="n">
-        <v>11125.6</v>
+        <v>11195.5</v>
       </c>
       <c r="G1384" t="n">
         <v>6</v>
@@ -46132,16 +46132,16 @@
         <v>82.59999999999999</v>
       </c>
       <c r="E1385" t="n">
-        <v>1552.5</v>
+        <v>1611.7</v>
       </c>
       <c r="F1385" t="n">
-        <v>9087.5</v>
+        <v>9146.700000000001</v>
       </c>
       <c r="G1385" t="n">
         <v>3</v>
       </c>
       <c r="H1385" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1385" t="n">
         <v>8</v>
@@ -46165,16 +46165,16 @@
         <v>100.5</v>
       </c>
       <c r="E1386" t="n">
-        <v>1585.1</v>
+        <v>1628.8</v>
       </c>
       <c r="F1386" t="n">
-        <v>12296.2</v>
+        <v>12339.9</v>
       </c>
       <c r="G1386" t="n">
         <v>1</v>
       </c>
       <c r="H1386" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1386" t="n">
         <v>3</v>
@@ -46198,10 +46198,10 @@
         <v>80.3</v>
       </c>
       <c r="E1387" t="n">
-        <v>1625.2</v>
+        <v>1691.2</v>
       </c>
       <c r="F1387" t="n">
-        <v>12316.2</v>
+        <v>12382.2</v>
       </c>
       <c r="G1387" t="n">
         <v>2</v>
@@ -46231,16 +46231,16 @@
         <v>60.3</v>
       </c>
       <c r="E1388" t="n">
-        <v>1608.6</v>
+        <v>1683.3</v>
       </c>
       <c r="F1388" t="n">
-        <v>11473.7</v>
+        <v>11548.4</v>
       </c>
       <c r="G1388" t="n">
         <v>6</v>
       </c>
       <c r="H1388" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1388" t="n">
         <v>4</v>
@@ -46264,10 +46264,10 @@
         <v>67.59999999999999</v>
       </c>
       <c r="E1389" t="n">
-        <v>1484.6</v>
+        <v>1538.2</v>
       </c>
       <c r="F1389" t="n">
-        <v>11149.2</v>
+        <v>11202.8</v>
       </c>
       <c r="G1389" t="n">
         <v>4</v>
@@ -46297,10 +46297,10 @@
         <v>70.2</v>
       </c>
       <c r="E1390" t="n">
-        <v>1742.3</v>
+        <v>1823</v>
       </c>
       <c r="F1390" t="n">
-        <v>12677.1</v>
+        <v>12757.8</v>
       </c>
       <c r="G1390" t="n">
         <v>3</v>
@@ -46330,10 +46330,10 @@
         <v>61.2</v>
       </c>
       <c r="E1391" t="n">
-        <v>1400.2</v>
+        <v>1453.1</v>
       </c>
       <c r="F1391" t="n">
-        <v>10234.1</v>
+        <v>10287</v>
       </c>
       <c r="G1391" t="n">
         <v>5</v>
@@ -46363,16 +46363,16 @@
         <v>50.8</v>
       </c>
       <c r="E1392" t="n">
-        <v>1572.3</v>
+        <v>1642.2</v>
       </c>
       <c r="F1392" t="n">
-        <v>11176.4</v>
+        <v>11246.3</v>
       </c>
       <c r="G1392" t="n">
         <v>8</v>
       </c>
       <c r="H1392" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1392" t="n">
         <v>5</v>
@@ -46396,16 +46396,16 @@
         <v>58.9</v>
       </c>
       <c r="E1393" t="n">
-        <v>1611.4</v>
+        <v>1670.6</v>
       </c>
       <c r="F1393" t="n">
-        <v>9146.4</v>
+        <v>9205.6</v>
       </c>
       <c r="G1393" t="n">
         <v>7</v>
       </c>
       <c r="H1393" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1393" t="n">
         <v>8</v>
@@ -46429,16 +46429,16 @@
         <v>92</v>
       </c>
       <c r="E1394" t="n">
-        <v>1677.1</v>
+        <v>1720.8</v>
       </c>
       <c r="F1394" t="n">
-        <v>12388.2</v>
+        <v>12431.9</v>
       </c>
       <c r="G1394" t="n">
         <v>2</v>
       </c>
       <c r="H1394" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1394" t="n">
         <v>3</v>
@@ -46462,10 +46462,10 @@
         <v>77.2</v>
       </c>
       <c r="E1395" t="n">
-        <v>1702.4</v>
+        <v>1768.4</v>
       </c>
       <c r="F1395" t="n">
-        <v>12393.4</v>
+        <v>12459.4</v>
       </c>
       <c r="G1395" t="n">
         <v>4</v>
@@ -46495,10 +46495,10 @@
         <v>80.3</v>
       </c>
       <c r="E1396" t="n">
-        <v>1688.9</v>
+        <v>1763.6</v>
       </c>
       <c r="F1396" t="n">
-        <v>11554</v>
+        <v>11628.7</v>
       </c>
       <c r="G1396" t="n">
         <v>3</v>
@@ -46528,10 +46528,10 @@
         <v>50.6</v>
       </c>
       <c r="E1397" t="n">
-        <v>1535.2</v>
+        <v>1588.8</v>
       </c>
       <c r="F1397" t="n">
-        <v>11199.8</v>
+        <v>11253.4</v>
       </c>
       <c r="G1397" t="n">
         <v>7</v>
@@ -46561,10 +46561,10 @@
         <v>76.7</v>
       </c>
       <c r="E1398" t="n">
-        <v>1819</v>
+        <v>1899.7</v>
       </c>
       <c r="F1398" t="n">
-        <v>12753.8</v>
+        <v>12834.5</v>
       </c>
       <c r="G1398" t="n">
         <v>5</v>
@@ -46594,10 +46594,10 @@
         <v>48.7</v>
       </c>
       <c r="E1399" t="n">
-        <v>1448.9</v>
+        <v>1501.8</v>
       </c>
       <c r="F1399" t="n">
-        <v>10282.8</v>
+        <v>10335.7</v>
       </c>
       <c r="G1399" t="n">
         <v>8</v>
@@ -46627,16 +46627,16 @@
         <v>92.5</v>
       </c>
       <c r="E1400" t="n">
-        <v>1664.8</v>
+        <v>1734.7</v>
       </c>
       <c r="F1400" t="n">
-        <v>11268.9</v>
+        <v>11338.8</v>
       </c>
       <c r="G1400" t="n">
         <v>1</v>
       </c>
       <c r="H1400" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1400" t="n">
         <v>5</v>
@@ -46660,10 +46660,10 @@
         <v>73.10000000000001</v>
       </c>
       <c r="E1401" t="n">
-        <v>1684.5</v>
+        <v>1743.7</v>
       </c>
       <c r="F1401" t="n">
-        <v>9219.5</v>
+        <v>9278.700000000001</v>
       </c>
       <c r="G1401" t="n">
         <v>6</v>
@@ -46693,16 +46693,16 @@
         <v>75.59999999999999</v>
       </c>
       <c r="E1402" t="n">
-        <v>1752.7</v>
+        <v>1796.4</v>
       </c>
       <c r="F1402" t="n">
-        <v>12463.8</v>
+        <v>12507.5</v>
       </c>
       <c r="G1402" t="n">
         <v>3</v>
       </c>
       <c r="H1402" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I1402" t="n">
         <v>3</v>
@@ -46726,10 +46726,10 @@
         <v>84.09999999999999</v>
       </c>
       <c r="E1403" t="n">
-        <v>1786.5</v>
+        <v>1852.5</v>
       </c>
       <c r="F1403" t="n">
-        <v>12477.5</v>
+        <v>12543.5</v>
       </c>
       <c r="G1403" t="n">
         <v>1</v>
@@ -46759,16 +46759,16 @@
         <v>59.3</v>
       </c>
       <c r="E1404" t="n">
-        <v>1748.2</v>
+        <v>1822.9</v>
       </c>
       <c r="F1404" t="n">
-        <v>11613.3</v>
+        <v>11688</v>
       </c>
       <c r="G1404" t="n">
         <v>8</v>
       </c>
       <c r="H1404" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I1404" t="n">
         <v>4</v>
@@ -46792,10 +46792,10 @@
         <v>71.5</v>
       </c>
       <c r="E1405" t="n">
-        <v>1606.7</v>
+        <v>1660.3</v>
       </c>
       <c r="F1405" t="n">
-        <v>11271.3</v>
+        <v>11324.9</v>
       </c>
       <c r="G1405" t="n">
         <v>6</v>
@@ -46825,10 +46825,10 @@
         <v>75.39999999999999</v>
       </c>
       <c r="E1406" t="n">
-        <v>1894.4</v>
+        <v>1975.1</v>
       </c>
       <c r="F1406" t="n">
-        <v>12829.2</v>
+        <v>12909.9</v>
       </c>
       <c r="G1406" t="n">
         <v>4</v>
@@ -46858,10 +46858,10 @@
         <v>62.7</v>
       </c>
       <c r="E1407" t="n">
-        <v>1511.6</v>
+        <v>1564.5</v>
       </c>
       <c r="F1407" t="n">
-        <v>10345.5</v>
+        <v>10398.4</v>
       </c>
       <c r="G1407" t="n">
         <v>7</v>
@@ -46891,16 +46891,16 @@
         <v>72</v>
       </c>
       <c r="E1408" t="n">
-        <v>1736.8</v>
+        <v>1806.7</v>
       </c>
       <c r="F1408" t="n">
-        <v>11340.9</v>
+        <v>11410.8</v>
       </c>
       <c r="G1408" t="n">
         <v>5</v>
       </c>
       <c r="H1408" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1408" t="n">
         <v>5</v>
@@ -46924,16 +46924,16 @@
         <v>79.09999999999999</v>
       </c>
       <c r="E1409" t="n">
-        <v>1763.6</v>
+        <v>1822.8</v>
       </c>
       <c r="F1409" t="n">
-        <v>9298.6</v>
+        <v>9357.799999999999</v>
       </c>
       <c r="G1409" t="n">
         <v>2</v>
       </c>
       <c r="H1409" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1409" t="n">
         <v>8</v>
@@ -46957,16 +46957,16 @@
         <v>73.2</v>
       </c>
       <c r="E1410" t="n">
-        <v>1825.9</v>
+        <v>1869.6</v>
       </c>
       <c r="F1410" t="n">
-        <v>12537</v>
+        <v>12580.7</v>
       </c>
       <c r="G1410" t="n">
         <v>2</v>
       </c>
       <c r="H1410" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1410" t="n">
         <v>3</v>
@@ -46990,10 +46990,10 @@
         <v>62.7</v>
       </c>
       <c r="E1411" t="n">
-        <v>1849.2</v>
+        <v>1915.2</v>
       </c>
       <c r="F1411" t="n">
-        <v>12540.2</v>
+        <v>12606.2</v>
       </c>
       <c r="G1411" t="n">
         <v>5</v>
@@ -47023,16 +47023,16 @@
         <v>49.2</v>
       </c>
       <c r="E1412" t="n">
-        <v>1797.4</v>
+        <v>1872.1</v>
       </c>
       <c r="F1412" t="n">
-        <v>11662.5</v>
+        <v>11737.2</v>
       </c>
       <c r="G1412" t="n">
         <v>6</v>
       </c>
       <c r="H1412" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1412" t="n">
         <v>4</v>
@@ -47056,10 +47056,10 @@
         <v>43.9</v>
       </c>
       <c r="E1413" t="n">
-        <v>1650.6</v>
+        <v>1704.2</v>
       </c>
       <c r="F1413" t="n">
-        <v>11315.2</v>
+        <v>11368.8</v>
       </c>
       <c r="G1413" t="n">
         <v>7</v>
@@ -47089,10 +47089,10 @@
         <v>71.2</v>
       </c>
       <c r="E1414" t="n">
-        <v>1965.6</v>
+        <v>2046.3</v>
       </c>
       <c r="F1414" t="n">
-        <v>12900.4</v>
+        <v>12981.1</v>
       </c>
       <c r="G1414" t="n">
         <v>3</v>
@@ -47122,10 +47122,10 @@
         <v>64.09999999999999</v>
       </c>
       <c r="E1415" t="n">
-        <v>1575.7</v>
+        <v>1628.6</v>
       </c>
       <c r="F1415" t="n">
-        <v>10409.6</v>
+        <v>10462.5</v>
       </c>
       <c r="G1415" t="n">
         <v>4</v>
@@ -47155,10 +47155,10 @@
         <v>42.9</v>
       </c>
       <c r="E1416" t="n">
-        <v>1779.7</v>
+        <v>1849.6</v>
       </c>
       <c r="F1416" t="n">
-        <v>11383.8</v>
+        <v>11453.7</v>
       </c>
       <c r="G1416" t="n">
         <v>8</v>
@@ -47188,10 +47188,10 @@
         <v>73.8</v>
       </c>
       <c r="E1417" t="n">
-        <v>1837.4</v>
+        <v>1896.6</v>
       </c>
       <c r="F1417" t="n">
-        <v>9372.4</v>
+        <v>9431.6</v>
       </c>
       <c r="G1417" t="n">
         <v>1</v>
@@ -47221,19 +47221,19 @@
         <v>79.3</v>
       </c>
       <c r="E1418" t="n">
-        <v>1905.2</v>
+        <v>1948.9</v>
       </c>
       <c r="F1418" t="n">
-        <v>12616.3</v>
+        <v>12660</v>
       </c>
       <c r="G1418" t="n">
         <v>1</v>
       </c>
       <c r="H1418" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1418" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1419">
@@ -47254,10 +47254,10 @@
         <v>62.3</v>
       </c>
       <c r="E1419" t="n">
-        <v>1911.5</v>
+        <v>1977.5</v>
       </c>
       <c r="F1419" t="n">
-        <v>12602.5</v>
+        <v>12668.5</v>
       </c>
       <c r="G1419" t="n">
         <v>4</v>
@@ -47266,7 +47266,7 @@
         <v>2</v>
       </c>
       <c r="I1419" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1420">
@@ -47287,10 +47287,10 @@
         <v>50.4</v>
       </c>
       <c r="E1420" t="n">
-        <v>1847.8</v>
+        <v>1922.5</v>
       </c>
       <c r="F1420" t="n">
-        <v>11712.9</v>
+        <v>11787.6</v>
       </c>
       <c r="G1420" t="n">
         <v>7</v>
@@ -47320,10 +47320,10 @@
         <v>48.8</v>
       </c>
       <c r="E1421" t="n">
-        <v>1699.4</v>
+        <v>1753</v>
       </c>
       <c r="F1421" t="n">
-        <v>11364</v>
+        <v>11417.6</v>
       </c>
       <c r="G1421" t="n">
         <v>8</v>
@@ -47353,10 +47353,10 @@
         <v>75</v>
       </c>
       <c r="E1422" t="n">
-        <v>2040.6</v>
+        <v>2121.3</v>
       </c>
       <c r="F1422" t="n">
-        <v>12975.4</v>
+        <v>13056.1</v>
       </c>
       <c r="G1422" t="n">
         <v>2</v>
@@ -47386,10 +47386,10 @@
         <v>64.5</v>
       </c>
       <c r="E1423" t="n">
-        <v>1640.2</v>
+        <v>1693.1</v>
       </c>
       <c r="F1423" t="n">
-        <v>10474.1</v>
+        <v>10527</v>
       </c>
       <c r="G1423" t="n">
         <v>3</v>
@@ -47419,10 +47419,10 @@
         <v>59.7</v>
       </c>
       <c r="E1424" t="n">
-        <v>1839.4</v>
+        <v>1909.3</v>
       </c>
       <c r="F1424" t="n">
-        <v>11443.5</v>
+        <v>11513.4</v>
       </c>
       <c r="G1424" t="n">
         <v>5</v>
@@ -47452,16 +47452,16 @@
         <v>57.7</v>
       </c>
       <c r="E1425" t="n">
-        <v>1895.1</v>
+        <v>1954.3</v>
       </c>
       <c r="F1425" t="n">
-        <v>9430.1</v>
+        <v>9489.299999999999</v>
       </c>
       <c r="G1425" t="n">
         <v>6</v>
       </c>
       <c r="H1425" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1425" t="n">
         <v>8</v>
@@ -47485,16 +47485,16 @@
         <v>86.3</v>
       </c>
       <c r="E1426" t="n">
-        <v>1991.5</v>
+        <v>2035.2</v>
       </c>
       <c r="F1426" t="n">
-        <v>12702.6</v>
+        <v>12746.3</v>
       </c>
       <c r="G1426" t="n">
         <v>2</v>
       </c>
       <c r="H1426" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1426" t="n">
         <v>2</v>
@@ -47518,16 +47518,16 @@
         <v>75.59999999999999</v>
       </c>
       <c r="E1427" t="n">
-        <v>1987.1</v>
+        <v>2053.1</v>
       </c>
       <c r="F1427" t="n">
-        <v>12678.1</v>
+        <v>12744.1</v>
       </c>
       <c r="G1427" t="n">
         <v>3</v>
       </c>
       <c r="H1427" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I1427" t="n">
         <v>3</v>
@@ -47551,10 +47551,10 @@
         <v>50.9</v>
       </c>
       <c r="E1428" t="n">
-        <v>1898.7</v>
+        <v>1973.4</v>
       </c>
       <c r="F1428" t="n">
-        <v>11763.8</v>
+        <v>11838.5</v>
       </c>
       <c r="G1428" t="n">
         <v>8</v>
@@ -47584,10 +47584,10 @@
         <v>65.3</v>
       </c>
       <c r="E1429" t="n">
-        <v>1764.7</v>
+        <v>1818.3</v>
       </c>
       <c r="F1429" t="n">
-        <v>11429.3</v>
+        <v>11482.9</v>
       </c>
       <c r="G1429" t="n">
         <v>4</v>
@@ -47617,10 +47617,10 @@
         <v>58.4</v>
       </c>
       <c r="E1430" t="n">
-        <v>2099</v>
+        <v>2179.7</v>
       </c>
       <c r="F1430" t="n">
-        <v>13033.8</v>
+        <v>13114.5</v>
       </c>
       <c r="G1430" t="n">
         <v>6</v>
@@ -47650,10 +47650,10 @@
         <v>58.6</v>
       </c>
       <c r="E1431" t="n">
-        <v>1698.8</v>
+        <v>1751.7</v>
       </c>
       <c r="F1431" t="n">
-        <v>10532.7</v>
+        <v>10585.6</v>
       </c>
       <c r="G1431" t="n">
         <v>5</v>
@@ -47683,10 +47683,10 @@
         <v>55.3</v>
       </c>
       <c r="E1432" t="n">
-        <v>1894.7</v>
+        <v>1964.6</v>
       </c>
       <c r="F1432" t="n">
-        <v>11498.8</v>
+        <v>11568.7</v>
       </c>
       <c r="G1432" t="n">
         <v>7</v>
@@ -47716,10 +47716,10 @@
         <v>96</v>
       </c>
       <c r="E1433" t="n">
-        <v>1991.1</v>
+        <v>2050.3</v>
       </c>
       <c r="F1433" t="n">
-        <v>9526.1</v>
+        <v>9585.299999999999</v>
       </c>
       <c r="G1433" t="n">
         <v>1</v>
@@ -47749,16 +47749,16 @@
         <v>84.5</v>
       </c>
       <c r="E1434" t="n">
-        <v>2076</v>
+        <v>2119.7</v>
       </c>
       <c r="F1434" t="n">
-        <v>12787.1</v>
+        <v>12830.8</v>
       </c>
       <c r="G1434" t="n">
         <v>1</v>
       </c>
       <c r="H1434" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1434" t="n">
         <v>2</v>
@@ -47782,16 +47782,16 @@
         <v>66.59999999999999</v>
       </c>
       <c r="E1435" t="n">
-        <v>2053.7</v>
+        <v>2119.7</v>
       </c>
       <c r="F1435" t="n">
-        <v>12744.7</v>
+        <v>12810.7</v>
       </c>
       <c r="G1435" t="n">
         <v>4</v>
       </c>
       <c r="H1435" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1435" t="n">
         <v>3</v>
@@ -47815,16 +47815,16 @@
         <v>60.1</v>
       </c>
       <c r="E1436" t="n">
-        <v>1958.8</v>
+        <v>2033.5</v>
       </c>
       <c r="F1436" t="n">
-        <v>11823.9</v>
+        <v>11898.6</v>
       </c>
       <c r="G1436" t="n">
         <v>6</v>
       </c>
       <c r="H1436" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1436" t="n">
         <v>4</v>
@@ -47848,10 +47848,10 @@
         <v>74.09999999999999</v>
       </c>
       <c r="E1437" t="n">
-        <v>1838.8</v>
+        <v>1892.4</v>
       </c>
       <c r="F1437" t="n">
-        <v>11503.4</v>
+        <v>11557</v>
       </c>
       <c r="G1437" t="n">
         <v>3</v>
@@ -47881,10 +47881,10 @@
         <v>57.4</v>
       </c>
       <c r="E1438" t="n">
-        <v>2156.4</v>
+        <v>2237.1</v>
       </c>
       <c r="F1438" t="n">
-        <v>13091.2</v>
+        <v>13171.9</v>
       </c>
       <c r="G1438" t="n">
         <v>7</v>
@@ -47914,10 +47914,10 @@
         <v>0</v>
       </c>
       <c r="E1439" t="n">
-        <v>1698.8</v>
+        <v>1751.7</v>
       </c>
       <c r="F1439" t="n">
-        <v>10532.7</v>
+        <v>10585.6</v>
       </c>
       <c r="G1439" t="n">
         <v>8</v>
@@ -47947,16 +47947,16 @@
         <v>65.90000000000001</v>
       </c>
       <c r="E1440" t="n">
-        <v>1960.6</v>
+        <v>2030.5</v>
       </c>
       <c r="F1440" t="n">
-        <v>11564.7</v>
+        <v>11634.6</v>
       </c>
       <c r="G1440" t="n">
         <v>5</v>
       </c>
       <c r="H1440" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1440" t="n">
         <v>5</v>
@@ -47980,16 +47980,16 @@
         <v>76</v>
       </c>
       <c r="E1441" t="n">
-        <v>2067.1</v>
+        <v>2126.3</v>
       </c>
       <c r="F1441" t="n">
-        <v>9602.1</v>
+        <v>9661.299999999999</v>
       </c>
       <c r="G1441" t="n">
         <v>2</v>
       </c>
       <c r="H1441" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1441" t="n">
         <v>8</v>
@@ -48013,16 +48013,16 @@
         <v>73.09999999999999</v>
       </c>
       <c r="E1442" t="n">
-        <v>2149.1</v>
+        <v>2192.8</v>
       </c>
       <c r="F1442" t="n">
-        <v>12860.2</v>
+        <v>12903.9</v>
       </c>
       <c r="G1442" t="n">
         <v>6</v>
       </c>
       <c r="H1442" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1442" t="n">
         <v>2</v>
@@ -48046,16 +48046,16 @@
         <v>92.90000000000001</v>
       </c>
       <c r="E1443" t="n">
-        <v>2146.6</v>
+        <v>2212.6</v>
       </c>
       <c r="F1443" t="n">
-        <v>12837.6</v>
+        <v>12903.6</v>
       </c>
       <c r="G1443" t="n">
         <v>2</v>
       </c>
       <c r="H1443" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1443" t="n">
         <v>3</v>
@@ -48079,10 +48079,10 @@
         <v>51.6</v>
       </c>
       <c r="E1444" t="n">
-        <v>2010.4</v>
+        <v>2085.1</v>
       </c>
       <c r="F1444" t="n">
-        <v>11875.5</v>
+        <v>11950.2</v>
       </c>
       <c r="G1444" t="n">
         <v>8</v>
@@ -48112,10 +48112,10 @@
         <v>62.1</v>
       </c>
       <c r="E1445" t="n">
-        <v>1900.9</v>
+        <v>1954.5</v>
       </c>
       <c r="F1445" t="n">
-        <v>11565.5</v>
+        <v>11619.1</v>
       </c>
       <c r="G1445" t="n">
         <v>7</v>
@@ -48145,10 +48145,10 @@
         <v>86.7</v>
       </c>
       <c r="E1446" t="n">
-        <v>2243.1</v>
+        <v>2323.8</v>
       </c>
       <c r="F1446" t="n">
-        <v>13177.9</v>
+        <v>13258.6</v>
       </c>
       <c r="G1446" t="n">
         <v>4</v>
@@ -48178,10 +48178,10 @@
         <v>88.2</v>
       </c>
       <c r="E1447" t="n">
-        <v>1787</v>
+        <v>1839.9</v>
       </c>
       <c r="F1447" t="n">
-        <v>10620.9</v>
+        <v>10673.8</v>
       </c>
       <c r="G1447" t="n">
         <v>3</v>
@@ -48211,10 +48211,10 @@
         <v>73.3</v>
       </c>
       <c r="E1448" t="n">
-        <v>2033.9</v>
+        <v>2103.8</v>
       </c>
       <c r="F1448" t="n">
-        <v>11638</v>
+        <v>11707.9</v>
       </c>
       <c r="G1448" t="n">
         <v>5</v>
@@ -48244,10 +48244,10 @@
         <v>100.9</v>
       </c>
       <c r="E1449" t="n">
-        <v>2168</v>
+        <v>2227.2</v>
       </c>
       <c r="F1449" t="n">
-        <v>9703</v>
+        <v>9762.200000000001</v>
       </c>
       <c r="G1449" t="n">
         <v>1</v>
@@ -48277,16 +48277,16 @@
         <v>82.5</v>
       </c>
       <c r="E1450" t="n">
-        <v>2231.6</v>
+        <v>2275.3</v>
       </c>
       <c r="F1450" t="n">
-        <v>12942.7</v>
+        <v>12986.4</v>
       </c>
       <c r="G1450" t="n">
         <v>3</v>
       </c>
       <c r="H1450" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1450" t="n">
         <v>2</v>
@@ -48310,16 +48310,16 @@
         <v>73.5</v>
       </c>
       <c r="E1451" t="n">
-        <v>2220.1</v>
+        <v>2286.1</v>
       </c>
       <c r="F1451" t="n">
-        <v>12911.1</v>
+        <v>12977.1</v>
       </c>
       <c r="G1451" t="n">
         <v>4</v>
       </c>
       <c r="H1451" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1451" t="n">
         <v>3</v>
@@ -48343,10 +48343,10 @@
         <v>114.5</v>
       </c>
       <c r="E1452" t="n">
-        <v>2124.9</v>
+        <v>2199.6</v>
       </c>
       <c r="F1452" t="n">
-        <v>11990</v>
+        <v>12064.7</v>
       </c>
       <c r="G1452" t="n">
         <v>1</v>
@@ -48376,10 +48376,10 @@
         <v>85.90000000000001</v>
       </c>
       <c r="E1453" t="n">
-        <v>1986.8</v>
+        <v>2040.4</v>
       </c>
       <c r="F1453" t="n">
-        <v>11651.4</v>
+        <v>11705</v>
       </c>
       <c r="G1453" t="n">
         <v>2</v>
@@ -48409,10 +48409,10 @@
         <v>48.6</v>
       </c>
       <c r="E1454" t="n">
-        <v>2291.7</v>
+        <v>2372.4</v>
       </c>
       <c r="F1454" t="n">
-        <v>13226.5</v>
+        <v>13307.2</v>
       </c>
       <c r="G1454" t="n">
         <v>6</v>
@@ -48442,10 +48442,10 @@
         <v>52.8</v>
       </c>
       <c r="E1455" t="n">
-        <v>1839.8</v>
+        <v>1892.7</v>
       </c>
       <c r="F1455" t="n">
-        <v>10673.7</v>
+        <v>10726.6</v>
       </c>
       <c r="G1455" t="n">
         <v>5</v>
@@ -48475,10 +48475,10 @@
         <v>47.9</v>
       </c>
       <c r="E1456" t="n">
-        <v>2081.8</v>
+        <v>2151.7</v>
       </c>
       <c r="F1456" t="n">
-        <v>11685.9</v>
+        <v>11755.8</v>
       </c>
       <c r="G1456" t="n">
         <v>7</v>
@@ -48508,10 +48508,10 @@
         <v>43.3</v>
       </c>
       <c r="E1457" t="n">
-        <v>2211.3</v>
+        <v>2270.5</v>
       </c>
       <c r="F1457" t="n">
-        <v>9746.299999999999</v>
+        <v>9805.5</v>
       </c>
       <c r="G1457" t="n">
         <v>8</v>
@@ -48541,16 +48541,16 @@
         <v>66.5</v>
       </c>
       <c r="E1458" t="n">
-        <v>2298.1</v>
+        <v>2341.8</v>
       </c>
       <c r="F1458" t="n">
-        <v>13009.2</v>
+        <v>13052.9</v>
       </c>
       <c r="G1458" t="n">
         <v>5</v>
       </c>
       <c r="H1458" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1458" t="n">
         <v>2</v>
@@ -48574,16 +48574,16 @@
         <v>65.5</v>
       </c>
       <c r="E1459" t="n">
-        <v>2285.6</v>
+        <v>2351.6</v>
       </c>
       <c r="F1459" t="n">
-        <v>12976.6</v>
+        <v>13042.6</v>
       </c>
       <c r="G1459" t="n">
         <v>7</v>
       </c>
       <c r="H1459" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1459" t="n">
         <v>3</v>
@@ -48607,10 +48607,10 @@
         <v>83.90000000000001</v>
       </c>
       <c r="E1460" t="n">
-        <v>2208.8</v>
+        <v>2283.5</v>
       </c>
       <c r="F1460" t="n">
-        <v>12073.9</v>
+        <v>12148.6</v>
       </c>
       <c r="G1460" t="n">
         <v>3</v>
@@ -48640,10 +48640,10 @@
         <v>66.40000000000001</v>
       </c>
       <c r="E1461" t="n">
-        <v>2053.2</v>
+        <v>2106.8</v>
       </c>
       <c r="F1461" t="n">
-        <v>11717.8</v>
+        <v>11771.4</v>
       </c>
       <c r="G1461" t="n">
         <v>6</v>
@@ -48673,10 +48673,10 @@
         <v>107</v>
       </c>
       <c r="E1462" t="n">
-        <v>2398.7</v>
+        <v>2479.4</v>
       </c>
       <c r="F1462" t="n">
-        <v>13333.5</v>
+        <v>13414.2</v>
       </c>
       <c r="G1462" t="n">
         <v>1</v>
@@ -48706,10 +48706,10 @@
         <v>46.5</v>
       </c>
       <c r="E1463" t="n">
-        <v>1886.3</v>
+        <v>1939.2</v>
       </c>
       <c r="F1463" t="n">
-        <v>10720.2</v>
+        <v>10773.1</v>
       </c>
       <c r="G1463" t="n">
         <v>8</v>
@@ -48739,10 +48739,10 @@
         <v>67.40000000000001</v>
       </c>
       <c r="E1464" t="n">
-        <v>2149.2</v>
+        <v>2219.1</v>
       </c>
       <c r="F1464" t="n">
-        <v>11753.3</v>
+        <v>11823.2</v>
       </c>
       <c r="G1464" t="n">
         <v>4</v>
@@ -48772,16 +48772,16 @@
         <v>85.59999999999999</v>
       </c>
       <c r="E1465" t="n">
-        <v>2296.9</v>
+        <v>2356.1</v>
       </c>
       <c r="F1465" t="n">
-        <v>9831.9</v>
+        <v>9891.1</v>
       </c>
       <c r="G1465" t="n">
         <v>2</v>
       </c>
       <c r="H1465" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1465" t="n">
         <v>8</v>
@@ -48805,16 +48805,16 @@
         <v>100.6</v>
       </c>
       <c r="E1466" t="n">
-        <v>2398.7</v>
+        <v>2442.4</v>
       </c>
       <c r="F1466" t="n">
-        <v>13109.8</v>
+        <v>13153.5</v>
       </c>
       <c r="G1466" t="n">
         <v>1</v>
       </c>
       <c r="H1466" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1466" t="n">
         <v>2</v>
@@ -48838,10 +48838,10 @@
         <v>65.90000000000001</v>
       </c>
       <c r="E1467" t="n">
-        <v>2351.5</v>
+        <v>2417.5</v>
       </c>
       <c r="F1467" t="n">
-        <v>13042.5</v>
+        <v>13108.5</v>
       </c>
       <c r="G1467" t="n">
         <v>5</v>
@@ -48871,10 +48871,10 @@
         <v>70.8</v>
       </c>
       <c r="E1468" t="n">
-        <v>2279.6</v>
+        <v>2354.3</v>
       </c>
       <c r="F1468" t="n">
-        <v>12144.7</v>
+        <v>12219.4</v>
       </c>
       <c r="G1468" t="n">
         <v>4</v>
@@ -48904,10 +48904,10 @@
         <v>60.5</v>
       </c>
       <c r="E1469" t="n">
-        <v>2113.7</v>
+        <v>2167.3</v>
       </c>
       <c r="F1469" t="n">
-        <v>11778.3</v>
+        <v>11831.9</v>
       </c>
       <c r="G1469" t="n">
         <v>7</v>
@@ -48937,10 +48937,10 @@
         <v>64.59999999999999</v>
       </c>
       <c r="E1470" t="n">
-        <v>2463.3</v>
+        <v>2544</v>
       </c>
       <c r="F1470" t="n">
-        <v>13398.1</v>
+        <v>13478.8</v>
       </c>
       <c r="G1470" t="n">
         <v>6</v>
@@ -48970,10 +48970,10 @@
         <v>73.7</v>
       </c>
       <c r="E1471" t="n">
-        <v>1960</v>
+        <v>2012.9</v>
       </c>
       <c r="F1471" t="n">
-        <v>10793.9</v>
+        <v>10846.8</v>
       </c>
       <c r="G1471" t="n">
         <v>3</v>
@@ -49003,10 +49003,10 @@
         <v>55.2</v>
       </c>
       <c r="E1472" t="n">
-        <v>2204.4</v>
+        <v>2274.3</v>
       </c>
       <c r="F1472" t="n">
-        <v>11808.5</v>
+        <v>11878.4</v>
       </c>
       <c r="G1472" t="n">
         <v>8</v>
@@ -49036,16 +49036,16 @@
         <v>88</v>
       </c>
       <c r="E1473" t="n">
-        <v>2384.9</v>
+        <v>2444.1</v>
       </c>
       <c r="F1473" t="n">
-        <v>9919.9</v>
+        <v>9979.1</v>
       </c>
       <c r="G1473" t="n">
         <v>2</v>
       </c>
       <c r="H1473" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1473" t="n">
         <v>8</v>
@@ -49069,10 +49069,10 @@
         <v>70.09999999999999</v>
       </c>
       <c r="E1474" t="n">
-        <v>2468.8</v>
+        <v>2512.5</v>
       </c>
       <c r="F1474" t="n">
-        <v>13179.9</v>
+        <v>13223.6</v>
       </c>
       <c r="G1474" t="n">
         <v>4</v>
@@ -49102,10 +49102,10 @@
         <v>77.90000000000001</v>
       </c>
       <c r="E1475" t="n">
-        <v>2429.4</v>
+        <v>2495.4</v>
       </c>
       <c r="F1475" t="n">
-        <v>13120.4</v>
+        <v>13186.4</v>
       </c>
       <c r="G1475" t="n">
         <v>3</v>
@@ -49135,10 +49135,10 @@
         <v>80.8</v>
       </c>
       <c r="E1476" t="n">
-        <v>2360.4</v>
+        <v>2435.1</v>
       </c>
       <c r="F1476" t="n">
-        <v>12225.5</v>
+        <v>12300.2</v>
       </c>
       <c r="G1476" t="n">
         <v>2</v>
@@ -49168,10 +49168,10 @@
         <v>53</v>
       </c>
       <c r="E1477" t="n">
-        <v>2166.7</v>
+        <v>2220.3</v>
       </c>
       <c r="F1477" t="n">
-        <v>11831.3</v>
+        <v>11884.9</v>
       </c>
       <c r="G1477" t="n">
         <v>7</v>
@@ -49201,10 +49201,10 @@
         <v>59.8</v>
       </c>
       <c r="E1478" t="n">
-        <v>2523.1</v>
+        <v>2603.8</v>
       </c>
       <c r="F1478" t="n">
-        <v>13457.9</v>
+        <v>13538.6</v>
       </c>
       <c r="G1478" t="n">
         <v>6</v>
@@ -49234,10 +49234,10 @@
         <v>68.39999999999999</v>
       </c>
       <c r="E1479" t="n">
-        <v>2028.4</v>
+        <v>2081.3</v>
       </c>
       <c r="F1479" t="n">
-        <v>10862.3</v>
+        <v>10915.2</v>
       </c>
       <c r="G1479" t="n">
         <v>5</v>
@@ -49267,10 +49267,10 @@
         <v>48.4</v>
       </c>
       <c r="E1480" t="n">
-        <v>2252.8</v>
+        <v>2322.7</v>
       </c>
       <c r="F1480" t="n">
-        <v>11856.9</v>
+        <v>11926.8</v>
       </c>
       <c r="G1480" t="n">
         <v>8</v>
@@ -49300,10 +49300,10 @@
         <v>104.8</v>
       </c>
       <c r="E1481" t="n">
-        <v>2489.7</v>
+        <v>2548.9</v>
       </c>
       <c r="F1481" t="n">
-        <v>10024.7</v>
+        <v>10083.9</v>
       </c>
       <c r="G1481" t="n">
         <v>1</v>
@@ -49333,10 +49333,10 @@
         <v>76.3</v>
       </c>
       <c r="E1482" t="n">
-        <v>2545.1</v>
+        <v>2588.8</v>
       </c>
       <c r="F1482" t="n">
-        <v>13256.2</v>
+        <v>13299.9</v>
       </c>
       <c r="G1482" t="n">
         <v>3</v>
@@ -49366,10 +49366,10 @@
         <v>73.3</v>
       </c>
       <c r="E1483" t="n">
-        <v>2502.7</v>
+        <v>2568.7</v>
       </c>
       <c r="F1483" t="n">
-        <v>13193.7</v>
+        <v>13259.7</v>
       </c>
       <c r="G1483" t="n">
         <v>5</v>
@@ -49399,10 +49399,10 @@
         <v>56.5</v>
       </c>
       <c r="E1484" t="n">
-        <v>2416.9</v>
+        <v>2491.6</v>
       </c>
       <c r="F1484" t="n">
-        <v>12282</v>
+        <v>12356.7</v>
       </c>
       <c r="G1484" t="n">
         <v>7</v>
@@ -49432,10 +49432,10 @@
         <v>75.09999999999999</v>
       </c>
       <c r="E1485" t="n">
-        <v>2241.8</v>
+        <v>2295.4</v>
       </c>
       <c r="F1485" t="n">
-        <v>11906.4</v>
+        <v>11960</v>
       </c>
       <c r="G1485" t="n">
         <v>4</v>
@@ -49444,7 +49444,7 @@
         <v>7</v>
       </c>
       <c r="I1485" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1486">
@@ -49465,10 +49465,10 @@
         <v>69.7</v>
       </c>
       <c r="E1486" t="n">
-        <v>2592.8</v>
+        <v>2673.5</v>
       </c>
       <c r="F1486" t="n">
-        <v>13527.6</v>
+        <v>13608.3</v>
       </c>
       <c r="G1486" t="n">
         <v>6</v>
@@ -49498,10 +49498,10 @@
         <v>80.09999999999999</v>
       </c>
       <c r="E1487" t="n">
-        <v>2108.5</v>
+        <v>2161.4</v>
       </c>
       <c r="F1487" t="n">
-        <v>10942.4</v>
+        <v>10995.3</v>
       </c>
       <c r="G1487" t="n">
         <v>2</v>
@@ -49531,10 +49531,10 @@
         <v>44.90000000000001</v>
       </c>
       <c r="E1488" t="n">
-        <v>2297.7</v>
+        <v>2367.6</v>
       </c>
       <c r="F1488" t="n">
-        <v>11901.8</v>
+        <v>11971.7</v>
       </c>
       <c r="G1488" t="n">
         <v>8</v>
@@ -49543,7 +49543,7 @@
         <v>6</v>
       </c>
       <c r="I1488" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1489">
@@ -49564,10 +49564,10 @@
         <v>82.40000000000001</v>
       </c>
       <c r="E1489" t="n">
-        <v>2572.1</v>
+        <v>2631.3</v>
       </c>
       <c r="F1489" t="n">
-        <v>10107.1</v>
+        <v>10166.3</v>
       </c>
       <c r="G1489" t="n">
         <v>1</v>
@@ -49597,10 +49597,10 @@
         <v>94.09999999999999</v>
       </c>
       <c r="E1490" t="n">
-        <v>2639.2</v>
+        <v>2682.9</v>
       </c>
       <c r="F1490" t="n">
-        <v>13350.3</v>
+        <v>13394</v>
       </c>
       <c r="G1490" t="n">
         <v>3</v>
@@ -49630,10 +49630,10 @@
         <v>94.90000000000001</v>
       </c>
       <c r="E1491" t="n">
-        <v>2597.6</v>
+        <v>2663.6</v>
       </c>
       <c r="F1491" t="n">
-        <v>13288.6</v>
+        <v>13354.6</v>
       </c>
       <c r="G1491" t="n">
         <v>2</v>
@@ -49663,10 +49663,10 @@
         <v>75.2</v>
       </c>
       <c r="E1492" t="n">
-        <v>2492.1</v>
+        <v>2566.8</v>
       </c>
       <c r="F1492" t="n">
-        <v>12357.2</v>
+        <v>12431.9</v>
       </c>
       <c r="G1492" t="n">
         <v>5</v>
@@ -49696,10 +49696,10 @@
         <v>38.3</v>
       </c>
       <c r="E1493" t="n">
-        <v>2280.1</v>
+        <v>2333.7</v>
       </c>
       <c r="F1493" t="n">
-        <v>11944.7</v>
+        <v>11998.3</v>
       </c>
       <c r="G1493" t="n">
         <v>8</v>
@@ -49729,10 +49729,10 @@
         <v>52.9</v>
       </c>
       <c r="E1494" t="n">
-        <v>2645.7</v>
+        <v>2726.4</v>
       </c>
       <c r="F1494" t="n">
-        <v>13580.5</v>
+        <v>13661.2</v>
       </c>
       <c r="G1494" t="n">
         <v>6</v>
@@ -49762,10 +49762,10 @@
         <v>78.7</v>
       </c>
       <c r="E1495" t="n">
-        <v>2187.2</v>
+        <v>2240.1</v>
       </c>
       <c r="F1495" t="n">
-        <v>11021.1</v>
+        <v>11074</v>
       </c>
       <c r="G1495" t="n">
         <v>4</v>
@@ -49795,10 +49795,10 @@
         <v>44.4</v>
       </c>
       <c r="E1496" t="n">
-        <v>2342.1</v>
+        <v>2412</v>
       </c>
       <c r="F1496" t="n">
-        <v>11946.2</v>
+        <v>12016.1</v>
       </c>
       <c r="G1496" t="n">
         <v>7</v>
@@ -49828,10 +49828,10 @@
         <v>95.3</v>
       </c>
       <c r="E1497" t="n">
-        <v>2667.4</v>
+        <v>2726.6</v>
       </c>
       <c r="F1497" t="n">
-        <v>10202.4</v>
+        <v>10261.6</v>
       </c>
       <c r="G1497" t="n">
         <v>1</v>
@@ -49861,16 +49861,16 @@
         <v>72.8</v>
       </c>
       <c r="E1498" t="n">
-        <v>2712</v>
+        <v>2755.7</v>
       </c>
       <c r="F1498" t="n">
-        <v>13423.1</v>
+        <v>13466.8</v>
       </c>
       <c r="G1498" t="n">
         <v>2</v>
       </c>
       <c r="H1498" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1498" t="n">
         <v>2</v>
@@ -49894,10 +49894,10 @@
         <v>42</v>
       </c>
       <c r="E1499" t="n">
-        <v>2639.6</v>
+        <v>2705.6</v>
       </c>
       <c r="F1499" t="n">
-        <v>13330.6</v>
+        <v>13396.6</v>
       </c>
       <c r="G1499" t="n">
         <v>7</v>
@@ -49927,10 +49927,10 @@
         <v>65.10000000000001</v>
       </c>
       <c r="E1500" t="n">
-        <v>2557.2</v>
+        <v>2631.9</v>
       </c>
       <c r="F1500" t="n">
-        <v>12422.3</v>
+        <v>12497</v>
       </c>
       <c r="G1500" t="n">
         <v>5</v>
@@ -49960,10 +49960,10 @@
         <v>39.8</v>
       </c>
       <c r="E1501" t="n">
-        <v>2319.9</v>
+        <v>2373.5</v>
       </c>
       <c r="F1501" t="n">
-        <v>11984.5</v>
+        <v>12038.1</v>
       </c>
       <c r="G1501" t="n">
         <v>8</v>
@@ -49993,16 +49993,16 @@
         <v>65.8</v>
       </c>
       <c r="E1502" t="n">
-        <v>2711.5</v>
+        <v>2792.2</v>
       </c>
       <c r="F1502" t="n">
-        <v>13646.3</v>
+        <v>13727</v>
       </c>
       <c r="G1502" t="n">
         <v>4</v>
       </c>
       <c r="H1502" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1502" t="n">
         <v>1</v>
@@ -50026,10 +50026,10 @@
         <v>66.40000000000001</v>
       </c>
       <c r="E1503" t="n">
-        <v>2253.6</v>
+        <v>2306.5</v>
       </c>
       <c r="F1503" t="n">
-        <v>11087.5</v>
+        <v>11140.4</v>
       </c>
       <c r="G1503" t="n">
         <v>3</v>
@@ -50059,10 +50059,10 @@
         <v>52.7</v>
       </c>
       <c r="E1504" t="n">
-        <v>2394.8</v>
+        <v>2464.7</v>
       </c>
       <c r="F1504" t="n">
-        <v>11998.9</v>
+        <v>12068.8</v>
       </c>
       <c r="G1504" t="n">
         <v>6</v>
@@ -50092,10 +50092,10 @@
         <v>81.3</v>
       </c>
       <c r="E1505" t="n">
-        <v>2748.7</v>
+        <v>2807.9</v>
       </c>
       <c r="F1505" t="n">
-        <v>10283.7</v>
+        <v>10342.9</v>
       </c>
       <c r="G1505" t="n">
         <v>1</v>
@@ -50125,16 +50125,16 @@
         <v>70.59999999999999</v>
       </c>
       <c r="E1506" t="n">
-        <v>2782.6</v>
+        <v>2826.3</v>
       </c>
       <c r="F1506" t="n">
-        <v>13493.7</v>
+        <v>13537.4</v>
       </c>
       <c r="G1506" t="n">
         <v>4</v>
       </c>
       <c r="H1506" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1506" t="n">
         <v>2</v>
@@ -50158,10 +50158,10 @@
         <v>76.40000000000001</v>
       </c>
       <c r="E1507" t="n">
-        <v>2716</v>
+        <v>2782</v>
       </c>
       <c r="F1507" t="n">
-        <v>13407</v>
+        <v>13473</v>
       </c>
       <c r="G1507" t="n">
         <v>2</v>
@@ -50191,10 +50191,10 @@
         <v>60.3</v>
       </c>
       <c r="E1508" t="n">
-        <v>2617.5</v>
+        <v>2692.2</v>
       </c>
       <c r="F1508" t="n">
-        <v>12482.6</v>
+        <v>12557.3</v>
       </c>
       <c r="G1508" t="n">
         <v>6</v>
@@ -50224,10 +50224,10 @@
         <v>60.4</v>
       </c>
       <c r="E1509" t="n">
-        <v>2380.3</v>
+        <v>2433.9</v>
       </c>
       <c r="F1509" t="n">
-        <v>12044.9</v>
+        <v>12098.5</v>
       </c>
       <c r="G1509" t="n">
         <v>5</v>
@@ -50257,16 +50257,16 @@
         <v>53.9</v>
       </c>
       <c r="E1510" t="n">
-        <v>2765.4</v>
+        <v>2846.1</v>
       </c>
       <c r="F1510" t="n">
-        <v>13700.2</v>
+        <v>13780.9</v>
       </c>
       <c r="G1510" t="n">
         <v>7</v>
       </c>
       <c r="H1510" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1510" t="n">
         <v>1</v>
@@ -50290,10 +50290,10 @@
         <v>75.80000000000001</v>
       </c>
       <c r="E1511" t="n">
-        <v>2329.4</v>
+        <v>2382.3</v>
       </c>
       <c r="F1511" t="n">
-        <v>11163.3</v>
+        <v>11216.2</v>
       </c>
       <c r="G1511" t="n">
         <v>3</v>
@@ -50323,10 +50323,10 @@
         <v>53.2</v>
       </c>
       <c r="E1512" t="n">
-        <v>2448</v>
+        <v>2517.9</v>
       </c>
       <c r="F1512" t="n">
-        <v>12052.1</v>
+        <v>12122</v>
       </c>
       <c r="G1512" t="n">
         <v>8</v>
@@ -50356,10 +50356,10 @@
         <v>87.59999999999999</v>
       </c>
       <c r="E1513" t="n">
-        <v>2836.3</v>
+        <v>2895.5</v>
       </c>
       <c r="F1513" t="n">
-        <v>10371.3</v>
+        <v>10430.5</v>
       </c>
       <c r="G1513" t="n">
         <v>1</v>
@@ -50389,16 +50389,16 @@
         <v>58.2</v>
       </c>
       <c r="E1514" t="n">
-        <v>2840.8</v>
+        <v>2884.5</v>
       </c>
       <c r="F1514" t="n">
-        <v>13551.9</v>
+        <v>13595.6</v>
       </c>
       <c r="G1514" t="n">
         <v>4</v>
       </c>
       <c r="H1514" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1514" t="n">
         <v>2</v>
@@ -50422,10 +50422,10 @@
         <v>49.3</v>
       </c>
       <c r="E1515" t="n">
-        <v>2765.3</v>
+        <v>2831.3</v>
       </c>
       <c r="F1515" t="n">
-        <v>13456.3</v>
+        <v>13522.3</v>
       </c>
       <c r="G1515" t="n">
         <v>5</v>
@@ -50455,10 +50455,10 @@
         <v>69.09999999999999</v>
       </c>
       <c r="E1516" t="n">
-        <v>2686.6</v>
+        <v>2761.3</v>
       </c>
       <c r="F1516" t="n">
-        <v>12551.7</v>
+        <v>12626.4</v>
       </c>
       <c r="G1516" t="n">
         <v>3</v>
@@ -50488,10 +50488,10 @@
         <v>48.4</v>
       </c>
       <c r="E1517" t="n">
-        <v>2428.7</v>
+        <v>2482.3</v>
       </c>
       <c r="F1517" t="n">
-        <v>12093.3</v>
+        <v>12146.9</v>
       </c>
       <c r="G1517" t="n">
         <v>6</v>
@@ -50521,16 +50521,16 @@
         <v>47.6</v>
       </c>
       <c r="E1518" t="n">
-        <v>2813</v>
+        <v>2893.7</v>
       </c>
       <c r="F1518" t="n">
-        <v>13747.8</v>
+        <v>13828.5</v>
       </c>
       <c r="G1518" t="n">
         <v>7</v>
       </c>
       <c r="H1518" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1518" t="n">
         <v>1</v>
@@ -50554,10 +50554,10 @@
         <v>34.8</v>
       </c>
       <c r="E1519" t="n">
-        <v>2364.2</v>
+        <v>2417.1</v>
       </c>
       <c r="F1519" t="n">
-        <v>11198.1</v>
+        <v>11251</v>
       </c>
       <c r="G1519" t="n">
         <v>8</v>
@@ -50587,10 +50587,10 @@
         <v>73.3</v>
       </c>
       <c r="E1520" t="n">
-        <v>2521.3</v>
+        <v>2591.2</v>
       </c>
       <c r="F1520" t="n">
-        <v>12125.4</v>
+        <v>12195.3</v>
       </c>
       <c r="G1520" t="n">
         <v>2</v>
@@ -50620,10 +50620,10 @@
         <v>97.7</v>
       </c>
       <c r="E1521" t="n">
-        <v>2934</v>
+        <v>2993.2</v>
       </c>
       <c r="F1521" t="n">
-        <v>10469</v>
+        <v>10528.2</v>
       </c>
       <c r="G1521" t="n">
         <v>1</v>
@@ -50653,10 +50653,10 @@
         <v>95.7</v>
       </c>
       <c r="E1522" t="n">
-        <v>2936.5</v>
+        <v>2980.2</v>
       </c>
       <c r="F1522" t="n">
-        <v>13647.6</v>
+        <v>13691.3</v>
       </c>
       <c r="G1522" t="n">
         <v>1</v>
@@ -50686,10 +50686,10 @@
         <v>0</v>
       </c>
       <c r="E1523" t="n">
-        <v>2765.3</v>
+        <v>2831.3</v>
       </c>
       <c r="F1523" t="n">
-        <v>13456.3</v>
+        <v>13522.3</v>
       </c>
       <c r="G1523" t="n">
         <v>8</v>
@@ -50719,10 +50719,10 @@
         <v>40.7</v>
       </c>
       <c r="E1524" t="n">
-        <v>2727.3</v>
+        <v>2802</v>
       </c>
       <c r="F1524" t="n">
-        <v>12592.4</v>
+        <v>12667.1</v>
       </c>
       <c r="G1524" t="n">
         <v>7</v>
@@ -50752,10 +50752,10 @@
         <v>68.2</v>
       </c>
       <c r="E1525" t="n">
-        <v>2496.9</v>
+        <v>2550.5</v>
       </c>
       <c r="F1525" t="n">
-        <v>12161.5</v>
+        <v>12215.1</v>
       </c>
       <c r="G1525" t="n">
         <v>4</v>
@@ -50785,10 +50785,10 @@
         <v>66.59999999999999</v>
       </c>
       <c r="E1526" t="n">
-        <v>2879.6</v>
+        <v>2960.3</v>
       </c>
       <c r="F1526" t="n">
-        <v>13814.4</v>
+        <v>13895.1</v>
       </c>
       <c r="G1526" t="n">
         <v>5</v>
@@ -50818,10 +50818,10 @@
         <v>80.59999999999999</v>
       </c>
       <c r="E1527" t="n">
-        <v>2444.8</v>
+        <v>2497.7</v>
       </c>
       <c r="F1527" t="n">
-        <v>11278.7</v>
+        <v>11331.6</v>
       </c>
       <c r="G1527" t="n">
         <v>2</v>
@@ -50851,10 +50851,10 @@
         <v>46.4</v>
       </c>
       <c r="E1528" t="n">
-        <v>2567.7</v>
+        <v>2637.6</v>
       </c>
       <c r="F1528" t="n">
-        <v>12171.8</v>
+        <v>12241.7</v>
       </c>
       <c r="G1528" t="n">
         <v>6</v>
@@ -50884,10 +50884,10 @@
         <v>80.40000000000001</v>
       </c>
       <c r="E1529" t="n">
-        <v>3014.4</v>
+        <v>3073.6</v>
       </c>
       <c r="F1529" t="n">
-        <v>10549.4</v>
+        <v>10608.6</v>
       </c>
       <c r="G1529" t="n">
         <v>3</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -42172,7 +42172,7 @@
         <v>114.8</v>
       </c>
       <c r="E1265" t="n">
-        <v>551.5999999999999</v>
+        <v>551.6</v>
       </c>
       <c r="F1265" t="n">
         <v>8086.6</v>
@@ -43492,7 +43492,7 @@
         <v>66.3</v>
       </c>
       <c r="E1305" t="n">
-        <v>847.1999999999999</v>
+        <v>847.2</v>
       </c>
       <c r="F1305" t="n">
         <v>8382.200000000001</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -42202,16 +42202,16 @@
         </is>
       </c>
       <c r="D1266" t="n">
-        <v>34.2</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="E1266" t="n">
-        <v>518.3</v>
+        <v>553</v>
       </c>
       <c r="F1266" t="n">
-        <v>11229.4</v>
+        <v>11264.1</v>
       </c>
       <c r="G1266" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H1266" t="n">
         <v>8</v>
@@ -42235,16 +42235,16 @@
         </is>
       </c>
       <c r="D1267" t="n">
-        <v>45.6</v>
+        <v>108</v>
       </c>
       <c r="E1267" t="n">
-        <v>653.6</v>
+        <v>716</v>
       </c>
       <c r="F1267" t="n">
-        <v>11344.6</v>
+        <v>11407</v>
       </c>
       <c r="G1267" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H1267" t="n">
         <v>3</v>
@@ -42268,13 +42268,13 @@
         </is>
       </c>
       <c r="D1268" t="n">
-        <v>56.1</v>
+        <v>103.4</v>
       </c>
       <c r="E1268" t="n">
-        <v>645.6</v>
+        <v>692.9</v>
       </c>
       <c r="F1268" t="n">
-        <v>10510.7</v>
+        <v>10558</v>
       </c>
       <c r="G1268" t="n">
         <v>3</v>
@@ -42301,16 +42301,16 @@
         </is>
       </c>
       <c r="D1269" t="n">
-        <v>61.7</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="E1269" t="n">
-        <v>718.8000000000001</v>
+        <v>748.2</v>
       </c>
       <c r="F1269" t="n">
-        <v>10383.4</v>
+        <v>10412.8</v>
       </c>
       <c r="G1269" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H1269" t="n">
         <v>2</v>
@@ -42334,16 +42334,16 @@
         </is>
       </c>
       <c r="D1270" t="n">
-        <v>58.3</v>
+        <v>135.1</v>
       </c>
       <c r="E1270" t="n">
-        <v>727.1999999999999</v>
+        <v>804</v>
       </c>
       <c r="F1270" t="n">
-        <v>11662</v>
+        <v>11738.8</v>
       </c>
       <c r="G1270" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1270" t="n">
         <v>1</v>
@@ -42367,16 +42367,16 @@
         </is>
       </c>
       <c r="D1271" t="n">
-        <v>47.9</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="E1271" t="n">
-        <v>562</v>
+        <v>591.2</v>
       </c>
       <c r="F1271" t="n">
-        <v>9395.9</v>
+        <v>9425.1</v>
       </c>
       <c r="G1271" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H1271" t="n">
         <v>7</v>
@@ -42400,16 +42400,16 @@
         </is>
       </c>
       <c r="D1272" t="n">
-        <v>32.4</v>
+        <v>81.3</v>
       </c>
       <c r="E1272" t="n">
-        <v>603.1999999999999</v>
+        <v>652.1</v>
       </c>
       <c r="F1272" t="n">
-        <v>10207.3</v>
+        <v>10256.2</v>
       </c>
       <c r="G1272" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H1272" t="n">
         <v>5</v>
@@ -42433,16 +42433,16 @@
         </is>
       </c>
       <c r="D1273" t="n">
-        <v>34.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="E1273" t="n">
-        <v>585.8</v>
+        <v>649.7</v>
       </c>
       <c r="F1273" t="n">
-        <v>8120.8</v>
+        <v>8184.7</v>
       </c>
       <c r="G1273" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1273" t="n">
         <v>6</v>
@@ -42469,10 +42469,10 @@
         <v>73.59999999999999</v>
       </c>
       <c r="E1274" t="n">
-        <v>591.9</v>
+        <v>626.6</v>
       </c>
       <c r="F1274" t="n">
-        <v>11303</v>
+        <v>11337.7</v>
       </c>
       <c r="G1274" t="n">
         <v>3</v>
@@ -42502,16 +42502,16 @@
         <v>59.40000000000001</v>
       </c>
       <c r="E1275" t="n">
-        <v>713</v>
+        <v>775.4</v>
       </c>
       <c r="F1275" t="n">
-        <v>11404</v>
+        <v>11466.4</v>
       </c>
       <c r="G1275" t="n">
         <v>5</v>
       </c>
       <c r="H1275" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1275" t="n">
         <v>2</v>
@@ -42535,16 +42535,16 @@
         <v>78.59999999999999</v>
       </c>
       <c r="E1276" t="n">
-        <v>724.2</v>
+        <v>771.5</v>
       </c>
       <c r="F1276" t="n">
-        <v>10589.3</v>
+        <v>10636.6</v>
       </c>
       <c r="G1276" t="n">
         <v>1</v>
       </c>
       <c r="H1276" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1276" t="n">
         <v>4</v>
@@ -42568,10 +42568,10 @@
         <v>46</v>
       </c>
       <c r="E1277" t="n">
-        <v>764.8000000000001</v>
+        <v>794.2</v>
       </c>
       <c r="F1277" t="n">
-        <v>10429.4</v>
+        <v>10458.8</v>
       </c>
       <c r="G1277" t="n">
         <v>8</v>
@@ -42601,10 +42601,10 @@
         <v>70.09999999999999</v>
       </c>
       <c r="E1278" t="n">
-        <v>797.3</v>
+        <v>874.1</v>
       </c>
       <c r="F1278" t="n">
-        <v>11732.1</v>
+        <v>11808.9</v>
       </c>
       <c r="G1278" t="n">
         <v>4</v>
@@ -42634,10 +42634,10 @@
         <v>52.5</v>
       </c>
       <c r="E1279" t="n">
-        <v>614.5</v>
+        <v>643.7</v>
       </c>
       <c r="F1279" t="n">
-        <v>9448.4</v>
+        <v>9477.6</v>
       </c>
       <c r="G1279" t="n">
         <v>7</v>
@@ -42667,10 +42667,10 @@
         <v>74.90000000000001</v>
       </c>
       <c r="E1280" t="n">
-        <v>678.1</v>
+        <v>727</v>
       </c>
       <c r="F1280" t="n">
-        <v>10282.2</v>
+        <v>10331.1</v>
       </c>
       <c r="G1280" t="n">
         <v>2</v>
@@ -42700,10 +42700,10 @@
         <v>58.2</v>
       </c>
       <c r="E1281" t="n">
-        <v>644</v>
+        <v>707.9</v>
       </c>
       <c r="F1281" t="n">
-        <v>8179</v>
+        <v>8242.9</v>
       </c>
       <c r="G1281" t="n">
         <v>6</v>
@@ -42733,10 +42733,10 @@
         <v>53.8</v>
       </c>
       <c r="E1282" t="n">
-        <v>645.6999999999999</v>
+        <v>680.4</v>
       </c>
       <c r="F1282" t="n">
-        <v>11356.8</v>
+        <v>11391.5</v>
       </c>
       <c r="G1282" t="n">
         <v>7</v>
@@ -42766,10 +42766,10 @@
         <v>51.1</v>
       </c>
       <c r="E1283" t="n">
-        <v>764.1</v>
+        <v>826.5</v>
       </c>
       <c r="F1283" t="n">
-        <v>11455.1</v>
+        <v>11517.5</v>
       </c>
       <c r="G1283" t="n">
         <v>8</v>
@@ -42799,10 +42799,10 @@
         <v>62.1</v>
       </c>
       <c r="E1284" t="n">
-        <v>786.3</v>
+        <v>833.6</v>
       </c>
       <c r="F1284" t="n">
-        <v>10651.4</v>
+        <v>10698.7</v>
       </c>
       <c r="G1284" t="n">
         <v>3</v>
@@ -42832,10 +42832,10 @@
         <v>69.5</v>
       </c>
       <c r="E1285" t="n">
-        <v>834.3000000000001</v>
+        <v>863.7</v>
       </c>
       <c r="F1285" t="n">
-        <v>10498.9</v>
+        <v>10528.3</v>
       </c>
       <c r="G1285" t="n">
         <v>1</v>
@@ -42865,10 +42865,10 @@
         <v>59.5</v>
       </c>
       <c r="E1286" t="n">
-        <v>856.8</v>
+        <v>933.6</v>
       </c>
       <c r="F1286" t="n">
-        <v>11791.6</v>
+        <v>11868.4</v>
       </c>
       <c r="G1286" t="n">
         <v>5</v>
@@ -42898,10 +42898,10 @@
         <v>54.1</v>
       </c>
       <c r="E1287" t="n">
-        <v>668.6</v>
+        <v>697.8</v>
       </c>
       <c r="F1287" t="n">
-        <v>9502.5</v>
+        <v>9531.700000000001</v>
       </c>
       <c r="G1287" t="n">
         <v>6</v>
@@ -42931,10 +42931,10 @@
         <v>69.2</v>
       </c>
       <c r="E1288" t="n">
-        <v>747.3</v>
+        <v>796.2</v>
       </c>
       <c r="F1288" t="n">
-        <v>10351.4</v>
+        <v>10400.3</v>
       </c>
       <c r="G1288" t="n">
         <v>2</v>
@@ -42964,10 +42964,10 @@
         <v>60</v>
       </c>
       <c r="E1289" t="n">
-        <v>704</v>
+        <v>767.9</v>
       </c>
       <c r="F1289" t="n">
-        <v>8239</v>
+        <v>8302.9</v>
       </c>
       <c r="G1289" t="n">
         <v>4</v>
@@ -42997,10 +42997,10 @@
         <v>87.8</v>
       </c>
       <c r="E1290" t="n">
-        <v>733.5</v>
+        <v>768.1999999999999</v>
       </c>
       <c r="F1290" t="n">
-        <v>11444.6</v>
+        <v>11479.3</v>
       </c>
       <c r="G1290" t="n">
         <v>1</v>
@@ -43030,16 +43030,16 @@
         <v>67</v>
       </c>
       <c r="E1291" t="n">
-        <v>831.1</v>
+        <v>893.5</v>
       </c>
       <c r="F1291" t="n">
-        <v>11522.1</v>
+        <v>11584.5</v>
       </c>
       <c r="G1291" t="n">
         <v>4</v>
       </c>
       <c r="H1291" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1291" t="n">
         <v>2</v>
@@ -43063,16 +43063,16 @@
         <v>55.4</v>
       </c>
       <c r="E1292" t="n">
-        <v>841.7</v>
+        <v>889</v>
       </c>
       <c r="F1292" t="n">
-        <v>10706.8</v>
+        <v>10754.1</v>
       </c>
       <c r="G1292" t="n">
         <v>7</v>
       </c>
       <c r="H1292" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1292" t="n">
         <v>4</v>
@@ -43096,10 +43096,10 @@
         <v>57.6</v>
       </c>
       <c r="E1293" t="n">
-        <v>891.9</v>
+        <v>921.3000000000001</v>
       </c>
       <c r="F1293" t="n">
-        <v>10556.5</v>
+        <v>10585.9</v>
       </c>
       <c r="G1293" t="n">
         <v>6</v>
@@ -43129,10 +43129,10 @@
         <v>66.3</v>
       </c>
       <c r="E1294" t="n">
-        <v>923.1</v>
+        <v>999.9</v>
       </c>
       <c r="F1294" t="n">
-        <v>11857.9</v>
+        <v>11934.7</v>
       </c>
       <c r="G1294" t="n">
         <v>5</v>
@@ -43162,10 +43162,10 @@
         <v>52.1</v>
       </c>
       <c r="E1295" t="n">
-        <v>720.7</v>
+        <v>749.9</v>
       </c>
       <c r="F1295" t="n">
-        <v>9554.6</v>
+        <v>9583.799999999999</v>
       </c>
       <c r="G1295" t="n">
         <v>8</v>
@@ -43195,10 +43195,10 @@
         <v>81.09999999999999</v>
       </c>
       <c r="E1296" t="n">
-        <v>828.4</v>
+        <v>877.3</v>
       </c>
       <c r="F1296" t="n">
-        <v>10432.5</v>
+        <v>10481.4</v>
       </c>
       <c r="G1296" t="n">
         <v>2</v>
@@ -43228,10 +43228,10 @@
         <v>76.89999999999999</v>
       </c>
       <c r="E1297" t="n">
-        <v>780.9</v>
+        <v>844.8</v>
       </c>
       <c r="F1297" t="n">
-        <v>8315.9</v>
+        <v>8379.799999999999</v>
       </c>
       <c r="G1297" t="n">
         <v>3</v>
@@ -43261,10 +43261,10 @@
         <v>77.90000000000001</v>
       </c>
       <c r="E1298" t="n">
-        <v>811.4</v>
+        <v>846.1</v>
       </c>
       <c r="F1298" t="n">
-        <v>11522.5</v>
+        <v>11557.2</v>
       </c>
       <c r="G1298" t="n">
         <v>1</v>
@@ -43294,16 +43294,16 @@
         <v>54.8</v>
       </c>
       <c r="E1299" t="n">
-        <v>885.9</v>
+        <v>948.3</v>
       </c>
       <c r="F1299" t="n">
-        <v>11576.9</v>
+        <v>11639.3</v>
       </c>
       <c r="G1299" t="n">
         <v>7</v>
       </c>
       <c r="H1299" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1299" t="n">
         <v>2</v>
@@ -43327,10 +43327,10 @@
         <v>68.8</v>
       </c>
       <c r="E1300" t="n">
-        <v>910.5</v>
+        <v>957.8</v>
       </c>
       <c r="F1300" t="n">
-        <v>10775.6</v>
+        <v>10822.9</v>
       </c>
       <c r="G1300" t="n">
         <v>3</v>
@@ -43360,10 +43360,10 @@
         <v>60.2</v>
       </c>
       <c r="E1301" t="n">
-        <v>952.1</v>
+        <v>981.5</v>
       </c>
       <c r="F1301" t="n">
-        <v>10616.7</v>
+        <v>10646.1</v>
       </c>
       <c r="G1301" t="n">
         <v>6</v>
@@ -43393,10 +43393,10 @@
         <v>62.8</v>
       </c>
       <c r="E1302" t="n">
-        <v>985.9</v>
+        <v>1062.7</v>
       </c>
       <c r="F1302" t="n">
-        <v>11920.7</v>
+        <v>11997.5</v>
       </c>
       <c r="G1302" t="n">
         <v>5</v>
@@ -43426,10 +43426,10 @@
         <v>50.9</v>
       </c>
       <c r="E1303" t="n">
-        <v>771.6</v>
+        <v>800.8</v>
       </c>
       <c r="F1303" t="n">
-        <v>9605.5</v>
+        <v>9634.700000000001</v>
       </c>
       <c r="G1303" t="n">
         <v>8</v>
@@ -43459,16 +43459,16 @@
         <v>69.40000000000001</v>
       </c>
       <c r="E1304" t="n">
-        <v>897.8</v>
+        <v>946.7</v>
       </c>
       <c r="F1304" t="n">
-        <v>10501.9</v>
+        <v>10550.8</v>
       </c>
       <c r="G1304" t="n">
         <v>2</v>
       </c>
       <c r="H1304" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1304" t="n">
         <v>6</v>
@@ -43492,10 +43492,10 @@
         <v>66.3</v>
       </c>
       <c r="E1305" t="n">
-        <v>847.2</v>
+        <v>911.1</v>
       </c>
       <c r="F1305" t="n">
-        <v>8382.200000000001</v>
+        <v>8446.1</v>
       </c>
       <c r="G1305" t="n">
         <v>4</v>
@@ -43525,10 +43525,10 @@
         <v>68</v>
       </c>
       <c r="E1306" t="n">
-        <v>879.4</v>
+        <v>914.1</v>
       </c>
       <c r="F1306" t="n">
-        <v>11590.5</v>
+        <v>11625.2</v>
       </c>
       <c r="G1306" t="n">
         <v>5</v>
@@ -43558,16 +43558,16 @@
         <v>89.2</v>
       </c>
       <c r="E1307" t="n">
-        <v>975.1</v>
+        <v>1037.5</v>
       </c>
       <c r="F1307" t="n">
-        <v>11666.1</v>
+        <v>11728.5</v>
       </c>
       <c r="G1307" t="n">
         <v>2</v>
       </c>
       <c r="H1307" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1307" t="n">
         <v>2</v>
@@ -43591,16 +43591,16 @@
         <v>79.3</v>
       </c>
       <c r="E1308" t="n">
-        <v>989.8</v>
+        <v>1037.1</v>
       </c>
       <c r="F1308" t="n">
-        <v>10854.9</v>
+        <v>10902.2</v>
       </c>
       <c r="G1308" t="n">
         <v>3</v>
       </c>
       <c r="H1308" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1308" t="n">
         <v>4</v>
@@ -43624,10 +43624,10 @@
         <v>61</v>
       </c>
       <c r="E1309" t="n">
-        <v>1013.1</v>
+        <v>1042.5</v>
       </c>
       <c r="F1309" t="n">
-        <v>10677.7</v>
+        <v>10707.1</v>
       </c>
       <c r="G1309" t="n">
         <v>6</v>
@@ -43657,10 +43657,10 @@
         <v>57.4</v>
       </c>
       <c r="E1310" t="n">
-        <v>1043.3</v>
+        <v>1120.1</v>
       </c>
       <c r="F1310" t="n">
-        <v>11978.1</v>
+        <v>12054.9</v>
       </c>
       <c r="G1310" t="n">
         <v>7</v>
@@ -43690,10 +43690,10 @@
         <v>46.4</v>
       </c>
       <c r="E1311" t="n">
-        <v>818</v>
+        <v>847.2</v>
       </c>
       <c r="F1311" t="n">
-        <v>9651.9</v>
+        <v>9681.1</v>
       </c>
       <c r="G1311" t="n">
         <v>8</v>
@@ -43723,10 +43723,10 @@
         <v>77.2</v>
       </c>
       <c r="E1312" t="n">
-        <v>975</v>
+        <v>1023.9</v>
       </c>
       <c r="F1312" t="n">
-        <v>10579.1</v>
+        <v>10628</v>
       </c>
       <c r="G1312" t="n">
         <v>4</v>
@@ -43756,10 +43756,10 @@
         <v>95.2</v>
       </c>
       <c r="E1313" t="n">
-        <v>942.4</v>
+        <v>1006.3</v>
       </c>
       <c r="F1313" t="n">
-        <v>8477.4</v>
+        <v>8541.299999999999</v>
       </c>
       <c r="G1313" t="n">
         <v>1</v>
@@ -43789,10 +43789,10 @@
         <v>78</v>
       </c>
       <c r="E1314" t="n">
-        <v>957.4</v>
+        <v>992.1</v>
       </c>
       <c r="F1314" t="n">
-        <v>11668.5</v>
+        <v>11703.2</v>
       </c>
       <c r="G1314" t="n">
         <v>3</v>
@@ -43822,16 +43822,16 @@
         <v>78.59999999999999</v>
       </c>
       <c r="E1315" t="n">
-        <v>1053.7</v>
+        <v>1116.1</v>
       </c>
       <c r="F1315" t="n">
-        <v>11744.7</v>
+        <v>11807.1</v>
       </c>
       <c r="G1315" t="n">
         <v>2</v>
       </c>
       <c r="H1315" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I1315" t="n">
         <v>2</v>
@@ -43855,16 +43855,16 @@
         <v>76.90000000000001</v>
       </c>
       <c r="E1316" t="n">
-        <v>1066.7</v>
+        <v>1114</v>
       </c>
       <c r="F1316" t="n">
-        <v>10931.8</v>
+        <v>10979.1</v>
       </c>
       <c r="G1316" t="n">
         <v>4</v>
       </c>
       <c r="H1316" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1316" t="n">
         <v>4</v>
@@ -43888,16 +43888,16 @@
         <v>48.4</v>
       </c>
       <c r="E1317" t="n">
-        <v>1061.5</v>
+        <v>1090.9</v>
       </c>
       <c r="F1317" t="n">
-        <v>10726.1</v>
+        <v>10755.5</v>
       </c>
       <c r="G1317" t="n">
         <v>8</v>
       </c>
       <c r="H1317" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1317" t="n">
         <v>5</v>
@@ -43921,10 +43921,10 @@
         <v>67.59999999999999</v>
       </c>
       <c r="E1318" t="n">
-        <v>1110.9</v>
+        <v>1187.7</v>
       </c>
       <c r="F1318" t="n">
-        <v>12045.7</v>
+        <v>12122.5</v>
       </c>
       <c r="G1318" t="n">
         <v>5</v>
@@ -43954,10 +43954,10 @@
         <v>58.1</v>
       </c>
       <c r="E1319" t="n">
-        <v>876.1</v>
+        <v>905.3</v>
       </c>
       <c r="F1319" t="n">
-        <v>9710</v>
+        <v>9739.200000000001</v>
       </c>
       <c r="G1319" t="n">
         <v>7</v>
@@ -43987,16 +43987,16 @@
         <v>61.4</v>
       </c>
       <c r="E1320" t="n">
-        <v>1036.4</v>
+        <v>1085.3</v>
       </c>
       <c r="F1320" t="n">
-        <v>10640.5</v>
+        <v>10689.4</v>
       </c>
       <c r="G1320" t="n">
         <v>6</v>
       </c>
       <c r="H1320" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1320" t="n">
         <v>6</v>
@@ -44020,16 +44020,16 @@
         <v>81.59999999999999</v>
       </c>
       <c r="E1321" t="n">
-        <v>1024</v>
+        <v>1087.9</v>
       </c>
       <c r="F1321" t="n">
-        <v>8559</v>
+        <v>8622.9</v>
       </c>
       <c r="G1321" t="n">
         <v>1</v>
       </c>
       <c r="H1321" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1321" t="n">
         <v>8</v>
@@ -44053,10 +44053,10 @@
         <v>67.5</v>
       </c>
       <c r="E1322" t="n">
-        <v>1024.9</v>
+        <v>1059.6</v>
       </c>
       <c r="F1322" t="n">
-        <v>11736</v>
+        <v>11770.7</v>
       </c>
       <c r="G1322" t="n">
         <v>5</v>
@@ -44086,16 +44086,16 @@
         <v>69.8</v>
       </c>
       <c r="E1323" t="n">
-        <v>1123.5</v>
+        <v>1185.9</v>
       </c>
       <c r="F1323" t="n">
-        <v>11814.5</v>
+        <v>11876.9</v>
       </c>
       <c r="G1323" t="n">
         <v>2</v>
       </c>
       <c r="H1323" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1323" t="n">
         <v>2</v>
@@ -44119,16 +44119,16 @@
         <v>68.3</v>
       </c>
       <c r="E1324" t="n">
-        <v>1135</v>
+        <v>1182.3</v>
       </c>
       <c r="F1324" t="n">
-        <v>11000.1</v>
+        <v>11047.4</v>
       </c>
       <c r="G1324" t="n">
         <v>3</v>
       </c>
       <c r="H1324" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1324" t="n">
         <v>4</v>
@@ -44152,16 +44152,16 @@
         <v>52.1</v>
       </c>
       <c r="E1325" t="n">
-        <v>1113.6</v>
+        <v>1143</v>
       </c>
       <c r="F1325" t="n">
-        <v>10778.2</v>
+        <v>10807.6</v>
       </c>
       <c r="G1325" t="n">
         <v>8</v>
       </c>
       <c r="H1325" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I1325" t="n">
         <v>5</v>
@@ -44185,10 +44185,10 @@
         <v>79.7</v>
       </c>
       <c r="E1326" t="n">
-        <v>1190.6</v>
+        <v>1267.4</v>
       </c>
       <c r="F1326" t="n">
-        <v>12125.4</v>
+        <v>12202.2</v>
       </c>
       <c r="G1326" t="n">
         <v>1</v>
@@ -44218,10 +44218,10 @@
         <v>58</v>
       </c>
       <c r="E1327" t="n">
-        <v>934.1</v>
+        <v>963.3</v>
       </c>
       <c r="F1327" t="n">
-        <v>9768</v>
+        <v>9797.200000000001</v>
       </c>
       <c r="G1327" t="n">
         <v>7</v>
@@ -44251,10 +44251,10 @@
         <v>59.5</v>
       </c>
       <c r="E1328" t="n">
-        <v>1095.9</v>
+        <v>1144.8</v>
       </c>
       <c r="F1328" t="n">
-        <v>10700</v>
+        <v>10748.9</v>
       </c>
       <c r="G1328" t="n">
         <v>6</v>
@@ -44284,16 +44284,16 @@
         <v>68.10000000000001</v>
       </c>
       <c r="E1329" t="n">
-        <v>1092.1</v>
+        <v>1156</v>
       </c>
       <c r="F1329" t="n">
-        <v>8627.1</v>
+        <v>8691</v>
       </c>
       <c r="G1329" t="n">
         <v>4</v>
       </c>
       <c r="H1329" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I1329" t="n">
         <v>8</v>
@@ -44317,10 +44317,10 @@
         <v>58.6</v>
       </c>
       <c r="E1330" t="n">
-        <v>1083.5</v>
+        <v>1118.2</v>
       </c>
       <c r="F1330" t="n">
-        <v>11794.6</v>
+        <v>11829.3</v>
       </c>
       <c r="G1330" t="n">
         <v>6</v>
@@ -44350,10 +44350,10 @@
         <v>105.7</v>
       </c>
       <c r="E1331" t="n">
-        <v>1229.2</v>
+        <v>1291.6</v>
       </c>
       <c r="F1331" t="n">
-        <v>11920.2</v>
+        <v>11982.6</v>
       </c>
       <c r="G1331" t="n">
         <v>1</v>
@@ -44383,16 +44383,16 @@
         <v>58.4</v>
       </c>
       <c r="E1332" t="n">
-        <v>1193.4</v>
+        <v>1240.7</v>
       </c>
       <c r="F1332" t="n">
-        <v>11058.5</v>
+        <v>11105.8</v>
       </c>
       <c r="G1332" t="n">
         <v>7</v>
       </c>
       <c r="H1332" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1332" t="n">
         <v>4</v>
@@ -44416,16 +44416,16 @@
         <v>57.4</v>
       </c>
       <c r="E1333" t="n">
-        <v>1171</v>
+        <v>1200.4</v>
       </c>
       <c r="F1333" t="n">
-        <v>10835.6</v>
+        <v>10865</v>
       </c>
       <c r="G1333" t="n">
         <v>8</v>
       </c>
       <c r="H1333" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1333" t="n">
         <v>5</v>
@@ -44449,10 +44449,10 @@
         <v>83.40000000000001</v>
       </c>
       <c r="E1334" t="n">
-        <v>1274</v>
+        <v>1350.8</v>
       </c>
       <c r="F1334" t="n">
-        <v>12208.8</v>
+        <v>12285.6</v>
       </c>
       <c r="G1334" t="n">
         <v>3</v>
@@ -44482,10 +44482,10 @@
         <v>74.3</v>
       </c>
       <c r="E1335" t="n">
-        <v>1008.4</v>
+        <v>1037.6</v>
       </c>
       <c r="F1335" t="n">
-        <v>9842.299999999999</v>
+        <v>9871.5</v>
       </c>
       <c r="G1335" t="n">
         <v>4</v>
@@ -44515,16 +44515,16 @@
         <v>72</v>
       </c>
       <c r="E1336" t="n">
-        <v>1167.9</v>
+        <v>1216.8</v>
       </c>
       <c r="F1336" t="n">
-        <v>10772</v>
+        <v>10820.9</v>
       </c>
       <c r="G1336" t="n">
         <v>5</v>
       </c>
       <c r="H1336" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1336" t="n">
         <v>6</v>
@@ -44548,16 +44548,16 @@
         <v>87.09999999999999</v>
       </c>
       <c r="E1337" t="n">
-        <v>1179.2</v>
+        <v>1243.1</v>
       </c>
       <c r="F1337" t="n">
-        <v>8714.200000000001</v>
+        <v>8778.1</v>
       </c>
       <c r="G1337" t="n">
         <v>2</v>
       </c>
       <c r="H1337" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1337" t="n">
         <v>8</v>
@@ -44581,10 +44581,10 @@
         <v>61.2</v>
       </c>
       <c r="E1338" t="n">
-        <v>1144.7</v>
+        <v>1179.4</v>
       </c>
       <c r="F1338" t="n">
-        <v>11855.8</v>
+        <v>11890.5</v>
       </c>
       <c r="G1338" t="n">
         <v>5</v>
@@ -44614,10 +44614,10 @@
         <v>55.59999999999999</v>
       </c>
       <c r="E1339" t="n">
-        <v>1284.8</v>
+        <v>1347.2</v>
       </c>
       <c r="F1339" t="n">
-        <v>11975.8</v>
+        <v>12038.2</v>
       </c>
       <c r="G1339" t="n">
         <v>7</v>
@@ -44647,16 +44647,16 @@
         <v>50.59999999999999</v>
       </c>
       <c r="E1340" t="n">
-        <v>1244</v>
+        <v>1291.3</v>
       </c>
       <c r="F1340" t="n">
-        <v>11109.1</v>
+        <v>11156.4</v>
       </c>
       <c r="G1340" t="n">
         <v>8</v>
       </c>
       <c r="H1340" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1340" t="n">
         <v>4</v>
@@ -44680,10 +44680,10 @@
         <v>62.40000000000001</v>
       </c>
       <c r="E1341" t="n">
-        <v>1233.4</v>
+        <v>1262.8</v>
       </c>
       <c r="F1341" t="n">
-        <v>10898</v>
+        <v>10927.4</v>
       </c>
       <c r="G1341" t="n">
         <v>4</v>
@@ -44713,10 +44713,10 @@
         <v>81.90000000000001</v>
       </c>
       <c r="E1342" t="n">
-        <v>1355.9</v>
+        <v>1432.7</v>
       </c>
       <c r="F1342" t="n">
-        <v>12290.7</v>
+        <v>12367.5</v>
       </c>
       <c r="G1342" t="n">
         <v>2</v>
@@ -44746,10 +44746,10 @@
         <v>63.3</v>
       </c>
       <c r="E1343" t="n">
-        <v>1071.7</v>
+        <v>1100.9</v>
       </c>
       <c r="F1343" t="n">
-        <v>9905.6</v>
+        <v>9934.799999999999</v>
       </c>
       <c r="G1343" t="n">
         <v>3</v>
@@ -44779,10 +44779,10 @@
         <v>86</v>
       </c>
       <c r="E1344" t="n">
-        <v>1253.9</v>
+        <v>1302.8</v>
       </c>
       <c r="F1344" t="n">
-        <v>10858</v>
+        <v>10906.9</v>
       </c>
       <c r="G1344" t="n">
         <v>1</v>
@@ -44812,16 +44812,16 @@
         <v>58.1</v>
       </c>
       <c r="E1345" t="n">
-        <v>1237.3</v>
+        <v>1301.2</v>
       </c>
       <c r="F1345" t="n">
-        <v>8772.299999999999</v>
+        <v>8836.200000000001</v>
       </c>
       <c r="G1345" t="n">
         <v>6</v>
       </c>
       <c r="H1345" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1345" t="n">
         <v>8</v>
@@ -44845,10 +44845,10 @@
         <v>64.2</v>
       </c>
       <c r="E1346" t="n">
-        <v>1208.9</v>
+        <v>1243.6</v>
       </c>
       <c r="F1346" t="n">
-        <v>11920</v>
+        <v>11954.7</v>
       </c>
       <c r="G1346" t="n">
         <v>5</v>
@@ -44878,10 +44878,10 @@
         <v>88.7</v>
       </c>
       <c r="E1347" t="n">
-        <v>1373.5</v>
+        <v>1435.9</v>
       </c>
       <c r="F1347" t="n">
-        <v>12064.5</v>
+        <v>12126.9</v>
       </c>
       <c r="G1347" t="n">
         <v>1</v>
@@ -44911,10 +44911,10 @@
         <v>76.8</v>
       </c>
       <c r="E1348" t="n">
-        <v>1320.8</v>
+        <v>1368.1</v>
       </c>
       <c r="F1348" t="n">
-        <v>11185.9</v>
+        <v>11233.2</v>
       </c>
       <c r="G1348" t="n">
         <v>3</v>
@@ -44944,10 +44944,10 @@
         <v>45</v>
       </c>
       <c r="E1349" t="n">
-        <v>1278.4</v>
+        <v>1307.8</v>
       </c>
       <c r="F1349" t="n">
-        <v>10943</v>
+        <v>10972.4</v>
       </c>
       <c r="G1349" t="n">
         <v>8</v>
@@ -44956,7 +44956,7 @@
         <v>6</v>
       </c>
       <c r="I1349" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1350">
@@ -44977,10 +44977,10 @@
         <v>81.2</v>
       </c>
       <c r="E1350" t="n">
-        <v>1437.1</v>
+        <v>1513.9</v>
       </c>
       <c r="F1350" t="n">
-        <v>12371.9</v>
+        <v>12448.7</v>
       </c>
       <c r="G1350" t="n">
         <v>2</v>
@@ -45010,10 +45010,10 @@
         <v>63.7</v>
       </c>
       <c r="E1351" t="n">
-        <v>1135.4</v>
+        <v>1164.6</v>
       </c>
       <c r="F1351" t="n">
-        <v>9969.299999999999</v>
+        <v>9998.5</v>
       </c>
       <c r="G1351" t="n">
         <v>6</v>
@@ -45043,10 +45043,10 @@
         <v>67.7</v>
       </c>
       <c r="E1352" t="n">
-        <v>1321.6</v>
+        <v>1370.5</v>
       </c>
       <c r="F1352" t="n">
-        <v>10925.7</v>
+        <v>10974.6</v>
       </c>
       <c r="G1352" t="n">
         <v>4</v>
@@ -45055,7 +45055,7 @@
         <v>3</v>
       </c>
       <c r="I1352" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1353">
@@ -45076,10 +45076,10 @@
         <v>60.2</v>
       </c>
       <c r="E1353" t="n">
-        <v>1297.5</v>
+        <v>1361.4</v>
       </c>
       <c r="F1353" t="n">
-        <v>8832.5</v>
+        <v>8896.4</v>
       </c>
       <c r="G1353" t="n">
         <v>7</v>
@@ -45109,10 +45109,10 @@
         <v>88.09999999999999</v>
       </c>
       <c r="E1354" t="n">
-        <v>1297</v>
+        <v>1331.7</v>
       </c>
       <c r="F1354" t="n">
-        <v>12008.1</v>
+        <v>12042.8</v>
       </c>
       <c r="G1354" t="n">
         <v>3</v>
@@ -45142,10 +45142,10 @@
         <v>59.9</v>
       </c>
       <c r="E1355" t="n">
-        <v>1433.4</v>
+        <v>1495.8</v>
       </c>
       <c r="F1355" t="n">
-        <v>12124.4</v>
+        <v>12186.8</v>
       </c>
       <c r="G1355" t="n">
         <v>6</v>
@@ -45175,16 +45175,16 @@
         <v>70.2</v>
       </c>
       <c r="E1356" t="n">
-        <v>1391</v>
+        <v>1438.3</v>
       </c>
       <c r="F1356" t="n">
-        <v>11256.1</v>
+        <v>11303.4</v>
       </c>
       <c r="G1356" t="n">
         <v>4</v>
       </c>
       <c r="H1356" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1356" t="n">
         <v>4</v>
@@ -45208,10 +45208,10 @@
         <v>0</v>
       </c>
       <c r="E1357" t="n">
-        <v>1278.4</v>
+        <v>1307.8</v>
       </c>
       <c r="F1357" t="n">
-        <v>10943</v>
+        <v>10972.4</v>
       </c>
       <c r="G1357" t="n">
         <v>8</v>
@@ -45241,10 +45241,10 @@
         <v>94</v>
       </c>
       <c r="E1358" t="n">
-        <v>1531.1</v>
+        <v>1607.9</v>
       </c>
       <c r="F1358" t="n">
-        <v>12465.9</v>
+        <v>12542.7</v>
       </c>
       <c r="G1358" t="n">
         <v>1</v>
@@ -45274,10 +45274,10 @@
         <v>61.6</v>
       </c>
       <c r="E1359" t="n">
-        <v>1197</v>
+        <v>1226.2</v>
       </c>
       <c r="F1359" t="n">
-        <v>10030.9</v>
+        <v>10060.1</v>
       </c>
       <c r="G1359" t="n">
         <v>5</v>
@@ -45307,10 +45307,10 @@
         <v>58.6</v>
       </c>
       <c r="E1360" t="n">
-        <v>1380.2</v>
+        <v>1429.1</v>
       </c>
       <c r="F1360" t="n">
-        <v>10984.3</v>
+        <v>11033.2</v>
       </c>
       <c r="G1360" t="n">
         <v>7</v>
@@ -45340,16 +45340,16 @@
         <v>89.5</v>
       </c>
       <c r="E1361" t="n">
-        <v>1387</v>
+        <v>1450.9</v>
       </c>
       <c r="F1361" t="n">
-        <v>8922</v>
+        <v>8985.9</v>
       </c>
       <c r="G1361" t="n">
         <v>2</v>
       </c>
       <c r="H1361" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1361" t="n">
         <v>8</v>
@@ -45373,10 +45373,10 @@
         <v>66.7</v>
       </c>
       <c r="E1362" t="n">
-        <v>1363.7</v>
+        <v>1398.4</v>
       </c>
       <c r="F1362" t="n">
-        <v>12074.8</v>
+        <v>12109.5</v>
       </c>
       <c r="G1362" t="n">
         <v>4</v>
@@ -45406,10 +45406,10 @@
         <v>35.8</v>
       </c>
       <c r="E1363" t="n">
-        <v>1469.2</v>
+        <v>1531.6</v>
       </c>
       <c r="F1363" t="n">
-        <v>12160.2</v>
+        <v>12222.6</v>
       </c>
       <c r="G1363" t="n">
         <v>8</v>
@@ -45439,10 +45439,10 @@
         <v>59.2</v>
       </c>
       <c r="E1364" t="n">
-        <v>1450.2</v>
+        <v>1497.5</v>
       </c>
       <c r="F1364" t="n">
-        <v>11315.3</v>
+        <v>11362.6</v>
       </c>
       <c r="G1364" t="n">
         <v>6</v>
@@ -45472,10 +45472,10 @@
         <v>82.2</v>
       </c>
       <c r="E1365" t="n">
-        <v>1360.6</v>
+        <v>1390</v>
       </c>
       <c r="F1365" t="n">
-        <v>11025.2</v>
+        <v>11054.6</v>
       </c>
       <c r="G1365" t="n">
         <v>2</v>
@@ -45505,10 +45505,10 @@
         <v>63</v>
       </c>
       <c r="E1366" t="n">
-        <v>1594.1</v>
+        <v>1670.9</v>
       </c>
       <c r="F1366" t="n">
-        <v>12528.9</v>
+        <v>12605.7</v>
       </c>
       <c r="G1366" t="n">
         <v>5</v>
@@ -45538,10 +45538,10 @@
         <v>56.6</v>
       </c>
       <c r="E1367" t="n">
-        <v>1253.6</v>
+        <v>1282.8</v>
       </c>
       <c r="F1367" t="n">
-        <v>10087.5</v>
+        <v>10116.7</v>
       </c>
       <c r="G1367" t="n">
         <v>7</v>
@@ -45571,10 +45571,10 @@
         <v>78.59999999999999</v>
       </c>
       <c r="E1368" t="n">
-        <v>1458.8</v>
+        <v>1507.7</v>
       </c>
       <c r="F1368" t="n">
-        <v>11062.9</v>
+        <v>11111.8</v>
       </c>
       <c r="G1368" t="n">
         <v>3</v>
@@ -45604,10 +45604,10 @@
         <v>87.3</v>
       </c>
       <c r="E1369" t="n">
-        <v>1474.3</v>
+        <v>1538.2</v>
       </c>
       <c r="F1369" t="n">
-        <v>9009.299999999999</v>
+        <v>9073.200000000001</v>
       </c>
       <c r="G1369" t="n">
         <v>1</v>
@@ -45637,10 +45637,10 @@
         <v>70.8</v>
       </c>
       <c r="E1370" t="n">
-        <v>1434.5</v>
+        <v>1469.2</v>
       </c>
       <c r="F1370" t="n">
-        <v>12145.6</v>
+        <v>12180.3</v>
       </c>
       <c r="G1370" t="n">
         <v>4</v>
@@ -45670,10 +45670,10 @@
         <v>76.5</v>
       </c>
       <c r="E1371" t="n">
-        <v>1545.7</v>
+        <v>1608.1</v>
       </c>
       <c r="F1371" t="n">
-        <v>12236.7</v>
+        <v>12299.1</v>
       </c>
       <c r="G1371" t="n">
         <v>2</v>
@@ -45703,16 +45703,16 @@
         <v>75.2</v>
       </c>
       <c r="E1372" t="n">
-        <v>1525.4</v>
+        <v>1572.7</v>
       </c>
       <c r="F1372" t="n">
-        <v>11390.5</v>
+        <v>11437.8</v>
       </c>
       <c r="G1372" t="n">
         <v>3</v>
       </c>
       <c r="H1372" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1372" t="n">
         <v>4</v>
@@ -45736,10 +45736,10 @@
         <v>46.7</v>
       </c>
       <c r="E1373" t="n">
-        <v>1407.3</v>
+        <v>1436.7</v>
       </c>
       <c r="F1373" t="n">
-        <v>11071.9</v>
+        <v>11101.3</v>
       </c>
       <c r="G1373" t="n">
         <v>8</v>
@@ -45769,10 +45769,10 @@
         <v>79.40000000000001</v>
       </c>
       <c r="E1374" t="n">
-        <v>1673.5</v>
+        <v>1750.3</v>
       </c>
       <c r="F1374" t="n">
-        <v>12608.3</v>
+        <v>12685.1</v>
       </c>
       <c r="G1374" t="n">
         <v>1</v>
@@ -45802,10 +45802,10 @@
         <v>56.59999999999999</v>
       </c>
       <c r="E1375" t="n">
-        <v>1310.2</v>
+        <v>1339.4</v>
       </c>
       <c r="F1375" t="n">
-        <v>10144.1</v>
+        <v>10173.3</v>
       </c>
       <c r="G1375" t="n">
         <v>6</v>
@@ -45835,16 +45835,16 @@
         <v>65.2</v>
       </c>
       <c r="E1376" t="n">
-        <v>1524</v>
+        <v>1572.9</v>
       </c>
       <c r="F1376" t="n">
-        <v>11128.1</v>
+        <v>11177</v>
       </c>
       <c r="G1376" t="n">
         <v>5</v>
       </c>
       <c r="H1376" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1376" t="n">
         <v>5</v>
@@ -45868,10 +45868,10 @@
         <v>54.8</v>
       </c>
       <c r="E1377" t="n">
-        <v>1529.1</v>
+        <v>1593</v>
       </c>
       <c r="F1377" t="n">
-        <v>9064.1</v>
+        <v>9128</v>
       </c>
       <c r="G1377" t="n">
         <v>7</v>
@@ -45901,10 +45901,10 @@
         <v>93.8</v>
       </c>
       <c r="E1378" t="n">
-        <v>1528.3</v>
+        <v>1563</v>
       </c>
       <c r="F1378" t="n">
-        <v>12239.4</v>
+        <v>12274.1</v>
       </c>
       <c r="G1378" t="n">
         <v>2</v>
@@ -45934,16 +45934,16 @@
         <v>65.2</v>
       </c>
       <c r="E1379" t="n">
-        <v>1610.9</v>
+        <v>1673.3</v>
       </c>
       <c r="F1379" t="n">
-        <v>12301.9</v>
+        <v>12364.3</v>
       </c>
       <c r="G1379" t="n">
         <v>7</v>
       </c>
       <c r="H1379" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1379" t="n">
         <v>2</v>
@@ -45967,16 +45967,16 @@
         <v>97.59999999999999</v>
       </c>
       <c r="E1380" t="n">
-        <v>1623</v>
+        <v>1670.3</v>
       </c>
       <c r="F1380" t="n">
-        <v>11488.1</v>
+        <v>11535.4</v>
       </c>
       <c r="G1380" t="n">
         <v>1</v>
       </c>
       <c r="H1380" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1380" t="n">
         <v>4</v>
@@ -46000,10 +46000,10 @@
         <v>63.3</v>
       </c>
       <c r="E1381" t="n">
-        <v>1470.6</v>
+        <v>1500</v>
       </c>
       <c r="F1381" t="n">
-        <v>11135.2</v>
+        <v>11164.6</v>
       </c>
       <c r="G1381" t="n">
         <v>8</v>
@@ -46033,10 +46033,10 @@
         <v>79.3</v>
       </c>
       <c r="E1382" t="n">
-        <v>1752.8</v>
+        <v>1829.6</v>
       </c>
       <c r="F1382" t="n">
-        <v>12687.6</v>
+        <v>12764.4</v>
       </c>
       <c r="G1382" t="n">
         <v>5</v>
@@ -46066,10 +46066,10 @@
         <v>81.7</v>
       </c>
       <c r="E1383" t="n">
-        <v>1391.9</v>
+        <v>1421.1</v>
       </c>
       <c r="F1383" t="n">
-        <v>10225.8</v>
+        <v>10255</v>
       </c>
       <c r="G1383" t="n">
         <v>4</v>
@@ -46099,10 +46099,10 @@
         <v>67.40000000000001</v>
       </c>
       <c r="E1384" t="n">
-        <v>1591.4</v>
+        <v>1640.3</v>
       </c>
       <c r="F1384" t="n">
-        <v>11195.5</v>
+        <v>11244.4</v>
       </c>
       <c r="G1384" t="n">
         <v>6</v>
@@ -46132,16 +46132,16 @@
         <v>82.59999999999999</v>
       </c>
       <c r="E1385" t="n">
-        <v>1611.7</v>
+        <v>1675.6</v>
       </c>
       <c r="F1385" t="n">
-        <v>9146.700000000001</v>
+        <v>9210.6</v>
       </c>
       <c r="G1385" t="n">
         <v>3</v>
       </c>
       <c r="H1385" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1385" t="n">
         <v>8</v>
@@ -46165,10 +46165,10 @@
         <v>100.5</v>
       </c>
       <c r="E1386" t="n">
-        <v>1628.8</v>
+        <v>1663.5</v>
       </c>
       <c r="F1386" t="n">
-        <v>12339.9</v>
+        <v>12374.6</v>
       </c>
       <c r="G1386" t="n">
         <v>1</v>
@@ -46198,10 +46198,10 @@
         <v>80.3</v>
       </c>
       <c r="E1387" t="n">
-        <v>1691.2</v>
+        <v>1753.6</v>
       </c>
       <c r="F1387" t="n">
-        <v>12382.2</v>
+        <v>12444.6</v>
       </c>
       <c r="G1387" t="n">
         <v>2</v>
@@ -46231,16 +46231,16 @@
         <v>60.3</v>
       </c>
       <c r="E1388" t="n">
-        <v>1683.3</v>
+        <v>1730.6</v>
       </c>
       <c r="F1388" t="n">
-        <v>11548.4</v>
+        <v>11595.7</v>
       </c>
       <c r="G1388" t="n">
         <v>6</v>
       </c>
       <c r="H1388" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1388" t="n">
         <v>4</v>
@@ -46264,10 +46264,10 @@
         <v>67.59999999999999</v>
       </c>
       <c r="E1389" t="n">
-        <v>1538.2</v>
+        <v>1567.6</v>
       </c>
       <c r="F1389" t="n">
-        <v>11202.8</v>
+        <v>11232.2</v>
       </c>
       <c r="G1389" t="n">
         <v>4</v>
@@ -46297,10 +46297,10 @@
         <v>70.2</v>
       </c>
       <c r="E1390" t="n">
-        <v>1823</v>
+        <v>1899.8</v>
       </c>
       <c r="F1390" t="n">
-        <v>12757.8</v>
+        <v>12834.6</v>
       </c>
       <c r="G1390" t="n">
         <v>3</v>
@@ -46330,10 +46330,10 @@
         <v>61.2</v>
       </c>
       <c r="E1391" t="n">
-        <v>1453.1</v>
+        <v>1482.3</v>
       </c>
       <c r="F1391" t="n">
-        <v>10287</v>
+        <v>10316.2</v>
       </c>
       <c r="G1391" t="n">
         <v>5</v>
@@ -46363,10 +46363,10 @@
         <v>50.8</v>
       </c>
       <c r="E1392" t="n">
-        <v>1642.2</v>
+        <v>1691.1</v>
       </c>
       <c r="F1392" t="n">
-        <v>11246.3</v>
+        <v>11295.2</v>
       </c>
       <c r="G1392" t="n">
         <v>8</v>
@@ -46396,16 +46396,16 @@
         <v>58.9</v>
       </c>
       <c r="E1393" t="n">
-        <v>1670.6</v>
+        <v>1734.5</v>
       </c>
       <c r="F1393" t="n">
-        <v>9205.6</v>
+        <v>9269.5</v>
       </c>
       <c r="G1393" t="n">
         <v>7</v>
       </c>
       <c r="H1393" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1393" t="n">
         <v>8</v>
@@ -46429,10 +46429,10 @@
         <v>92</v>
       </c>
       <c r="E1394" t="n">
-        <v>1720.8</v>
+        <v>1755.5</v>
       </c>
       <c r="F1394" t="n">
-        <v>12431.9</v>
+        <v>12466.6</v>
       </c>
       <c r="G1394" t="n">
         <v>2</v>
@@ -46462,10 +46462,10 @@
         <v>77.2</v>
       </c>
       <c r="E1395" t="n">
-        <v>1768.4</v>
+        <v>1830.8</v>
       </c>
       <c r="F1395" t="n">
-        <v>12459.4</v>
+        <v>12521.8</v>
       </c>
       <c r="G1395" t="n">
         <v>4</v>
@@ -46495,10 +46495,10 @@
         <v>80.3</v>
       </c>
       <c r="E1396" t="n">
-        <v>1763.6</v>
+        <v>1810.9</v>
       </c>
       <c r="F1396" t="n">
-        <v>11628.7</v>
+        <v>11676</v>
       </c>
       <c r="G1396" t="n">
         <v>3</v>
@@ -46528,10 +46528,10 @@
         <v>50.6</v>
       </c>
       <c r="E1397" t="n">
-        <v>1588.8</v>
+        <v>1618.2</v>
       </c>
       <c r="F1397" t="n">
-        <v>11253.4</v>
+        <v>11282.8</v>
       </c>
       <c r="G1397" t="n">
         <v>7</v>
@@ -46561,10 +46561,10 @@
         <v>76.7</v>
       </c>
       <c r="E1398" t="n">
-        <v>1899.7</v>
+        <v>1976.5</v>
       </c>
       <c r="F1398" t="n">
-        <v>12834.5</v>
+        <v>12911.3</v>
       </c>
       <c r="G1398" t="n">
         <v>5</v>
@@ -46594,10 +46594,10 @@
         <v>48.7</v>
       </c>
       <c r="E1399" t="n">
-        <v>1501.8</v>
+        <v>1531</v>
       </c>
       <c r="F1399" t="n">
-        <v>10335.7</v>
+        <v>10364.9</v>
       </c>
       <c r="G1399" t="n">
         <v>8</v>
@@ -46627,10 +46627,10 @@
         <v>92.5</v>
       </c>
       <c r="E1400" t="n">
-        <v>1734.7</v>
+        <v>1783.6</v>
       </c>
       <c r="F1400" t="n">
-        <v>11338.8</v>
+        <v>11387.7</v>
       </c>
       <c r="G1400" t="n">
         <v>1</v>
@@ -46660,10 +46660,10 @@
         <v>73.10000000000001</v>
       </c>
       <c r="E1401" t="n">
-        <v>1743.7</v>
+        <v>1807.6</v>
       </c>
       <c r="F1401" t="n">
-        <v>9278.700000000001</v>
+        <v>9342.6</v>
       </c>
       <c r="G1401" t="n">
         <v>6</v>
@@ -46693,10 +46693,10 @@
         <v>75.59999999999999</v>
       </c>
       <c r="E1402" t="n">
-        <v>1796.4</v>
+        <v>1831.1</v>
       </c>
       <c r="F1402" t="n">
-        <v>12507.5</v>
+        <v>12542.2</v>
       </c>
       <c r="G1402" t="n">
         <v>3</v>
@@ -46726,10 +46726,10 @@
         <v>84.09999999999999</v>
       </c>
       <c r="E1403" t="n">
-        <v>1852.5</v>
+        <v>1914.9</v>
       </c>
       <c r="F1403" t="n">
-        <v>12543.5</v>
+        <v>12605.9</v>
       </c>
       <c r="G1403" t="n">
         <v>1</v>
@@ -46759,16 +46759,16 @@
         <v>59.3</v>
       </c>
       <c r="E1404" t="n">
-        <v>1822.9</v>
+        <v>1870.2</v>
       </c>
       <c r="F1404" t="n">
-        <v>11688</v>
+        <v>11735.3</v>
       </c>
       <c r="G1404" t="n">
         <v>8</v>
       </c>
       <c r="H1404" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1404" t="n">
         <v>4</v>
@@ -46792,10 +46792,10 @@
         <v>71.5</v>
       </c>
       <c r="E1405" t="n">
-        <v>1660.3</v>
+        <v>1689.7</v>
       </c>
       <c r="F1405" t="n">
-        <v>11324.9</v>
+        <v>11354.3</v>
       </c>
       <c r="G1405" t="n">
         <v>6</v>
@@ -46825,10 +46825,10 @@
         <v>75.39999999999999</v>
       </c>
       <c r="E1406" t="n">
-        <v>1975.1</v>
+        <v>2051.9</v>
       </c>
       <c r="F1406" t="n">
-        <v>12909.9</v>
+        <v>12986.7</v>
       </c>
       <c r="G1406" t="n">
         <v>4</v>
@@ -46858,10 +46858,10 @@
         <v>62.7</v>
       </c>
       <c r="E1407" t="n">
-        <v>1564.5</v>
+        <v>1593.7</v>
       </c>
       <c r="F1407" t="n">
-        <v>10398.4</v>
+        <v>10427.6</v>
       </c>
       <c r="G1407" t="n">
         <v>7</v>
@@ -46891,10 +46891,10 @@
         <v>72</v>
       </c>
       <c r="E1408" t="n">
-        <v>1806.7</v>
+        <v>1855.6</v>
       </c>
       <c r="F1408" t="n">
-        <v>11410.8</v>
+        <v>11459.7</v>
       </c>
       <c r="G1408" t="n">
         <v>5</v>
@@ -46924,16 +46924,16 @@
         <v>79.09999999999999</v>
       </c>
       <c r="E1409" t="n">
-        <v>1822.8</v>
+        <v>1886.7</v>
       </c>
       <c r="F1409" t="n">
-        <v>9357.799999999999</v>
+        <v>9421.700000000001</v>
       </c>
       <c r="G1409" t="n">
         <v>2</v>
       </c>
       <c r="H1409" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1409" t="n">
         <v>8</v>
@@ -46957,10 +46957,10 @@
         <v>73.2</v>
       </c>
       <c r="E1410" t="n">
-        <v>1869.6</v>
+        <v>1904.3</v>
       </c>
       <c r="F1410" t="n">
-        <v>12580.7</v>
+        <v>12615.4</v>
       </c>
       <c r="G1410" t="n">
         <v>2</v>
@@ -46990,10 +46990,10 @@
         <v>62.7</v>
       </c>
       <c r="E1411" t="n">
-        <v>1915.2</v>
+        <v>1977.6</v>
       </c>
       <c r="F1411" t="n">
-        <v>12606.2</v>
+        <v>12668.6</v>
       </c>
       <c r="G1411" t="n">
         <v>5</v>
@@ -47023,10 +47023,10 @@
         <v>49.2</v>
       </c>
       <c r="E1412" t="n">
-        <v>1872.1</v>
+        <v>1919.4</v>
       </c>
       <c r="F1412" t="n">
-        <v>11737.2</v>
+        <v>11784.5</v>
       </c>
       <c r="G1412" t="n">
         <v>6</v>
@@ -47056,10 +47056,10 @@
         <v>43.9</v>
       </c>
       <c r="E1413" t="n">
-        <v>1704.2</v>
+        <v>1733.6</v>
       </c>
       <c r="F1413" t="n">
-        <v>11368.8</v>
+        <v>11398.2</v>
       </c>
       <c r="G1413" t="n">
         <v>7</v>
@@ -47089,10 +47089,10 @@
         <v>71.2</v>
       </c>
       <c r="E1414" t="n">
-        <v>2046.3</v>
+        <v>2123.1</v>
       </c>
       <c r="F1414" t="n">
-        <v>12981.1</v>
+        <v>13057.9</v>
       </c>
       <c r="G1414" t="n">
         <v>3</v>
@@ -47122,10 +47122,10 @@
         <v>64.09999999999999</v>
       </c>
       <c r="E1415" t="n">
-        <v>1628.6</v>
+        <v>1657.8</v>
       </c>
       <c r="F1415" t="n">
-        <v>10462.5</v>
+        <v>10491.7</v>
       </c>
       <c r="G1415" t="n">
         <v>4</v>
@@ -47155,10 +47155,10 @@
         <v>42.9</v>
       </c>
       <c r="E1416" t="n">
-        <v>1849.6</v>
+        <v>1898.5</v>
       </c>
       <c r="F1416" t="n">
-        <v>11453.7</v>
+        <v>11502.6</v>
       </c>
       <c r="G1416" t="n">
         <v>8</v>
@@ -47188,10 +47188,10 @@
         <v>73.8</v>
       </c>
       <c r="E1417" t="n">
-        <v>1896.6</v>
+        <v>1960.5</v>
       </c>
       <c r="F1417" t="n">
-        <v>9431.6</v>
+        <v>9495.5</v>
       </c>
       <c r="G1417" t="n">
         <v>1</v>
@@ -47221,10 +47221,10 @@
         <v>79.3</v>
       </c>
       <c r="E1418" t="n">
-        <v>1948.9</v>
+        <v>1983.6</v>
       </c>
       <c r="F1418" t="n">
-        <v>12660</v>
+        <v>12694.7</v>
       </c>
       <c r="G1418" t="n">
         <v>1</v>
@@ -47254,10 +47254,10 @@
         <v>62.3</v>
       </c>
       <c r="E1419" t="n">
-        <v>1977.5</v>
+        <v>2039.9</v>
       </c>
       <c r="F1419" t="n">
-        <v>12668.5</v>
+        <v>12730.9</v>
       </c>
       <c r="G1419" t="n">
         <v>4</v>
@@ -47287,10 +47287,10 @@
         <v>50.4</v>
       </c>
       <c r="E1420" t="n">
-        <v>1922.5</v>
+        <v>1969.8</v>
       </c>
       <c r="F1420" t="n">
-        <v>11787.6</v>
+        <v>11834.9</v>
       </c>
       <c r="G1420" t="n">
         <v>7</v>
@@ -47320,10 +47320,10 @@
         <v>48.8</v>
       </c>
       <c r="E1421" t="n">
-        <v>1753</v>
+        <v>1782.4</v>
       </c>
       <c r="F1421" t="n">
-        <v>11417.6</v>
+        <v>11447</v>
       </c>
       <c r="G1421" t="n">
         <v>8</v>
@@ -47353,10 +47353,10 @@
         <v>75</v>
       </c>
       <c r="E1422" t="n">
-        <v>2121.3</v>
+        <v>2198.1</v>
       </c>
       <c r="F1422" t="n">
-        <v>13056.1</v>
+        <v>13132.9</v>
       </c>
       <c r="G1422" t="n">
         <v>2</v>
@@ -47386,10 +47386,10 @@
         <v>64.5</v>
       </c>
       <c r="E1423" t="n">
-        <v>1693.1</v>
+        <v>1722.3</v>
       </c>
       <c r="F1423" t="n">
-        <v>10527</v>
+        <v>10556.2</v>
       </c>
       <c r="G1423" t="n">
         <v>3</v>
@@ -47419,10 +47419,10 @@
         <v>59.7</v>
       </c>
       <c r="E1424" t="n">
-        <v>1909.3</v>
+        <v>1958.2</v>
       </c>
       <c r="F1424" t="n">
-        <v>11513.4</v>
+        <v>11562.3</v>
       </c>
       <c r="G1424" t="n">
         <v>5</v>
@@ -47452,10 +47452,10 @@
         <v>57.7</v>
       </c>
       <c r="E1425" t="n">
-        <v>1954.3</v>
+        <v>2018.2</v>
       </c>
       <c r="F1425" t="n">
-        <v>9489.299999999999</v>
+        <v>9553.200000000001</v>
       </c>
       <c r="G1425" t="n">
         <v>6</v>
@@ -47485,10 +47485,10 @@
         <v>86.3</v>
       </c>
       <c r="E1426" t="n">
-        <v>2035.2</v>
+        <v>2069.9</v>
       </c>
       <c r="F1426" t="n">
-        <v>12746.3</v>
+        <v>12781</v>
       </c>
       <c r="G1426" t="n">
         <v>2</v>
@@ -47497,7 +47497,7 @@
         <v>4</v>
       </c>
       <c r="I1426" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1427">
@@ -47518,10 +47518,10 @@
         <v>75.59999999999999</v>
       </c>
       <c r="E1427" t="n">
-        <v>2053.1</v>
+        <v>2115.5</v>
       </c>
       <c r="F1427" t="n">
-        <v>12744.1</v>
+        <v>12806.5</v>
       </c>
       <c r="G1427" t="n">
         <v>3</v>
@@ -47530,7 +47530,7 @@
         <v>2</v>
       </c>
       <c r="I1427" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1428">
@@ -47551,10 +47551,10 @@
         <v>50.9</v>
       </c>
       <c r="E1428" t="n">
-        <v>1973.4</v>
+        <v>2020.7</v>
       </c>
       <c r="F1428" t="n">
-        <v>11838.5</v>
+        <v>11885.8</v>
       </c>
       <c r="G1428" t="n">
         <v>8</v>
@@ -47584,10 +47584,10 @@
         <v>65.3</v>
       </c>
       <c r="E1429" t="n">
-        <v>1818.3</v>
+        <v>1847.7</v>
       </c>
       <c r="F1429" t="n">
-        <v>11482.9</v>
+        <v>11512.3</v>
       </c>
       <c r="G1429" t="n">
         <v>4</v>
@@ -47617,10 +47617,10 @@
         <v>58.4</v>
       </c>
       <c r="E1430" t="n">
-        <v>2179.7</v>
+        <v>2256.5</v>
       </c>
       <c r="F1430" t="n">
-        <v>13114.5</v>
+        <v>13191.3</v>
       </c>
       <c r="G1430" t="n">
         <v>6</v>
@@ -47650,10 +47650,10 @@
         <v>58.6</v>
       </c>
       <c r="E1431" t="n">
-        <v>1751.7</v>
+        <v>1780.9</v>
       </c>
       <c r="F1431" t="n">
-        <v>10585.6</v>
+        <v>10614.8</v>
       </c>
       <c r="G1431" t="n">
         <v>5</v>
@@ -47683,10 +47683,10 @@
         <v>55.3</v>
       </c>
       <c r="E1432" t="n">
-        <v>1964.6</v>
+        <v>2013.5</v>
       </c>
       <c r="F1432" t="n">
-        <v>11568.7</v>
+        <v>11617.6</v>
       </c>
       <c r="G1432" t="n">
         <v>7</v>
@@ -47716,10 +47716,10 @@
         <v>96</v>
       </c>
       <c r="E1433" t="n">
-        <v>2050.3</v>
+        <v>2114.2</v>
       </c>
       <c r="F1433" t="n">
-        <v>9585.299999999999</v>
+        <v>9649.200000000001</v>
       </c>
       <c r="G1433" t="n">
         <v>1</v>
@@ -47749,19 +47749,19 @@
         <v>84.5</v>
       </c>
       <c r="E1434" t="n">
-        <v>2119.7</v>
+        <v>2154.4</v>
       </c>
       <c r="F1434" t="n">
-        <v>12830.8</v>
+        <v>12865.5</v>
       </c>
       <c r="G1434" t="n">
         <v>1</v>
       </c>
       <c r="H1434" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1434" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1435">
@@ -47782,10 +47782,10 @@
         <v>66.59999999999999</v>
       </c>
       <c r="E1435" t="n">
-        <v>2119.7</v>
+        <v>2182.1</v>
       </c>
       <c r="F1435" t="n">
-        <v>12810.7</v>
+        <v>12873.1</v>
       </c>
       <c r="G1435" t="n">
         <v>4</v>
@@ -47794,7 +47794,7 @@
         <v>3</v>
       </c>
       <c r="I1435" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1436">
@@ -47815,10 +47815,10 @@
         <v>60.1</v>
       </c>
       <c r="E1436" t="n">
-        <v>2033.5</v>
+        <v>2080.8</v>
       </c>
       <c r="F1436" t="n">
-        <v>11898.6</v>
+        <v>11945.9</v>
       </c>
       <c r="G1436" t="n">
         <v>6</v>
@@ -47848,10 +47848,10 @@
         <v>74.09999999999999</v>
       </c>
       <c r="E1437" t="n">
-        <v>1892.4</v>
+        <v>1921.8</v>
       </c>
       <c r="F1437" t="n">
-        <v>11557</v>
+        <v>11586.4</v>
       </c>
       <c r="G1437" t="n">
         <v>3</v>
@@ -47881,10 +47881,10 @@
         <v>57.4</v>
       </c>
       <c r="E1438" t="n">
-        <v>2237.1</v>
+        <v>2313.9</v>
       </c>
       <c r="F1438" t="n">
-        <v>13171.9</v>
+        <v>13248.7</v>
       </c>
       <c r="G1438" t="n">
         <v>7</v>
@@ -47914,10 +47914,10 @@
         <v>0</v>
       </c>
       <c r="E1439" t="n">
-        <v>1751.7</v>
+        <v>1780.9</v>
       </c>
       <c r="F1439" t="n">
-        <v>10585.6</v>
+        <v>10614.8</v>
       </c>
       <c r="G1439" t="n">
         <v>8</v>
@@ -47947,10 +47947,10 @@
         <v>65.90000000000001</v>
       </c>
       <c r="E1440" t="n">
-        <v>2030.5</v>
+        <v>2079.4</v>
       </c>
       <c r="F1440" t="n">
-        <v>11634.6</v>
+        <v>11683.5</v>
       </c>
       <c r="G1440" t="n">
         <v>5</v>
@@ -47980,10 +47980,10 @@
         <v>76</v>
       </c>
       <c r="E1441" t="n">
-        <v>2126.3</v>
+        <v>2190.2</v>
       </c>
       <c r="F1441" t="n">
-        <v>9661.299999999999</v>
+        <v>9725.200000000001</v>
       </c>
       <c r="G1441" t="n">
         <v>2</v>
@@ -48013,10 +48013,10 @@
         <v>73.09999999999999</v>
       </c>
       <c r="E1442" t="n">
-        <v>2192.8</v>
+        <v>2227.5</v>
       </c>
       <c r="F1442" t="n">
-        <v>12903.9</v>
+        <v>12938.6</v>
       </c>
       <c r="G1442" t="n">
         <v>6</v>
@@ -48025,7 +48025,7 @@
         <v>4</v>
       </c>
       <c r="I1442" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1443">
@@ -48046,10 +48046,10 @@
         <v>92.90000000000001</v>
       </c>
       <c r="E1443" t="n">
-        <v>2212.6</v>
+        <v>2275</v>
       </c>
       <c r="F1443" t="n">
-        <v>12903.6</v>
+        <v>12966</v>
       </c>
       <c r="G1443" t="n">
         <v>2</v>
@@ -48058,7 +48058,7 @@
         <v>3</v>
       </c>
       <c r="I1443" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1444">
@@ -48079,10 +48079,10 @@
         <v>51.6</v>
       </c>
       <c r="E1444" t="n">
-        <v>2085.1</v>
+        <v>2132.4</v>
       </c>
       <c r="F1444" t="n">
-        <v>11950.2</v>
+        <v>11997.5</v>
       </c>
       <c r="G1444" t="n">
         <v>8</v>
@@ -48112,10 +48112,10 @@
         <v>62.1</v>
       </c>
       <c r="E1445" t="n">
-        <v>1954.5</v>
+        <v>1983.9</v>
       </c>
       <c r="F1445" t="n">
-        <v>11619.1</v>
+        <v>11648.5</v>
       </c>
       <c r="G1445" t="n">
         <v>7</v>
@@ -48145,10 +48145,10 @@
         <v>86.7</v>
       </c>
       <c r="E1446" t="n">
-        <v>2323.8</v>
+        <v>2400.6</v>
       </c>
       <c r="F1446" t="n">
-        <v>13258.6</v>
+        <v>13335.4</v>
       </c>
       <c r="G1446" t="n">
         <v>4</v>
@@ -48178,10 +48178,10 @@
         <v>88.2</v>
       </c>
       <c r="E1447" t="n">
-        <v>1839.9</v>
+        <v>1869.1</v>
       </c>
       <c r="F1447" t="n">
-        <v>10673.8</v>
+        <v>10703</v>
       </c>
       <c r="G1447" t="n">
         <v>3</v>
@@ -48211,10 +48211,10 @@
         <v>73.3</v>
       </c>
       <c r="E1448" t="n">
-        <v>2103.8</v>
+        <v>2152.7</v>
       </c>
       <c r="F1448" t="n">
-        <v>11707.9</v>
+        <v>11756.8</v>
       </c>
       <c r="G1448" t="n">
         <v>5</v>
@@ -48244,10 +48244,10 @@
         <v>100.9</v>
       </c>
       <c r="E1449" t="n">
-        <v>2227.2</v>
+        <v>2291.1</v>
       </c>
       <c r="F1449" t="n">
-        <v>9762.200000000001</v>
+        <v>9826.1</v>
       </c>
       <c r="G1449" t="n">
         <v>1</v>
@@ -48277,19 +48277,19 @@
         <v>82.5</v>
       </c>
       <c r="E1450" t="n">
-        <v>2275.3</v>
+        <v>2310</v>
       </c>
       <c r="F1450" t="n">
-        <v>12986.4</v>
+        <v>13021.1</v>
       </c>
       <c r="G1450" t="n">
         <v>3</v>
       </c>
       <c r="H1450" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1450" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1451">
@@ -48310,10 +48310,10 @@
         <v>73.5</v>
       </c>
       <c r="E1451" t="n">
-        <v>2286.1</v>
+        <v>2348.5</v>
       </c>
       <c r="F1451" t="n">
-        <v>12977.1</v>
+        <v>13039.5</v>
       </c>
       <c r="G1451" t="n">
         <v>4</v>
@@ -48322,7 +48322,7 @@
         <v>2</v>
       </c>
       <c r="I1451" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1452">
@@ -48343,10 +48343,10 @@
         <v>114.5</v>
       </c>
       <c r="E1452" t="n">
-        <v>2199.6</v>
+        <v>2246.9</v>
       </c>
       <c r="F1452" t="n">
-        <v>12064.7</v>
+        <v>12112</v>
       </c>
       <c r="G1452" t="n">
         <v>1</v>
@@ -48376,10 +48376,10 @@
         <v>85.90000000000001</v>
       </c>
       <c r="E1453" t="n">
-        <v>2040.4</v>
+        <v>2069.8</v>
       </c>
       <c r="F1453" t="n">
-        <v>11705</v>
+        <v>11734.4</v>
       </c>
       <c r="G1453" t="n">
         <v>2</v>
@@ -48409,10 +48409,10 @@
         <v>48.6</v>
       </c>
       <c r="E1454" t="n">
-        <v>2372.4</v>
+        <v>2449.2</v>
       </c>
       <c r="F1454" t="n">
-        <v>13307.2</v>
+        <v>13384</v>
       </c>
       <c r="G1454" t="n">
         <v>6</v>
@@ -48442,10 +48442,10 @@
         <v>52.8</v>
       </c>
       <c r="E1455" t="n">
-        <v>1892.7</v>
+        <v>1921.9</v>
       </c>
       <c r="F1455" t="n">
-        <v>10726.6</v>
+        <v>10755.8</v>
       </c>
       <c r="G1455" t="n">
         <v>5</v>
@@ -48475,10 +48475,10 @@
         <v>47.9</v>
       </c>
       <c r="E1456" t="n">
-        <v>2151.7</v>
+        <v>2200.6</v>
       </c>
       <c r="F1456" t="n">
-        <v>11755.8</v>
+        <v>11804.7</v>
       </c>
       <c r="G1456" t="n">
         <v>7</v>
@@ -48508,16 +48508,16 @@
         <v>43.3</v>
       </c>
       <c r="E1457" t="n">
-        <v>2270.5</v>
+        <v>2334.4</v>
       </c>
       <c r="F1457" t="n">
-        <v>9805.5</v>
+        <v>9869.4</v>
       </c>
       <c r="G1457" t="n">
         <v>8</v>
       </c>
       <c r="H1457" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1457" t="n">
         <v>8</v>
@@ -48541,10 +48541,10 @@
         <v>66.5</v>
       </c>
       <c r="E1458" t="n">
-        <v>2341.8</v>
+        <v>2376.5</v>
       </c>
       <c r="F1458" t="n">
-        <v>13052.9</v>
+        <v>13087.6</v>
       </c>
       <c r="G1458" t="n">
         <v>5</v>
@@ -48553,7 +48553,7 @@
         <v>4</v>
       </c>
       <c r="I1458" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1459">
@@ -48574,10 +48574,10 @@
         <v>65.5</v>
       </c>
       <c r="E1459" t="n">
-        <v>2351.6</v>
+        <v>2414</v>
       </c>
       <c r="F1459" t="n">
-        <v>13042.6</v>
+        <v>13105</v>
       </c>
       <c r="G1459" t="n">
         <v>7</v>
@@ -48586,7 +48586,7 @@
         <v>3</v>
       </c>
       <c r="I1459" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1460">
@@ -48607,10 +48607,10 @@
         <v>83.90000000000001</v>
       </c>
       <c r="E1460" t="n">
-        <v>2283.5</v>
+        <v>2330.8</v>
       </c>
       <c r="F1460" t="n">
-        <v>12148.6</v>
+        <v>12195.9</v>
       </c>
       <c r="G1460" t="n">
         <v>3</v>
@@ -48640,10 +48640,10 @@
         <v>66.40000000000001</v>
       </c>
       <c r="E1461" t="n">
-        <v>2106.8</v>
+        <v>2136.2</v>
       </c>
       <c r="F1461" t="n">
-        <v>11771.4</v>
+        <v>11800.8</v>
       </c>
       <c r="G1461" t="n">
         <v>6</v>
@@ -48673,10 +48673,10 @@
         <v>107</v>
       </c>
       <c r="E1462" t="n">
-        <v>2479.4</v>
+        <v>2556.2</v>
       </c>
       <c r="F1462" t="n">
-        <v>13414.2</v>
+        <v>13491</v>
       </c>
       <c r="G1462" t="n">
         <v>1</v>
@@ -48706,10 +48706,10 @@
         <v>46.5</v>
       </c>
       <c r="E1463" t="n">
-        <v>1939.2</v>
+        <v>1968.4</v>
       </c>
       <c r="F1463" t="n">
-        <v>10773.1</v>
+        <v>10802.3</v>
       </c>
       <c r="G1463" t="n">
         <v>8</v>
@@ -48739,10 +48739,10 @@
         <v>67.40000000000001</v>
       </c>
       <c r="E1464" t="n">
-        <v>2219.1</v>
+        <v>2268</v>
       </c>
       <c r="F1464" t="n">
-        <v>11823.2</v>
+        <v>11872.1</v>
       </c>
       <c r="G1464" t="n">
         <v>4</v>
@@ -48772,10 +48772,10 @@
         <v>85.59999999999999</v>
       </c>
       <c r="E1465" t="n">
-        <v>2356.1</v>
+        <v>2420</v>
       </c>
       <c r="F1465" t="n">
-        <v>9891.1</v>
+        <v>9955</v>
       </c>
       <c r="G1465" t="n">
         <v>2</v>
@@ -48805,16 +48805,16 @@
         <v>100.6</v>
       </c>
       <c r="E1466" t="n">
-        <v>2442.4</v>
+        <v>2477.1</v>
       </c>
       <c r="F1466" t="n">
-        <v>13153.5</v>
+        <v>13188.2</v>
       </c>
       <c r="G1466" t="n">
         <v>1</v>
       </c>
       <c r="H1466" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1466" t="n">
         <v>2</v>
@@ -48838,16 +48838,16 @@
         <v>65.90000000000001</v>
       </c>
       <c r="E1467" t="n">
-        <v>2417.5</v>
+        <v>2479.9</v>
       </c>
       <c r="F1467" t="n">
-        <v>13108.5</v>
+        <v>13170.9</v>
       </c>
       <c r="G1467" t="n">
         <v>5</v>
       </c>
       <c r="H1467" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1467" t="n">
         <v>3</v>
@@ -48871,10 +48871,10 @@
         <v>70.8</v>
       </c>
       <c r="E1468" t="n">
-        <v>2354.3</v>
+        <v>2401.6</v>
       </c>
       <c r="F1468" t="n">
-        <v>12219.4</v>
+        <v>12266.7</v>
       </c>
       <c r="G1468" t="n">
         <v>4</v>
@@ -48904,10 +48904,10 @@
         <v>60.5</v>
       </c>
       <c r="E1469" t="n">
-        <v>2167.3</v>
+        <v>2196.7</v>
       </c>
       <c r="F1469" t="n">
-        <v>11831.9</v>
+        <v>11861.3</v>
       </c>
       <c r="G1469" t="n">
         <v>7</v>
@@ -48937,10 +48937,10 @@
         <v>64.59999999999999</v>
       </c>
       <c r="E1470" t="n">
-        <v>2544</v>
+        <v>2620.8</v>
       </c>
       <c r="F1470" t="n">
-        <v>13478.8</v>
+        <v>13555.6</v>
       </c>
       <c r="G1470" t="n">
         <v>6</v>
@@ -48970,10 +48970,10 @@
         <v>73.7</v>
       </c>
       <c r="E1471" t="n">
-        <v>2012.9</v>
+        <v>2042.1</v>
       </c>
       <c r="F1471" t="n">
-        <v>10846.8</v>
+        <v>10876</v>
       </c>
       <c r="G1471" t="n">
         <v>3</v>
@@ -49003,10 +49003,10 @@
         <v>55.2</v>
       </c>
       <c r="E1472" t="n">
-        <v>2274.3</v>
+        <v>2323.2</v>
       </c>
       <c r="F1472" t="n">
-        <v>11878.4</v>
+        <v>11927.3</v>
       </c>
       <c r="G1472" t="n">
         <v>8</v>
@@ -49036,10 +49036,10 @@
         <v>88</v>
       </c>
       <c r="E1473" t="n">
-        <v>2444.1</v>
+        <v>2508</v>
       </c>
       <c r="F1473" t="n">
-        <v>9979.1</v>
+        <v>10043</v>
       </c>
       <c r="G1473" t="n">
         <v>2</v>
@@ -49069,16 +49069,16 @@
         <v>70.09999999999999</v>
       </c>
       <c r="E1474" t="n">
-        <v>2512.5</v>
+        <v>2547.2</v>
       </c>
       <c r="F1474" t="n">
-        <v>13223.6</v>
+        <v>13258.3</v>
       </c>
       <c r="G1474" t="n">
         <v>4</v>
       </c>
       <c r="H1474" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1474" t="n">
         <v>2</v>
@@ -49102,16 +49102,16 @@
         <v>77.90000000000001</v>
       </c>
       <c r="E1475" t="n">
-        <v>2495.4</v>
+        <v>2557.8</v>
       </c>
       <c r="F1475" t="n">
-        <v>13186.4</v>
+        <v>13248.8</v>
       </c>
       <c r="G1475" t="n">
         <v>3</v>
       </c>
       <c r="H1475" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1475" t="n">
         <v>3</v>
@@ -49135,10 +49135,10 @@
         <v>80.8</v>
       </c>
       <c r="E1476" t="n">
-        <v>2435.1</v>
+        <v>2482.4</v>
       </c>
       <c r="F1476" t="n">
-        <v>12300.2</v>
+        <v>12347.5</v>
       </c>
       <c r="G1476" t="n">
         <v>2</v>
@@ -49168,10 +49168,10 @@
         <v>53</v>
       </c>
       <c r="E1477" t="n">
-        <v>2220.3</v>
+        <v>2249.7</v>
       </c>
       <c r="F1477" t="n">
-        <v>11884.9</v>
+        <v>11914.3</v>
       </c>
       <c r="G1477" t="n">
         <v>7</v>
@@ -49201,10 +49201,10 @@
         <v>59.8</v>
       </c>
       <c r="E1478" t="n">
-        <v>2603.8</v>
+        <v>2680.6</v>
       </c>
       <c r="F1478" t="n">
-        <v>13538.6</v>
+        <v>13615.4</v>
       </c>
       <c r="G1478" t="n">
         <v>6</v>
@@ -49234,10 +49234,10 @@
         <v>68.39999999999999</v>
       </c>
       <c r="E1479" t="n">
-        <v>2081.3</v>
+        <v>2110.5</v>
       </c>
       <c r="F1479" t="n">
-        <v>10915.2</v>
+        <v>10944.4</v>
       </c>
       <c r="G1479" t="n">
         <v>5</v>
@@ -49267,10 +49267,10 @@
         <v>48.4</v>
       </c>
       <c r="E1480" t="n">
-        <v>2322.7</v>
+        <v>2371.6</v>
       </c>
       <c r="F1480" t="n">
-        <v>11926.8</v>
+        <v>11975.7</v>
       </c>
       <c r="G1480" t="n">
         <v>8</v>
@@ -49300,10 +49300,10 @@
         <v>104.8</v>
       </c>
       <c r="E1481" t="n">
-        <v>2548.9</v>
+        <v>2612.8</v>
       </c>
       <c r="F1481" t="n">
-        <v>10083.9</v>
+        <v>10147.8</v>
       </c>
       <c r="G1481" t="n">
         <v>1</v>
@@ -49333,16 +49333,16 @@
         <v>76.3</v>
       </c>
       <c r="E1482" t="n">
-        <v>2588.8</v>
+        <v>2623.5</v>
       </c>
       <c r="F1482" t="n">
-        <v>13299.9</v>
+        <v>13334.6</v>
       </c>
       <c r="G1482" t="n">
         <v>3</v>
       </c>
       <c r="H1482" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1482" t="n">
         <v>2</v>
@@ -49366,16 +49366,16 @@
         <v>73.3</v>
       </c>
       <c r="E1483" t="n">
-        <v>2568.7</v>
+        <v>2631.1</v>
       </c>
       <c r="F1483" t="n">
-        <v>13259.7</v>
+        <v>13322.1</v>
       </c>
       <c r="G1483" t="n">
         <v>5</v>
       </c>
       <c r="H1483" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1483" t="n">
         <v>3</v>
@@ -49399,10 +49399,10 @@
         <v>56.5</v>
       </c>
       <c r="E1484" t="n">
-        <v>2491.6</v>
+        <v>2538.9</v>
       </c>
       <c r="F1484" t="n">
-        <v>12356.7</v>
+        <v>12404</v>
       </c>
       <c r="G1484" t="n">
         <v>7</v>
@@ -49432,10 +49432,10 @@
         <v>75.09999999999999</v>
       </c>
       <c r="E1485" t="n">
-        <v>2295.4</v>
+        <v>2324.8</v>
       </c>
       <c r="F1485" t="n">
-        <v>11960</v>
+        <v>11989.4</v>
       </c>
       <c r="G1485" t="n">
         <v>4</v>
@@ -49465,10 +49465,10 @@
         <v>69.7</v>
       </c>
       <c r="E1486" t="n">
-        <v>2673.5</v>
+        <v>2750.3</v>
       </c>
       <c r="F1486" t="n">
-        <v>13608.3</v>
+        <v>13685.1</v>
       </c>
       <c r="G1486" t="n">
         <v>6</v>
@@ -49498,10 +49498,10 @@
         <v>80.09999999999999</v>
       </c>
       <c r="E1487" t="n">
-        <v>2161.4</v>
+        <v>2190.6</v>
       </c>
       <c r="F1487" t="n">
-        <v>10995.3</v>
+        <v>11024.5</v>
       </c>
       <c r="G1487" t="n">
         <v>2</v>
@@ -49531,10 +49531,10 @@
         <v>44.90000000000001</v>
       </c>
       <c r="E1488" t="n">
-        <v>2367.6</v>
+        <v>2416.5</v>
       </c>
       <c r="F1488" t="n">
-        <v>11971.7</v>
+        <v>12020.6</v>
       </c>
       <c r="G1488" t="n">
         <v>8</v>
@@ -49564,10 +49564,10 @@
         <v>82.40000000000001</v>
       </c>
       <c r="E1489" t="n">
-        <v>2631.3</v>
+        <v>2695.2</v>
       </c>
       <c r="F1489" t="n">
-        <v>10166.3</v>
+        <v>10230.2</v>
       </c>
       <c r="G1489" t="n">
         <v>1</v>
@@ -49597,16 +49597,16 @@
         <v>94.09999999999999</v>
       </c>
       <c r="E1490" t="n">
-        <v>2682.9</v>
+        <v>2717.6</v>
       </c>
       <c r="F1490" t="n">
-        <v>13394</v>
+        <v>13428.7</v>
       </c>
       <c r="G1490" t="n">
         <v>3</v>
       </c>
       <c r="H1490" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1490" t="n">
         <v>2</v>
@@ -49630,16 +49630,16 @@
         <v>94.90000000000001</v>
       </c>
       <c r="E1491" t="n">
-        <v>2663.6</v>
+        <v>2726</v>
       </c>
       <c r="F1491" t="n">
-        <v>13354.6</v>
+        <v>13417</v>
       </c>
       <c r="G1491" t="n">
         <v>2</v>
       </c>
       <c r="H1491" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1491" t="n">
         <v>3</v>
@@ -49663,10 +49663,10 @@
         <v>75.2</v>
       </c>
       <c r="E1492" t="n">
-        <v>2566.8</v>
+        <v>2614.1</v>
       </c>
       <c r="F1492" t="n">
-        <v>12431.9</v>
+        <v>12479.2</v>
       </c>
       <c r="G1492" t="n">
         <v>5</v>
@@ -49696,10 +49696,10 @@
         <v>38.3</v>
       </c>
       <c r="E1493" t="n">
-        <v>2333.7</v>
+        <v>2363.1</v>
       </c>
       <c r="F1493" t="n">
-        <v>11998.3</v>
+        <v>12027.7</v>
       </c>
       <c r="G1493" t="n">
         <v>8</v>
@@ -49729,16 +49729,16 @@
         <v>52.9</v>
       </c>
       <c r="E1494" t="n">
-        <v>2726.4</v>
+        <v>2803.2</v>
       </c>
       <c r="F1494" t="n">
-        <v>13661.2</v>
+        <v>13738</v>
       </c>
       <c r="G1494" t="n">
         <v>6</v>
       </c>
       <c r="H1494" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1494" t="n">
         <v>1</v>
@@ -49762,10 +49762,10 @@
         <v>78.7</v>
       </c>
       <c r="E1495" t="n">
-        <v>2240.1</v>
+        <v>2269.3</v>
       </c>
       <c r="F1495" t="n">
-        <v>11074</v>
+        <v>11103.2</v>
       </c>
       <c r="G1495" t="n">
         <v>4</v>
@@ -49795,10 +49795,10 @@
         <v>44.4</v>
       </c>
       <c r="E1496" t="n">
-        <v>2412</v>
+        <v>2460.9</v>
       </c>
       <c r="F1496" t="n">
-        <v>12016.1</v>
+        <v>12065</v>
       </c>
       <c r="G1496" t="n">
         <v>7</v>
@@ -49828,16 +49828,16 @@
         <v>95.3</v>
       </c>
       <c r="E1497" t="n">
-        <v>2726.6</v>
+        <v>2790.5</v>
       </c>
       <c r="F1497" t="n">
-        <v>10261.6</v>
+        <v>10325.5</v>
       </c>
       <c r="G1497" t="n">
         <v>1</v>
       </c>
       <c r="H1497" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1497" t="n">
         <v>8</v>
@@ -49861,10 +49861,10 @@
         <v>72.8</v>
       </c>
       <c r="E1498" t="n">
-        <v>2755.7</v>
+        <v>2790.4</v>
       </c>
       <c r="F1498" t="n">
-        <v>13466.8</v>
+        <v>13501.5</v>
       </c>
       <c r="G1498" t="n">
         <v>2</v>
@@ -49894,10 +49894,10 @@
         <v>42</v>
       </c>
       <c r="E1499" t="n">
-        <v>2705.6</v>
+        <v>2768</v>
       </c>
       <c r="F1499" t="n">
-        <v>13396.6</v>
+        <v>13459</v>
       </c>
       <c r="G1499" t="n">
         <v>7</v>
@@ -49927,10 +49927,10 @@
         <v>65.10000000000001</v>
       </c>
       <c r="E1500" t="n">
-        <v>2631.9</v>
+        <v>2679.2</v>
       </c>
       <c r="F1500" t="n">
-        <v>12497</v>
+        <v>12544.3</v>
       </c>
       <c r="G1500" t="n">
         <v>5</v>
@@ -49960,10 +49960,10 @@
         <v>39.8</v>
       </c>
       <c r="E1501" t="n">
-        <v>2373.5</v>
+        <v>2402.9</v>
       </c>
       <c r="F1501" t="n">
-        <v>12038.1</v>
+        <v>12067.5</v>
       </c>
       <c r="G1501" t="n">
         <v>8</v>
@@ -49993,10 +49993,10 @@
         <v>65.8</v>
       </c>
       <c r="E1502" t="n">
-        <v>2792.2</v>
+        <v>2869</v>
       </c>
       <c r="F1502" t="n">
-        <v>13727</v>
+        <v>13803.8</v>
       </c>
       <c r="G1502" t="n">
         <v>4</v>
@@ -50026,10 +50026,10 @@
         <v>66.40000000000001</v>
       </c>
       <c r="E1503" t="n">
-        <v>2306.5</v>
+        <v>2335.7</v>
       </c>
       <c r="F1503" t="n">
-        <v>11140.4</v>
+        <v>11169.6</v>
       </c>
       <c r="G1503" t="n">
         <v>3</v>
@@ -50059,10 +50059,10 @@
         <v>52.7</v>
       </c>
       <c r="E1504" t="n">
-        <v>2464.7</v>
+        <v>2513.6</v>
       </c>
       <c r="F1504" t="n">
-        <v>12068.8</v>
+        <v>12117.7</v>
       </c>
       <c r="G1504" t="n">
         <v>6</v>
@@ -50092,10 +50092,10 @@
         <v>81.3</v>
       </c>
       <c r="E1505" t="n">
-        <v>2807.9</v>
+        <v>2871.8</v>
       </c>
       <c r="F1505" t="n">
-        <v>10342.9</v>
+        <v>10406.8</v>
       </c>
       <c r="G1505" t="n">
         <v>1</v>
@@ -50125,10 +50125,10 @@
         <v>70.59999999999999</v>
       </c>
       <c r="E1506" t="n">
-        <v>2826.3</v>
+        <v>2861</v>
       </c>
       <c r="F1506" t="n">
-        <v>13537.4</v>
+        <v>13572.1</v>
       </c>
       <c r="G1506" t="n">
         <v>4</v>
@@ -50158,10 +50158,10 @@
         <v>76.40000000000001</v>
       </c>
       <c r="E1507" t="n">
-        <v>2782</v>
+        <v>2844.4</v>
       </c>
       <c r="F1507" t="n">
-        <v>13473</v>
+        <v>13535.4</v>
       </c>
       <c r="G1507" t="n">
         <v>2</v>
@@ -50191,10 +50191,10 @@
         <v>60.3</v>
       </c>
       <c r="E1508" t="n">
-        <v>2692.2</v>
+        <v>2739.5</v>
       </c>
       <c r="F1508" t="n">
-        <v>12557.3</v>
+        <v>12604.6</v>
       </c>
       <c r="G1508" t="n">
         <v>6</v>
@@ -50224,10 +50224,10 @@
         <v>60.4</v>
       </c>
       <c r="E1509" t="n">
-        <v>2433.9</v>
+        <v>2463.3</v>
       </c>
       <c r="F1509" t="n">
-        <v>12098.5</v>
+        <v>12127.9</v>
       </c>
       <c r="G1509" t="n">
         <v>5</v>
@@ -50257,10 +50257,10 @@
         <v>53.9</v>
       </c>
       <c r="E1510" t="n">
-        <v>2846.1</v>
+        <v>2922.9</v>
       </c>
       <c r="F1510" t="n">
-        <v>13780.9</v>
+        <v>13857.7</v>
       </c>
       <c r="G1510" t="n">
         <v>7</v>
@@ -50290,10 +50290,10 @@
         <v>75.80000000000001</v>
       </c>
       <c r="E1511" t="n">
-        <v>2382.3</v>
+        <v>2411.5</v>
       </c>
       <c r="F1511" t="n">
-        <v>11216.2</v>
+        <v>11245.4</v>
       </c>
       <c r="G1511" t="n">
         <v>3</v>
@@ -50323,10 +50323,10 @@
         <v>53.2</v>
       </c>
       <c r="E1512" t="n">
-        <v>2517.9</v>
+        <v>2566.8</v>
       </c>
       <c r="F1512" t="n">
-        <v>12122</v>
+        <v>12170.9</v>
       </c>
       <c r="G1512" t="n">
         <v>8</v>
@@ -50356,10 +50356,10 @@
         <v>87.59999999999999</v>
       </c>
       <c r="E1513" t="n">
-        <v>2895.5</v>
+        <v>2959.4</v>
       </c>
       <c r="F1513" t="n">
-        <v>10430.5</v>
+        <v>10494.4</v>
       </c>
       <c r="G1513" t="n">
         <v>1</v>
@@ -50389,10 +50389,10 @@
         <v>58.2</v>
       </c>
       <c r="E1514" t="n">
-        <v>2884.5</v>
+        <v>2919.2</v>
       </c>
       <c r="F1514" t="n">
-        <v>13595.6</v>
+        <v>13630.3</v>
       </c>
       <c r="G1514" t="n">
         <v>4</v>
@@ -50422,10 +50422,10 @@
         <v>49.3</v>
       </c>
       <c r="E1515" t="n">
-        <v>2831.3</v>
+        <v>2893.7</v>
       </c>
       <c r="F1515" t="n">
-        <v>13522.3</v>
+        <v>13584.7</v>
       </c>
       <c r="G1515" t="n">
         <v>5</v>
@@ -50455,10 +50455,10 @@
         <v>69.09999999999999</v>
       </c>
       <c r="E1516" t="n">
-        <v>2761.3</v>
+        <v>2808.6</v>
       </c>
       <c r="F1516" t="n">
-        <v>12626.4</v>
+        <v>12673.7</v>
       </c>
       <c r="G1516" t="n">
         <v>3</v>
@@ -50488,10 +50488,10 @@
         <v>48.4</v>
       </c>
       <c r="E1517" t="n">
-        <v>2482.3</v>
+        <v>2511.7</v>
       </c>
       <c r="F1517" t="n">
-        <v>12146.9</v>
+        <v>12176.3</v>
       </c>
       <c r="G1517" t="n">
         <v>6</v>
@@ -50521,10 +50521,10 @@
         <v>47.6</v>
       </c>
       <c r="E1518" t="n">
-        <v>2893.7</v>
+        <v>2970.5</v>
       </c>
       <c r="F1518" t="n">
-        <v>13828.5</v>
+        <v>13905.3</v>
       </c>
       <c r="G1518" t="n">
         <v>7</v>
@@ -50554,10 +50554,10 @@
         <v>34.8</v>
       </c>
       <c r="E1519" t="n">
-        <v>2417.1</v>
+        <v>2446.3</v>
       </c>
       <c r="F1519" t="n">
-        <v>11251</v>
+        <v>11280.2</v>
       </c>
       <c r="G1519" t="n">
         <v>8</v>
@@ -50587,10 +50587,10 @@
         <v>73.3</v>
       </c>
       <c r="E1520" t="n">
-        <v>2591.2</v>
+        <v>2640.1</v>
       </c>
       <c r="F1520" t="n">
-        <v>12195.3</v>
+        <v>12244.2</v>
       </c>
       <c r="G1520" t="n">
         <v>2</v>
@@ -50620,10 +50620,10 @@
         <v>97.7</v>
       </c>
       <c r="E1521" t="n">
-        <v>2993.2</v>
+        <v>3057.1</v>
       </c>
       <c r="F1521" t="n">
-        <v>10528.2</v>
+        <v>10592.1</v>
       </c>
       <c r="G1521" t="n">
         <v>1</v>
@@ -50653,16 +50653,16 @@
         <v>95.7</v>
       </c>
       <c r="E1522" t="n">
-        <v>2980.2</v>
+        <v>3014.9</v>
       </c>
       <c r="F1522" t="n">
-        <v>13691.3</v>
+        <v>13726</v>
       </c>
       <c r="G1522" t="n">
         <v>1</v>
       </c>
       <c r="H1522" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1522" t="n">
         <v>2</v>
@@ -50686,10 +50686,10 @@
         <v>0</v>
       </c>
       <c r="E1523" t="n">
-        <v>2831.3</v>
+        <v>2893.7</v>
       </c>
       <c r="F1523" t="n">
-        <v>13522.3</v>
+        <v>13584.7</v>
       </c>
       <c r="G1523" t="n">
         <v>8</v>
@@ -50719,10 +50719,10 @@
         <v>40.7</v>
       </c>
       <c r="E1524" t="n">
-        <v>2802</v>
+        <v>2849.3</v>
       </c>
       <c r="F1524" t="n">
-        <v>12667.1</v>
+        <v>12714.4</v>
       </c>
       <c r="G1524" t="n">
         <v>7</v>
@@ -50752,10 +50752,10 @@
         <v>68.2</v>
       </c>
       <c r="E1525" t="n">
-        <v>2550.5</v>
+        <v>2579.9</v>
       </c>
       <c r="F1525" t="n">
-        <v>12215.1</v>
+        <v>12244.5</v>
       </c>
       <c r="G1525" t="n">
         <v>4</v>
@@ -50785,16 +50785,16 @@
         <v>66.59999999999999</v>
       </c>
       <c r="E1526" t="n">
-        <v>2960.3</v>
+        <v>3037.1</v>
       </c>
       <c r="F1526" t="n">
-        <v>13895.1</v>
+        <v>13971.9</v>
       </c>
       <c r="G1526" t="n">
         <v>5</v>
       </c>
       <c r="H1526" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1526" t="n">
         <v>1</v>
@@ -50818,10 +50818,10 @@
         <v>80.59999999999999</v>
       </c>
       <c r="E1527" t="n">
-        <v>2497.7</v>
+        <v>2526.9</v>
       </c>
       <c r="F1527" t="n">
-        <v>11331.6</v>
+        <v>11360.8</v>
       </c>
       <c r="G1527" t="n">
         <v>2</v>
@@ -50851,10 +50851,10 @@
         <v>46.4</v>
       </c>
       <c r="E1528" t="n">
-        <v>2637.6</v>
+        <v>2686.5</v>
       </c>
       <c r="F1528" t="n">
-        <v>12241.7</v>
+        <v>12290.6</v>
       </c>
       <c r="G1528" t="n">
         <v>6</v>
@@ -50884,10 +50884,10 @@
         <v>80.40000000000001</v>
       </c>
       <c r="E1529" t="n">
-        <v>3073.6</v>
+        <v>3137.5</v>
       </c>
       <c r="F1529" t="n">
-        <v>10608.6</v>
+        <v>10672.5</v>
       </c>
       <c r="G1529" t="n">
         <v>3</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -42436,7 +42436,7 @@
         <v>98.09999999999999</v>
       </c>
       <c r="E1273" t="n">
-        <v>649.7</v>
+        <v>649.6999999999999</v>
       </c>
       <c r="F1273" t="n">
         <v>8184.7</v>
@@ -43492,7 +43492,7 @@
         <v>66.3</v>
       </c>
       <c r="E1305" t="n">
-        <v>911.1</v>
+        <v>911.0999999999999</v>
       </c>
       <c r="F1305" t="n">
         <v>8446.1</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -42436,7 +42436,7 @@
         <v>98.09999999999999</v>
       </c>
       <c r="E1273" t="n">
-        <v>649.6999999999999</v>
+        <v>649.7</v>
       </c>
       <c r="F1273" t="n">
         <v>8184.7</v>
@@ -42601,7 +42601,7 @@
         <v>70.09999999999999</v>
       </c>
       <c r="E1278" t="n">
-        <v>874.1</v>
+        <v>874.0999999999999</v>
       </c>
       <c r="F1278" t="n">
         <v>11808.9</v>
@@ -42865,7 +42865,7 @@
         <v>59.5</v>
       </c>
       <c r="E1286" t="n">
-        <v>933.6</v>
+        <v>933.5999999999999</v>
       </c>
       <c r="F1286" t="n">
         <v>11868.4</v>
@@ -43492,7 +43492,7 @@
         <v>66.3</v>
       </c>
       <c r="E1305" t="n">
-        <v>911.0999999999999</v>
+        <v>911.1</v>
       </c>
       <c r="F1305" t="n">
         <v>8446.1</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -42466,16 +42466,16 @@
         </is>
       </c>
       <c r="D1274" t="n">
-        <v>73.59999999999999</v>
+        <v>112.6</v>
       </c>
       <c r="E1274" t="n">
-        <v>626.6</v>
+        <v>665.6</v>
       </c>
       <c r="F1274" t="n">
-        <v>11337.7</v>
+        <v>11376.7</v>
       </c>
       <c r="G1274" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H1274" t="n">
         <v>8</v>
@@ -42499,19 +42499,19 @@
         </is>
       </c>
       <c r="D1275" t="n">
-        <v>59.40000000000001</v>
+        <v>114.1</v>
       </c>
       <c r="E1275" t="n">
-        <v>775.4</v>
+        <v>830.1</v>
       </c>
       <c r="F1275" t="n">
-        <v>11466.4</v>
+        <v>11521.1</v>
       </c>
       <c r="G1275" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H1275" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1275" t="n">
         <v>2</v>
@@ -42532,19 +42532,19 @@
         </is>
       </c>
       <c r="D1276" t="n">
-        <v>78.59999999999999</v>
+        <v>140.4</v>
       </c>
       <c r="E1276" t="n">
-        <v>771.5</v>
+        <v>833.3</v>
       </c>
       <c r="F1276" t="n">
-        <v>10636.6</v>
+        <v>10698.4</v>
       </c>
       <c r="G1276" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1276" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1276" t="n">
         <v>4</v>
@@ -42565,16 +42565,16 @@
         </is>
       </c>
       <c r="D1277" t="n">
-        <v>46</v>
+        <v>127.6</v>
       </c>
       <c r="E1277" t="n">
-        <v>794.2</v>
+        <v>875.8</v>
       </c>
       <c r="F1277" t="n">
-        <v>10458.8</v>
+        <v>10540.4</v>
       </c>
       <c r="G1277" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H1277" t="n">
         <v>2</v>
@@ -42598,16 +42598,16 @@
         </is>
       </c>
       <c r="D1278" t="n">
-        <v>70.09999999999999</v>
+        <v>136.5</v>
       </c>
       <c r="E1278" t="n">
-        <v>874.0999999999999</v>
+        <v>940.5</v>
       </c>
       <c r="F1278" t="n">
-        <v>11808.9</v>
+        <v>11875.3</v>
       </c>
       <c r="G1278" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1278" t="n">
         <v>1</v>
@@ -42631,16 +42631,16 @@
         </is>
       </c>
       <c r="D1279" t="n">
-        <v>52.5</v>
+        <v>122.4</v>
       </c>
       <c r="E1279" t="n">
-        <v>643.7</v>
+        <v>713.6</v>
       </c>
       <c r="F1279" t="n">
-        <v>9477.6</v>
+        <v>9547.5</v>
       </c>
       <c r="G1279" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H1279" t="n">
         <v>7</v>
@@ -42664,16 +42664,16 @@
         </is>
       </c>
       <c r="D1280" t="n">
-        <v>74.90000000000001</v>
+        <v>154.1</v>
       </c>
       <c r="E1280" t="n">
-        <v>727</v>
+        <v>806.2</v>
       </c>
       <c r="F1280" t="n">
-        <v>10331.1</v>
+        <v>10410.3</v>
       </c>
       <c r="G1280" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1280" t="n">
         <v>5</v>
@@ -42697,13 +42697,13 @@
         </is>
       </c>
       <c r="D1281" t="n">
-        <v>58.2</v>
+        <v>121.1</v>
       </c>
       <c r="E1281" t="n">
-        <v>707.9</v>
+        <v>770.8</v>
       </c>
       <c r="F1281" t="n">
-        <v>8242.9</v>
+        <v>8305.799999999999</v>
       </c>
       <c r="G1281" t="n">
         <v>6</v>
@@ -42733,10 +42733,10 @@
         <v>53.8</v>
       </c>
       <c r="E1282" t="n">
-        <v>680.4</v>
+        <v>719.4</v>
       </c>
       <c r="F1282" t="n">
-        <v>11391.5</v>
+        <v>11430.5</v>
       </c>
       <c r="G1282" t="n">
         <v>7</v>
@@ -42766,10 +42766,10 @@
         <v>51.1</v>
       </c>
       <c r="E1283" t="n">
-        <v>826.5</v>
+        <v>881.2</v>
       </c>
       <c r="F1283" t="n">
-        <v>11517.5</v>
+        <v>11572.2</v>
       </c>
       <c r="G1283" t="n">
         <v>8</v>
@@ -42799,10 +42799,10 @@
         <v>62.1</v>
       </c>
       <c r="E1284" t="n">
-        <v>833.6</v>
+        <v>895.4</v>
       </c>
       <c r="F1284" t="n">
-        <v>10698.7</v>
+        <v>10760.5</v>
       </c>
       <c r="G1284" t="n">
         <v>3</v>
@@ -42832,10 +42832,10 @@
         <v>69.5</v>
       </c>
       <c r="E1285" t="n">
-        <v>863.7</v>
+        <v>945.3</v>
       </c>
       <c r="F1285" t="n">
-        <v>10528.3</v>
+        <v>10609.9</v>
       </c>
       <c r="G1285" t="n">
         <v>1</v>
@@ -42865,10 +42865,10 @@
         <v>59.5</v>
       </c>
       <c r="E1286" t="n">
-        <v>933.5999999999999</v>
+        <v>1000</v>
       </c>
       <c r="F1286" t="n">
-        <v>11868.4</v>
+        <v>11934.8</v>
       </c>
       <c r="G1286" t="n">
         <v>5</v>
@@ -42898,10 +42898,10 @@
         <v>54.1</v>
       </c>
       <c r="E1287" t="n">
-        <v>697.8</v>
+        <v>767.7</v>
       </c>
       <c r="F1287" t="n">
-        <v>9531.700000000001</v>
+        <v>9601.6</v>
       </c>
       <c r="G1287" t="n">
         <v>6</v>
@@ -42931,10 +42931,10 @@
         <v>69.2</v>
       </c>
       <c r="E1288" t="n">
-        <v>796.2</v>
+        <v>875.4</v>
       </c>
       <c r="F1288" t="n">
-        <v>10400.3</v>
+        <v>10479.5</v>
       </c>
       <c r="G1288" t="n">
         <v>2</v>
@@ -42964,10 +42964,10 @@
         <v>60</v>
       </c>
       <c r="E1289" t="n">
-        <v>767.9</v>
+        <v>830.8</v>
       </c>
       <c r="F1289" t="n">
-        <v>8302.9</v>
+        <v>8365.799999999999</v>
       </c>
       <c r="G1289" t="n">
         <v>4</v>
@@ -42997,16 +42997,16 @@
         <v>87.8</v>
       </c>
       <c r="E1290" t="n">
-        <v>768.1999999999999</v>
+        <v>807.2</v>
       </c>
       <c r="F1290" t="n">
-        <v>11479.3</v>
+        <v>11518.3</v>
       </c>
       <c r="G1290" t="n">
         <v>1</v>
       </c>
       <c r="H1290" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1290" t="n">
         <v>3</v>
@@ -43030,16 +43030,16 @@
         <v>67</v>
       </c>
       <c r="E1291" t="n">
-        <v>893.5</v>
+        <v>948.2</v>
       </c>
       <c r="F1291" t="n">
-        <v>11584.5</v>
+        <v>11639.2</v>
       </c>
       <c r="G1291" t="n">
         <v>4</v>
       </c>
       <c r="H1291" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I1291" t="n">
         <v>2</v>
@@ -43063,10 +43063,10 @@
         <v>55.4</v>
       </c>
       <c r="E1292" t="n">
-        <v>889</v>
+        <v>950.8</v>
       </c>
       <c r="F1292" t="n">
-        <v>10754.1</v>
+        <v>10815.9</v>
       </c>
       <c r="G1292" t="n">
         <v>7</v>
@@ -43096,10 +43096,10 @@
         <v>57.6</v>
       </c>
       <c r="E1293" t="n">
-        <v>921.3000000000001</v>
+        <v>1002.9</v>
       </c>
       <c r="F1293" t="n">
-        <v>10585.9</v>
+        <v>10667.5</v>
       </c>
       <c r="G1293" t="n">
         <v>6</v>
@@ -43129,10 +43129,10 @@
         <v>66.3</v>
       </c>
       <c r="E1294" t="n">
-        <v>999.9</v>
+        <v>1066.3</v>
       </c>
       <c r="F1294" t="n">
-        <v>11934.7</v>
+        <v>12001.1</v>
       </c>
       <c r="G1294" t="n">
         <v>5</v>
@@ -43162,16 +43162,16 @@
         <v>52.1</v>
       </c>
       <c r="E1295" t="n">
-        <v>749.9</v>
+        <v>819.8</v>
       </c>
       <c r="F1295" t="n">
-        <v>9583.799999999999</v>
+        <v>9653.700000000001</v>
       </c>
       <c r="G1295" t="n">
         <v>8</v>
       </c>
       <c r="H1295" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I1295" t="n">
         <v>7</v>
@@ -43195,16 +43195,16 @@
         <v>81.09999999999999</v>
       </c>
       <c r="E1296" t="n">
-        <v>877.3</v>
+        <v>956.5</v>
       </c>
       <c r="F1296" t="n">
-        <v>10481.4</v>
+        <v>10560.6</v>
       </c>
       <c r="G1296" t="n">
         <v>2</v>
       </c>
       <c r="H1296" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I1296" t="n">
         <v>6</v>
@@ -43228,10 +43228,10 @@
         <v>76.89999999999999</v>
       </c>
       <c r="E1297" t="n">
-        <v>844.8</v>
+        <v>907.7</v>
       </c>
       <c r="F1297" t="n">
-        <v>8379.799999999999</v>
+        <v>8442.700000000001</v>
       </c>
       <c r="G1297" t="n">
         <v>3</v>
@@ -43261,10 +43261,10 @@
         <v>77.90000000000001</v>
       </c>
       <c r="E1298" t="n">
-        <v>846.1</v>
+        <v>885.1</v>
       </c>
       <c r="F1298" t="n">
-        <v>11557.2</v>
+        <v>11596.2</v>
       </c>
       <c r="G1298" t="n">
         <v>1</v>
@@ -43294,16 +43294,16 @@
         <v>54.8</v>
       </c>
       <c r="E1299" t="n">
-        <v>948.3</v>
+        <v>1003</v>
       </c>
       <c r="F1299" t="n">
-        <v>11639.3</v>
+        <v>11694</v>
       </c>
       <c r="G1299" t="n">
         <v>7</v>
       </c>
       <c r="H1299" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1299" t="n">
         <v>2</v>
@@ -43327,16 +43327,16 @@
         <v>68.8</v>
       </c>
       <c r="E1300" t="n">
-        <v>957.8</v>
+        <v>1019.6</v>
       </c>
       <c r="F1300" t="n">
-        <v>10822.9</v>
+        <v>10884.7</v>
       </c>
       <c r="G1300" t="n">
         <v>3</v>
       </c>
       <c r="H1300" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1300" t="n">
         <v>4</v>
@@ -43360,10 +43360,10 @@
         <v>60.2</v>
       </c>
       <c r="E1301" t="n">
-        <v>981.5</v>
+        <v>1063.1</v>
       </c>
       <c r="F1301" t="n">
-        <v>10646.1</v>
+        <v>10727.7</v>
       </c>
       <c r="G1301" t="n">
         <v>6</v>
@@ -43393,10 +43393,10 @@
         <v>62.8</v>
       </c>
       <c r="E1302" t="n">
-        <v>1062.7</v>
+        <v>1129.1</v>
       </c>
       <c r="F1302" t="n">
-        <v>11997.5</v>
+        <v>12063.9</v>
       </c>
       <c r="G1302" t="n">
         <v>5</v>
@@ -43426,10 +43426,10 @@
         <v>50.9</v>
       </c>
       <c r="E1303" t="n">
-        <v>800.8</v>
+        <v>870.7</v>
       </c>
       <c r="F1303" t="n">
-        <v>9634.700000000001</v>
+        <v>9704.6</v>
       </c>
       <c r="G1303" t="n">
         <v>8</v>
@@ -43459,16 +43459,16 @@
         <v>69.40000000000001</v>
       </c>
       <c r="E1304" t="n">
-        <v>946.7</v>
+        <v>1025.9</v>
       </c>
       <c r="F1304" t="n">
-        <v>10550.8</v>
+        <v>10630</v>
       </c>
       <c r="G1304" t="n">
         <v>2</v>
       </c>
       <c r="H1304" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I1304" t="n">
         <v>6</v>
@@ -43492,10 +43492,10 @@
         <v>66.3</v>
       </c>
       <c r="E1305" t="n">
-        <v>911.1</v>
+        <v>974</v>
       </c>
       <c r="F1305" t="n">
-        <v>8446.1</v>
+        <v>8509</v>
       </c>
       <c r="G1305" t="n">
         <v>4</v>
@@ -43525,10 +43525,10 @@
         <v>68</v>
       </c>
       <c r="E1306" t="n">
-        <v>914.1</v>
+        <v>953.1</v>
       </c>
       <c r="F1306" t="n">
-        <v>11625.2</v>
+        <v>11664.2</v>
       </c>
       <c r="G1306" t="n">
         <v>5</v>
@@ -43558,16 +43558,16 @@
         <v>89.2</v>
       </c>
       <c r="E1307" t="n">
-        <v>1037.5</v>
+        <v>1092.2</v>
       </c>
       <c r="F1307" t="n">
-        <v>11728.5</v>
+        <v>11783.2</v>
       </c>
       <c r="G1307" t="n">
         <v>2</v>
       </c>
       <c r="H1307" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I1307" t="n">
         <v>2</v>
@@ -43591,10 +43591,10 @@
         <v>79.3</v>
       </c>
       <c r="E1308" t="n">
-        <v>1037.1</v>
+        <v>1098.9</v>
       </c>
       <c r="F1308" t="n">
-        <v>10902.2</v>
+        <v>10964</v>
       </c>
       <c r="G1308" t="n">
         <v>3</v>
@@ -43624,10 +43624,10 @@
         <v>61</v>
       </c>
       <c r="E1309" t="n">
-        <v>1042.5</v>
+        <v>1124.1</v>
       </c>
       <c r="F1309" t="n">
-        <v>10707.1</v>
+        <v>10788.7</v>
       </c>
       <c r="G1309" t="n">
         <v>6</v>
@@ -43657,10 +43657,10 @@
         <v>57.4</v>
       </c>
       <c r="E1310" t="n">
-        <v>1120.1</v>
+        <v>1186.5</v>
       </c>
       <c r="F1310" t="n">
-        <v>12054.9</v>
+        <v>12121.3</v>
       </c>
       <c r="G1310" t="n">
         <v>7</v>
@@ -43690,10 +43690,10 @@
         <v>46.4</v>
       </c>
       <c r="E1311" t="n">
-        <v>847.2</v>
+        <v>917.1</v>
       </c>
       <c r="F1311" t="n">
-        <v>9681.1</v>
+        <v>9751</v>
       </c>
       <c r="G1311" t="n">
         <v>8</v>
@@ -43723,16 +43723,16 @@
         <v>77.2</v>
       </c>
       <c r="E1312" t="n">
-        <v>1023.9</v>
+        <v>1103.1</v>
       </c>
       <c r="F1312" t="n">
-        <v>10628</v>
+        <v>10707.2</v>
       </c>
       <c r="G1312" t="n">
         <v>4</v>
       </c>
       <c r="H1312" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I1312" t="n">
         <v>6</v>
@@ -43756,10 +43756,10 @@
         <v>95.2</v>
       </c>
       <c r="E1313" t="n">
-        <v>1006.3</v>
+        <v>1069.2</v>
       </c>
       <c r="F1313" t="n">
-        <v>8541.299999999999</v>
+        <v>8604.200000000001</v>
       </c>
       <c r="G1313" t="n">
         <v>1</v>
@@ -43789,10 +43789,10 @@
         <v>78</v>
       </c>
       <c r="E1314" t="n">
-        <v>992.1</v>
+        <v>1031.1</v>
       </c>
       <c r="F1314" t="n">
-        <v>11703.2</v>
+        <v>11742.2</v>
       </c>
       <c r="G1314" t="n">
         <v>3</v>
@@ -43822,16 +43822,16 @@
         <v>78.59999999999999</v>
       </c>
       <c r="E1315" t="n">
-        <v>1116.1</v>
+        <v>1170.8</v>
       </c>
       <c r="F1315" t="n">
-        <v>11807.1</v>
+        <v>11861.8</v>
       </c>
       <c r="G1315" t="n">
         <v>2</v>
       </c>
       <c r="H1315" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1315" t="n">
         <v>2</v>
@@ -43855,16 +43855,16 @@
         <v>76.90000000000001</v>
       </c>
       <c r="E1316" t="n">
-        <v>1114</v>
+        <v>1175.8</v>
       </c>
       <c r="F1316" t="n">
-        <v>10979.1</v>
+        <v>11040.9</v>
       </c>
       <c r="G1316" t="n">
         <v>4</v>
       </c>
       <c r="H1316" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1316" t="n">
         <v>4</v>
@@ -43888,16 +43888,16 @@
         <v>48.4</v>
       </c>
       <c r="E1317" t="n">
-        <v>1090.9</v>
+        <v>1172.5</v>
       </c>
       <c r="F1317" t="n">
-        <v>10755.5</v>
+        <v>10837.1</v>
       </c>
       <c r="G1317" t="n">
         <v>8</v>
       </c>
       <c r="H1317" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1317" t="n">
         <v>5</v>
@@ -43921,10 +43921,10 @@
         <v>67.59999999999999</v>
       </c>
       <c r="E1318" t="n">
-        <v>1187.7</v>
+        <v>1254.1</v>
       </c>
       <c r="F1318" t="n">
-        <v>12122.5</v>
+        <v>12188.9</v>
       </c>
       <c r="G1318" t="n">
         <v>5</v>
@@ -43954,10 +43954,10 @@
         <v>58.1</v>
       </c>
       <c r="E1319" t="n">
-        <v>905.3</v>
+        <v>975.2</v>
       </c>
       <c r="F1319" t="n">
-        <v>9739.200000000001</v>
+        <v>9809.1</v>
       </c>
       <c r="G1319" t="n">
         <v>7</v>
@@ -43987,16 +43987,16 @@
         <v>61.4</v>
       </c>
       <c r="E1320" t="n">
-        <v>1085.3</v>
+        <v>1164.5</v>
       </c>
       <c r="F1320" t="n">
-        <v>10689.4</v>
+        <v>10768.6</v>
       </c>
       <c r="G1320" t="n">
         <v>6</v>
       </c>
       <c r="H1320" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1320" t="n">
         <v>6</v>
@@ -44020,16 +44020,16 @@
         <v>81.59999999999999</v>
       </c>
       <c r="E1321" t="n">
-        <v>1087.9</v>
+        <v>1150.8</v>
       </c>
       <c r="F1321" t="n">
-        <v>8622.9</v>
+        <v>8685.799999999999</v>
       </c>
       <c r="G1321" t="n">
         <v>1</v>
       </c>
       <c r="H1321" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1321" t="n">
         <v>8</v>
@@ -44053,10 +44053,10 @@
         <v>67.5</v>
       </c>
       <c r="E1322" t="n">
-        <v>1059.6</v>
+        <v>1098.6</v>
       </c>
       <c r="F1322" t="n">
-        <v>11770.7</v>
+        <v>11809.7</v>
       </c>
       <c r="G1322" t="n">
         <v>5</v>
@@ -44086,16 +44086,16 @@
         <v>69.8</v>
       </c>
       <c r="E1323" t="n">
-        <v>1185.9</v>
+        <v>1240.6</v>
       </c>
       <c r="F1323" t="n">
-        <v>11876.9</v>
+        <v>11931.6</v>
       </c>
       <c r="G1323" t="n">
         <v>2</v>
       </c>
       <c r="H1323" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1323" t="n">
         <v>2</v>
@@ -44119,16 +44119,16 @@
         <v>68.3</v>
       </c>
       <c r="E1324" t="n">
-        <v>1182.3</v>
+        <v>1244.1</v>
       </c>
       <c r="F1324" t="n">
-        <v>11047.4</v>
+        <v>11109.2</v>
       </c>
       <c r="G1324" t="n">
         <v>3</v>
       </c>
       <c r="H1324" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1324" t="n">
         <v>4</v>
@@ -44152,16 +44152,16 @@
         <v>52.1</v>
       </c>
       <c r="E1325" t="n">
-        <v>1143</v>
+        <v>1224.6</v>
       </c>
       <c r="F1325" t="n">
-        <v>10807.6</v>
+        <v>10889.2</v>
       </c>
       <c r="G1325" t="n">
         <v>8</v>
       </c>
       <c r="H1325" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I1325" t="n">
         <v>5</v>
@@ -44185,10 +44185,10 @@
         <v>79.7</v>
       </c>
       <c r="E1326" t="n">
-        <v>1267.4</v>
+        <v>1333.8</v>
       </c>
       <c r="F1326" t="n">
-        <v>12202.2</v>
+        <v>12268.6</v>
       </c>
       <c r="G1326" t="n">
         <v>1</v>
@@ -44218,10 +44218,10 @@
         <v>58</v>
       </c>
       <c r="E1327" t="n">
-        <v>963.3</v>
+        <v>1033.2</v>
       </c>
       <c r="F1327" t="n">
-        <v>9797.200000000001</v>
+        <v>9867.1</v>
       </c>
       <c r="G1327" t="n">
         <v>7</v>
@@ -44251,10 +44251,10 @@
         <v>59.5</v>
       </c>
       <c r="E1328" t="n">
-        <v>1144.8</v>
+        <v>1224</v>
       </c>
       <c r="F1328" t="n">
-        <v>10748.9</v>
+        <v>10828.1</v>
       </c>
       <c r="G1328" t="n">
         <v>6</v>
@@ -44284,16 +44284,16 @@
         <v>68.10000000000001</v>
       </c>
       <c r="E1329" t="n">
-        <v>1156</v>
+        <v>1218.9</v>
       </c>
       <c r="F1329" t="n">
-        <v>8691</v>
+        <v>8753.9</v>
       </c>
       <c r="G1329" t="n">
         <v>4</v>
       </c>
       <c r="H1329" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I1329" t="n">
         <v>8</v>
@@ -44317,10 +44317,10 @@
         <v>58.6</v>
       </c>
       <c r="E1330" t="n">
-        <v>1118.2</v>
+        <v>1157.2</v>
       </c>
       <c r="F1330" t="n">
-        <v>11829.3</v>
+        <v>11868.3</v>
       </c>
       <c r="G1330" t="n">
         <v>6</v>
@@ -44350,10 +44350,10 @@
         <v>105.7</v>
       </c>
       <c r="E1331" t="n">
-        <v>1291.6</v>
+        <v>1346.3</v>
       </c>
       <c r="F1331" t="n">
-        <v>11982.6</v>
+        <v>12037.3</v>
       </c>
       <c r="G1331" t="n">
         <v>1</v>
@@ -44383,10 +44383,10 @@
         <v>58.4</v>
       </c>
       <c r="E1332" t="n">
-        <v>1240.7</v>
+        <v>1302.5</v>
       </c>
       <c r="F1332" t="n">
-        <v>11105.8</v>
+        <v>11167.6</v>
       </c>
       <c r="G1332" t="n">
         <v>7</v>
@@ -44416,10 +44416,10 @@
         <v>57.4</v>
       </c>
       <c r="E1333" t="n">
-        <v>1200.4</v>
+        <v>1282</v>
       </c>
       <c r="F1333" t="n">
-        <v>10865</v>
+        <v>10946.6</v>
       </c>
       <c r="G1333" t="n">
         <v>8</v>
@@ -44449,10 +44449,10 @@
         <v>83.40000000000001</v>
       </c>
       <c r="E1334" t="n">
-        <v>1350.8</v>
+        <v>1417.2</v>
       </c>
       <c r="F1334" t="n">
-        <v>12285.6</v>
+        <v>12352</v>
       </c>
       <c r="G1334" t="n">
         <v>3</v>
@@ -44482,10 +44482,10 @@
         <v>74.3</v>
       </c>
       <c r="E1335" t="n">
-        <v>1037.6</v>
+        <v>1107.5</v>
       </c>
       <c r="F1335" t="n">
-        <v>9871.5</v>
+        <v>9941.4</v>
       </c>
       <c r="G1335" t="n">
         <v>4</v>
@@ -44515,10 +44515,10 @@
         <v>72</v>
       </c>
       <c r="E1336" t="n">
-        <v>1216.8</v>
+        <v>1296</v>
       </c>
       <c r="F1336" t="n">
-        <v>10820.9</v>
+        <v>10900.1</v>
       </c>
       <c r="G1336" t="n">
         <v>5</v>
@@ -44548,10 +44548,10 @@
         <v>87.09999999999999</v>
       </c>
       <c r="E1337" t="n">
-        <v>1243.1</v>
+        <v>1306</v>
       </c>
       <c r="F1337" t="n">
-        <v>8778.1</v>
+        <v>8841</v>
       </c>
       <c r="G1337" t="n">
         <v>2</v>
@@ -44581,10 +44581,10 @@
         <v>61.2</v>
       </c>
       <c r="E1338" t="n">
-        <v>1179.4</v>
+        <v>1218.4</v>
       </c>
       <c r="F1338" t="n">
-        <v>11890.5</v>
+        <v>11929.5</v>
       </c>
       <c r="G1338" t="n">
         <v>5</v>
@@ -44614,10 +44614,10 @@
         <v>55.59999999999999</v>
       </c>
       <c r="E1339" t="n">
-        <v>1347.2</v>
+        <v>1401.9</v>
       </c>
       <c r="F1339" t="n">
-        <v>12038.2</v>
+        <v>12092.9</v>
       </c>
       <c r="G1339" t="n">
         <v>7</v>
@@ -44647,10 +44647,10 @@
         <v>50.59999999999999</v>
       </c>
       <c r="E1340" t="n">
-        <v>1291.3</v>
+        <v>1353.1</v>
       </c>
       <c r="F1340" t="n">
-        <v>11156.4</v>
+        <v>11218.2</v>
       </c>
       <c r="G1340" t="n">
         <v>8</v>
@@ -44680,10 +44680,10 @@
         <v>62.40000000000001</v>
       </c>
       <c r="E1341" t="n">
-        <v>1262.8</v>
+        <v>1344.4</v>
       </c>
       <c r="F1341" t="n">
-        <v>10927.4</v>
+        <v>11009</v>
       </c>
       <c r="G1341" t="n">
         <v>4</v>
@@ -44713,10 +44713,10 @@
         <v>81.90000000000001</v>
       </c>
       <c r="E1342" t="n">
-        <v>1432.7</v>
+        <v>1499.1</v>
       </c>
       <c r="F1342" t="n">
-        <v>12367.5</v>
+        <v>12433.9</v>
       </c>
       <c r="G1342" t="n">
         <v>2</v>
@@ -44746,10 +44746,10 @@
         <v>63.3</v>
       </c>
       <c r="E1343" t="n">
-        <v>1100.9</v>
+        <v>1170.8</v>
       </c>
       <c r="F1343" t="n">
-        <v>9934.799999999999</v>
+        <v>10004.7</v>
       </c>
       <c r="G1343" t="n">
         <v>3</v>
@@ -44779,10 +44779,10 @@
         <v>86</v>
       </c>
       <c r="E1344" t="n">
-        <v>1302.8</v>
+        <v>1382</v>
       </c>
       <c r="F1344" t="n">
-        <v>10906.9</v>
+        <v>10986.1</v>
       </c>
       <c r="G1344" t="n">
         <v>1</v>
@@ -44812,10 +44812,10 @@
         <v>58.1</v>
       </c>
       <c r="E1345" t="n">
-        <v>1301.2</v>
+        <v>1364.1</v>
       </c>
       <c r="F1345" t="n">
-        <v>8836.200000000001</v>
+        <v>8899.1</v>
       </c>
       <c r="G1345" t="n">
         <v>6</v>
@@ -44845,10 +44845,10 @@
         <v>64.2</v>
       </c>
       <c r="E1346" t="n">
-        <v>1243.6</v>
+        <v>1282.6</v>
       </c>
       <c r="F1346" t="n">
-        <v>11954.7</v>
+        <v>11993.7</v>
       </c>
       <c r="G1346" t="n">
         <v>5</v>
@@ -44878,10 +44878,10 @@
         <v>88.7</v>
       </c>
       <c r="E1347" t="n">
-        <v>1435.9</v>
+        <v>1490.6</v>
       </c>
       <c r="F1347" t="n">
-        <v>12126.9</v>
+        <v>12181.6</v>
       </c>
       <c r="G1347" t="n">
         <v>1</v>
@@ -44911,10 +44911,10 @@
         <v>76.8</v>
       </c>
       <c r="E1348" t="n">
-        <v>1368.1</v>
+        <v>1429.9</v>
       </c>
       <c r="F1348" t="n">
-        <v>11233.2</v>
+        <v>11295</v>
       </c>
       <c r="G1348" t="n">
         <v>3</v>
@@ -44944,10 +44944,10 @@
         <v>45</v>
       </c>
       <c r="E1349" t="n">
-        <v>1307.8</v>
+        <v>1389.4</v>
       </c>
       <c r="F1349" t="n">
-        <v>10972.4</v>
+        <v>11054</v>
       </c>
       <c r="G1349" t="n">
         <v>8</v>
@@ -44956,7 +44956,7 @@
         <v>6</v>
       </c>
       <c r="I1349" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1350">
@@ -44977,10 +44977,10 @@
         <v>81.2</v>
       </c>
       <c r="E1350" t="n">
-        <v>1513.9</v>
+        <v>1580.3</v>
       </c>
       <c r="F1350" t="n">
-        <v>12448.7</v>
+        <v>12515.1</v>
       </c>
       <c r="G1350" t="n">
         <v>2</v>
@@ -45010,10 +45010,10 @@
         <v>63.7</v>
       </c>
       <c r="E1351" t="n">
-        <v>1164.6</v>
+        <v>1234.5</v>
       </c>
       <c r="F1351" t="n">
-        <v>9998.5</v>
+        <v>10068.4</v>
       </c>
       <c r="G1351" t="n">
         <v>6</v>
@@ -45043,10 +45043,10 @@
         <v>67.7</v>
       </c>
       <c r="E1352" t="n">
-        <v>1370.5</v>
+        <v>1449.7</v>
       </c>
       <c r="F1352" t="n">
-        <v>10974.6</v>
+        <v>11053.8</v>
       </c>
       <c r="G1352" t="n">
         <v>4</v>
@@ -45055,7 +45055,7 @@
         <v>3</v>
       </c>
       <c r="I1352" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1353">
@@ -45076,10 +45076,10 @@
         <v>60.2</v>
       </c>
       <c r="E1353" t="n">
-        <v>1361.4</v>
+        <v>1424.3</v>
       </c>
       <c r="F1353" t="n">
-        <v>8896.4</v>
+        <v>8959.299999999999</v>
       </c>
       <c r="G1353" t="n">
         <v>7</v>
@@ -45109,16 +45109,16 @@
         <v>88.09999999999999</v>
       </c>
       <c r="E1354" t="n">
-        <v>1331.7</v>
+        <v>1370.7</v>
       </c>
       <c r="F1354" t="n">
-        <v>12042.8</v>
+        <v>12081.8</v>
       </c>
       <c r="G1354" t="n">
         <v>3</v>
       </c>
       <c r="H1354" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1354" t="n">
         <v>3</v>
@@ -45142,10 +45142,10 @@
         <v>59.9</v>
       </c>
       <c r="E1355" t="n">
-        <v>1495.8</v>
+        <v>1550.5</v>
       </c>
       <c r="F1355" t="n">
-        <v>12186.8</v>
+        <v>12241.5</v>
       </c>
       <c r="G1355" t="n">
         <v>6</v>
@@ -45175,16 +45175,16 @@
         <v>70.2</v>
       </c>
       <c r="E1356" t="n">
-        <v>1438.3</v>
+        <v>1500.1</v>
       </c>
       <c r="F1356" t="n">
-        <v>11303.4</v>
+        <v>11365.2</v>
       </c>
       <c r="G1356" t="n">
         <v>4</v>
       </c>
       <c r="H1356" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1356" t="n">
         <v>4</v>
@@ -45208,16 +45208,16 @@
         <v>0</v>
       </c>
       <c r="E1357" t="n">
-        <v>1307.8</v>
+        <v>1389.4</v>
       </c>
       <c r="F1357" t="n">
-        <v>10972.4</v>
+        <v>11054</v>
       </c>
       <c r="G1357" t="n">
         <v>8</v>
       </c>
       <c r="H1357" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I1357" t="n">
         <v>6</v>
@@ -45241,10 +45241,10 @@
         <v>94</v>
       </c>
       <c r="E1358" t="n">
-        <v>1607.9</v>
+        <v>1674.3</v>
       </c>
       <c r="F1358" t="n">
-        <v>12542.7</v>
+        <v>12609.1</v>
       </c>
       <c r="G1358" t="n">
         <v>1</v>
@@ -45274,10 +45274,10 @@
         <v>61.6</v>
       </c>
       <c r="E1359" t="n">
-        <v>1226.2</v>
+        <v>1296.1</v>
       </c>
       <c r="F1359" t="n">
-        <v>10060.1</v>
+        <v>10130</v>
       </c>
       <c r="G1359" t="n">
         <v>5</v>
@@ -45307,16 +45307,16 @@
         <v>58.6</v>
       </c>
       <c r="E1360" t="n">
-        <v>1429.1</v>
+        <v>1508.3</v>
       </c>
       <c r="F1360" t="n">
-        <v>11033.2</v>
+        <v>11112.4</v>
       </c>
       <c r="G1360" t="n">
         <v>7</v>
       </c>
       <c r="H1360" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1360" t="n">
         <v>5</v>
@@ -45340,10 +45340,10 @@
         <v>89.5</v>
       </c>
       <c r="E1361" t="n">
-        <v>1450.9</v>
+        <v>1513.8</v>
       </c>
       <c r="F1361" t="n">
-        <v>8985.9</v>
+        <v>9048.799999999999</v>
       </c>
       <c r="G1361" t="n">
         <v>2</v>
@@ -45373,16 +45373,16 @@
         <v>66.7</v>
       </c>
       <c r="E1362" t="n">
-        <v>1398.4</v>
+        <v>1437.4</v>
       </c>
       <c r="F1362" t="n">
-        <v>12109.5</v>
+        <v>12148.5</v>
       </c>
       <c r="G1362" t="n">
         <v>4</v>
       </c>
       <c r="H1362" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1362" t="n">
         <v>3</v>
@@ -45406,16 +45406,16 @@
         <v>35.8</v>
       </c>
       <c r="E1363" t="n">
-        <v>1531.6</v>
+        <v>1586.3</v>
       </c>
       <c r="F1363" t="n">
-        <v>12222.6</v>
+        <v>12277.3</v>
       </c>
       <c r="G1363" t="n">
         <v>8</v>
       </c>
       <c r="H1363" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1363" t="n">
         <v>2</v>
@@ -45439,10 +45439,10 @@
         <v>59.2</v>
       </c>
       <c r="E1364" t="n">
-        <v>1497.5</v>
+        <v>1559.3</v>
       </c>
       <c r="F1364" t="n">
-        <v>11362.6</v>
+        <v>11424.4</v>
       </c>
       <c r="G1364" t="n">
         <v>6</v>
@@ -45472,16 +45472,16 @@
         <v>82.2</v>
       </c>
       <c r="E1365" t="n">
-        <v>1390</v>
+        <v>1471.6</v>
       </c>
       <c r="F1365" t="n">
-        <v>11054.6</v>
+        <v>11136.2</v>
       </c>
       <c r="G1365" t="n">
         <v>2</v>
       </c>
       <c r="H1365" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I1365" t="n">
         <v>6</v>
@@ -45505,10 +45505,10 @@
         <v>63</v>
       </c>
       <c r="E1366" t="n">
-        <v>1670.9</v>
+        <v>1737.3</v>
       </c>
       <c r="F1366" t="n">
-        <v>12605.7</v>
+        <v>12672.1</v>
       </c>
       <c r="G1366" t="n">
         <v>5</v>
@@ -45538,10 +45538,10 @@
         <v>56.6</v>
       </c>
       <c r="E1367" t="n">
-        <v>1282.8</v>
+        <v>1352.7</v>
       </c>
       <c r="F1367" t="n">
-        <v>10116.7</v>
+        <v>10186.6</v>
       </c>
       <c r="G1367" t="n">
         <v>7</v>
@@ -45571,16 +45571,16 @@
         <v>78.59999999999999</v>
       </c>
       <c r="E1368" t="n">
-        <v>1507.7</v>
+        <v>1586.9</v>
       </c>
       <c r="F1368" t="n">
-        <v>11111.8</v>
+        <v>11191</v>
       </c>
       <c r="G1368" t="n">
         <v>3</v>
       </c>
       <c r="H1368" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1368" t="n">
         <v>5</v>
@@ -45604,10 +45604,10 @@
         <v>87.3</v>
       </c>
       <c r="E1369" t="n">
-        <v>1538.2</v>
+        <v>1601.1</v>
       </c>
       <c r="F1369" t="n">
-        <v>9073.200000000001</v>
+        <v>9136.1</v>
       </c>
       <c r="G1369" t="n">
         <v>1</v>
@@ -45637,16 +45637,16 @@
         <v>70.8</v>
       </c>
       <c r="E1370" t="n">
-        <v>1469.2</v>
+        <v>1508.2</v>
       </c>
       <c r="F1370" t="n">
-        <v>12180.3</v>
+        <v>12219.3</v>
       </c>
       <c r="G1370" t="n">
         <v>4</v>
       </c>
       <c r="H1370" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1370" t="n">
         <v>3</v>
@@ -45670,10 +45670,10 @@
         <v>76.5</v>
       </c>
       <c r="E1371" t="n">
-        <v>1608.1</v>
+        <v>1662.8</v>
       </c>
       <c r="F1371" t="n">
-        <v>12299.1</v>
+        <v>12353.8</v>
       </c>
       <c r="G1371" t="n">
         <v>2</v>
@@ -45703,10 +45703,10 @@
         <v>75.2</v>
       </c>
       <c r="E1372" t="n">
-        <v>1572.7</v>
+        <v>1634.5</v>
       </c>
       <c r="F1372" t="n">
-        <v>11437.8</v>
+        <v>11499.6</v>
       </c>
       <c r="G1372" t="n">
         <v>3</v>
@@ -45736,16 +45736,16 @@
         <v>46.7</v>
       </c>
       <c r="E1373" t="n">
-        <v>1436.7</v>
+        <v>1518.3</v>
       </c>
       <c r="F1373" t="n">
-        <v>11101.3</v>
+        <v>11182.9</v>
       </c>
       <c r="G1373" t="n">
         <v>8</v>
       </c>
       <c r="H1373" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I1373" t="n">
         <v>6</v>
@@ -45769,10 +45769,10 @@
         <v>79.40000000000001</v>
       </c>
       <c r="E1374" t="n">
-        <v>1750.3</v>
+        <v>1816.7</v>
       </c>
       <c r="F1374" t="n">
-        <v>12685.1</v>
+        <v>12751.5</v>
       </c>
       <c r="G1374" t="n">
         <v>1</v>
@@ -45802,10 +45802,10 @@
         <v>56.59999999999999</v>
       </c>
       <c r="E1375" t="n">
-        <v>1339.4</v>
+        <v>1409.3</v>
       </c>
       <c r="F1375" t="n">
-        <v>10173.3</v>
+        <v>10243.2</v>
       </c>
       <c r="G1375" t="n">
         <v>6</v>
@@ -45835,10 +45835,10 @@
         <v>65.2</v>
       </c>
       <c r="E1376" t="n">
-        <v>1572.9</v>
+        <v>1652.1</v>
       </c>
       <c r="F1376" t="n">
-        <v>11177</v>
+        <v>11256.2</v>
       </c>
       <c r="G1376" t="n">
         <v>5</v>
@@ -45868,10 +45868,10 @@
         <v>54.8</v>
       </c>
       <c r="E1377" t="n">
-        <v>1593</v>
+        <v>1655.9</v>
       </c>
       <c r="F1377" t="n">
-        <v>9128</v>
+        <v>9190.9</v>
       </c>
       <c r="G1377" t="n">
         <v>7</v>
@@ -45901,10 +45901,10 @@
         <v>93.8</v>
       </c>
       <c r="E1378" t="n">
-        <v>1563</v>
+        <v>1602</v>
       </c>
       <c r="F1378" t="n">
-        <v>12274.1</v>
+        <v>12313.1</v>
       </c>
       <c r="G1378" t="n">
         <v>2</v>
@@ -45934,16 +45934,16 @@
         <v>65.2</v>
       </c>
       <c r="E1379" t="n">
-        <v>1673.3</v>
+        <v>1728</v>
       </c>
       <c r="F1379" t="n">
-        <v>12364.3</v>
+        <v>12419</v>
       </c>
       <c r="G1379" t="n">
         <v>7</v>
       </c>
       <c r="H1379" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1379" t="n">
         <v>2</v>
@@ -45967,16 +45967,16 @@
         <v>97.59999999999999</v>
       </c>
       <c r="E1380" t="n">
-        <v>1670.3</v>
+        <v>1732.1</v>
       </c>
       <c r="F1380" t="n">
-        <v>11535.4</v>
+        <v>11597.2</v>
       </c>
       <c r="G1380" t="n">
         <v>1</v>
       </c>
       <c r="H1380" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1380" t="n">
         <v>4</v>
@@ -46000,10 +46000,10 @@
         <v>63.3</v>
       </c>
       <c r="E1381" t="n">
-        <v>1500</v>
+        <v>1581.6</v>
       </c>
       <c r="F1381" t="n">
-        <v>11164.6</v>
+        <v>11246.2</v>
       </c>
       <c r="G1381" t="n">
         <v>8</v>
@@ -46033,10 +46033,10 @@
         <v>79.3</v>
       </c>
       <c r="E1382" t="n">
-        <v>1829.6</v>
+        <v>1896</v>
       </c>
       <c r="F1382" t="n">
-        <v>12764.4</v>
+        <v>12830.8</v>
       </c>
       <c r="G1382" t="n">
         <v>5</v>
@@ -46066,10 +46066,10 @@
         <v>81.7</v>
       </c>
       <c r="E1383" t="n">
-        <v>1421.1</v>
+        <v>1491</v>
       </c>
       <c r="F1383" t="n">
-        <v>10255</v>
+        <v>10324.9</v>
       </c>
       <c r="G1383" t="n">
         <v>4</v>
@@ -46099,10 +46099,10 @@
         <v>67.40000000000001</v>
       </c>
       <c r="E1384" t="n">
-        <v>1640.3</v>
+        <v>1719.5</v>
       </c>
       <c r="F1384" t="n">
-        <v>11244.4</v>
+        <v>11323.6</v>
       </c>
       <c r="G1384" t="n">
         <v>6</v>
@@ -46132,10 +46132,10 @@
         <v>82.59999999999999</v>
       </c>
       <c r="E1385" t="n">
-        <v>1675.6</v>
+        <v>1738.5</v>
       </c>
       <c r="F1385" t="n">
-        <v>9210.6</v>
+        <v>9273.5</v>
       </c>
       <c r="G1385" t="n">
         <v>3</v>
@@ -46165,10 +46165,10 @@
         <v>100.5</v>
       </c>
       <c r="E1386" t="n">
-        <v>1663.5</v>
+        <v>1702.5</v>
       </c>
       <c r="F1386" t="n">
-        <v>12374.6</v>
+        <v>12413.6</v>
       </c>
       <c r="G1386" t="n">
         <v>1</v>
@@ -46198,10 +46198,10 @@
         <v>80.3</v>
       </c>
       <c r="E1387" t="n">
-        <v>1753.6</v>
+        <v>1808.3</v>
       </c>
       <c r="F1387" t="n">
-        <v>12444.6</v>
+        <v>12499.3</v>
       </c>
       <c r="G1387" t="n">
         <v>2</v>
@@ -46231,10 +46231,10 @@
         <v>60.3</v>
       </c>
       <c r="E1388" t="n">
-        <v>1730.6</v>
+        <v>1792.4</v>
       </c>
       <c r="F1388" t="n">
-        <v>11595.7</v>
+        <v>11657.5</v>
       </c>
       <c r="G1388" t="n">
         <v>6</v>
@@ -46264,10 +46264,10 @@
         <v>67.59999999999999</v>
       </c>
       <c r="E1389" t="n">
-        <v>1567.6</v>
+        <v>1649.2</v>
       </c>
       <c r="F1389" t="n">
-        <v>11232.2</v>
+        <v>11313.8</v>
       </c>
       <c r="G1389" t="n">
         <v>4</v>
@@ -46297,10 +46297,10 @@
         <v>70.2</v>
       </c>
       <c r="E1390" t="n">
-        <v>1899.8</v>
+        <v>1966.2</v>
       </c>
       <c r="F1390" t="n">
-        <v>12834.6</v>
+        <v>12901</v>
       </c>
       <c r="G1390" t="n">
         <v>3</v>
@@ -46330,10 +46330,10 @@
         <v>61.2</v>
       </c>
       <c r="E1391" t="n">
-        <v>1482.3</v>
+        <v>1552.2</v>
       </c>
       <c r="F1391" t="n">
-        <v>10316.2</v>
+        <v>10386.1</v>
       </c>
       <c r="G1391" t="n">
         <v>5</v>
@@ -46363,10 +46363,10 @@
         <v>50.8</v>
       </c>
       <c r="E1392" t="n">
-        <v>1691.1</v>
+        <v>1770.3</v>
       </c>
       <c r="F1392" t="n">
-        <v>11295.2</v>
+        <v>11374.4</v>
       </c>
       <c r="G1392" t="n">
         <v>8</v>
@@ -46396,10 +46396,10 @@
         <v>58.9</v>
       </c>
       <c r="E1393" t="n">
-        <v>1734.5</v>
+        <v>1797.4</v>
       </c>
       <c r="F1393" t="n">
-        <v>9269.5</v>
+        <v>9332.4</v>
       </c>
       <c r="G1393" t="n">
         <v>7</v>
@@ -46429,10 +46429,10 @@
         <v>92</v>
       </c>
       <c r="E1394" t="n">
-        <v>1755.5</v>
+        <v>1794.5</v>
       </c>
       <c r="F1394" t="n">
-        <v>12466.6</v>
+        <v>12505.6</v>
       </c>
       <c r="G1394" t="n">
         <v>2</v>
@@ -46462,10 +46462,10 @@
         <v>77.2</v>
       </c>
       <c r="E1395" t="n">
-        <v>1830.8</v>
+        <v>1885.5</v>
       </c>
       <c r="F1395" t="n">
-        <v>12521.8</v>
+        <v>12576.5</v>
       </c>
       <c r="G1395" t="n">
         <v>4</v>
@@ -46495,10 +46495,10 @@
         <v>80.3</v>
       </c>
       <c r="E1396" t="n">
-        <v>1810.9</v>
+        <v>1872.7</v>
       </c>
       <c r="F1396" t="n">
-        <v>11676</v>
+        <v>11737.8</v>
       </c>
       <c r="G1396" t="n">
         <v>3</v>
@@ -46528,10 +46528,10 @@
         <v>50.6</v>
       </c>
       <c r="E1397" t="n">
-        <v>1618.2</v>
+        <v>1699.8</v>
       </c>
       <c r="F1397" t="n">
-        <v>11282.8</v>
+        <v>11364.4</v>
       </c>
       <c r="G1397" t="n">
         <v>7</v>
@@ -46561,10 +46561,10 @@
         <v>76.7</v>
       </c>
       <c r="E1398" t="n">
-        <v>1976.5</v>
+        <v>2042.9</v>
       </c>
       <c r="F1398" t="n">
-        <v>12911.3</v>
+        <v>12977.7</v>
       </c>
       <c r="G1398" t="n">
         <v>5</v>
@@ -46594,10 +46594,10 @@
         <v>48.7</v>
       </c>
       <c r="E1399" t="n">
-        <v>1531</v>
+        <v>1600.9</v>
       </c>
       <c r="F1399" t="n">
-        <v>10364.9</v>
+        <v>10434.8</v>
       </c>
       <c r="G1399" t="n">
         <v>8</v>
@@ -46627,10 +46627,10 @@
         <v>92.5</v>
       </c>
       <c r="E1400" t="n">
-        <v>1783.6</v>
+        <v>1862.8</v>
       </c>
       <c r="F1400" t="n">
-        <v>11387.7</v>
+        <v>11466.9</v>
       </c>
       <c r="G1400" t="n">
         <v>1</v>
@@ -46660,10 +46660,10 @@
         <v>73.10000000000001</v>
       </c>
       <c r="E1401" t="n">
-        <v>1807.6</v>
+        <v>1870.5</v>
       </c>
       <c r="F1401" t="n">
-        <v>9342.6</v>
+        <v>9405.5</v>
       </c>
       <c r="G1401" t="n">
         <v>6</v>
@@ -46693,10 +46693,10 @@
         <v>75.59999999999999</v>
       </c>
       <c r="E1402" t="n">
-        <v>1831.1</v>
+        <v>1870.1</v>
       </c>
       <c r="F1402" t="n">
-        <v>12542.2</v>
+        <v>12581.2</v>
       </c>
       <c r="G1402" t="n">
         <v>3</v>
@@ -46726,10 +46726,10 @@
         <v>84.09999999999999</v>
       </c>
       <c r="E1403" t="n">
-        <v>1914.9</v>
+        <v>1969.6</v>
       </c>
       <c r="F1403" t="n">
-        <v>12605.9</v>
+        <v>12660.6</v>
       </c>
       <c r="G1403" t="n">
         <v>1</v>
@@ -46759,16 +46759,16 @@
         <v>59.3</v>
       </c>
       <c r="E1404" t="n">
-        <v>1870.2</v>
+        <v>1932</v>
       </c>
       <c r="F1404" t="n">
-        <v>11735.3</v>
+        <v>11797.1</v>
       </c>
       <c r="G1404" t="n">
         <v>8</v>
       </c>
       <c r="H1404" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1404" t="n">
         <v>4</v>
@@ -46792,10 +46792,10 @@
         <v>71.5</v>
       </c>
       <c r="E1405" t="n">
-        <v>1689.7</v>
+        <v>1771.3</v>
       </c>
       <c r="F1405" t="n">
-        <v>11354.3</v>
+        <v>11435.9</v>
       </c>
       <c r="G1405" t="n">
         <v>6</v>
@@ -46825,10 +46825,10 @@
         <v>75.39999999999999</v>
       </c>
       <c r="E1406" t="n">
-        <v>2051.9</v>
+        <v>2118.3</v>
       </c>
       <c r="F1406" t="n">
-        <v>12986.7</v>
+        <v>13053.1</v>
       </c>
       <c r="G1406" t="n">
         <v>4</v>
@@ -46858,10 +46858,10 @@
         <v>62.7</v>
       </c>
       <c r="E1407" t="n">
-        <v>1593.7</v>
+        <v>1663.6</v>
       </c>
       <c r="F1407" t="n">
-        <v>10427.6</v>
+        <v>10497.5</v>
       </c>
       <c r="G1407" t="n">
         <v>7</v>
@@ -46891,16 +46891,16 @@
         <v>72</v>
       </c>
       <c r="E1408" t="n">
-        <v>1855.6</v>
+        <v>1934.8</v>
       </c>
       <c r="F1408" t="n">
-        <v>11459.7</v>
+        <v>11538.9</v>
       </c>
       <c r="G1408" t="n">
         <v>5</v>
       </c>
       <c r="H1408" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1408" t="n">
         <v>5</v>
@@ -46924,10 +46924,10 @@
         <v>79.09999999999999</v>
       </c>
       <c r="E1409" t="n">
-        <v>1886.7</v>
+        <v>1949.6</v>
       </c>
       <c r="F1409" t="n">
-        <v>9421.700000000001</v>
+        <v>9484.6</v>
       </c>
       <c r="G1409" t="n">
         <v>2</v>
@@ -46957,16 +46957,16 @@
         <v>73.2</v>
       </c>
       <c r="E1410" t="n">
-        <v>1904.3</v>
+        <v>1943.3</v>
       </c>
       <c r="F1410" t="n">
-        <v>12615.4</v>
+        <v>12654.4</v>
       </c>
       <c r="G1410" t="n">
         <v>2</v>
       </c>
       <c r="H1410" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1410" t="n">
         <v>3</v>
@@ -46990,10 +46990,10 @@
         <v>62.7</v>
       </c>
       <c r="E1411" t="n">
-        <v>1977.6</v>
+        <v>2032.3</v>
       </c>
       <c r="F1411" t="n">
-        <v>12668.6</v>
+        <v>12723.3</v>
       </c>
       <c r="G1411" t="n">
         <v>5</v>
@@ -47023,10 +47023,10 @@
         <v>49.2</v>
       </c>
       <c r="E1412" t="n">
-        <v>1919.4</v>
+        <v>1981.2</v>
       </c>
       <c r="F1412" t="n">
-        <v>11784.5</v>
+        <v>11846.3</v>
       </c>
       <c r="G1412" t="n">
         <v>6</v>
@@ -47056,10 +47056,10 @@
         <v>43.9</v>
       </c>
       <c r="E1413" t="n">
-        <v>1733.6</v>
+        <v>1815.2</v>
       </c>
       <c r="F1413" t="n">
-        <v>11398.2</v>
+        <v>11479.8</v>
       </c>
       <c r="G1413" t="n">
         <v>7</v>
@@ -47089,10 +47089,10 @@
         <v>71.2</v>
       </c>
       <c r="E1414" t="n">
-        <v>2123.1</v>
+        <v>2189.5</v>
       </c>
       <c r="F1414" t="n">
-        <v>13057.9</v>
+        <v>13124.3</v>
       </c>
       <c r="G1414" t="n">
         <v>3</v>
@@ -47122,10 +47122,10 @@
         <v>64.09999999999999</v>
       </c>
       <c r="E1415" t="n">
-        <v>1657.8</v>
+        <v>1727.7</v>
       </c>
       <c r="F1415" t="n">
-        <v>10491.7</v>
+        <v>10561.6</v>
       </c>
       <c r="G1415" t="n">
         <v>4</v>
@@ -47155,16 +47155,16 @@
         <v>42.9</v>
       </c>
       <c r="E1416" t="n">
-        <v>1898.5</v>
+        <v>1977.7</v>
       </c>
       <c r="F1416" t="n">
-        <v>11502.6</v>
+        <v>11581.8</v>
       </c>
       <c r="G1416" t="n">
         <v>8</v>
       </c>
       <c r="H1416" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1416" t="n">
         <v>5</v>
@@ -47188,10 +47188,10 @@
         <v>73.8</v>
       </c>
       <c r="E1417" t="n">
-        <v>1960.5</v>
+        <v>2023.4</v>
       </c>
       <c r="F1417" t="n">
-        <v>9495.5</v>
+        <v>9558.4</v>
       </c>
       <c r="G1417" t="n">
         <v>1</v>
@@ -47221,16 +47221,16 @@
         <v>79.3</v>
       </c>
       <c r="E1418" t="n">
-        <v>1983.6</v>
+        <v>2022.6</v>
       </c>
       <c r="F1418" t="n">
-        <v>12694.7</v>
+        <v>12733.7</v>
       </c>
       <c r="G1418" t="n">
         <v>1</v>
       </c>
       <c r="H1418" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I1418" t="n">
         <v>3</v>
@@ -47254,10 +47254,10 @@
         <v>62.3</v>
       </c>
       <c r="E1419" t="n">
-        <v>2039.9</v>
+        <v>2094.6</v>
       </c>
       <c r="F1419" t="n">
-        <v>12730.9</v>
+        <v>12785.6</v>
       </c>
       <c r="G1419" t="n">
         <v>4</v>
@@ -47287,10 +47287,10 @@
         <v>50.4</v>
       </c>
       <c r="E1420" t="n">
-        <v>1969.8</v>
+        <v>2031.6</v>
       </c>
       <c r="F1420" t="n">
-        <v>11834.9</v>
+        <v>11896.7</v>
       </c>
       <c r="G1420" t="n">
         <v>7</v>
@@ -47320,10 +47320,10 @@
         <v>48.8</v>
       </c>
       <c r="E1421" t="n">
-        <v>1782.4</v>
+        <v>1864</v>
       </c>
       <c r="F1421" t="n">
-        <v>11447</v>
+        <v>11528.6</v>
       </c>
       <c r="G1421" t="n">
         <v>8</v>
@@ -47353,10 +47353,10 @@
         <v>75</v>
       </c>
       <c r="E1422" t="n">
-        <v>2198.1</v>
+        <v>2264.5</v>
       </c>
       <c r="F1422" t="n">
-        <v>13132.9</v>
+        <v>13199.3</v>
       </c>
       <c r="G1422" t="n">
         <v>2</v>
@@ -47386,10 +47386,10 @@
         <v>64.5</v>
       </c>
       <c r="E1423" t="n">
-        <v>1722.3</v>
+        <v>1792.2</v>
       </c>
       <c r="F1423" t="n">
-        <v>10556.2</v>
+        <v>10626.1</v>
       </c>
       <c r="G1423" t="n">
         <v>3</v>
@@ -47419,16 +47419,16 @@
         <v>59.7</v>
       </c>
       <c r="E1424" t="n">
-        <v>1958.2</v>
+        <v>2037.4</v>
       </c>
       <c r="F1424" t="n">
-        <v>11562.3</v>
+        <v>11641.5</v>
       </c>
       <c r="G1424" t="n">
         <v>5</v>
       </c>
       <c r="H1424" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I1424" t="n">
         <v>5</v>
@@ -47452,10 +47452,10 @@
         <v>57.7</v>
       </c>
       <c r="E1425" t="n">
-        <v>2018.2</v>
+        <v>2081.1</v>
       </c>
       <c r="F1425" t="n">
-        <v>9553.200000000001</v>
+        <v>9616.1</v>
       </c>
       <c r="G1425" t="n">
         <v>6</v>
@@ -47485,10 +47485,10 @@
         <v>86.3</v>
       </c>
       <c r="E1426" t="n">
-        <v>2069.9</v>
+        <v>2108.9</v>
       </c>
       <c r="F1426" t="n">
-        <v>12781</v>
+        <v>12820</v>
       </c>
       <c r="G1426" t="n">
         <v>2</v>
@@ -47518,16 +47518,16 @@
         <v>75.59999999999999</v>
       </c>
       <c r="E1427" t="n">
-        <v>2115.5</v>
+        <v>2170.2</v>
       </c>
       <c r="F1427" t="n">
-        <v>12806.5</v>
+        <v>12861.2</v>
       </c>
       <c r="G1427" t="n">
         <v>3</v>
       </c>
       <c r="H1427" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1427" t="n">
         <v>2</v>
@@ -47551,16 +47551,16 @@
         <v>50.9</v>
       </c>
       <c r="E1428" t="n">
-        <v>2020.7</v>
+        <v>2082.5</v>
       </c>
       <c r="F1428" t="n">
-        <v>11885.8</v>
+        <v>11947.6</v>
       </c>
       <c r="G1428" t="n">
         <v>8</v>
       </c>
       <c r="H1428" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1428" t="n">
         <v>4</v>
@@ -47584,10 +47584,10 @@
         <v>65.3</v>
       </c>
       <c r="E1429" t="n">
-        <v>1847.7</v>
+        <v>1929.3</v>
       </c>
       <c r="F1429" t="n">
-        <v>11512.3</v>
+        <v>11593.9</v>
       </c>
       <c r="G1429" t="n">
         <v>4</v>
@@ -47617,10 +47617,10 @@
         <v>58.4</v>
       </c>
       <c r="E1430" t="n">
-        <v>2256.5</v>
+        <v>2322.9</v>
       </c>
       <c r="F1430" t="n">
-        <v>13191.3</v>
+        <v>13257.7</v>
       </c>
       <c r="G1430" t="n">
         <v>6</v>
@@ -47650,10 +47650,10 @@
         <v>58.6</v>
       </c>
       <c r="E1431" t="n">
-        <v>1780.9</v>
+        <v>1850.8</v>
       </c>
       <c r="F1431" t="n">
-        <v>10614.8</v>
+        <v>10684.7</v>
       </c>
       <c r="G1431" t="n">
         <v>5</v>
@@ -47683,16 +47683,16 @@
         <v>55.3</v>
       </c>
       <c r="E1432" t="n">
-        <v>2013.5</v>
+        <v>2092.7</v>
       </c>
       <c r="F1432" t="n">
-        <v>11617.6</v>
+        <v>11696.8</v>
       </c>
       <c r="G1432" t="n">
         <v>7</v>
       </c>
       <c r="H1432" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1432" t="n">
         <v>5</v>
@@ -47716,16 +47716,16 @@
         <v>96</v>
       </c>
       <c r="E1433" t="n">
-        <v>2114.2</v>
+        <v>2177.1</v>
       </c>
       <c r="F1433" t="n">
-        <v>9649.200000000001</v>
+        <v>9712.1</v>
       </c>
       <c r="G1433" t="n">
         <v>1</v>
       </c>
       <c r="H1433" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1433" t="n">
         <v>8</v>
@@ -47749,10 +47749,10 @@
         <v>84.5</v>
       </c>
       <c r="E1434" t="n">
-        <v>2154.4</v>
+        <v>2193.4</v>
       </c>
       <c r="F1434" t="n">
-        <v>12865.5</v>
+        <v>12904.5</v>
       </c>
       <c r="G1434" t="n">
         <v>1</v>
@@ -47782,10 +47782,10 @@
         <v>66.59999999999999</v>
       </c>
       <c r="E1435" t="n">
-        <v>2182.1</v>
+        <v>2236.8</v>
       </c>
       <c r="F1435" t="n">
-        <v>12873.1</v>
+        <v>12927.8</v>
       </c>
       <c r="G1435" t="n">
         <v>4</v>
@@ -47815,16 +47815,16 @@
         <v>60.1</v>
       </c>
       <c r="E1436" t="n">
-        <v>2080.8</v>
+        <v>2142.6</v>
       </c>
       <c r="F1436" t="n">
-        <v>11945.9</v>
+        <v>12007.7</v>
       </c>
       <c r="G1436" t="n">
         <v>6</v>
       </c>
       <c r="H1436" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1436" t="n">
         <v>4</v>
@@ -47848,10 +47848,10 @@
         <v>74.09999999999999</v>
       </c>
       <c r="E1437" t="n">
-        <v>1921.8</v>
+        <v>2003.4</v>
       </c>
       <c r="F1437" t="n">
-        <v>11586.4</v>
+        <v>11668</v>
       </c>
       <c r="G1437" t="n">
         <v>3</v>
@@ -47881,10 +47881,10 @@
         <v>57.4</v>
       </c>
       <c r="E1438" t="n">
-        <v>2313.9</v>
+        <v>2380.3</v>
       </c>
       <c r="F1438" t="n">
-        <v>13248.7</v>
+        <v>13315.1</v>
       </c>
       <c r="G1438" t="n">
         <v>7</v>
@@ -47914,10 +47914,10 @@
         <v>0</v>
       </c>
       <c r="E1439" t="n">
-        <v>1780.9</v>
+        <v>1850.8</v>
       </c>
       <c r="F1439" t="n">
-        <v>10614.8</v>
+        <v>10684.7</v>
       </c>
       <c r="G1439" t="n">
         <v>8</v>
@@ -47947,16 +47947,16 @@
         <v>65.90000000000001</v>
       </c>
       <c r="E1440" t="n">
-        <v>2079.4</v>
+        <v>2158.6</v>
       </c>
       <c r="F1440" t="n">
-        <v>11683.5</v>
+        <v>11762.7</v>
       </c>
       <c r="G1440" t="n">
         <v>5</v>
       </c>
       <c r="H1440" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1440" t="n">
         <v>5</v>
@@ -47980,10 +47980,10 @@
         <v>76</v>
       </c>
       <c r="E1441" t="n">
-        <v>2190.2</v>
+        <v>2253.1</v>
       </c>
       <c r="F1441" t="n">
-        <v>9725.200000000001</v>
+        <v>9788.1</v>
       </c>
       <c r="G1441" t="n">
         <v>2</v>
@@ -48013,10 +48013,10 @@
         <v>73.09999999999999</v>
       </c>
       <c r="E1442" t="n">
-        <v>2227.5</v>
+        <v>2266.5</v>
       </c>
       <c r="F1442" t="n">
-        <v>12938.6</v>
+        <v>12977.6</v>
       </c>
       <c r="G1442" t="n">
         <v>6</v>
@@ -48046,10 +48046,10 @@
         <v>92.90000000000001</v>
       </c>
       <c r="E1443" t="n">
-        <v>2275</v>
+        <v>2329.7</v>
       </c>
       <c r="F1443" t="n">
-        <v>12966</v>
+        <v>13020.7</v>
       </c>
       <c r="G1443" t="n">
         <v>2</v>
@@ -48079,10 +48079,10 @@
         <v>51.6</v>
       </c>
       <c r="E1444" t="n">
-        <v>2132.4</v>
+        <v>2194.2</v>
       </c>
       <c r="F1444" t="n">
-        <v>11997.5</v>
+        <v>12059.3</v>
       </c>
       <c r="G1444" t="n">
         <v>8</v>
@@ -48112,10 +48112,10 @@
         <v>62.1</v>
       </c>
       <c r="E1445" t="n">
-        <v>1983.9</v>
+        <v>2065.5</v>
       </c>
       <c r="F1445" t="n">
-        <v>11648.5</v>
+        <v>11730.1</v>
       </c>
       <c r="G1445" t="n">
         <v>7</v>
@@ -48145,10 +48145,10 @@
         <v>86.7</v>
       </c>
       <c r="E1446" t="n">
-        <v>2400.6</v>
+        <v>2467</v>
       </c>
       <c r="F1446" t="n">
-        <v>13335.4</v>
+        <v>13401.8</v>
       </c>
       <c r="G1446" t="n">
         <v>4</v>
@@ -48178,10 +48178,10 @@
         <v>88.2</v>
       </c>
       <c r="E1447" t="n">
-        <v>1869.1</v>
+        <v>1939</v>
       </c>
       <c r="F1447" t="n">
-        <v>10703</v>
+        <v>10772.9</v>
       </c>
       <c r="G1447" t="n">
         <v>3</v>
@@ -48211,10 +48211,10 @@
         <v>73.3</v>
       </c>
       <c r="E1448" t="n">
-        <v>2152.7</v>
+        <v>2231.9</v>
       </c>
       <c r="F1448" t="n">
-        <v>11756.8</v>
+        <v>11836</v>
       </c>
       <c r="G1448" t="n">
         <v>5</v>
@@ -48244,10 +48244,10 @@
         <v>100.9</v>
       </c>
       <c r="E1449" t="n">
-        <v>2291.1</v>
+        <v>2354</v>
       </c>
       <c r="F1449" t="n">
-        <v>9826.1</v>
+        <v>9889</v>
       </c>
       <c r="G1449" t="n">
         <v>1</v>
@@ -48277,10 +48277,10 @@
         <v>82.5</v>
       </c>
       <c r="E1450" t="n">
-        <v>2310</v>
+        <v>2349</v>
       </c>
       <c r="F1450" t="n">
-        <v>13021.1</v>
+        <v>13060.1</v>
       </c>
       <c r="G1450" t="n">
         <v>3</v>
@@ -48310,10 +48310,10 @@
         <v>73.5</v>
       </c>
       <c r="E1451" t="n">
-        <v>2348.5</v>
+        <v>2403.2</v>
       </c>
       <c r="F1451" t="n">
-        <v>13039.5</v>
+        <v>13094.2</v>
       </c>
       <c r="G1451" t="n">
         <v>4</v>
@@ -48343,10 +48343,10 @@
         <v>114.5</v>
       </c>
       <c r="E1452" t="n">
-        <v>2246.9</v>
+        <v>2308.7</v>
       </c>
       <c r="F1452" t="n">
-        <v>12112</v>
+        <v>12173.8</v>
       </c>
       <c r="G1452" t="n">
         <v>1</v>
@@ -48376,10 +48376,10 @@
         <v>85.90000000000001</v>
       </c>
       <c r="E1453" t="n">
-        <v>2069.8</v>
+        <v>2151.4</v>
       </c>
       <c r="F1453" t="n">
-        <v>11734.4</v>
+        <v>11816</v>
       </c>
       <c r="G1453" t="n">
         <v>2</v>
@@ -48409,10 +48409,10 @@
         <v>48.6</v>
       </c>
       <c r="E1454" t="n">
-        <v>2449.2</v>
+        <v>2515.6</v>
       </c>
       <c r="F1454" t="n">
-        <v>13384</v>
+        <v>13450.4</v>
       </c>
       <c r="G1454" t="n">
         <v>6</v>
@@ -48442,10 +48442,10 @@
         <v>52.8</v>
       </c>
       <c r="E1455" t="n">
-        <v>1921.9</v>
+        <v>1991.8</v>
       </c>
       <c r="F1455" t="n">
-        <v>10755.8</v>
+        <v>10825.7</v>
       </c>
       <c r="G1455" t="n">
         <v>5</v>
@@ -48475,10 +48475,10 @@
         <v>47.9</v>
       </c>
       <c r="E1456" t="n">
-        <v>2200.6</v>
+        <v>2279.8</v>
       </c>
       <c r="F1456" t="n">
-        <v>11804.7</v>
+        <v>11883.9</v>
       </c>
       <c r="G1456" t="n">
         <v>7</v>
@@ -48508,10 +48508,10 @@
         <v>43.3</v>
       </c>
       <c r="E1457" t="n">
-        <v>2334.4</v>
+        <v>2397.3</v>
       </c>
       <c r="F1457" t="n">
-        <v>9869.4</v>
+        <v>9932.299999999999</v>
       </c>
       <c r="G1457" t="n">
         <v>8</v>
@@ -48541,10 +48541,10 @@
         <v>66.5</v>
       </c>
       <c r="E1458" t="n">
-        <v>2376.5</v>
+        <v>2415.5</v>
       </c>
       <c r="F1458" t="n">
-        <v>13087.6</v>
+        <v>13126.6</v>
       </c>
       <c r="G1458" t="n">
         <v>5</v>
@@ -48574,10 +48574,10 @@
         <v>65.5</v>
       </c>
       <c r="E1459" t="n">
-        <v>2414</v>
+        <v>2468.7</v>
       </c>
       <c r="F1459" t="n">
-        <v>13105</v>
+        <v>13159.7</v>
       </c>
       <c r="G1459" t="n">
         <v>7</v>
@@ -48607,10 +48607,10 @@
         <v>83.90000000000001</v>
       </c>
       <c r="E1460" t="n">
-        <v>2330.8</v>
+        <v>2392.6</v>
       </c>
       <c r="F1460" t="n">
-        <v>12195.9</v>
+        <v>12257.7</v>
       </c>
       <c r="G1460" t="n">
         <v>3</v>
@@ -48640,10 +48640,10 @@
         <v>66.40000000000001</v>
       </c>
       <c r="E1461" t="n">
-        <v>2136.2</v>
+        <v>2217.8</v>
       </c>
       <c r="F1461" t="n">
-        <v>11800.8</v>
+        <v>11882.4</v>
       </c>
       <c r="G1461" t="n">
         <v>6</v>
@@ -48673,10 +48673,10 @@
         <v>107</v>
       </c>
       <c r="E1462" t="n">
-        <v>2556.2</v>
+        <v>2622.6</v>
       </c>
       <c r="F1462" t="n">
-        <v>13491</v>
+        <v>13557.4</v>
       </c>
       <c r="G1462" t="n">
         <v>1</v>
@@ -48706,10 +48706,10 @@
         <v>46.5</v>
       </c>
       <c r="E1463" t="n">
-        <v>1968.4</v>
+        <v>2038.3</v>
       </c>
       <c r="F1463" t="n">
-        <v>10802.3</v>
+        <v>10872.2</v>
       </c>
       <c r="G1463" t="n">
         <v>8</v>
@@ -48739,10 +48739,10 @@
         <v>67.40000000000001</v>
       </c>
       <c r="E1464" t="n">
-        <v>2268</v>
+        <v>2347.2</v>
       </c>
       <c r="F1464" t="n">
-        <v>11872.1</v>
+        <v>11951.3</v>
       </c>
       <c r="G1464" t="n">
         <v>4</v>
@@ -48772,10 +48772,10 @@
         <v>85.59999999999999</v>
       </c>
       <c r="E1465" t="n">
-        <v>2420</v>
+        <v>2482.9</v>
       </c>
       <c r="F1465" t="n">
-        <v>9955</v>
+        <v>10017.9</v>
       </c>
       <c r="G1465" t="n">
         <v>2</v>
@@ -48805,10 +48805,10 @@
         <v>100.6</v>
       </c>
       <c r="E1466" t="n">
-        <v>2477.1</v>
+        <v>2516.1</v>
       </c>
       <c r="F1466" t="n">
-        <v>13188.2</v>
+        <v>13227.2</v>
       </c>
       <c r="G1466" t="n">
         <v>1</v>
@@ -48838,10 +48838,10 @@
         <v>65.90000000000001</v>
       </c>
       <c r="E1467" t="n">
-        <v>2479.9</v>
+        <v>2534.6</v>
       </c>
       <c r="F1467" t="n">
-        <v>13170.9</v>
+        <v>13225.6</v>
       </c>
       <c r="G1467" t="n">
         <v>5</v>
@@ -48871,10 +48871,10 @@
         <v>70.8</v>
       </c>
       <c r="E1468" t="n">
-        <v>2401.6</v>
+        <v>2463.4</v>
       </c>
       <c r="F1468" t="n">
-        <v>12266.7</v>
+        <v>12328.5</v>
       </c>
       <c r="G1468" t="n">
         <v>4</v>
@@ -48904,10 +48904,10 @@
         <v>60.5</v>
       </c>
       <c r="E1469" t="n">
-        <v>2196.7</v>
+        <v>2278.3</v>
       </c>
       <c r="F1469" t="n">
-        <v>11861.3</v>
+        <v>11942.9</v>
       </c>
       <c r="G1469" t="n">
         <v>7</v>
@@ -48937,10 +48937,10 @@
         <v>64.59999999999999</v>
       </c>
       <c r="E1470" t="n">
-        <v>2620.8</v>
+        <v>2687.2</v>
       </c>
       <c r="F1470" t="n">
-        <v>13555.6</v>
+        <v>13622</v>
       </c>
       <c r="G1470" t="n">
         <v>6</v>
@@ -48970,10 +48970,10 @@
         <v>73.7</v>
       </c>
       <c r="E1471" t="n">
-        <v>2042.1</v>
+        <v>2112</v>
       </c>
       <c r="F1471" t="n">
-        <v>10876</v>
+        <v>10945.9</v>
       </c>
       <c r="G1471" t="n">
         <v>3</v>
@@ -49003,10 +49003,10 @@
         <v>55.2</v>
       </c>
       <c r="E1472" t="n">
-        <v>2323.2</v>
+        <v>2402.4</v>
       </c>
       <c r="F1472" t="n">
-        <v>11927.3</v>
+        <v>12006.5</v>
       </c>
       <c r="G1472" t="n">
         <v>8</v>
@@ -49036,10 +49036,10 @@
         <v>88</v>
       </c>
       <c r="E1473" t="n">
-        <v>2508</v>
+        <v>2570.9</v>
       </c>
       <c r="F1473" t="n">
-        <v>10043</v>
+        <v>10105.9</v>
       </c>
       <c r="G1473" t="n">
         <v>2</v>
@@ -49069,10 +49069,10 @@
         <v>70.09999999999999</v>
       </c>
       <c r="E1474" t="n">
-        <v>2547.2</v>
+        <v>2586.2</v>
       </c>
       <c r="F1474" t="n">
-        <v>13258.3</v>
+        <v>13297.3</v>
       </c>
       <c r="G1474" t="n">
         <v>4</v>
@@ -49081,7 +49081,7 @@
         <v>4</v>
       </c>
       <c r="I1474" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1475">
@@ -49102,10 +49102,10 @@
         <v>77.90000000000001</v>
       </c>
       <c r="E1475" t="n">
-        <v>2557.8</v>
+        <v>2612.5</v>
       </c>
       <c r="F1475" t="n">
-        <v>13248.8</v>
+        <v>13303.5</v>
       </c>
       <c r="G1475" t="n">
         <v>3</v>
@@ -49114,7 +49114,7 @@
         <v>3</v>
       </c>
       <c r="I1475" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1476">
@@ -49135,10 +49135,10 @@
         <v>80.8</v>
       </c>
       <c r="E1476" t="n">
-        <v>2482.4</v>
+        <v>2544.2</v>
       </c>
       <c r="F1476" t="n">
-        <v>12347.5</v>
+        <v>12409.3</v>
       </c>
       <c r="G1476" t="n">
         <v>2</v>
@@ -49168,10 +49168,10 @@
         <v>53</v>
       </c>
       <c r="E1477" t="n">
-        <v>2249.7</v>
+        <v>2331.3</v>
       </c>
       <c r="F1477" t="n">
-        <v>11914.3</v>
+        <v>11995.9</v>
       </c>
       <c r="G1477" t="n">
         <v>7</v>
@@ -49201,10 +49201,10 @@
         <v>59.8</v>
       </c>
       <c r="E1478" t="n">
-        <v>2680.6</v>
+        <v>2747</v>
       </c>
       <c r="F1478" t="n">
-        <v>13615.4</v>
+        <v>13681.8</v>
       </c>
       <c r="G1478" t="n">
         <v>6</v>
@@ -49234,10 +49234,10 @@
         <v>68.39999999999999</v>
       </c>
       <c r="E1479" t="n">
-        <v>2110.5</v>
+        <v>2180.4</v>
       </c>
       <c r="F1479" t="n">
-        <v>10944.4</v>
+        <v>11014.3</v>
       </c>
       <c r="G1479" t="n">
         <v>5</v>
@@ -49267,10 +49267,10 @@
         <v>48.4</v>
       </c>
       <c r="E1480" t="n">
-        <v>2371.6</v>
+        <v>2450.8</v>
       </c>
       <c r="F1480" t="n">
-        <v>11975.7</v>
+        <v>12054.9</v>
       </c>
       <c r="G1480" t="n">
         <v>8</v>
@@ -49300,10 +49300,10 @@
         <v>104.8</v>
       </c>
       <c r="E1481" t="n">
-        <v>2612.8</v>
+        <v>2675.7</v>
       </c>
       <c r="F1481" t="n">
-        <v>10147.8</v>
+        <v>10210.7</v>
       </c>
       <c r="G1481" t="n">
         <v>1</v>
@@ -49333,10 +49333,10 @@
         <v>76.3</v>
       </c>
       <c r="E1482" t="n">
-        <v>2623.5</v>
+        <v>2662.5</v>
       </c>
       <c r="F1482" t="n">
-        <v>13334.6</v>
+        <v>13373.6</v>
       </c>
       <c r="G1482" t="n">
         <v>3</v>
@@ -49345,7 +49345,7 @@
         <v>4</v>
       </c>
       <c r="I1482" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1483">
@@ -49366,10 +49366,10 @@
         <v>73.3</v>
       </c>
       <c r="E1483" t="n">
-        <v>2631.1</v>
+        <v>2685.8</v>
       </c>
       <c r="F1483" t="n">
-        <v>13322.1</v>
+        <v>13376.8</v>
       </c>
       <c r="G1483" t="n">
         <v>5</v>
@@ -49378,7 +49378,7 @@
         <v>3</v>
       </c>
       <c r="I1483" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1484">
@@ -49399,10 +49399,10 @@
         <v>56.5</v>
       </c>
       <c r="E1484" t="n">
-        <v>2538.9</v>
+        <v>2600.7</v>
       </c>
       <c r="F1484" t="n">
-        <v>12404</v>
+        <v>12465.8</v>
       </c>
       <c r="G1484" t="n">
         <v>7</v>
@@ -49432,10 +49432,10 @@
         <v>75.09999999999999</v>
       </c>
       <c r="E1485" t="n">
-        <v>2324.8</v>
+        <v>2406.4</v>
       </c>
       <c r="F1485" t="n">
-        <v>11989.4</v>
+        <v>12071</v>
       </c>
       <c r="G1485" t="n">
         <v>4</v>
@@ -49465,10 +49465,10 @@
         <v>69.7</v>
       </c>
       <c r="E1486" t="n">
-        <v>2750.3</v>
+        <v>2816.7</v>
       </c>
       <c r="F1486" t="n">
-        <v>13685.1</v>
+        <v>13751.5</v>
       </c>
       <c r="G1486" t="n">
         <v>6</v>
@@ -49498,10 +49498,10 @@
         <v>80.09999999999999</v>
       </c>
       <c r="E1487" t="n">
-        <v>2190.6</v>
+        <v>2260.5</v>
       </c>
       <c r="F1487" t="n">
-        <v>11024.5</v>
+        <v>11094.4</v>
       </c>
       <c r="G1487" t="n">
         <v>2</v>
@@ -49531,10 +49531,10 @@
         <v>44.90000000000001</v>
       </c>
       <c r="E1488" t="n">
-        <v>2416.5</v>
+        <v>2495.7</v>
       </c>
       <c r="F1488" t="n">
-        <v>12020.6</v>
+        <v>12099.8</v>
       </c>
       <c r="G1488" t="n">
         <v>8</v>
@@ -49564,10 +49564,10 @@
         <v>82.40000000000001</v>
       </c>
       <c r="E1489" t="n">
-        <v>2695.2</v>
+        <v>2758.1</v>
       </c>
       <c r="F1489" t="n">
-        <v>10230.2</v>
+        <v>10293.1</v>
       </c>
       <c r="G1489" t="n">
         <v>1</v>
@@ -49597,10 +49597,10 @@
         <v>94.09999999999999</v>
       </c>
       <c r="E1490" t="n">
-        <v>2717.6</v>
+        <v>2756.6</v>
       </c>
       <c r="F1490" t="n">
-        <v>13428.7</v>
+        <v>13467.7</v>
       </c>
       <c r="G1490" t="n">
         <v>3</v>
@@ -49609,7 +49609,7 @@
         <v>4</v>
       </c>
       <c r="I1490" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1491">
@@ -49630,10 +49630,10 @@
         <v>94.90000000000001</v>
       </c>
       <c r="E1491" t="n">
-        <v>2726</v>
+        <v>2780.7</v>
       </c>
       <c r="F1491" t="n">
-        <v>13417</v>
+        <v>13471.7</v>
       </c>
       <c r="G1491" t="n">
         <v>2</v>
@@ -49642,7 +49642,7 @@
         <v>3</v>
       </c>
       <c r="I1491" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1492">
@@ -49663,10 +49663,10 @@
         <v>75.2</v>
       </c>
       <c r="E1492" t="n">
-        <v>2614.1</v>
+        <v>2675.9</v>
       </c>
       <c r="F1492" t="n">
-        <v>12479.2</v>
+        <v>12541</v>
       </c>
       <c r="G1492" t="n">
         <v>5</v>
@@ -49696,10 +49696,10 @@
         <v>38.3</v>
       </c>
       <c r="E1493" t="n">
-        <v>2363.1</v>
+        <v>2444.7</v>
       </c>
       <c r="F1493" t="n">
-        <v>12027.7</v>
+        <v>12109.3</v>
       </c>
       <c r="G1493" t="n">
         <v>8</v>
@@ -49729,10 +49729,10 @@
         <v>52.9</v>
       </c>
       <c r="E1494" t="n">
-        <v>2803.2</v>
+        <v>2869.6</v>
       </c>
       <c r="F1494" t="n">
-        <v>13738</v>
+        <v>13804.4</v>
       </c>
       <c r="G1494" t="n">
         <v>6</v>
@@ -49762,10 +49762,10 @@
         <v>78.7</v>
       </c>
       <c r="E1495" t="n">
-        <v>2269.3</v>
+        <v>2339.2</v>
       </c>
       <c r="F1495" t="n">
-        <v>11103.2</v>
+        <v>11173.1</v>
       </c>
       <c r="G1495" t="n">
         <v>4</v>
@@ -49795,10 +49795,10 @@
         <v>44.4</v>
       </c>
       <c r="E1496" t="n">
-        <v>2460.9</v>
+        <v>2540.1</v>
       </c>
       <c r="F1496" t="n">
-        <v>12065</v>
+        <v>12144.2</v>
       </c>
       <c r="G1496" t="n">
         <v>7</v>
@@ -49828,10 +49828,10 @@
         <v>95.3</v>
       </c>
       <c r="E1497" t="n">
-        <v>2790.5</v>
+        <v>2853.4</v>
       </c>
       <c r="F1497" t="n">
-        <v>10325.5</v>
+        <v>10388.4</v>
       </c>
       <c r="G1497" t="n">
         <v>1</v>
@@ -49861,10 +49861,10 @@
         <v>72.8</v>
       </c>
       <c r="E1498" t="n">
-        <v>2790.4</v>
+        <v>2829.4</v>
       </c>
       <c r="F1498" t="n">
-        <v>13501.5</v>
+        <v>13540.5</v>
       </c>
       <c r="G1498" t="n">
         <v>2</v>
@@ -49894,10 +49894,10 @@
         <v>42</v>
       </c>
       <c r="E1499" t="n">
-        <v>2768</v>
+        <v>2822.7</v>
       </c>
       <c r="F1499" t="n">
-        <v>13459</v>
+        <v>13513.7</v>
       </c>
       <c r="G1499" t="n">
         <v>7</v>
@@ -49927,10 +49927,10 @@
         <v>65.10000000000001</v>
       </c>
       <c r="E1500" t="n">
-        <v>2679.2</v>
+        <v>2741</v>
       </c>
       <c r="F1500" t="n">
-        <v>12544.3</v>
+        <v>12606.1</v>
       </c>
       <c r="G1500" t="n">
         <v>5</v>
@@ -49960,10 +49960,10 @@
         <v>39.8</v>
       </c>
       <c r="E1501" t="n">
-        <v>2402.9</v>
+        <v>2484.5</v>
       </c>
       <c r="F1501" t="n">
-        <v>12067.5</v>
+        <v>12149.1</v>
       </c>
       <c r="G1501" t="n">
         <v>8</v>
@@ -49993,16 +49993,16 @@
         <v>65.8</v>
       </c>
       <c r="E1502" t="n">
-        <v>2869</v>
+        <v>2935.4</v>
       </c>
       <c r="F1502" t="n">
-        <v>13803.8</v>
+        <v>13870.2</v>
       </c>
       <c r="G1502" t="n">
         <v>4</v>
       </c>
       <c r="H1502" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1502" t="n">
         <v>1</v>
@@ -50026,10 +50026,10 @@
         <v>66.40000000000001</v>
       </c>
       <c r="E1503" t="n">
-        <v>2335.7</v>
+        <v>2405.6</v>
       </c>
       <c r="F1503" t="n">
-        <v>11169.6</v>
+        <v>11239.5</v>
       </c>
       <c r="G1503" t="n">
         <v>3</v>
@@ -50059,10 +50059,10 @@
         <v>52.7</v>
       </c>
       <c r="E1504" t="n">
-        <v>2513.6</v>
+        <v>2592.8</v>
       </c>
       <c r="F1504" t="n">
-        <v>12117.7</v>
+        <v>12196.9</v>
       </c>
       <c r="G1504" t="n">
         <v>6</v>
@@ -50092,16 +50092,16 @@
         <v>81.3</v>
       </c>
       <c r="E1505" t="n">
-        <v>2871.8</v>
+        <v>2934.7</v>
       </c>
       <c r="F1505" t="n">
-        <v>10406.8</v>
+        <v>10469.7</v>
       </c>
       <c r="G1505" t="n">
         <v>1</v>
       </c>
       <c r="H1505" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1505" t="n">
         <v>8</v>
@@ -50125,10 +50125,10 @@
         <v>70.59999999999999</v>
       </c>
       <c r="E1506" t="n">
-        <v>2861</v>
+        <v>2900</v>
       </c>
       <c r="F1506" t="n">
-        <v>13572.1</v>
+        <v>13611.1</v>
       </c>
       <c r="G1506" t="n">
         <v>4</v>
@@ -50158,10 +50158,10 @@
         <v>76.40000000000001</v>
       </c>
       <c r="E1507" t="n">
-        <v>2844.4</v>
+        <v>2899.1</v>
       </c>
       <c r="F1507" t="n">
-        <v>13535.4</v>
+        <v>13590.1</v>
       </c>
       <c r="G1507" t="n">
         <v>2</v>
@@ -50191,10 +50191,10 @@
         <v>60.3</v>
       </c>
       <c r="E1508" t="n">
-        <v>2739.5</v>
+        <v>2801.3</v>
       </c>
       <c r="F1508" t="n">
-        <v>12604.6</v>
+        <v>12666.4</v>
       </c>
       <c r="G1508" t="n">
         <v>6</v>
@@ -50224,10 +50224,10 @@
         <v>60.4</v>
       </c>
       <c r="E1509" t="n">
-        <v>2463.3</v>
+        <v>2544.9</v>
       </c>
       <c r="F1509" t="n">
-        <v>12127.9</v>
+        <v>12209.5</v>
       </c>
       <c r="G1509" t="n">
         <v>5</v>
@@ -50257,10 +50257,10 @@
         <v>53.9</v>
       </c>
       <c r="E1510" t="n">
-        <v>2922.9</v>
+        <v>2989.3</v>
       </c>
       <c r="F1510" t="n">
-        <v>13857.7</v>
+        <v>13924.1</v>
       </c>
       <c r="G1510" t="n">
         <v>7</v>
@@ -50290,10 +50290,10 @@
         <v>75.80000000000001</v>
       </c>
       <c r="E1511" t="n">
-        <v>2411.5</v>
+        <v>2481.4</v>
       </c>
       <c r="F1511" t="n">
-        <v>11245.4</v>
+        <v>11315.3</v>
       </c>
       <c r="G1511" t="n">
         <v>3</v>
@@ -50323,10 +50323,10 @@
         <v>53.2</v>
       </c>
       <c r="E1512" t="n">
-        <v>2566.8</v>
+        <v>2646</v>
       </c>
       <c r="F1512" t="n">
-        <v>12170.9</v>
+        <v>12250.1</v>
       </c>
       <c r="G1512" t="n">
         <v>8</v>
@@ -50356,10 +50356,10 @@
         <v>87.59999999999999</v>
       </c>
       <c r="E1513" t="n">
-        <v>2959.4</v>
+        <v>3022.3</v>
       </c>
       <c r="F1513" t="n">
-        <v>10494.4</v>
+        <v>10557.3</v>
       </c>
       <c r="G1513" t="n">
         <v>1</v>
@@ -50389,10 +50389,10 @@
         <v>58.2</v>
       </c>
       <c r="E1514" t="n">
-        <v>2919.2</v>
+        <v>2958.2</v>
       </c>
       <c r="F1514" t="n">
-        <v>13630.3</v>
+        <v>13669.3</v>
       </c>
       <c r="G1514" t="n">
         <v>4</v>
@@ -50422,10 +50422,10 @@
         <v>49.3</v>
       </c>
       <c r="E1515" t="n">
-        <v>2893.7</v>
+        <v>2948.4</v>
       </c>
       <c r="F1515" t="n">
-        <v>13584.7</v>
+        <v>13639.4</v>
       </c>
       <c r="G1515" t="n">
         <v>5</v>
@@ -50455,10 +50455,10 @@
         <v>69.09999999999999</v>
       </c>
       <c r="E1516" t="n">
-        <v>2808.6</v>
+        <v>2870.4</v>
       </c>
       <c r="F1516" t="n">
-        <v>12673.7</v>
+        <v>12735.5</v>
       </c>
       <c r="G1516" t="n">
         <v>3</v>
@@ -50488,10 +50488,10 @@
         <v>48.4</v>
       </c>
       <c r="E1517" t="n">
-        <v>2511.7</v>
+        <v>2593.3</v>
       </c>
       <c r="F1517" t="n">
-        <v>12176.3</v>
+        <v>12257.9</v>
       </c>
       <c r="G1517" t="n">
         <v>6</v>
@@ -50521,10 +50521,10 @@
         <v>47.6</v>
       </c>
       <c r="E1518" t="n">
-        <v>2970.5</v>
+        <v>3036.9</v>
       </c>
       <c r="F1518" t="n">
-        <v>13905.3</v>
+        <v>13971.7</v>
       </c>
       <c r="G1518" t="n">
         <v>7</v>
@@ -50554,10 +50554,10 @@
         <v>34.8</v>
       </c>
       <c r="E1519" t="n">
-        <v>2446.3</v>
+        <v>2516.2</v>
       </c>
       <c r="F1519" t="n">
-        <v>11280.2</v>
+        <v>11350.1</v>
       </c>
       <c r="G1519" t="n">
         <v>8</v>
@@ -50587,10 +50587,10 @@
         <v>73.3</v>
       </c>
       <c r="E1520" t="n">
-        <v>2640.1</v>
+        <v>2719.3</v>
       </c>
       <c r="F1520" t="n">
-        <v>12244.2</v>
+        <v>12323.4</v>
       </c>
       <c r="G1520" t="n">
         <v>2</v>
@@ -50620,10 +50620,10 @@
         <v>97.7</v>
       </c>
       <c r="E1521" t="n">
-        <v>3057.1</v>
+        <v>3120</v>
       </c>
       <c r="F1521" t="n">
-        <v>10592.1</v>
+        <v>10655</v>
       </c>
       <c r="G1521" t="n">
         <v>1</v>
@@ -50653,10 +50653,10 @@
         <v>95.7</v>
       </c>
       <c r="E1522" t="n">
-        <v>3014.9</v>
+        <v>3053.9</v>
       </c>
       <c r="F1522" t="n">
-        <v>13726</v>
+        <v>13765</v>
       </c>
       <c r="G1522" t="n">
         <v>1</v>
@@ -50686,10 +50686,10 @@
         <v>0</v>
       </c>
       <c r="E1523" t="n">
-        <v>2893.7</v>
+        <v>2948.4</v>
       </c>
       <c r="F1523" t="n">
-        <v>13584.7</v>
+        <v>13639.4</v>
       </c>
       <c r="G1523" t="n">
         <v>8</v>
@@ -50719,10 +50719,10 @@
         <v>40.7</v>
       </c>
       <c r="E1524" t="n">
-        <v>2849.3</v>
+        <v>2911.1</v>
       </c>
       <c r="F1524" t="n">
-        <v>12714.4</v>
+        <v>12776.2</v>
       </c>
       <c r="G1524" t="n">
         <v>7</v>
@@ -50752,10 +50752,10 @@
         <v>68.2</v>
       </c>
       <c r="E1525" t="n">
-        <v>2579.9</v>
+        <v>2661.5</v>
       </c>
       <c r="F1525" t="n">
-        <v>12244.5</v>
+        <v>12326.1</v>
       </c>
       <c r="G1525" t="n">
         <v>4</v>
@@ -50785,10 +50785,10 @@
         <v>66.59999999999999</v>
       </c>
       <c r="E1526" t="n">
-        <v>3037.1</v>
+        <v>3103.5</v>
       </c>
       <c r="F1526" t="n">
-        <v>13971.9</v>
+        <v>14038.3</v>
       </c>
       <c r="G1526" t="n">
         <v>5</v>
@@ -50818,10 +50818,10 @@
         <v>80.59999999999999</v>
       </c>
       <c r="E1527" t="n">
-        <v>2526.9</v>
+        <v>2596.8</v>
       </c>
       <c r="F1527" t="n">
-        <v>11360.8</v>
+        <v>11430.7</v>
       </c>
       <c r="G1527" t="n">
         <v>2</v>
@@ -50851,10 +50851,10 @@
         <v>46.4</v>
       </c>
       <c r="E1528" t="n">
-        <v>2686.5</v>
+        <v>2765.7</v>
       </c>
       <c r="F1528" t="n">
-        <v>12290.6</v>
+        <v>12369.8</v>
       </c>
       <c r="G1528" t="n">
         <v>6</v>
@@ -50884,10 +50884,10 @@
         <v>80.40000000000001</v>
       </c>
       <c r="E1529" t="n">
-        <v>3137.5</v>
+        <v>3200.4</v>
       </c>
       <c r="F1529" t="n">
-        <v>10672.5</v>
+        <v>10735.4</v>
       </c>
       <c r="G1529" t="n">
         <v>3</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -42436,7 +42436,7 @@
         <v>98.09999999999999</v>
       </c>
       <c r="E1273" t="n">
-        <v>649.7</v>
+        <v>649.6999999999999</v>
       </c>
       <c r="F1273" t="n">
         <v>8184.7</v>
@@ -43228,7 +43228,7 @@
         <v>76.89999999999999</v>
       </c>
       <c r="E1297" t="n">
-        <v>907.7</v>
+        <v>907.6999999999999</v>
       </c>
       <c r="F1297" t="n">
         <v>8442.700000000001</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -42436,7 +42436,7 @@
         <v>98.09999999999999</v>
       </c>
       <c r="E1273" t="n">
-        <v>649.6999999999999</v>
+        <v>649.7</v>
       </c>
       <c r="F1273" t="n">
         <v>8184.7</v>
@@ -42997,7 +42997,7 @@
         <v>87.8</v>
       </c>
       <c r="E1290" t="n">
-        <v>807.2</v>
+        <v>807.1999999999999</v>
       </c>
       <c r="F1290" t="n">
         <v>11518.3</v>
@@ -43228,7 +43228,7 @@
         <v>76.89999999999999</v>
       </c>
       <c r="E1297" t="n">
-        <v>907.6999999999999</v>
+        <v>907.7</v>
       </c>
       <c r="F1297" t="n">
         <v>8442.700000000001</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -42997,7 +42997,7 @@
         <v>87.8</v>
       </c>
       <c r="E1290" t="n">
-        <v>807.1999999999999</v>
+        <v>807.2</v>
       </c>
       <c r="F1290" t="n">
         <v>11518.3</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -42436,7 +42436,7 @@
         <v>98.09999999999999</v>
       </c>
       <c r="E1273" t="n">
-        <v>649.7</v>
+        <v>649.6999999999999</v>
       </c>
       <c r="F1273" t="n">
         <v>8184.7</v>
@@ -42997,7 +42997,7 @@
         <v>87.8</v>
       </c>
       <c r="E1290" t="n">
-        <v>807.2</v>
+        <v>807.1999999999999</v>
       </c>
       <c r="F1290" t="n">
         <v>11518.3</v>
@@ -43228,7 +43228,7 @@
         <v>76.89999999999999</v>
       </c>
       <c r="E1297" t="n">
-        <v>907.7</v>
+        <v>907.6999999999999</v>
       </c>
       <c r="F1297" t="n">
         <v>8442.700000000001</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -42436,7 +42436,7 @@
         <v>98.09999999999999</v>
       </c>
       <c r="E1273" t="n">
-        <v>649.6999999999999</v>
+        <v>649.7</v>
       </c>
       <c r="F1273" t="n">
         <v>8184.7</v>
@@ -42997,7 +42997,7 @@
         <v>87.8</v>
       </c>
       <c r="E1290" t="n">
-        <v>807.1999999999999</v>
+        <v>807.2</v>
       </c>
       <c r="F1290" t="n">
         <v>11518.3</v>
@@ -43228,7 +43228,7 @@
         <v>76.89999999999999</v>
       </c>
       <c r="E1297" t="n">
-        <v>907.6999999999999</v>
+        <v>907.7</v>
       </c>
       <c r="F1297" t="n">
         <v>8442.700000000001</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -42172,7 +42172,7 @@
         <v>114.8</v>
       </c>
       <c r="E1265" t="n">
-        <v>551.6</v>
+        <v>551.5999999999999</v>
       </c>
       <c r="F1265" t="n">
         <v>8086.6</v>
@@ -42436,7 +42436,7 @@
         <v>98.09999999999999</v>
       </c>
       <c r="E1273" t="n">
-        <v>649.7</v>
+        <v>649.6999999999999</v>
       </c>
       <c r="F1273" t="n">
         <v>8184.7</v>
@@ -43228,7 +43228,7 @@
         <v>76.89999999999999</v>
       </c>
       <c r="E1297" t="n">
-        <v>907.7</v>
+        <v>907.6999999999999</v>
       </c>
       <c r="F1297" t="n">
         <v>8442.700000000001</v>
@@ -43492,7 +43492,7 @@
         <v>66.3</v>
       </c>
       <c r="E1305" t="n">
-        <v>974</v>
+        <v>973.9999999999999</v>
       </c>
       <c r="F1305" t="n">
         <v>8509</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -42172,7 +42172,7 @@
         <v>114.8</v>
       </c>
       <c r="E1265" t="n">
-        <v>551.5999999999999</v>
+        <v>551.6</v>
       </c>
       <c r="F1265" t="n">
         <v>8086.6</v>
@@ -42436,7 +42436,7 @@
         <v>98.09999999999999</v>
       </c>
       <c r="E1273" t="n">
-        <v>649.6999999999999</v>
+        <v>649.7</v>
       </c>
       <c r="F1273" t="n">
         <v>8184.7</v>
@@ -43228,7 +43228,7 @@
         <v>76.89999999999999</v>
       </c>
       <c r="E1297" t="n">
-        <v>907.6999999999999</v>
+        <v>907.7</v>
       </c>
       <c r="F1297" t="n">
         <v>8442.700000000001</v>
@@ -43492,7 +43492,7 @@
         <v>66.3</v>
       </c>
       <c r="E1305" t="n">
-        <v>973.9999999999999</v>
+        <v>974</v>
       </c>
       <c r="F1305" t="n">
         <v>8509</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -42172,7 +42172,7 @@
         <v>114.8</v>
       </c>
       <c r="E1265" t="n">
-        <v>551.5999999999999</v>
+        <v>551.6</v>
       </c>
       <c r="F1265" t="n">
         <v>8086.6</v>
@@ -42997,7 +42997,7 @@
         <v>87.8</v>
       </c>
       <c r="E1290" t="n">
-        <v>807.2</v>
+        <v>807.1999999999999</v>
       </c>
       <c r="F1290" t="n">
         <v>11518.3</v>
@@ -43492,7 +43492,7 @@
         <v>66.3</v>
       </c>
       <c r="E1305" t="n">
-        <v>973.9999999999999</v>
+        <v>974</v>
       </c>
       <c r="F1305" t="n">
         <v>8509</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -42997,7 +42997,7 @@
         <v>87.8</v>
       </c>
       <c r="E1290" t="n">
-        <v>807.2</v>
+        <v>807.1999999999999</v>
       </c>
       <c r="F1290" t="n">
         <v>11518.3</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -42436,7 +42436,7 @@
         <v>98.09999999999999</v>
       </c>
       <c r="E1273" t="n">
-        <v>649.7</v>
+        <v>649.6999999999999</v>
       </c>
       <c r="F1273" t="n">
         <v>8184.7</v>
@@ -42997,7 +42997,7 @@
         <v>87.8</v>
       </c>
       <c r="E1290" t="n">
-        <v>807.1999999999999</v>
+        <v>807.2</v>
       </c>
       <c r="F1290" t="n">
         <v>11518.3</v>
@@ -43228,7 +43228,7 @@
         <v>76.89999999999999</v>
       </c>
       <c r="E1297" t="n">
-        <v>907.7</v>
+        <v>907.6999999999999</v>
       </c>
       <c r="F1297" t="n">
         <v>8442.700000000001</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -42730,13 +42730,13 @@
         </is>
       </c>
       <c r="D1282" t="n">
-        <v>53.8</v>
+        <v>116.1</v>
       </c>
       <c r="E1282" t="n">
-        <v>719.4</v>
+        <v>781.7</v>
       </c>
       <c r="F1282" t="n">
-        <v>11430.5</v>
+        <v>11492.8</v>
       </c>
       <c r="G1282" t="n">
         <v>7</v>
@@ -42763,16 +42763,16 @@
         </is>
       </c>
       <c r="D1283" t="n">
-        <v>51.1</v>
+        <v>126.9</v>
       </c>
       <c r="E1283" t="n">
-        <v>881.2</v>
+        <v>957</v>
       </c>
       <c r="F1283" t="n">
-        <v>11572.2</v>
+        <v>11648</v>
       </c>
       <c r="G1283" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H1283" t="n">
         <v>4</v>
@@ -42796,16 +42796,16 @@
         </is>
       </c>
       <c r="D1284" t="n">
-        <v>62.1</v>
+        <v>137.3</v>
       </c>
       <c r="E1284" t="n">
-        <v>895.4</v>
+        <v>970.6</v>
       </c>
       <c r="F1284" t="n">
-        <v>10760.5</v>
+        <v>10835.7</v>
       </c>
       <c r="G1284" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1284" t="n">
         <v>3</v>
@@ -42829,16 +42829,16 @@
         </is>
       </c>
       <c r="D1285" t="n">
-        <v>69.5</v>
+        <v>120.6</v>
       </c>
       <c r="E1285" t="n">
-        <v>945.3</v>
+        <v>996.4</v>
       </c>
       <c r="F1285" t="n">
-        <v>10609.9</v>
+        <v>10661</v>
       </c>
       <c r="G1285" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H1285" t="n">
         <v>2</v>
@@ -42862,16 +42862,16 @@
         </is>
       </c>
       <c r="D1286" t="n">
-        <v>59.5</v>
+        <v>139</v>
       </c>
       <c r="E1286" t="n">
-        <v>1000</v>
+        <v>1079.5</v>
       </c>
       <c r="F1286" t="n">
-        <v>11934.8</v>
+        <v>12014.3</v>
       </c>
       <c r="G1286" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1286" t="n">
         <v>1</v>
@@ -42895,16 +42895,16 @@
         </is>
       </c>
       <c r="D1287" t="n">
-        <v>54.1</v>
+        <v>102.5</v>
       </c>
       <c r="E1287" t="n">
-        <v>767.7</v>
+        <v>816.1</v>
       </c>
       <c r="F1287" t="n">
-        <v>9601.6</v>
+        <v>9650</v>
       </c>
       <c r="G1287" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H1287" t="n">
         <v>7</v>
@@ -42928,16 +42928,16 @@
         </is>
       </c>
       <c r="D1288" t="n">
-        <v>69.2</v>
+        <v>123.6</v>
       </c>
       <c r="E1288" t="n">
-        <v>875.4</v>
+        <v>929.8</v>
       </c>
       <c r="F1288" t="n">
-        <v>10479.5</v>
+        <v>10533.9</v>
       </c>
       <c r="G1288" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1288" t="n">
         <v>5</v>
@@ -42961,13 +42961,13 @@
         </is>
       </c>
       <c r="D1289" t="n">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="E1289" t="n">
-        <v>830.8</v>
+        <v>894.8</v>
       </c>
       <c r="F1289" t="n">
-        <v>8365.799999999999</v>
+        <v>8429.799999999999</v>
       </c>
       <c r="G1289" t="n">
         <v>4</v>
@@ -42997,16 +42997,16 @@
         <v>87.8</v>
       </c>
       <c r="E1290" t="n">
-        <v>807.2</v>
+        <v>869.5</v>
       </c>
       <c r="F1290" t="n">
-        <v>11518.3</v>
+        <v>11580.6</v>
       </c>
       <c r="G1290" t="n">
         <v>1</v>
       </c>
       <c r="H1290" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I1290" t="n">
         <v>3</v>
@@ -43030,16 +43030,16 @@
         <v>67</v>
       </c>
       <c r="E1291" t="n">
-        <v>948.2</v>
+        <v>1024</v>
       </c>
       <c r="F1291" t="n">
-        <v>11639.2</v>
+        <v>11715</v>
       </c>
       <c r="G1291" t="n">
         <v>4</v>
       </c>
       <c r="H1291" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1291" t="n">
         <v>2</v>
@@ -43063,16 +43063,16 @@
         <v>55.4</v>
       </c>
       <c r="E1292" t="n">
-        <v>950.8</v>
+        <v>1026</v>
       </c>
       <c r="F1292" t="n">
-        <v>10815.9</v>
+        <v>10891.1</v>
       </c>
       <c r="G1292" t="n">
         <v>7</v>
       </c>
       <c r="H1292" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1292" t="n">
         <v>4</v>
@@ -43096,10 +43096,10 @@
         <v>57.6</v>
       </c>
       <c r="E1293" t="n">
-        <v>1002.9</v>
+        <v>1054</v>
       </c>
       <c r="F1293" t="n">
-        <v>10667.5</v>
+        <v>10718.6</v>
       </c>
       <c r="G1293" t="n">
         <v>6</v>
@@ -43129,10 +43129,10 @@
         <v>66.3</v>
       </c>
       <c r="E1294" t="n">
-        <v>1066.3</v>
+        <v>1145.8</v>
       </c>
       <c r="F1294" t="n">
-        <v>12001.1</v>
+        <v>12080.6</v>
       </c>
       <c r="G1294" t="n">
         <v>5</v>
@@ -43162,16 +43162,16 @@
         <v>52.1</v>
       </c>
       <c r="E1295" t="n">
-        <v>819.8</v>
+        <v>868.2</v>
       </c>
       <c r="F1295" t="n">
-        <v>9653.700000000001</v>
+        <v>9702.1</v>
       </c>
       <c r="G1295" t="n">
         <v>8</v>
       </c>
       <c r="H1295" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1295" t="n">
         <v>7</v>
@@ -43195,16 +43195,16 @@
         <v>81.09999999999999</v>
       </c>
       <c r="E1296" t="n">
-        <v>956.5</v>
+        <v>1010.9</v>
       </c>
       <c r="F1296" t="n">
-        <v>10560.6</v>
+        <v>10615</v>
       </c>
       <c r="G1296" t="n">
         <v>2</v>
       </c>
       <c r="H1296" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I1296" t="n">
         <v>6</v>
@@ -43228,10 +43228,10 @@
         <v>76.89999999999999</v>
       </c>
       <c r="E1297" t="n">
-        <v>907.7</v>
+        <v>971.7</v>
       </c>
       <c r="F1297" t="n">
-        <v>8442.700000000001</v>
+        <v>8506.700000000001</v>
       </c>
       <c r="G1297" t="n">
         <v>3</v>
@@ -43261,10 +43261,10 @@
         <v>77.90000000000001</v>
       </c>
       <c r="E1298" t="n">
-        <v>885.1</v>
+        <v>947.4</v>
       </c>
       <c r="F1298" t="n">
-        <v>11596.2</v>
+        <v>11658.5</v>
       </c>
       <c r="G1298" t="n">
         <v>1</v>
@@ -43294,10 +43294,10 @@
         <v>54.8</v>
       </c>
       <c r="E1299" t="n">
-        <v>1003</v>
+        <v>1078.8</v>
       </c>
       <c r="F1299" t="n">
-        <v>11694</v>
+        <v>11769.8</v>
       </c>
       <c r="G1299" t="n">
         <v>7</v>
@@ -43327,16 +43327,16 @@
         <v>68.8</v>
       </c>
       <c r="E1300" t="n">
-        <v>1019.6</v>
+        <v>1094.8</v>
       </c>
       <c r="F1300" t="n">
-        <v>10884.7</v>
+        <v>10959.9</v>
       </c>
       <c r="G1300" t="n">
         <v>3</v>
       </c>
       <c r="H1300" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1300" t="n">
         <v>4</v>
@@ -43360,10 +43360,10 @@
         <v>60.2</v>
       </c>
       <c r="E1301" t="n">
-        <v>1063.1</v>
+        <v>1114.2</v>
       </c>
       <c r="F1301" t="n">
-        <v>10727.7</v>
+        <v>10778.8</v>
       </c>
       <c r="G1301" t="n">
         <v>6</v>
@@ -43393,10 +43393,10 @@
         <v>62.8</v>
       </c>
       <c r="E1302" t="n">
-        <v>1129.1</v>
+        <v>1208.6</v>
       </c>
       <c r="F1302" t="n">
-        <v>12063.9</v>
+        <v>12143.4</v>
       </c>
       <c r="G1302" t="n">
         <v>5</v>
@@ -43426,10 +43426,10 @@
         <v>50.9</v>
       </c>
       <c r="E1303" t="n">
-        <v>870.7</v>
+        <v>919.1</v>
       </c>
       <c r="F1303" t="n">
-        <v>9704.6</v>
+        <v>9753</v>
       </c>
       <c r="G1303" t="n">
         <v>8</v>
@@ -43459,16 +43459,16 @@
         <v>69.40000000000001</v>
       </c>
       <c r="E1304" t="n">
-        <v>1025.9</v>
+        <v>1080.3</v>
       </c>
       <c r="F1304" t="n">
-        <v>10630</v>
+        <v>10684.4</v>
       </c>
       <c r="G1304" t="n">
         <v>2</v>
       </c>
       <c r="H1304" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1304" t="n">
         <v>6</v>
@@ -43492,10 +43492,10 @@
         <v>66.3</v>
       </c>
       <c r="E1305" t="n">
-        <v>974</v>
+        <v>1038</v>
       </c>
       <c r="F1305" t="n">
-        <v>8509</v>
+        <v>8573</v>
       </c>
       <c r="G1305" t="n">
         <v>4</v>
@@ -43525,10 +43525,10 @@
         <v>68</v>
       </c>
       <c r="E1306" t="n">
-        <v>953.1</v>
+        <v>1015.4</v>
       </c>
       <c r="F1306" t="n">
-        <v>11664.2</v>
+        <v>11726.5</v>
       </c>
       <c r="G1306" t="n">
         <v>5</v>
@@ -43558,16 +43558,16 @@
         <v>89.2</v>
       </c>
       <c r="E1307" t="n">
-        <v>1092.2</v>
+        <v>1168</v>
       </c>
       <c r="F1307" t="n">
-        <v>11783.2</v>
+        <v>11859</v>
       </c>
       <c r="G1307" t="n">
         <v>2</v>
       </c>
       <c r="H1307" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1307" t="n">
         <v>2</v>
@@ -43591,16 +43591,16 @@
         <v>79.3</v>
       </c>
       <c r="E1308" t="n">
-        <v>1098.9</v>
+        <v>1174.1</v>
       </c>
       <c r="F1308" t="n">
-        <v>10964</v>
+        <v>11039.2</v>
       </c>
       <c r="G1308" t="n">
         <v>3</v>
       </c>
       <c r="H1308" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1308" t="n">
         <v>4</v>
@@ -43624,10 +43624,10 @@
         <v>61</v>
       </c>
       <c r="E1309" t="n">
-        <v>1124.1</v>
+        <v>1175.2</v>
       </c>
       <c r="F1309" t="n">
-        <v>10788.7</v>
+        <v>10839.8</v>
       </c>
       <c r="G1309" t="n">
         <v>6</v>
@@ -43657,10 +43657,10 @@
         <v>57.4</v>
       </c>
       <c r="E1310" t="n">
-        <v>1186.5</v>
+        <v>1266</v>
       </c>
       <c r="F1310" t="n">
-        <v>12121.3</v>
+        <v>12200.8</v>
       </c>
       <c r="G1310" t="n">
         <v>7</v>
@@ -43690,10 +43690,10 @@
         <v>46.4</v>
       </c>
       <c r="E1311" t="n">
-        <v>917.1</v>
+        <v>965.5</v>
       </c>
       <c r="F1311" t="n">
-        <v>9751</v>
+        <v>9799.4</v>
       </c>
       <c r="G1311" t="n">
         <v>8</v>
@@ -43723,16 +43723,16 @@
         <v>77.2</v>
       </c>
       <c r="E1312" t="n">
-        <v>1103.1</v>
+        <v>1157.5</v>
       </c>
       <c r="F1312" t="n">
-        <v>10707.2</v>
+        <v>10761.6</v>
       </c>
       <c r="G1312" t="n">
         <v>4</v>
       </c>
       <c r="H1312" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I1312" t="n">
         <v>6</v>
@@ -43756,10 +43756,10 @@
         <v>95.2</v>
       </c>
       <c r="E1313" t="n">
-        <v>1069.2</v>
+        <v>1133.2</v>
       </c>
       <c r="F1313" t="n">
-        <v>8604.200000000001</v>
+        <v>8668.200000000001</v>
       </c>
       <c r="G1313" t="n">
         <v>1</v>
@@ -43789,10 +43789,10 @@
         <v>78</v>
       </c>
       <c r="E1314" t="n">
-        <v>1031.1</v>
+        <v>1093.4</v>
       </c>
       <c r="F1314" t="n">
-        <v>11742.2</v>
+        <v>11804.5</v>
       </c>
       <c r="G1314" t="n">
         <v>3</v>
@@ -43822,16 +43822,16 @@
         <v>78.59999999999999</v>
       </c>
       <c r="E1315" t="n">
-        <v>1170.8</v>
+        <v>1246.6</v>
       </c>
       <c r="F1315" t="n">
-        <v>11861.8</v>
+        <v>11937.6</v>
       </c>
       <c r="G1315" t="n">
         <v>2</v>
       </c>
       <c r="H1315" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1315" t="n">
         <v>2</v>
@@ -43855,10 +43855,10 @@
         <v>76.90000000000001</v>
       </c>
       <c r="E1316" t="n">
-        <v>1175.8</v>
+        <v>1251</v>
       </c>
       <c r="F1316" t="n">
-        <v>11040.9</v>
+        <v>11116.1</v>
       </c>
       <c r="G1316" t="n">
         <v>4</v>
@@ -43888,16 +43888,16 @@
         <v>48.4</v>
       </c>
       <c r="E1317" t="n">
-        <v>1172.5</v>
+        <v>1223.6</v>
       </c>
       <c r="F1317" t="n">
-        <v>10837.1</v>
+        <v>10888.2</v>
       </c>
       <c r="G1317" t="n">
         <v>8</v>
       </c>
       <c r="H1317" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1317" t="n">
         <v>5</v>
@@ -43921,10 +43921,10 @@
         <v>67.59999999999999</v>
       </c>
       <c r="E1318" t="n">
-        <v>1254.1</v>
+        <v>1333.6</v>
       </c>
       <c r="F1318" t="n">
-        <v>12188.9</v>
+        <v>12268.4</v>
       </c>
       <c r="G1318" t="n">
         <v>5</v>
@@ -43954,10 +43954,10 @@
         <v>58.1</v>
       </c>
       <c r="E1319" t="n">
-        <v>975.2</v>
+        <v>1023.6</v>
       </c>
       <c r="F1319" t="n">
-        <v>9809.1</v>
+        <v>9857.5</v>
       </c>
       <c r="G1319" t="n">
         <v>7</v>
@@ -43987,10 +43987,10 @@
         <v>61.4</v>
       </c>
       <c r="E1320" t="n">
-        <v>1164.5</v>
+        <v>1218.9</v>
       </c>
       <c r="F1320" t="n">
-        <v>10768.6</v>
+        <v>10823</v>
       </c>
       <c r="G1320" t="n">
         <v>6</v>
@@ -44020,10 +44020,10 @@
         <v>81.59999999999999</v>
       </c>
       <c r="E1321" t="n">
-        <v>1150.8</v>
+        <v>1214.8</v>
       </c>
       <c r="F1321" t="n">
-        <v>8685.799999999999</v>
+        <v>8749.799999999999</v>
       </c>
       <c r="G1321" t="n">
         <v>1</v>
@@ -44053,10 +44053,10 @@
         <v>67.5</v>
       </c>
       <c r="E1322" t="n">
-        <v>1098.6</v>
+        <v>1160.9</v>
       </c>
       <c r="F1322" t="n">
-        <v>11809.7</v>
+        <v>11872</v>
       </c>
       <c r="G1322" t="n">
         <v>5</v>
@@ -44086,10 +44086,10 @@
         <v>69.8</v>
       </c>
       <c r="E1323" t="n">
-        <v>1240.6</v>
+        <v>1316.4</v>
       </c>
       <c r="F1323" t="n">
-        <v>11931.6</v>
+        <v>12007.4</v>
       </c>
       <c r="G1323" t="n">
         <v>2</v>
@@ -44119,10 +44119,10 @@
         <v>68.3</v>
       </c>
       <c r="E1324" t="n">
-        <v>1244.1</v>
+        <v>1319.3</v>
       </c>
       <c r="F1324" t="n">
-        <v>11109.2</v>
+        <v>11184.4</v>
       </c>
       <c r="G1324" t="n">
         <v>3</v>
@@ -44152,16 +44152,16 @@
         <v>52.1</v>
       </c>
       <c r="E1325" t="n">
-        <v>1224.6</v>
+        <v>1275.7</v>
       </c>
       <c r="F1325" t="n">
-        <v>10889.2</v>
+        <v>10940.3</v>
       </c>
       <c r="G1325" t="n">
         <v>8</v>
       </c>
       <c r="H1325" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I1325" t="n">
         <v>5</v>
@@ -44185,10 +44185,10 @@
         <v>79.7</v>
       </c>
       <c r="E1326" t="n">
-        <v>1333.8</v>
+        <v>1413.3</v>
       </c>
       <c r="F1326" t="n">
-        <v>12268.6</v>
+        <v>12348.1</v>
       </c>
       <c r="G1326" t="n">
         <v>1</v>
@@ -44218,10 +44218,10 @@
         <v>58</v>
       </c>
       <c r="E1327" t="n">
-        <v>1033.2</v>
+        <v>1081.6</v>
       </c>
       <c r="F1327" t="n">
-        <v>9867.1</v>
+        <v>9915.5</v>
       </c>
       <c r="G1327" t="n">
         <v>7</v>
@@ -44251,10 +44251,10 @@
         <v>59.5</v>
       </c>
       <c r="E1328" t="n">
-        <v>1224</v>
+        <v>1278.4</v>
       </c>
       <c r="F1328" t="n">
-        <v>10828.1</v>
+        <v>10882.5</v>
       </c>
       <c r="G1328" t="n">
         <v>6</v>
@@ -44284,16 +44284,16 @@
         <v>68.10000000000001</v>
       </c>
       <c r="E1329" t="n">
-        <v>1218.9</v>
+        <v>1282.9</v>
       </c>
       <c r="F1329" t="n">
-        <v>8753.9</v>
+        <v>8817.9</v>
       </c>
       <c r="G1329" t="n">
         <v>4</v>
       </c>
       <c r="H1329" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I1329" t="n">
         <v>8</v>
@@ -44317,10 +44317,10 @@
         <v>58.6</v>
       </c>
       <c r="E1330" t="n">
-        <v>1157.2</v>
+        <v>1219.5</v>
       </c>
       <c r="F1330" t="n">
-        <v>11868.3</v>
+        <v>11930.6</v>
       </c>
       <c r="G1330" t="n">
         <v>6</v>
@@ -44350,10 +44350,10 @@
         <v>105.7</v>
       </c>
       <c r="E1331" t="n">
-        <v>1346.3</v>
+        <v>1422.1</v>
       </c>
       <c r="F1331" t="n">
-        <v>12037.3</v>
+        <v>12113.1</v>
       </c>
       <c r="G1331" t="n">
         <v>1</v>
@@ -44383,16 +44383,16 @@
         <v>58.4</v>
       </c>
       <c r="E1332" t="n">
-        <v>1302.5</v>
+        <v>1377.7</v>
       </c>
       <c r="F1332" t="n">
-        <v>11167.6</v>
+        <v>11242.8</v>
       </c>
       <c r="G1332" t="n">
         <v>7</v>
       </c>
       <c r="H1332" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1332" t="n">
         <v>4</v>
@@ -44416,10 +44416,10 @@
         <v>57.4</v>
       </c>
       <c r="E1333" t="n">
-        <v>1282</v>
+        <v>1333.1</v>
       </c>
       <c r="F1333" t="n">
-        <v>10946.6</v>
+        <v>10997.7</v>
       </c>
       <c r="G1333" t="n">
         <v>8</v>
@@ -44449,10 +44449,10 @@
         <v>83.40000000000001</v>
       </c>
       <c r="E1334" t="n">
-        <v>1417.2</v>
+        <v>1496.7</v>
       </c>
       <c r="F1334" t="n">
-        <v>12352</v>
+        <v>12431.5</v>
       </c>
       <c r="G1334" t="n">
         <v>3</v>
@@ -44482,10 +44482,10 @@
         <v>74.3</v>
       </c>
       <c r="E1335" t="n">
-        <v>1107.5</v>
+        <v>1155.9</v>
       </c>
       <c r="F1335" t="n">
-        <v>9941.4</v>
+        <v>9989.799999999999</v>
       </c>
       <c r="G1335" t="n">
         <v>4</v>
@@ -44515,10 +44515,10 @@
         <v>72</v>
       </c>
       <c r="E1336" t="n">
-        <v>1296</v>
+        <v>1350.4</v>
       </c>
       <c r="F1336" t="n">
-        <v>10900.1</v>
+        <v>10954.5</v>
       </c>
       <c r="G1336" t="n">
         <v>5</v>
@@ -44548,16 +44548,16 @@
         <v>87.09999999999999</v>
       </c>
       <c r="E1337" t="n">
-        <v>1306</v>
+        <v>1370</v>
       </c>
       <c r="F1337" t="n">
-        <v>8841</v>
+        <v>8905</v>
       </c>
       <c r="G1337" t="n">
         <v>2</v>
       </c>
       <c r="H1337" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1337" t="n">
         <v>8</v>
@@ -44581,10 +44581,10 @@
         <v>61.2</v>
       </c>
       <c r="E1338" t="n">
-        <v>1218.4</v>
+        <v>1280.7</v>
       </c>
       <c r="F1338" t="n">
-        <v>11929.5</v>
+        <v>11991.8</v>
       </c>
       <c r="G1338" t="n">
         <v>5</v>
@@ -44614,10 +44614,10 @@
         <v>55.59999999999999</v>
       </c>
       <c r="E1339" t="n">
-        <v>1401.9</v>
+        <v>1477.7</v>
       </c>
       <c r="F1339" t="n">
-        <v>12092.9</v>
+        <v>12168.7</v>
       </c>
       <c r="G1339" t="n">
         <v>7</v>
@@ -44647,16 +44647,16 @@
         <v>50.59999999999999</v>
       </c>
       <c r="E1340" t="n">
-        <v>1353.1</v>
+        <v>1428.3</v>
       </c>
       <c r="F1340" t="n">
-        <v>11218.2</v>
+        <v>11293.4</v>
       </c>
       <c r="G1340" t="n">
         <v>8</v>
       </c>
       <c r="H1340" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1340" t="n">
         <v>4</v>
@@ -44680,10 +44680,10 @@
         <v>62.40000000000001</v>
       </c>
       <c r="E1341" t="n">
-        <v>1344.4</v>
+        <v>1395.5</v>
       </c>
       <c r="F1341" t="n">
-        <v>11009</v>
+        <v>11060.1</v>
       </c>
       <c r="G1341" t="n">
         <v>4</v>
@@ -44713,10 +44713,10 @@
         <v>81.90000000000001</v>
       </c>
       <c r="E1342" t="n">
-        <v>1499.1</v>
+        <v>1578.6</v>
       </c>
       <c r="F1342" t="n">
-        <v>12433.9</v>
+        <v>12513.4</v>
       </c>
       <c r="G1342" t="n">
         <v>2</v>
@@ -44746,10 +44746,10 @@
         <v>63.3</v>
       </c>
       <c r="E1343" t="n">
-        <v>1170.8</v>
+        <v>1219.2</v>
       </c>
       <c r="F1343" t="n">
-        <v>10004.7</v>
+        <v>10053.1</v>
       </c>
       <c r="G1343" t="n">
         <v>3</v>
@@ -44779,10 +44779,10 @@
         <v>86</v>
       </c>
       <c r="E1344" t="n">
-        <v>1382</v>
+        <v>1436.4</v>
       </c>
       <c r="F1344" t="n">
-        <v>10986.1</v>
+        <v>11040.5</v>
       </c>
       <c r="G1344" t="n">
         <v>1</v>
@@ -44812,16 +44812,16 @@
         <v>58.1</v>
       </c>
       <c r="E1345" t="n">
-        <v>1364.1</v>
+        <v>1428.1</v>
       </c>
       <c r="F1345" t="n">
-        <v>8899.1</v>
+        <v>8963.1</v>
       </c>
       <c r="G1345" t="n">
         <v>6</v>
       </c>
       <c r="H1345" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1345" t="n">
         <v>8</v>
@@ -44845,10 +44845,10 @@
         <v>64.2</v>
       </c>
       <c r="E1346" t="n">
-        <v>1282.6</v>
+        <v>1344.9</v>
       </c>
       <c r="F1346" t="n">
-        <v>11993.7</v>
+        <v>12056</v>
       </c>
       <c r="G1346" t="n">
         <v>5</v>
@@ -44878,10 +44878,10 @@
         <v>88.7</v>
       </c>
       <c r="E1347" t="n">
-        <v>1490.6</v>
+        <v>1566.4</v>
       </c>
       <c r="F1347" t="n">
-        <v>12181.6</v>
+        <v>12257.4</v>
       </c>
       <c r="G1347" t="n">
         <v>1</v>
@@ -44911,16 +44911,16 @@
         <v>76.8</v>
       </c>
       <c r="E1348" t="n">
-        <v>1429.9</v>
+        <v>1505.1</v>
       </c>
       <c r="F1348" t="n">
-        <v>11295</v>
+        <v>11370.2</v>
       </c>
       <c r="G1348" t="n">
         <v>3</v>
       </c>
       <c r="H1348" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1348" t="n">
         <v>4</v>
@@ -44944,10 +44944,10 @@
         <v>45</v>
       </c>
       <c r="E1349" t="n">
-        <v>1389.4</v>
+        <v>1440.5</v>
       </c>
       <c r="F1349" t="n">
-        <v>11054</v>
+        <v>11105.1</v>
       </c>
       <c r="G1349" t="n">
         <v>8</v>
@@ -44956,7 +44956,7 @@
         <v>6</v>
       </c>
       <c r="I1349" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1350">
@@ -44977,10 +44977,10 @@
         <v>81.2</v>
       </c>
       <c r="E1350" t="n">
-        <v>1580.3</v>
+        <v>1659.8</v>
       </c>
       <c r="F1350" t="n">
-        <v>12515.1</v>
+        <v>12594.6</v>
       </c>
       <c r="G1350" t="n">
         <v>2</v>
@@ -45010,10 +45010,10 @@
         <v>63.7</v>
       </c>
       <c r="E1351" t="n">
-        <v>1234.5</v>
+        <v>1282.9</v>
       </c>
       <c r="F1351" t="n">
-        <v>10068.4</v>
+        <v>10116.8</v>
       </c>
       <c r="G1351" t="n">
         <v>6</v>
@@ -45043,19 +45043,19 @@
         <v>67.7</v>
       </c>
       <c r="E1352" t="n">
-        <v>1449.7</v>
+        <v>1504.1</v>
       </c>
       <c r="F1352" t="n">
-        <v>11053.8</v>
+        <v>11108.2</v>
       </c>
       <c r="G1352" t="n">
         <v>4</v>
       </c>
       <c r="H1352" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1352" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1353">
@@ -45076,10 +45076,10 @@
         <v>60.2</v>
       </c>
       <c r="E1353" t="n">
-        <v>1424.3</v>
+        <v>1488.3</v>
       </c>
       <c r="F1353" t="n">
-        <v>8959.299999999999</v>
+        <v>9023.299999999999</v>
       </c>
       <c r="G1353" t="n">
         <v>7</v>
@@ -45109,10 +45109,10 @@
         <v>88.09999999999999</v>
       </c>
       <c r="E1354" t="n">
-        <v>1370.7</v>
+        <v>1433</v>
       </c>
       <c r="F1354" t="n">
-        <v>12081.8</v>
+        <v>12144.1</v>
       </c>
       <c r="G1354" t="n">
         <v>3</v>
@@ -45142,10 +45142,10 @@
         <v>59.9</v>
       </c>
       <c r="E1355" t="n">
-        <v>1550.5</v>
+        <v>1626.3</v>
       </c>
       <c r="F1355" t="n">
-        <v>12241.5</v>
+        <v>12317.3</v>
       </c>
       <c r="G1355" t="n">
         <v>6</v>
@@ -45175,16 +45175,16 @@
         <v>70.2</v>
       </c>
       <c r="E1356" t="n">
-        <v>1500.1</v>
+        <v>1575.3</v>
       </c>
       <c r="F1356" t="n">
-        <v>11365.2</v>
+        <v>11440.4</v>
       </c>
       <c r="G1356" t="n">
         <v>4</v>
       </c>
       <c r="H1356" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1356" t="n">
         <v>4</v>
@@ -45208,10 +45208,10 @@
         <v>0</v>
       </c>
       <c r="E1357" t="n">
-        <v>1389.4</v>
+        <v>1440.5</v>
       </c>
       <c r="F1357" t="n">
-        <v>11054</v>
+        <v>11105.1</v>
       </c>
       <c r="G1357" t="n">
         <v>8</v>
@@ -45241,10 +45241,10 @@
         <v>94</v>
       </c>
       <c r="E1358" t="n">
-        <v>1674.3</v>
+        <v>1753.8</v>
       </c>
       <c r="F1358" t="n">
-        <v>12609.1</v>
+        <v>12688.6</v>
       </c>
       <c r="G1358" t="n">
         <v>1</v>
@@ -45274,10 +45274,10 @@
         <v>61.6</v>
       </c>
       <c r="E1359" t="n">
-        <v>1296.1</v>
+        <v>1344.5</v>
       </c>
       <c r="F1359" t="n">
-        <v>10130</v>
+        <v>10178.4</v>
       </c>
       <c r="G1359" t="n">
         <v>5</v>
@@ -45307,16 +45307,16 @@
         <v>58.6</v>
       </c>
       <c r="E1360" t="n">
-        <v>1508.3</v>
+        <v>1562.7</v>
       </c>
       <c r="F1360" t="n">
-        <v>11112.4</v>
+        <v>11166.8</v>
       </c>
       <c r="G1360" t="n">
         <v>7</v>
       </c>
       <c r="H1360" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1360" t="n">
         <v>5</v>
@@ -45340,10 +45340,10 @@
         <v>89.5</v>
       </c>
       <c r="E1361" t="n">
-        <v>1513.8</v>
+        <v>1577.8</v>
       </c>
       <c r="F1361" t="n">
-        <v>9048.799999999999</v>
+        <v>9112.799999999999</v>
       </c>
       <c r="G1361" t="n">
         <v>2</v>
@@ -45373,10 +45373,10 @@
         <v>66.7</v>
       </c>
       <c r="E1362" t="n">
-        <v>1437.4</v>
+        <v>1499.7</v>
       </c>
       <c r="F1362" t="n">
-        <v>12148.5</v>
+        <v>12210.8</v>
       </c>
       <c r="G1362" t="n">
         <v>4</v>
@@ -45406,16 +45406,16 @@
         <v>35.8</v>
       </c>
       <c r="E1363" t="n">
-        <v>1586.3</v>
+        <v>1662.1</v>
       </c>
       <c r="F1363" t="n">
-        <v>12277.3</v>
+        <v>12353.1</v>
       </c>
       <c r="G1363" t="n">
         <v>8</v>
       </c>
       <c r="H1363" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1363" t="n">
         <v>2</v>
@@ -45439,10 +45439,10 @@
         <v>59.2</v>
       </c>
       <c r="E1364" t="n">
-        <v>1559.3</v>
+        <v>1634.5</v>
       </c>
       <c r="F1364" t="n">
-        <v>11424.4</v>
+        <v>11499.6</v>
       </c>
       <c r="G1364" t="n">
         <v>6</v>
@@ -45472,10 +45472,10 @@
         <v>82.2</v>
       </c>
       <c r="E1365" t="n">
-        <v>1471.6</v>
+        <v>1522.7</v>
       </c>
       <c r="F1365" t="n">
-        <v>11136.2</v>
+        <v>11187.3</v>
       </c>
       <c r="G1365" t="n">
         <v>2</v>
@@ -45505,10 +45505,10 @@
         <v>63</v>
       </c>
       <c r="E1366" t="n">
-        <v>1737.3</v>
+        <v>1816.8</v>
       </c>
       <c r="F1366" t="n">
-        <v>12672.1</v>
+        <v>12751.6</v>
       </c>
       <c r="G1366" t="n">
         <v>5</v>
@@ -45538,10 +45538,10 @@
         <v>56.6</v>
       </c>
       <c r="E1367" t="n">
-        <v>1352.7</v>
+        <v>1401.1</v>
       </c>
       <c r="F1367" t="n">
-        <v>10186.6</v>
+        <v>10235</v>
       </c>
       <c r="G1367" t="n">
         <v>7</v>
@@ -45571,16 +45571,16 @@
         <v>78.59999999999999</v>
       </c>
       <c r="E1368" t="n">
-        <v>1586.9</v>
+        <v>1641.3</v>
       </c>
       <c r="F1368" t="n">
-        <v>11191</v>
+        <v>11245.4</v>
       </c>
       <c r="G1368" t="n">
         <v>3</v>
       </c>
       <c r="H1368" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1368" t="n">
         <v>5</v>
@@ -45604,10 +45604,10 @@
         <v>87.3</v>
       </c>
       <c r="E1369" t="n">
-        <v>1601.1</v>
+        <v>1665.1</v>
       </c>
       <c r="F1369" t="n">
-        <v>9136.1</v>
+        <v>9200.1</v>
       </c>
       <c r="G1369" t="n">
         <v>1</v>
@@ -45637,16 +45637,16 @@
         <v>70.8</v>
       </c>
       <c r="E1370" t="n">
-        <v>1508.2</v>
+        <v>1570.5</v>
       </c>
       <c r="F1370" t="n">
-        <v>12219.3</v>
+        <v>12281.6</v>
       </c>
       <c r="G1370" t="n">
         <v>4</v>
       </c>
       <c r="H1370" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I1370" t="n">
         <v>3</v>
@@ -45670,10 +45670,10 @@
         <v>76.5</v>
       </c>
       <c r="E1371" t="n">
-        <v>1662.8</v>
+        <v>1738.6</v>
       </c>
       <c r="F1371" t="n">
-        <v>12353.8</v>
+        <v>12429.6</v>
       </c>
       <c r="G1371" t="n">
         <v>2</v>
@@ -45703,16 +45703,16 @@
         <v>75.2</v>
       </c>
       <c r="E1372" t="n">
-        <v>1634.5</v>
+        <v>1709.7</v>
       </c>
       <c r="F1372" t="n">
-        <v>11499.6</v>
+        <v>11574.8</v>
       </c>
       <c r="G1372" t="n">
         <v>3</v>
       </c>
       <c r="H1372" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1372" t="n">
         <v>4</v>
@@ -45736,16 +45736,16 @@
         <v>46.7</v>
       </c>
       <c r="E1373" t="n">
-        <v>1518.3</v>
+        <v>1569.4</v>
       </c>
       <c r="F1373" t="n">
-        <v>11182.9</v>
+        <v>11234</v>
       </c>
       <c r="G1373" t="n">
         <v>8</v>
       </c>
       <c r="H1373" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1373" t="n">
         <v>6</v>
@@ -45769,10 +45769,10 @@
         <v>79.40000000000001</v>
       </c>
       <c r="E1374" t="n">
-        <v>1816.7</v>
+        <v>1896.2</v>
       </c>
       <c r="F1374" t="n">
-        <v>12751.5</v>
+        <v>12831</v>
       </c>
       <c r="G1374" t="n">
         <v>1</v>
@@ -45802,10 +45802,10 @@
         <v>56.59999999999999</v>
       </c>
       <c r="E1375" t="n">
-        <v>1409.3</v>
+        <v>1457.7</v>
       </c>
       <c r="F1375" t="n">
-        <v>10243.2</v>
+        <v>10291.6</v>
       </c>
       <c r="G1375" t="n">
         <v>6</v>
@@ -45835,16 +45835,16 @@
         <v>65.2</v>
       </c>
       <c r="E1376" t="n">
-        <v>1652.1</v>
+        <v>1706.5</v>
       </c>
       <c r="F1376" t="n">
-        <v>11256.2</v>
+        <v>11310.6</v>
       </c>
       <c r="G1376" t="n">
         <v>5</v>
       </c>
       <c r="H1376" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1376" t="n">
         <v>5</v>
@@ -45868,10 +45868,10 @@
         <v>54.8</v>
       </c>
       <c r="E1377" t="n">
-        <v>1655.9</v>
+        <v>1719.9</v>
       </c>
       <c r="F1377" t="n">
-        <v>9190.9</v>
+        <v>9254.9</v>
       </c>
       <c r="G1377" t="n">
         <v>7</v>
@@ -45901,10 +45901,10 @@
         <v>93.8</v>
       </c>
       <c r="E1378" t="n">
-        <v>1602</v>
+        <v>1664.3</v>
       </c>
       <c r="F1378" t="n">
-        <v>12313.1</v>
+        <v>12375.4</v>
       </c>
       <c r="G1378" t="n">
         <v>2</v>
@@ -45934,16 +45934,16 @@
         <v>65.2</v>
       </c>
       <c r="E1379" t="n">
-        <v>1728</v>
+        <v>1803.8</v>
       </c>
       <c r="F1379" t="n">
-        <v>12419</v>
+        <v>12494.8</v>
       </c>
       <c r="G1379" t="n">
         <v>7</v>
       </c>
       <c r="H1379" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1379" t="n">
         <v>2</v>
@@ -45967,16 +45967,16 @@
         <v>97.59999999999999</v>
       </c>
       <c r="E1380" t="n">
-        <v>1732.1</v>
+        <v>1807.3</v>
       </c>
       <c r="F1380" t="n">
-        <v>11597.2</v>
+        <v>11672.4</v>
       </c>
       <c r="G1380" t="n">
         <v>1</v>
       </c>
       <c r="H1380" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1380" t="n">
         <v>4</v>
@@ -46000,10 +46000,10 @@
         <v>63.3</v>
       </c>
       <c r="E1381" t="n">
-        <v>1581.6</v>
+        <v>1632.7</v>
       </c>
       <c r="F1381" t="n">
-        <v>11246.2</v>
+        <v>11297.3</v>
       </c>
       <c r="G1381" t="n">
         <v>8</v>
@@ -46033,10 +46033,10 @@
         <v>79.3</v>
       </c>
       <c r="E1382" t="n">
-        <v>1896</v>
+        <v>1975.5</v>
       </c>
       <c r="F1382" t="n">
-        <v>12830.8</v>
+        <v>12910.3</v>
       </c>
       <c r="G1382" t="n">
         <v>5</v>
@@ -46066,10 +46066,10 @@
         <v>81.7</v>
       </c>
       <c r="E1383" t="n">
-        <v>1491</v>
+        <v>1539.4</v>
       </c>
       <c r="F1383" t="n">
-        <v>10324.9</v>
+        <v>10373.3</v>
       </c>
       <c r="G1383" t="n">
         <v>4</v>
@@ -46099,10 +46099,10 @@
         <v>67.40000000000001</v>
       </c>
       <c r="E1384" t="n">
-        <v>1719.5</v>
+        <v>1773.9</v>
       </c>
       <c r="F1384" t="n">
-        <v>11323.6</v>
+        <v>11378</v>
       </c>
       <c r="G1384" t="n">
         <v>6</v>
@@ -46132,16 +46132,16 @@
         <v>82.59999999999999</v>
       </c>
       <c r="E1385" t="n">
-        <v>1738.5</v>
+        <v>1802.5</v>
       </c>
       <c r="F1385" t="n">
-        <v>9273.5</v>
+        <v>9337.5</v>
       </c>
       <c r="G1385" t="n">
         <v>3</v>
       </c>
       <c r="H1385" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1385" t="n">
         <v>8</v>
@@ -46165,10 +46165,10 @@
         <v>100.5</v>
       </c>
       <c r="E1386" t="n">
-        <v>1702.5</v>
+        <v>1764.8</v>
       </c>
       <c r="F1386" t="n">
-        <v>12413.6</v>
+        <v>12475.9</v>
       </c>
       <c r="G1386" t="n">
         <v>1</v>
@@ -46198,10 +46198,10 @@
         <v>80.3</v>
       </c>
       <c r="E1387" t="n">
-        <v>1808.3</v>
+        <v>1884.1</v>
       </c>
       <c r="F1387" t="n">
-        <v>12499.3</v>
+        <v>12575.1</v>
       </c>
       <c r="G1387" t="n">
         <v>2</v>
@@ -46231,16 +46231,16 @@
         <v>60.3</v>
       </c>
       <c r="E1388" t="n">
-        <v>1792.4</v>
+        <v>1867.6</v>
       </c>
       <c r="F1388" t="n">
-        <v>11657.5</v>
+        <v>11732.7</v>
       </c>
       <c r="G1388" t="n">
         <v>6</v>
       </c>
       <c r="H1388" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1388" t="n">
         <v>4</v>
@@ -46264,10 +46264,10 @@
         <v>67.59999999999999</v>
       </c>
       <c r="E1389" t="n">
-        <v>1649.2</v>
+        <v>1700.3</v>
       </c>
       <c r="F1389" t="n">
-        <v>11313.8</v>
+        <v>11364.9</v>
       </c>
       <c r="G1389" t="n">
         <v>4</v>
@@ -46297,10 +46297,10 @@
         <v>70.2</v>
       </c>
       <c r="E1390" t="n">
-        <v>1966.2</v>
+        <v>2045.7</v>
       </c>
       <c r="F1390" t="n">
-        <v>12901</v>
+        <v>12980.5</v>
       </c>
       <c r="G1390" t="n">
         <v>3</v>
@@ -46330,10 +46330,10 @@
         <v>61.2</v>
       </c>
       <c r="E1391" t="n">
-        <v>1552.2</v>
+        <v>1600.6</v>
       </c>
       <c r="F1391" t="n">
-        <v>10386.1</v>
+        <v>10434.5</v>
       </c>
       <c r="G1391" t="n">
         <v>5</v>
@@ -46363,10 +46363,10 @@
         <v>50.8</v>
       </c>
       <c r="E1392" t="n">
-        <v>1770.3</v>
+        <v>1824.7</v>
       </c>
       <c r="F1392" t="n">
-        <v>11374.4</v>
+        <v>11428.8</v>
       </c>
       <c r="G1392" t="n">
         <v>8</v>
@@ -46396,16 +46396,16 @@
         <v>58.9</v>
       </c>
       <c r="E1393" t="n">
-        <v>1797.4</v>
+        <v>1861.4</v>
       </c>
       <c r="F1393" t="n">
-        <v>9332.4</v>
+        <v>9396.4</v>
       </c>
       <c r="G1393" t="n">
         <v>7</v>
       </c>
       <c r="H1393" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1393" t="n">
         <v>8</v>
@@ -46429,10 +46429,10 @@
         <v>92</v>
       </c>
       <c r="E1394" t="n">
-        <v>1794.5</v>
+        <v>1856.8</v>
       </c>
       <c r="F1394" t="n">
-        <v>12505.6</v>
+        <v>12567.9</v>
       </c>
       <c r="G1394" t="n">
         <v>2</v>
@@ -46462,10 +46462,10 @@
         <v>77.2</v>
       </c>
       <c r="E1395" t="n">
-        <v>1885.5</v>
+        <v>1961.3</v>
       </c>
       <c r="F1395" t="n">
-        <v>12576.5</v>
+        <v>12652.3</v>
       </c>
       <c r="G1395" t="n">
         <v>4</v>
@@ -46495,10 +46495,10 @@
         <v>80.3</v>
       </c>
       <c r="E1396" t="n">
-        <v>1872.7</v>
+        <v>1947.9</v>
       </c>
       <c r="F1396" t="n">
-        <v>11737.8</v>
+        <v>11813</v>
       </c>
       <c r="G1396" t="n">
         <v>3</v>
@@ -46528,10 +46528,10 @@
         <v>50.6</v>
       </c>
       <c r="E1397" t="n">
-        <v>1699.8</v>
+        <v>1750.9</v>
       </c>
       <c r="F1397" t="n">
-        <v>11364.4</v>
+        <v>11415.5</v>
       </c>
       <c r="G1397" t="n">
         <v>7</v>
@@ -46561,10 +46561,10 @@
         <v>76.7</v>
       </c>
       <c r="E1398" t="n">
-        <v>2042.9</v>
+        <v>2122.4</v>
       </c>
       <c r="F1398" t="n">
-        <v>12977.7</v>
+        <v>13057.2</v>
       </c>
       <c r="G1398" t="n">
         <v>5</v>
@@ -46594,10 +46594,10 @@
         <v>48.7</v>
       </c>
       <c r="E1399" t="n">
-        <v>1600.9</v>
+        <v>1649.3</v>
       </c>
       <c r="F1399" t="n">
-        <v>10434.8</v>
+        <v>10483.2</v>
       </c>
       <c r="G1399" t="n">
         <v>8</v>
@@ -46627,10 +46627,10 @@
         <v>92.5</v>
       </c>
       <c r="E1400" t="n">
-        <v>1862.8</v>
+        <v>1917.2</v>
       </c>
       <c r="F1400" t="n">
-        <v>11466.9</v>
+        <v>11521.3</v>
       </c>
       <c r="G1400" t="n">
         <v>1</v>
@@ -46660,10 +46660,10 @@
         <v>73.10000000000001</v>
       </c>
       <c r="E1401" t="n">
-        <v>1870.5</v>
+        <v>1934.5</v>
       </c>
       <c r="F1401" t="n">
-        <v>9405.5</v>
+        <v>9469.5</v>
       </c>
       <c r="G1401" t="n">
         <v>6</v>
@@ -46693,10 +46693,10 @@
         <v>75.59999999999999</v>
       </c>
       <c r="E1402" t="n">
-        <v>1870.1</v>
+        <v>1932.4</v>
       </c>
       <c r="F1402" t="n">
-        <v>12581.2</v>
+        <v>12643.5</v>
       </c>
       <c r="G1402" t="n">
         <v>3</v>
@@ -46726,10 +46726,10 @@
         <v>84.09999999999999</v>
       </c>
       <c r="E1403" t="n">
-        <v>1969.6</v>
+        <v>2045.4</v>
       </c>
       <c r="F1403" t="n">
-        <v>12660.6</v>
+        <v>12736.4</v>
       </c>
       <c r="G1403" t="n">
         <v>1</v>
@@ -46759,16 +46759,16 @@
         <v>59.3</v>
       </c>
       <c r="E1404" t="n">
-        <v>1932</v>
+        <v>2007.2</v>
       </c>
       <c r="F1404" t="n">
-        <v>11797.1</v>
+        <v>11872.3</v>
       </c>
       <c r="G1404" t="n">
         <v>8</v>
       </c>
       <c r="H1404" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1404" t="n">
         <v>4</v>
@@ -46792,10 +46792,10 @@
         <v>71.5</v>
       </c>
       <c r="E1405" t="n">
-        <v>1771.3</v>
+        <v>1822.4</v>
       </c>
       <c r="F1405" t="n">
-        <v>11435.9</v>
+        <v>11487</v>
       </c>
       <c r="G1405" t="n">
         <v>6</v>
@@ -46825,10 +46825,10 @@
         <v>75.39999999999999</v>
       </c>
       <c r="E1406" t="n">
-        <v>2118.3</v>
+        <v>2197.8</v>
       </c>
       <c r="F1406" t="n">
-        <v>13053.1</v>
+        <v>13132.6</v>
       </c>
       <c r="G1406" t="n">
         <v>4</v>
@@ -46858,10 +46858,10 @@
         <v>62.7</v>
       </c>
       <c r="E1407" t="n">
-        <v>1663.6</v>
+        <v>1712</v>
       </c>
       <c r="F1407" t="n">
-        <v>10497.5</v>
+        <v>10545.9</v>
       </c>
       <c r="G1407" t="n">
         <v>7</v>
@@ -46891,16 +46891,16 @@
         <v>72</v>
       </c>
       <c r="E1408" t="n">
-        <v>1934.8</v>
+        <v>1989.2</v>
       </c>
       <c r="F1408" t="n">
-        <v>11538.9</v>
+        <v>11593.3</v>
       </c>
       <c r="G1408" t="n">
         <v>5</v>
       </c>
       <c r="H1408" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1408" t="n">
         <v>5</v>
@@ -46924,10 +46924,10 @@
         <v>79.09999999999999</v>
       </c>
       <c r="E1409" t="n">
-        <v>1949.6</v>
+        <v>2013.6</v>
       </c>
       <c r="F1409" t="n">
-        <v>9484.6</v>
+        <v>9548.6</v>
       </c>
       <c r="G1409" t="n">
         <v>2</v>
@@ -46957,10 +46957,10 @@
         <v>73.2</v>
       </c>
       <c r="E1410" t="n">
-        <v>1943.3</v>
+        <v>2005.6</v>
       </c>
       <c r="F1410" t="n">
-        <v>12654.4</v>
+        <v>12716.7</v>
       </c>
       <c r="G1410" t="n">
         <v>2</v>
@@ -46990,10 +46990,10 @@
         <v>62.7</v>
       </c>
       <c r="E1411" t="n">
-        <v>2032.3</v>
+        <v>2108.1</v>
       </c>
       <c r="F1411" t="n">
-        <v>12723.3</v>
+        <v>12799.1</v>
       </c>
       <c r="G1411" t="n">
         <v>5</v>
@@ -47023,10 +47023,10 @@
         <v>49.2</v>
       </c>
       <c r="E1412" t="n">
-        <v>1981.2</v>
+        <v>2056.4</v>
       </c>
       <c r="F1412" t="n">
-        <v>11846.3</v>
+        <v>11921.5</v>
       </c>
       <c r="G1412" t="n">
         <v>6</v>
@@ -47056,10 +47056,10 @@
         <v>43.9</v>
       </c>
       <c r="E1413" t="n">
-        <v>1815.2</v>
+        <v>1866.3</v>
       </c>
       <c r="F1413" t="n">
-        <v>11479.8</v>
+        <v>11530.9</v>
       </c>
       <c r="G1413" t="n">
         <v>7</v>
@@ -47089,10 +47089,10 @@
         <v>71.2</v>
       </c>
       <c r="E1414" t="n">
-        <v>2189.5</v>
+        <v>2269</v>
       </c>
       <c r="F1414" t="n">
-        <v>13124.3</v>
+        <v>13203.8</v>
       </c>
       <c r="G1414" t="n">
         <v>3</v>
@@ -47122,10 +47122,10 @@
         <v>64.09999999999999</v>
       </c>
       <c r="E1415" t="n">
-        <v>1727.7</v>
+        <v>1776.1</v>
       </c>
       <c r="F1415" t="n">
-        <v>10561.6</v>
+        <v>10610</v>
       </c>
       <c r="G1415" t="n">
         <v>4</v>
@@ -47155,10 +47155,10 @@
         <v>42.9</v>
       </c>
       <c r="E1416" t="n">
-        <v>1977.7</v>
+        <v>2032.1</v>
       </c>
       <c r="F1416" t="n">
-        <v>11581.8</v>
+        <v>11636.2</v>
       </c>
       <c r="G1416" t="n">
         <v>8</v>
@@ -47188,10 +47188,10 @@
         <v>73.8</v>
       </c>
       <c r="E1417" t="n">
-        <v>2023.4</v>
+        <v>2087.4</v>
       </c>
       <c r="F1417" t="n">
-        <v>9558.4</v>
+        <v>9622.4</v>
       </c>
       <c r="G1417" t="n">
         <v>1</v>
@@ -47221,10 +47221,10 @@
         <v>79.3</v>
       </c>
       <c r="E1418" t="n">
-        <v>2022.6</v>
+        <v>2084.9</v>
       </c>
       <c r="F1418" t="n">
-        <v>12733.7</v>
+        <v>12796</v>
       </c>
       <c r="G1418" t="n">
         <v>1</v>
@@ -47254,10 +47254,10 @@
         <v>62.3</v>
       </c>
       <c r="E1419" t="n">
-        <v>2094.6</v>
+        <v>2170.4</v>
       </c>
       <c r="F1419" t="n">
-        <v>12785.6</v>
+        <v>12861.4</v>
       </c>
       <c r="G1419" t="n">
         <v>4</v>
@@ -47287,16 +47287,16 @@
         <v>50.4</v>
       </c>
       <c r="E1420" t="n">
-        <v>2031.6</v>
+        <v>2106.8</v>
       </c>
       <c r="F1420" t="n">
-        <v>11896.7</v>
+        <v>11971.9</v>
       </c>
       <c r="G1420" t="n">
         <v>7</v>
       </c>
       <c r="H1420" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1420" t="n">
         <v>4</v>
@@ -47320,10 +47320,10 @@
         <v>48.8</v>
       </c>
       <c r="E1421" t="n">
-        <v>1864</v>
+        <v>1915.1</v>
       </c>
       <c r="F1421" t="n">
-        <v>11528.6</v>
+        <v>11579.7</v>
       </c>
       <c r="G1421" t="n">
         <v>8</v>
@@ -47353,10 +47353,10 @@
         <v>75</v>
       </c>
       <c r="E1422" t="n">
-        <v>2264.5</v>
+        <v>2344</v>
       </c>
       <c r="F1422" t="n">
-        <v>13199.3</v>
+        <v>13278.8</v>
       </c>
       <c r="G1422" t="n">
         <v>2</v>
@@ -47386,10 +47386,10 @@
         <v>64.5</v>
       </c>
       <c r="E1423" t="n">
-        <v>1792.2</v>
+        <v>1840.6</v>
       </c>
       <c r="F1423" t="n">
-        <v>10626.1</v>
+        <v>10674.5</v>
       </c>
       <c r="G1423" t="n">
         <v>3</v>
@@ -47419,16 +47419,16 @@
         <v>59.7</v>
       </c>
       <c r="E1424" t="n">
-        <v>2037.4</v>
+        <v>2091.8</v>
       </c>
       <c r="F1424" t="n">
-        <v>11641.5</v>
+        <v>11695.9</v>
       </c>
       <c r="G1424" t="n">
         <v>5</v>
       </c>
       <c r="H1424" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1424" t="n">
         <v>5</v>
@@ -47452,10 +47452,10 @@
         <v>57.7</v>
       </c>
       <c r="E1425" t="n">
-        <v>2081.1</v>
+        <v>2145.1</v>
       </c>
       <c r="F1425" t="n">
-        <v>9616.1</v>
+        <v>9680.1</v>
       </c>
       <c r="G1425" t="n">
         <v>6</v>
@@ -47485,10 +47485,10 @@
         <v>86.3</v>
       </c>
       <c r="E1426" t="n">
-        <v>2108.9</v>
+        <v>2171.2</v>
       </c>
       <c r="F1426" t="n">
-        <v>12820</v>
+        <v>12882.3</v>
       </c>
       <c r="G1426" t="n">
         <v>2</v>
@@ -47518,16 +47518,16 @@
         <v>75.59999999999999</v>
       </c>
       <c r="E1427" t="n">
-        <v>2170.2</v>
+        <v>2246</v>
       </c>
       <c r="F1427" t="n">
-        <v>12861.2</v>
+        <v>12937</v>
       </c>
       <c r="G1427" t="n">
         <v>3</v>
       </c>
       <c r="H1427" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1427" t="n">
         <v>2</v>
@@ -47551,16 +47551,16 @@
         <v>50.9</v>
       </c>
       <c r="E1428" t="n">
-        <v>2082.5</v>
+        <v>2157.7</v>
       </c>
       <c r="F1428" t="n">
-        <v>11947.6</v>
+        <v>12022.8</v>
       </c>
       <c r="G1428" t="n">
         <v>8</v>
       </c>
       <c r="H1428" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1428" t="n">
         <v>4</v>
@@ -47584,10 +47584,10 @@
         <v>65.3</v>
       </c>
       <c r="E1429" t="n">
-        <v>1929.3</v>
+        <v>1980.4</v>
       </c>
       <c r="F1429" t="n">
-        <v>11593.9</v>
+        <v>11645</v>
       </c>
       <c r="G1429" t="n">
         <v>4</v>
@@ -47617,10 +47617,10 @@
         <v>58.4</v>
       </c>
       <c r="E1430" t="n">
-        <v>2322.9</v>
+        <v>2402.4</v>
       </c>
       <c r="F1430" t="n">
-        <v>13257.7</v>
+        <v>13337.2</v>
       </c>
       <c r="G1430" t="n">
         <v>6</v>
@@ -47650,10 +47650,10 @@
         <v>58.6</v>
       </c>
       <c r="E1431" t="n">
-        <v>1850.8</v>
+        <v>1899.2</v>
       </c>
       <c r="F1431" t="n">
-        <v>10684.7</v>
+        <v>10733.1</v>
       </c>
       <c r="G1431" t="n">
         <v>5</v>
@@ -47683,16 +47683,16 @@
         <v>55.3</v>
       </c>
       <c r="E1432" t="n">
-        <v>2092.7</v>
+        <v>2147.1</v>
       </c>
       <c r="F1432" t="n">
-        <v>11696.8</v>
+        <v>11751.2</v>
       </c>
       <c r="G1432" t="n">
         <v>7</v>
       </c>
       <c r="H1432" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1432" t="n">
         <v>5</v>
@@ -47716,16 +47716,16 @@
         <v>96</v>
       </c>
       <c r="E1433" t="n">
-        <v>2177.1</v>
+        <v>2241.1</v>
       </c>
       <c r="F1433" t="n">
-        <v>9712.1</v>
+        <v>9776.1</v>
       </c>
       <c r="G1433" t="n">
         <v>1</v>
       </c>
       <c r="H1433" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1433" t="n">
         <v>8</v>
@@ -47749,10 +47749,10 @@
         <v>84.5</v>
       </c>
       <c r="E1434" t="n">
-        <v>2193.4</v>
+        <v>2255.7</v>
       </c>
       <c r="F1434" t="n">
-        <v>12904.5</v>
+        <v>12966.8</v>
       </c>
       <c r="G1434" t="n">
         <v>1</v>
@@ -47782,10 +47782,10 @@
         <v>66.59999999999999</v>
       </c>
       <c r="E1435" t="n">
-        <v>2236.8</v>
+        <v>2312.6</v>
       </c>
       <c r="F1435" t="n">
-        <v>12927.8</v>
+        <v>13003.6</v>
       </c>
       <c r="G1435" t="n">
         <v>4</v>
@@ -47815,16 +47815,16 @@
         <v>60.1</v>
       </c>
       <c r="E1436" t="n">
-        <v>2142.6</v>
+        <v>2217.8</v>
       </c>
       <c r="F1436" t="n">
-        <v>12007.7</v>
+        <v>12082.9</v>
       </c>
       <c r="G1436" t="n">
         <v>6</v>
       </c>
       <c r="H1436" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1436" t="n">
         <v>4</v>
@@ -47848,10 +47848,10 @@
         <v>74.09999999999999</v>
       </c>
       <c r="E1437" t="n">
-        <v>2003.4</v>
+        <v>2054.5</v>
       </c>
       <c r="F1437" t="n">
-        <v>11668</v>
+        <v>11719.1</v>
       </c>
       <c r="G1437" t="n">
         <v>3</v>
@@ -47881,10 +47881,10 @@
         <v>57.4</v>
       </c>
       <c r="E1438" t="n">
-        <v>2380.3</v>
+        <v>2459.8</v>
       </c>
       <c r="F1438" t="n">
-        <v>13315.1</v>
+        <v>13394.6</v>
       </c>
       <c r="G1438" t="n">
         <v>7</v>
@@ -47914,10 +47914,10 @@
         <v>0</v>
       </c>
       <c r="E1439" t="n">
-        <v>1850.8</v>
+        <v>1899.2</v>
       </c>
       <c r="F1439" t="n">
-        <v>10684.7</v>
+        <v>10733.1</v>
       </c>
       <c r="G1439" t="n">
         <v>8</v>
@@ -47947,16 +47947,16 @@
         <v>65.90000000000001</v>
       </c>
       <c r="E1440" t="n">
-        <v>2158.6</v>
+        <v>2213</v>
       </c>
       <c r="F1440" t="n">
-        <v>11762.7</v>
+        <v>11817.1</v>
       </c>
       <c r="G1440" t="n">
         <v>5</v>
       </c>
       <c r="H1440" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1440" t="n">
         <v>5</v>
@@ -47980,10 +47980,10 @@
         <v>76</v>
       </c>
       <c r="E1441" t="n">
-        <v>2253.1</v>
+        <v>2317.1</v>
       </c>
       <c r="F1441" t="n">
-        <v>9788.1</v>
+        <v>9852.1</v>
       </c>
       <c r="G1441" t="n">
         <v>2</v>
@@ -48013,10 +48013,10 @@
         <v>73.09999999999999</v>
       </c>
       <c r="E1442" t="n">
-        <v>2266.5</v>
+        <v>2328.8</v>
       </c>
       <c r="F1442" t="n">
-        <v>12977.6</v>
+        <v>13039.9</v>
       </c>
       <c r="G1442" t="n">
         <v>6</v>
@@ -48046,10 +48046,10 @@
         <v>92.90000000000001</v>
       </c>
       <c r="E1443" t="n">
-        <v>2329.7</v>
+        <v>2405.5</v>
       </c>
       <c r="F1443" t="n">
-        <v>13020.7</v>
+        <v>13096.5</v>
       </c>
       <c r="G1443" t="n">
         <v>2</v>
@@ -48079,10 +48079,10 @@
         <v>51.6</v>
       </c>
       <c r="E1444" t="n">
-        <v>2194.2</v>
+        <v>2269.4</v>
       </c>
       <c r="F1444" t="n">
-        <v>12059.3</v>
+        <v>12134.5</v>
       </c>
       <c r="G1444" t="n">
         <v>8</v>
@@ -48112,10 +48112,10 @@
         <v>62.1</v>
       </c>
       <c r="E1445" t="n">
-        <v>2065.5</v>
+        <v>2116.6</v>
       </c>
       <c r="F1445" t="n">
-        <v>11730.1</v>
+        <v>11781.2</v>
       </c>
       <c r="G1445" t="n">
         <v>7</v>
@@ -48145,10 +48145,10 @@
         <v>86.7</v>
       </c>
       <c r="E1446" t="n">
-        <v>2467</v>
+        <v>2546.5</v>
       </c>
       <c r="F1446" t="n">
-        <v>13401.8</v>
+        <v>13481.3</v>
       </c>
       <c r="G1446" t="n">
         <v>4</v>
@@ -48178,10 +48178,10 @@
         <v>88.2</v>
       </c>
       <c r="E1447" t="n">
-        <v>1939</v>
+        <v>1987.4</v>
       </c>
       <c r="F1447" t="n">
-        <v>10772.9</v>
+        <v>10821.3</v>
       </c>
       <c r="G1447" t="n">
         <v>3</v>
@@ -48211,10 +48211,10 @@
         <v>73.3</v>
       </c>
       <c r="E1448" t="n">
-        <v>2231.9</v>
+        <v>2286.3</v>
       </c>
       <c r="F1448" t="n">
-        <v>11836</v>
+        <v>11890.4</v>
       </c>
       <c r="G1448" t="n">
         <v>5</v>
@@ -48244,10 +48244,10 @@
         <v>100.9</v>
       </c>
       <c r="E1449" t="n">
-        <v>2354</v>
+        <v>2418</v>
       </c>
       <c r="F1449" t="n">
-        <v>9889</v>
+        <v>9953</v>
       </c>
       <c r="G1449" t="n">
         <v>1</v>
@@ -48277,10 +48277,10 @@
         <v>82.5</v>
       </c>
       <c r="E1450" t="n">
-        <v>2349</v>
+        <v>2411.3</v>
       </c>
       <c r="F1450" t="n">
-        <v>13060.1</v>
+        <v>13122.4</v>
       </c>
       <c r="G1450" t="n">
         <v>3</v>
@@ -48310,10 +48310,10 @@
         <v>73.5</v>
       </c>
       <c r="E1451" t="n">
-        <v>2403.2</v>
+        <v>2479</v>
       </c>
       <c r="F1451" t="n">
-        <v>13094.2</v>
+        <v>13170</v>
       </c>
       <c r="G1451" t="n">
         <v>4</v>
@@ -48343,10 +48343,10 @@
         <v>114.5</v>
       </c>
       <c r="E1452" t="n">
-        <v>2308.7</v>
+        <v>2383.9</v>
       </c>
       <c r="F1452" t="n">
-        <v>12173.8</v>
+        <v>12249</v>
       </c>
       <c r="G1452" t="n">
         <v>1</v>
@@ -48376,10 +48376,10 @@
         <v>85.90000000000001</v>
       </c>
       <c r="E1453" t="n">
-        <v>2151.4</v>
+        <v>2202.5</v>
       </c>
       <c r="F1453" t="n">
-        <v>11816</v>
+        <v>11867.1</v>
       </c>
       <c r="G1453" t="n">
         <v>2</v>
@@ -48409,10 +48409,10 @@
         <v>48.6</v>
       </c>
       <c r="E1454" t="n">
-        <v>2515.6</v>
+        <v>2595.1</v>
       </c>
       <c r="F1454" t="n">
-        <v>13450.4</v>
+        <v>13529.9</v>
       </c>
       <c r="G1454" t="n">
         <v>6</v>
@@ -48442,10 +48442,10 @@
         <v>52.8</v>
       </c>
       <c r="E1455" t="n">
-        <v>1991.8</v>
+        <v>2040.2</v>
       </c>
       <c r="F1455" t="n">
-        <v>10825.7</v>
+        <v>10874.1</v>
       </c>
       <c r="G1455" t="n">
         <v>5</v>
@@ -48475,10 +48475,10 @@
         <v>47.9</v>
       </c>
       <c r="E1456" t="n">
-        <v>2279.8</v>
+        <v>2334.2</v>
       </c>
       <c r="F1456" t="n">
-        <v>11883.9</v>
+        <v>11938.3</v>
       </c>
       <c r="G1456" t="n">
         <v>7</v>
@@ -48508,10 +48508,10 @@
         <v>43.3</v>
       </c>
       <c r="E1457" t="n">
-        <v>2397.3</v>
+        <v>2461.3</v>
       </c>
       <c r="F1457" t="n">
-        <v>9932.299999999999</v>
+        <v>9996.299999999999</v>
       </c>
       <c r="G1457" t="n">
         <v>8</v>
@@ -48541,10 +48541,10 @@
         <v>66.5</v>
       </c>
       <c r="E1458" t="n">
-        <v>2415.5</v>
+        <v>2477.8</v>
       </c>
       <c r="F1458" t="n">
-        <v>13126.6</v>
+        <v>13188.9</v>
       </c>
       <c r="G1458" t="n">
         <v>5</v>
@@ -48574,10 +48574,10 @@
         <v>65.5</v>
       </c>
       <c r="E1459" t="n">
-        <v>2468.7</v>
+        <v>2544.5</v>
       </c>
       <c r="F1459" t="n">
-        <v>13159.7</v>
+        <v>13235.5</v>
       </c>
       <c r="G1459" t="n">
         <v>7</v>
@@ -48607,10 +48607,10 @@
         <v>83.90000000000001</v>
       </c>
       <c r="E1460" t="n">
-        <v>2392.6</v>
+        <v>2467.8</v>
       </c>
       <c r="F1460" t="n">
-        <v>12257.7</v>
+        <v>12332.9</v>
       </c>
       <c r="G1460" t="n">
         <v>3</v>
@@ -48640,10 +48640,10 @@
         <v>66.40000000000001</v>
       </c>
       <c r="E1461" t="n">
-        <v>2217.8</v>
+        <v>2268.9</v>
       </c>
       <c r="F1461" t="n">
-        <v>11882.4</v>
+        <v>11933.5</v>
       </c>
       <c r="G1461" t="n">
         <v>6</v>
@@ -48673,10 +48673,10 @@
         <v>107</v>
       </c>
       <c r="E1462" t="n">
-        <v>2622.6</v>
+        <v>2702.1</v>
       </c>
       <c r="F1462" t="n">
-        <v>13557.4</v>
+        <v>13636.9</v>
       </c>
       <c r="G1462" t="n">
         <v>1</v>
@@ -48706,10 +48706,10 @@
         <v>46.5</v>
       </c>
       <c r="E1463" t="n">
-        <v>2038.3</v>
+        <v>2086.7</v>
       </c>
       <c r="F1463" t="n">
-        <v>10872.2</v>
+        <v>10920.6</v>
       </c>
       <c r="G1463" t="n">
         <v>8</v>
@@ -48739,10 +48739,10 @@
         <v>67.40000000000001</v>
       </c>
       <c r="E1464" t="n">
-        <v>2347.2</v>
+        <v>2401.6</v>
       </c>
       <c r="F1464" t="n">
-        <v>11951.3</v>
+        <v>12005.7</v>
       </c>
       <c r="G1464" t="n">
         <v>4</v>
@@ -48772,10 +48772,10 @@
         <v>85.59999999999999</v>
       </c>
       <c r="E1465" t="n">
-        <v>2482.9</v>
+        <v>2546.9</v>
       </c>
       <c r="F1465" t="n">
-        <v>10017.9</v>
+        <v>10081.9</v>
       </c>
       <c r="G1465" t="n">
         <v>2</v>
@@ -48805,10 +48805,10 @@
         <v>100.6</v>
       </c>
       <c r="E1466" t="n">
-        <v>2516.1</v>
+        <v>2578.4</v>
       </c>
       <c r="F1466" t="n">
-        <v>13227.2</v>
+        <v>13289.5</v>
       </c>
       <c r="G1466" t="n">
         <v>1</v>
@@ -48817,7 +48817,7 @@
         <v>4</v>
       </c>
       <c r="I1466" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1467">
@@ -48838,10 +48838,10 @@
         <v>65.90000000000001</v>
       </c>
       <c r="E1467" t="n">
-        <v>2534.6</v>
+        <v>2610.4</v>
       </c>
       <c r="F1467" t="n">
-        <v>13225.6</v>
+        <v>13301.4</v>
       </c>
       <c r="G1467" t="n">
         <v>5</v>
@@ -48850,7 +48850,7 @@
         <v>3</v>
       </c>
       <c r="I1467" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1468">
@@ -48871,10 +48871,10 @@
         <v>70.8</v>
       </c>
       <c r="E1468" t="n">
-        <v>2463.4</v>
+        <v>2538.6</v>
       </c>
       <c r="F1468" t="n">
-        <v>12328.5</v>
+        <v>12403.7</v>
       </c>
       <c r="G1468" t="n">
         <v>4</v>
@@ -48904,10 +48904,10 @@
         <v>60.5</v>
       </c>
       <c r="E1469" t="n">
-        <v>2278.3</v>
+        <v>2329.4</v>
       </c>
       <c r="F1469" t="n">
-        <v>11942.9</v>
+        <v>11994</v>
       </c>
       <c r="G1469" t="n">
         <v>7</v>
@@ -48937,10 +48937,10 @@
         <v>64.59999999999999</v>
       </c>
       <c r="E1470" t="n">
-        <v>2687.2</v>
+        <v>2766.7</v>
       </c>
       <c r="F1470" t="n">
-        <v>13622</v>
+        <v>13701.5</v>
       </c>
       <c r="G1470" t="n">
         <v>6</v>
@@ -48970,10 +48970,10 @@
         <v>73.7</v>
       </c>
       <c r="E1471" t="n">
-        <v>2112</v>
+        <v>2160.4</v>
       </c>
       <c r="F1471" t="n">
-        <v>10945.9</v>
+        <v>10994.3</v>
       </c>
       <c r="G1471" t="n">
         <v>3</v>
@@ -49003,10 +49003,10 @@
         <v>55.2</v>
       </c>
       <c r="E1472" t="n">
-        <v>2402.4</v>
+        <v>2456.8</v>
       </c>
       <c r="F1472" t="n">
-        <v>12006.5</v>
+        <v>12060.9</v>
       </c>
       <c r="G1472" t="n">
         <v>8</v>
@@ -49036,10 +49036,10 @@
         <v>88</v>
       </c>
       <c r="E1473" t="n">
-        <v>2570.9</v>
+        <v>2634.9</v>
       </c>
       <c r="F1473" t="n">
-        <v>10105.9</v>
+        <v>10169.9</v>
       </c>
       <c r="G1473" t="n">
         <v>2</v>
@@ -49069,10 +49069,10 @@
         <v>70.09999999999999</v>
       </c>
       <c r="E1474" t="n">
-        <v>2586.2</v>
+        <v>2648.5</v>
       </c>
       <c r="F1474" t="n">
-        <v>13297.3</v>
+        <v>13359.6</v>
       </c>
       <c r="G1474" t="n">
         <v>4</v>
@@ -49102,10 +49102,10 @@
         <v>77.90000000000001</v>
       </c>
       <c r="E1475" t="n">
-        <v>2612.5</v>
+        <v>2688.3</v>
       </c>
       <c r="F1475" t="n">
-        <v>13303.5</v>
+        <v>13379.3</v>
       </c>
       <c r="G1475" t="n">
         <v>3</v>
@@ -49135,10 +49135,10 @@
         <v>80.8</v>
       </c>
       <c r="E1476" t="n">
-        <v>2544.2</v>
+        <v>2619.4</v>
       </c>
       <c r="F1476" t="n">
-        <v>12409.3</v>
+        <v>12484.5</v>
       </c>
       <c r="G1476" t="n">
         <v>2</v>
@@ -49168,10 +49168,10 @@
         <v>53</v>
       </c>
       <c r="E1477" t="n">
-        <v>2331.3</v>
+        <v>2382.4</v>
       </c>
       <c r="F1477" t="n">
-        <v>11995.9</v>
+        <v>12047</v>
       </c>
       <c r="G1477" t="n">
         <v>7</v>
@@ -49201,10 +49201,10 @@
         <v>59.8</v>
       </c>
       <c r="E1478" t="n">
-        <v>2747</v>
+        <v>2826.5</v>
       </c>
       <c r="F1478" t="n">
-        <v>13681.8</v>
+        <v>13761.3</v>
       </c>
       <c r="G1478" t="n">
         <v>6</v>
@@ -49234,10 +49234,10 @@
         <v>68.39999999999999</v>
       </c>
       <c r="E1479" t="n">
-        <v>2180.4</v>
+        <v>2228.8</v>
       </c>
       <c r="F1479" t="n">
-        <v>11014.3</v>
+        <v>11062.7</v>
       </c>
       <c r="G1479" t="n">
         <v>5</v>
@@ -49267,10 +49267,10 @@
         <v>48.4</v>
       </c>
       <c r="E1480" t="n">
-        <v>2450.8</v>
+        <v>2505.2</v>
       </c>
       <c r="F1480" t="n">
-        <v>12054.9</v>
+        <v>12109.3</v>
       </c>
       <c r="G1480" t="n">
         <v>8</v>
@@ -49300,10 +49300,10 @@
         <v>104.8</v>
       </c>
       <c r="E1481" t="n">
-        <v>2675.7</v>
+        <v>2739.7</v>
       </c>
       <c r="F1481" t="n">
-        <v>10210.7</v>
+        <v>10274.7</v>
       </c>
       <c r="G1481" t="n">
         <v>1</v>
@@ -49333,10 +49333,10 @@
         <v>76.3</v>
       </c>
       <c r="E1482" t="n">
-        <v>2662.5</v>
+        <v>2724.8</v>
       </c>
       <c r="F1482" t="n">
-        <v>13373.6</v>
+        <v>13435.9</v>
       </c>
       <c r="G1482" t="n">
         <v>3</v>
@@ -49366,10 +49366,10 @@
         <v>73.3</v>
       </c>
       <c r="E1483" t="n">
-        <v>2685.8</v>
+        <v>2761.6</v>
       </c>
       <c r="F1483" t="n">
-        <v>13376.8</v>
+        <v>13452.6</v>
       </c>
       <c r="G1483" t="n">
         <v>5</v>
@@ -49399,10 +49399,10 @@
         <v>56.5</v>
       </c>
       <c r="E1484" t="n">
-        <v>2600.7</v>
+        <v>2675.9</v>
       </c>
       <c r="F1484" t="n">
-        <v>12465.8</v>
+        <v>12541</v>
       </c>
       <c r="G1484" t="n">
         <v>7</v>
@@ -49432,10 +49432,10 @@
         <v>75.09999999999999</v>
       </c>
       <c r="E1485" t="n">
-        <v>2406.4</v>
+        <v>2457.5</v>
       </c>
       <c r="F1485" t="n">
-        <v>12071</v>
+        <v>12122.1</v>
       </c>
       <c r="G1485" t="n">
         <v>4</v>
@@ -49465,10 +49465,10 @@
         <v>69.7</v>
       </c>
       <c r="E1486" t="n">
-        <v>2816.7</v>
+        <v>2896.2</v>
       </c>
       <c r="F1486" t="n">
-        <v>13751.5</v>
+        <v>13831</v>
       </c>
       <c r="G1486" t="n">
         <v>6</v>
@@ -49498,10 +49498,10 @@
         <v>80.09999999999999</v>
       </c>
       <c r="E1487" t="n">
-        <v>2260.5</v>
+        <v>2308.9</v>
       </c>
       <c r="F1487" t="n">
-        <v>11094.4</v>
+        <v>11142.8</v>
       </c>
       <c r="G1487" t="n">
         <v>2</v>
@@ -49531,10 +49531,10 @@
         <v>44.90000000000001</v>
       </c>
       <c r="E1488" t="n">
-        <v>2495.7</v>
+        <v>2550.1</v>
       </c>
       <c r="F1488" t="n">
-        <v>12099.8</v>
+        <v>12154.2</v>
       </c>
       <c r="G1488" t="n">
         <v>8</v>
@@ -49564,10 +49564,10 @@
         <v>82.40000000000001</v>
       </c>
       <c r="E1489" t="n">
-        <v>2758.1</v>
+        <v>2822.1</v>
       </c>
       <c r="F1489" t="n">
-        <v>10293.1</v>
+        <v>10357.1</v>
       </c>
       <c r="G1489" t="n">
         <v>1</v>
@@ -49597,10 +49597,10 @@
         <v>94.09999999999999</v>
       </c>
       <c r="E1490" t="n">
-        <v>2756.6</v>
+        <v>2818.9</v>
       </c>
       <c r="F1490" t="n">
-        <v>13467.7</v>
+        <v>13530</v>
       </c>
       <c r="G1490" t="n">
         <v>3</v>
@@ -49630,10 +49630,10 @@
         <v>94.90000000000001</v>
       </c>
       <c r="E1491" t="n">
-        <v>2780.7</v>
+        <v>2856.5</v>
       </c>
       <c r="F1491" t="n">
-        <v>13471.7</v>
+        <v>13547.5</v>
       </c>
       <c r="G1491" t="n">
         <v>2</v>
@@ -49663,10 +49663,10 @@
         <v>75.2</v>
       </c>
       <c r="E1492" t="n">
-        <v>2675.9</v>
+        <v>2751.1</v>
       </c>
       <c r="F1492" t="n">
-        <v>12541</v>
+        <v>12616.2</v>
       </c>
       <c r="G1492" t="n">
         <v>5</v>
@@ -49696,10 +49696,10 @@
         <v>38.3</v>
       </c>
       <c r="E1493" t="n">
-        <v>2444.7</v>
+        <v>2495.8</v>
       </c>
       <c r="F1493" t="n">
-        <v>12109.3</v>
+        <v>12160.4</v>
       </c>
       <c r="G1493" t="n">
         <v>8</v>
@@ -49729,10 +49729,10 @@
         <v>52.9</v>
       </c>
       <c r="E1494" t="n">
-        <v>2869.6</v>
+        <v>2949.1</v>
       </c>
       <c r="F1494" t="n">
-        <v>13804.4</v>
+        <v>13883.9</v>
       </c>
       <c r="G1494" t="n">
         <v>6</v>
@@ -49762,10 +49762,10 @@
         <v>78.7</v>
       </c>
       <c r="E1495" t="n">
-        <v>2339.2</v>
+        <v>2387.6</v>
       </c>
       <c r="F1495" t="n">
-        <v>11173.1</v>
+        <v>11221.5</v>
       </c>
       <c r="G1495" t="n">
         <v>4</v>
@@ -49795,10 +49795,10 @@
         <v>44.4</v>
       </c>
       <c r="E1496" t="n">
-        <v>2540.1</v>
+        <v>2594.5</v>
       </c>
       <c r="F1496" t="n">
-        <v>12144.2</v>
+        <v>12198.6</v>
       </c>
       <c r="G1496" t="n">
         <v>7</v>
@@ -49828,10 +49828,10 @@
         <v>95.3</v>
       </c>
       <c r="E1497" t="n">
-        <v>2853.4</v>
+        <v>2917.4</v>
       </c>
       <c r="F1497" t="n">
-        <v>10388.4</v>
+        <v>10452.4</v>
       </c>
       <c r="G1497" t="n">
         <v>1</v>
@@ -49861,16 +49861,16 @@
         <v>72.8</v>
       </c>
       <c r="E1498" t="n">
-        <v>2829.4</v>
+        <v>2891.7</v>
       </c>
       <c r="F1498" t="n">
-        <v>13540.5</v>
+        <v>13602.8</v>
       </c>
       <c r="G1498" t="n">
         <v>2</v>
       </c>
       <c r="H1498" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1498" t="n">
         <v>2</v>
@@ -49894,16 +49894,16 @@
         <v>42</v>
       </c>
       <c r="E1499" t="n">
-        <v>2822.7</v>
+        <v>2898.5</v>
       </c>
       <c r="F1499" t="n">
-        <v>13513.7</v>
+        <v>13589.5</v>
       </c>
       <c r="G1499" t="n">
         <v>7</v>
       </c>
       <c r="H1499" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1499" t="n">
         <v>3</v>
@@ -49927,10 +49927,10 @@
         <v>65.10000000000001</v>
       </c>
       <c r="E1500" t="n">
-        <v>2741</v>
+        <v>2816.2</v>
       </c>
       <c r="F1500" t="n">
-        <v>12606.1</v>
+        <v>12681.3</v>
       </c>
       <c r="G1500" t="n">
         <v>5</v>
@@ -49960,10 +49960,10 @@
         <v>39.8</v>
       </c>
       <c r="E1501" t="n">
-        <v>2484.5</v>
+        <v>2535.6</v>
       </c>
       <c r="F1501" t="n">
-        <v>12149.1</v>
+        <v>12200.2</v>
       </c>
       <c r="G1501" t="n">
         <v>8</v>
@@ -49993,10 +49993,10 @@
         <v>65.8</v>
       </c>
       <c r="E1502" t="n">
-        <v>2935.4</v>
+        <v>3014.9</v>
       </c>
       <c r="F1502" t="n">
-        <v>13870.2</v>
+        <v>13949.7</v>
       </c>
       <c r="G1502" t="n">
         <v>4</v>
@@ -50026,10 +50026,10 @@
         <v>66.40000000000001</v>
       </c>
       <c r="E1503" t="n">
-        <v>2405.6</v>
+        <v>2454</v>
       </c>
       <c r="F1503" t="n">
-        <v>11239.5</v>
+        <v>11287.9</v>
       </c>
       <c r="G1503" t="n">
         <v>3</v>
@@ -50059,10 +50059,10 @@
         <v>52.7</v>
       </c>
       <c r="E1504" t="n">
-        <v>2592.8</v>
+        <v>2647.2</v>
       </c>
       <c r="F1504" t="n">
-        <v>12196.9</v>
+        <v>12251.3</v>
       </c>
       <c r="G1504" t="n">
         <v>6</v>
@@ -50092,10 +50092,10 @@
         <v>81.3</v>
       </c>
       <c r="E1505" t="n">
-        <v>2934.7</v>
+        <v>2998.7</v>
       </c>
       <c r="F1505" t="n">
-        <v>10469.7</v>
+        <v>10533.7</v>
       </c>
       <c r="G1505" t="n">
         <v>1</v>
@@ -50125,16 +50125,16 @@
         <v>70.59999999999999</v>
       </c>
       <c r="E1506" t="n">
-        <v>2900</v>
+        <v>2962.3</v>
       </c>
       <c r="F1506" t="n">
-        <v>13611.1</v>
+        <v>13673.4</v>
       </c>
       <c r="G1506" t="n">
         <v>4</v>
       </c>
       <c r="H1506" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1506" t="n">
         <v>2</v>
@@ -50158,16 +50158,16 @@
         <v>76.40000000000001</v>
       </c>
       <c r="E1507" t="n">
-        <v>2899.1</v>
+        <v>2974.9</v>
       </c>
       <c r="F1507" t="n">
-        <v>13590.1</v>
+        <v>13665.9</v>
       </c>
       <c r="G1507" t="n">
         <v>2</v>
       </c>
       <c r="H1507" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1507" t="n">
         <v>3</v>
@@ -50191,10 +50191,10 @@
         <v>60.3</v>
       </c>
       <c r="E1508" t="n">
-        <v>2801.3</v>
+        <v>2876.5</v>
       </c>
       <c r="F1508" t="n">
-        <v>12666.4</v>
+        <v>12741.6</v>
       </c>
       <c r="G1508" t="n">
         <v>6</v>
@@ -50224,10 +50224,10 @@
         <v>60.4</v>
       </c>
       <c r="E1509" t="n">
-        <v>2544.9</v>
+        <v>2596</v>
       </c>
       <c r="F1509" t="n">
-        <v>12209.5</v>
+        <v>12260.6</v>
       </c>
       <c r="G1509" t="n">
         <v>5</v>
@@ -50257,10 +50257,10 @@
         <v>53.9</v>
       </c>
       <c r="E1510" t="n">
-        <v>2989.3</v>
+        <v>3068.8</v>
       </c>
       <c r="F1510" t="n">
-        <v>13924.1</v>
+        <v>14003.6</v>
       </c>
       <c r="G1510" t="n">
         <v>7</v>
@@ -50290,10 +50290,10 @@
         <v>75.80000000000001</v>
       </c>
       <c r="E1511" t="n">
-        <v>2481.4</v>
+        <v>2529.8</v>
       </c>
       <c r="F1511" t="n">
-        <v>11315.3</v>
+        <v>11363.7</v>
       </c>
       <c r="G1511" t="n">
         <v>3</v>
@@ -50323,10 +50323,10 @@
         <v>53.2</v>
       </c>
       <c r="E1512" t="n">
-        <v>2646</v>
+        <v>2700.4</v>
       </c>
       <c r="F1512" t="n">
-        <v>12250.1</v>
+        <v>12304.5</v>
       </c>
       <c r="G1512" t="n">
         <v>8</v>
@@ -50356,10 +50356,10 @@
         <v>87.59999999999999</v>
       </c>
       <c r="E1513" t="n">
-        <v>3022.3</v>
+        <v>3086.3</v>
       </c>
       <c r="F1513" t="n">
-        <v>10557.3</v>
+        <v>10621.3</v>
       </c>
       <c r="G1513" t="n">
         <v>1</v>
@@ -50389,16 +50389,16 @@
         <v>58.2</v>
       </c>
       <c r="E1514" t="n">
-        <v>2958.2</v>
+        <v>3020.5</v>
       </c>
       <c r="F1514" t="n">
-        <v>13669.3</v>
+        <v>13731.6</v>
       </c>
       <c r="G1514" t="n">
         <v>4</v>
       </c>
       <c r="H1514" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1514" t="n">
         <v>2</v>
@@ -50422,16 +50422,16 @@
         <v>49.3</v>
       </c>
       <c r="E1515" t="n">
-        <v>2948.4</v>
+        <v>3024.2</v>
       </c>
       <c r="F1515" t="n">
-        <v>13639.4</v>
+        <v>13715.2</v>
       </c>
       <c r="G1515" t="n">
         <v>5</v>
       </c>
       <c r="H1515" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1515" t="n">
         <v>3</v>
@@ -50455,10 +50455,10 @@
         <v>69.09999999999999</v>
       </c>
       <c r="E1516" t="n">
-        <v>2870.4</v>
+        <v>2945.6</v>
       </c>
       <c r="F1516" t="n">
-        <v>12735.5</v>
+        <v>12810.7</v>
       </c>
       <c r="G1516" t="n">
         <v>3</v>
@@ -50488,10 +50488,10 @@
         <v>48.4</v>
       </c>
       <c r="E1517" t="n">
-        <v>2593.3</v>
+        <v>2644.4</v>
       </c>
       <c r="F1517" t="n">
-        <v>12257.9</v>
+        <v>12309</v>
       </c>
       <c r="G1517" t="n">
         <v>6</v>
@@ -50521,10 +50521,10 @@
         <v>47.6</v>
       </c>
       <c r="E1518" t="n">
-        <v>3036.9</v>
+        <v>3116.4</v>
       </c>
       <c r="F1518" t="n">
-        <v>13971.7</v>
+        <v>14051.2</v>
       </c>
       <c r="G1518" t="n">
         <v>7</v>
@@ -50554,10 +50554,10 @@
         <v>34.8</v>
       </c>
       <c r="E1519" t="n">
-        <v>2516.2</v>
+        <v>2564.6</v>
       </c>
       <c r="F1519" t="n">
-        <v>11350.1</v>
+        <v>11398.5</v>
       </c>
       <c r="G1519" t="n">
         <v>8</v>
@@ -50587,10 +50587,10 @@
         <v>73.3</v>
       </c>
       <c r="E1520" t="n">
-        <v>2719.3</v>
+        <v>2773.7</v>
       </c>
       <c r="F1520" t="n">
-        <v>12323.4</v>
+        <v>12377.8</v>
       </c>
       <c r="G1520" t="n">
         <v>2</v>
@@ -50620,10 +50620,10 @@
         <v>97.7</v>
       </c>
       <c r="E1521" t="n">
-        <v>3120</v>
+        <v>3184</v>
       </c>
       <c r="F1521" t="n">
-        <v>10655</v>
+        <v>10719</v>
       </c>
       <c r="G1521" t="n">
         <v>1</v>
@@ -50653,10 +50653,10 @@
         <v>95.7</v>
       </c>
       <c r="E1522" t="n">
-        <v>3053.9</v>
+        <v>3116.2</v>
       </c>
       <c r="F1522" t="n">
-        <v>13765</v>
+        <v>13827.3</v>
       </c>
       <c r="G1522" t="n">
         <v>1</v>
@@ -50686,10 +50686,10 @@
         <v>0</v>
       </c>
       <c r="E1523" t="n">
-        <v>2948.4</v>
+        <v>3024.2</v>
       </c>
       <c r="F1523" t="n">
-        <v>13639.4</v>
+        <v>13715.2</v>
       </c>
       <c r="G1523" t="n">
         <v>8</v>
@@ -50719,10 +50719,10 @@
         <v>40.7</v>
       </c>
       <c r="E1524" t="n">
-        <v>2911.1</v>
+        <v>2986.3</v>
       </c>
       <c r="F1524" t="n">
-        <v>12776.2</v>
+        <v>12851.4</v>
       </c>
       <c r="G1524" t="n">
         <v>7</v>
@@ -50752,10 +50752,10 @@
         <v>68.2</v>
       </c>
       <c r="E1525" t="n">
-        <v>2661.5</v>
+        <v>2712.6</v>
       </c>
       <c r="F1525" t="n">
-        <v>12326.1</v>
+        <v>12377.2</v>
       </c>
       <c r="G1525" t="n">
         <v>4</v>
@@ -50785,10 +50785,10 @@
         <v>66.59999999999999</v>
       </c>
       <c r="E1526" t="n">
-        <v>3103.5</v>
+        <v>3183</v>
       </c>
       <c r="F1526" t="n">
-        <v>14038.3</v>
+        <v>14117.8</v>
       </c>
       <c r="G1526" t="n">
         <v>5</v>
@@ -50818,10 +50818,10 @@
         <v>80.59999999999999</v>
       </c>
       <c r="E1527" t="n">
-        <v>2596.8</v>
+        <v>2645.2</v>
       </c>
       <c r="F1527" t="n">
-        <v>11430.7</v>
+        <v>11479.1</v>
       </c>
       <c r="G1527" t="n">
         <v>2</v>
@@ -50851,10 +50851,10 @@
         <v>46.4</v>
       </c>
       <c r="E1528" t="n">
-        <v>2765.7</v>
+        <v>2820.1</v>
       </c>
       <c r="F1528" t="n">
-        <v>12369.8</v>
+        <v>12424.2</v>
       </c>
       <c r="G1528" t="n">
         <v>6</v>
@@ -50884,10 +50884,10 @@
         <v>80.40000000000001</v>
       </c>
       <c r="E1529" t="n">
-        <v>3200.4</v>
+        <v>3264.4</v>
       </c>
       <c r="F1529" t="n">
-        <v>10735.4</v>
+        <v>10799.4</v>
       </c>
       <c r="G1529" t="n">
         <v>3</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -42733,7 +42733,7 @@
         <v>116.1</v>
       </c>
       <c r="E1282" t="n">
-        <v>781.7</v>
+        <v>781.6999999999999</v>
       </c>
       <c r="F1282" t="n">
         <v>11492.8</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -42436,7 +42436,7 @@
         <v>98.09999999999999</v>
       </c>
       <c r="E1273" t="n">
-        <v>649.7</v>
+        <v>649.6999999999999</v>
       </c>
       <c r="F1273" t="n">
         <v>8184.7</v>
@@ -43228,7 +43228,7 @@
         <v>76.89999999999999</v>
       </c>
       <c r="E1297" t="n">
-        <v>971.7</v>
+        <v>971.6999999999999</v>
       </c>
       <c r="F1297" t="n">
         <v>8506.700000000001</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -42172,7 +42172,7 @@
         <v>114.8</v>
       </c>
       <c r="E1265" t="n">
-        <v>551.6</v>
+        <v>551.5999999999999</v>
       </c>
       <c r="F1265" t="n">
         <v>8086.6</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -42172,7 +42172,7 @@
         <v>114.8</v>
       </c>
       <c r="E1265" t="n">
-        <v>551.5999999999999</v>
+        <v>551.6</v>
       </c>
       <c r="F1265" t="n">
         <v>8086.6</v>
@@ -42436,7 +42436,7 @@
         <v>98.09999999999999</v>
       </c>
       <c r="E1273" t="n">
-        <v>649.6999999999999</v>
+        <v>649.7</v>
       </c>
       <c r="F1273" t="n">
         <v>8184.7</v>
@@ -43228,7 +43228,7 @@
         <v>76.89999999999999</v>
       </c>
       <c r="E1297" t="n">
-        <v>971.6999999999999</v>
+        <v>971.7</v>
       </c>
       <c r="F1297" t="n">
         <v>8506.700000000001</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -42733,7 +42733,7 @@
         <v>116.1</v>
       </c>
       <c r="E1282" t="n">
-        <v>781.6999999999999</v>
+        <v>781.7</v>
       </c>
       <c r="F1282" t="n">
         <v>11492.8</v>
@@ -42994,19 +42994,19 @@
         </is>
       </c>
       <c r="D1290" t="n">
-        <v>87.8</v>
+        <v>146</v>
       </c>
       <c r="E1290" t="n">
-        <v>869.5</v>
+        <v>927.7</v>
       </c>
       <c r="F1290" t="n">
-        <v>11580.6</v>
+        <v>11638.8</v>
       </c>
       <c r="G1290" t="n">
         <v>1</v>
       </c>
       <c r="H1290" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1290" t="n">
         <v>3</v>
@@ -43027,19 +43027,19 @@
         </is>
       </c>
       <c r="D1291" t="n">
-        <v>67</v>
+        <v>130.8</v>
       </c>
       <c r="E1291" t="n">
-        <v>1024</v>
+        <v>1087.8</v>
       </c>
       <c r="F1291" t="n">
-        <v>11715</v>
+        <v>11778.8</v>
       </c>
       <c r="G1291" t="n">
         <v>4</v>
       </c>
       <c r="H1291" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1291" t="n">
         <v>2</v>
@@ -43060,19 +43060,19 @@
         </is>
       </c>
       <c r="D1292" t="n">
-        <v>55.4</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="E1292" t="n">
-        <v>1026</v>
+        <v>1060.7</v>
       </c>
       <c r="F1292" t="n">
-        <v>10891.1</v>
+        <v>10925.8</v>
       </c>
       <c r="G1292" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H1292" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I1292" t="n">
         <v>4</v>
@@ -43093,16 +43093,16 @@
         </is>
       </c>
       <c r="D1293" t="n">
-        <v>57.6</v>
+        <v>99.5</v>
       </c>
       <c r="E1293" t="n">
-        <v>1054</v>
+        <v>1095.9</v>
       </c>
       <c r="F1293" t="n">
-        <v>10718.6</v>
+        <v>10760.5</v>
       </c>
       <c r="G1293" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1293" t="n">
         <v>2</v>
@@ -43126,16 +43126,16 @@
         </is>
       </c>
       <c r="D1294" t="n">
-        <v>66.3</v>
+        <v>135.4</v>
       </c>
       <c r="E1294" t="n">
-        <v>1145.8</v>
+        <v>1214.9</v>
       </c>
       <c r="F1294" t="n">
-        <v>12080.6</v>
+        <v>12149.7</v>
       </c>
       <c r="G1294" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H1294" t="n">
         <v>1</v>
@@ -43159,19 +43159,19 @@
         </is>
       </c>
       <c r="D1295" t="n">
-        <v>52.1</v>
+        <v>124.7</v>
       </c>
       <c r="E1295" t="n">
-        <v>868.2</v>
+        <v>940.8</v>
       </c>
       <c r="F1295" t="n">
-        <v>9702.1</v>
+        <v>9774.700000000001</v>
       </c>
       <c r="G1295" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H1295" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I1295" t="n">
         <v>7</v>
@@ -43192,19 +43192,19 @@
         </is>
       </c>
       <c r="D1296" t="n">
-        <v>81.09999999999999</v>
+        <v>142.1</v>
       </c>
       <c r="E1296" t="n">
-        <v>1010.9</v>
+        <v>1071.9</v>
       </c>
       <c r="F1296" t="n">
-        <v>10615</v>
+        <v>10676</v>
       </c>
       <c r="G1296" t="n">
         <v>2</v>
       </c>
       <c r="H1296" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1296" t="n">
         <v>6</v>
@@ -43225,16 +43225,16 @@
         </is>
       </c>
       <c r="D1297" t="n">
-        <v>76.89999999999999</v>
+        <v>128.9</v>
       </c>
       <c r="E1297" t="n">
-        <v>971.7</v>
+        <v>1023.7</v>
       </c>
       <c r="F1297" t="n">
-        <v>8506.700000000001</v>
+        <v>8558.700000000001</v>
       </c>
       <c r="G1297" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1297" t="n">
         <v>6</v>
@@ -43261,10 +43261,10 @@
         <v>77.90000000000001</v>
       </c>
       <c r="E1298" t="n">
-        <v>947.4</v>
+        <v>1005.6</v>
       </c>
       <c r="F1298" t="n">
-        <v>11658.5</v>
+        <v>11716.7</v>
       </c>
       <c r="G1298" t="n">
         <v>1</v>
@@ -43294,16 +43294,16 @@
         <v>54.8</v>
       </c>
       <c r="E1299" t="n">
-        <v>1078.8</v>
+        <v>1142.6</v>
       </c>
       <c r="F1299" t="n">
-        <v>11769.8</v>
+        <v>11833.6</v>
       </c>
       <c r="G1299" t="n">
         <v>7</v>
       </c>
       <c r="H1299" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I1299" t="n">
         <v>2</v>
@@ -43327,16 +43327,16 @@
         <v>68.8</v>
       </c>
       <c r="E1300" t="n">
-        <v>1094.8</v>
+        <v>1129.5</v>
       </c>
       <c r="F1300" t="n">
-        <v>10959.9</v>
+        <v>10994.6</v>
       </c>
       <c r="G1300" t="n">
         <v>3</v>
       </c>
       <c r="H1300" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I1300" t="n">
         <v>4</v>
@@ -43360,10 +43360,10 @@
         <v>60.2</v>
       </c>
       <c r="E1301" t="n">
-        <v>1114.2</v>
+        <v>1156.1</v>
       </c>
       <c r="F1301" t="n">
-        <v>10778.8</v>
+        <v>10820.7</v>
       </c>
       <c r="G1301" t="n">
         <v>6</v>
@@ -43393,10 +43393,10 @@
         <v>62.8</v>
       </c>
       <c r="E1302" t="n">
-        <v>1208.6</v>
+        <v>1277.7</v>
       </c>
       <c r="F1302" t="n">
-        <v>12143.4</v>
+        <v>12212.5</v>
       </c>
       <c r="G1302" t="n">
         <v>5</v>
@@ -43426,10 +43426,10 @@
         <v>50.9</v>
       </c>
       <c r="E1303" t="n">
-        <v>919.1</v>
+        <v>991.7</v>
       </c>
       <c r="F1303" t="n">
-        <v>9753</v>
+        <v>9825.6</v>
       </c>
       <c r="G1303" t="n">
         <v>8</v>
@@ -43459,10 +43459,10 @@
         <v>69.40000000000001</v>
       </c>
       <c r="E1304" t="n">
-        <v>1080.3</v>
+        <v>1141.3</v>
       </c>
       <c r="F1304" t="n">
-        <v>10684.4</v>
+        <v>10745.4</v>
       </c>
       <c r="G1304" t="n">
         <v>2</v>
@@ -43492,10 +43492,10 @@
         <v>66.3</v>
       </c>
       <c r="E1305" t="n">
-        <v>1038</v>
+        <v>1090</v>
       </c>
       <c r="F1305" t="n">
-        <v>8573</v>
+        <v>8625</v>
       </c>
       <c r="G1305" t="n">
         <v>4</v>
@@ -43525,10 +43525,10 @@
         <v>68</v>
       </c>
       <c r="E1306" t="n">
-        <v>1015.4</v>
+        <v>1073.6</v>
       </c>
       <c r="F1306" t="n">
-        <v>11726.5</v>
+        <v>11784.7</v>
       </c>
       <c r="G1306" t="n">
         <v>5</v>
@@ -43558,16 +43558,16 @@
         <v>89.2</v>
       </c>
       <c r="E1307" t="n">
-        <v>1168</v>
+        <v>1231.8</v>
       </c>
       <c r="F1307" t="n">
-        <v>11859</v>
+        <v>11922.8</v>
       </c>
       <c r="G1307" t="n">
         <v>2</v>
       </c>
       <c r="H1307" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I1307" t="n">
         <v>2</v>
@@ -43591,16 +43591,16 @@
         <v>79.3</v>
       </c>
       <c r="E1308" t="n">
-        <v>1174.1</v>
+        <v>1208.8</v>
       </c>
       <c r="F1308" t="n">
-        <v>11039.2</v>
+        <v>11073.9</v>
       </c>
       <c r="G1308" t="n">
         <v>3</v>
       </c>
       <c r="H1308" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I1308" t="n">
         <v>4</v>
@@ -43624,16 +43624,16 @@
         <v>61</v>
       </c>
       <c r="E1309" t="n">
-        <v>1175.2</v>
+        <v>1217.1</v>
       </c>
       <c r="F1309" t="n">
-        <v>10839.8</v>
+        <v>10881.7</v>
       </c>
       <c r="G1309" t="n">
         <v>6</v>
       </c>
       <c r="H1309" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1309" t="n">
         <v>5</v>
@@ -43657,10 +43657,10 @@
         <v>57.4</v>
       </c>
       <c r="E1310" t="n">
-        <v>1266</v>
+        <v>1335.1</v>
       </c>
       <c r="F1310" t="n">
-        <v>12200.8</v>
+        <v>12269.9</v>
       </c>
       <c r="G1310" t="n">
         <v>7</v>
@@ -43690,10 +43690,10 @@
         <v>46.4</v>
       </c>
       <c r="E1311" t="n">
-        <v>965.5</v>
+        <v>1038.1</v>
       </c>
       <c r="F1311" t="n">
-        <v>9799.4</v>
+        <v>9872</v>
       </c>
       <c r="G1311" t="n">
         <v>8</v>
@@ -43723,16 +43723,16 @@
         <v>77.2</v>
       </c>
       <c r="E1312" t="n">
-        <v>1157.5</v>
+        <v>1218.5</v>
       </c>
       <c r="F1312" t="n">
-        <v>10761.6</v>
+        <v>10822.6</v>
       </c>
       <c r="G1312" t="n">
         <v>4</v>
       </c>
       <c r="H1312" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I1312" t="n">
         <v>6</v>
@@ -43756,10 +43756,10 @@
         <v>95.2</v>
       </c>
       <c r="E1313" t="n">
-        <v>1133.2</v>
+        <v>1185.2</v>
       </c>
       <c r="F1313" t="n">
-        <v>8668.200000000001</v>
+        <v>8720.200000000001</v>
       </c>
       <c r="G1313" t="n">
         <v>1</v>
@@ -43789,10 +43789,10 @@
         <v>78</v>
       </c>
       <c r="E1314" t="n">
-        <v>1093.4</v>
+        <v>1151.6</v>
       </c>
       <c r="F1314" t="n">
-        <v>11804.5</v>
+        <v>11862.7</v>
       </c>
       <c r="G1314" t="n">
         <v>3</v>
@@ -43822,16 +43822,16 @@
         <v>78.59999999999999</v>
       </c>
       <c r="E1315" t="n">
-        <v>1246.6</v>
+        <v>1310.4</v>
       </c>
       <c r="F1315" t="n">
-        <v>11937.6</v>
+        <v>12001.4</v>
       </c>
       <c r="G1315" t="n">
         <v>2</v>
       </c>
       <c r="H1315" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1315" t="n">
         <v>2</v>
@@ -43855,16 +43855,16 @@
         <v>76.90000000000001</v>
       </c>
       <c r="E1316" t="n">
-        <v>1251</v>
+        <v>1285.7</v>
       </c>
       <c r="F1316" t="n">
-        <v>11116.1</v>
+        <v>11150.8</v>
       </c>
       <c r="G1316" t="n">
         <v>4</v>
       </c>
       <c r="H1316" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1316" t="n">
         <v>4</v>
@@ -43888,16 +43888,16 @@
         <v>48.4</v>
       </c>
       <c r="E1317" t="n">
-        <v>1223.6</v>
+        <v>1265.5</v>
       </c>
       <c r="F1317" t="n">
-        <v>10888.2</v>
+        <v>10930.1</v>
       </c>
       <c r="G1317" t="n">
         <v>8</v>
       </c>
       <c r="H1317" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I1317" t="n">
         <v>5</v>
@@ -43921,10 +43921,10 @@
         <v>67.59999999999999</v>
       </c>
       <c r="E1318" t="n">
-        <v>1333.6</v>
+        <v>1402.7</v>
       </c>
       <c r="F1318" t="n">
-        <v>12268.4</v>
+        <v>12337.5</v>
       </c>
       <c r="G1318" t="n">
         <v>5</v>
@@ -43954,10 +43954,10 @@
         <v>58.1</v>
       </c>
       <c r="E1319" t="n">
-        <v>1023.6</v>
+        <v>1096.2</v>
       </c>
       <c r="F1319" t="n">
-        <v>9857.5</v>
+        <v>9930.1</v>
       </c>
       <c r="G1319" t="n">
         <v>7</v>
@@ -43987,16 +43987,16 @@
         <v>61.4</v>
       </c>
       <c r="E1320" t="n">
-        <v>1218.9</v>
+        <v>1279.9</v>
       </c>
       <c r="F1320" t="n">
-        <v>10823</v>
+        <v>10884</v>
       </c>
       <c r="G1320" t="n">
         <v>6</v>
       </c>
       <c r="H1320" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1320" t="n">
         <v>6</v>
@@ -44020,16 +44020,16 @@
         <v>81.59999999999999</v>
       </c>
       <c r="E1321" t="n">
-        <v>1214.8</v>
+        <v>1266.8</v>
       </c>
       <c r="F1321" t="n">
-        <v>8749.799999999999</v>
+        <v>8801.799999999999</v>
       </c>
       <c r="G1321" t="n">
         <v>1</v>
       </c>
       <c r="H1321" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1321" t="n">
         <v>8</v>
@@ -44053,10 +44053,10 @@
         <v>67.5</v>
       </c>
       <c r="E1322" t="n">
-        <v>1160.9</v>
+        <v>1219.1</v>
       </c>
       <c r="F1322" t="n">
-        <v>11872</v>
+        <v>11930.2</v>
       </c>
       <c r="G1322" t="n">
         <v>5</v>
@@ -44086,16 +44086,16 @@
         <v>69.8</v>
       </c>
       <c r="E1323" t="n">
-        <v>1316.4</v>
+        <v>1380.2</v>
       </c>
       <c r="F1323" t="n">
-        <v>12007.4</v>
+        <v>12071.2</v>
       </c>
       <c r="G1323" t="n">
         <v>2</v>
       </c>
       <c r="H1323" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1323" t="n">
         <v>2</v>
@@ -44119,16 +44119,16 @@
         <v>68.3</v>
       </c>
       <c r="E1324" t="n">
-        <v>1319.3</v>
+        <v>1354</v>
       </c>
       <c r="F1324" t="n">
-        <v>11184.4</v>
+        <v>11219.1</v>
       </c>
       <c r="G1324" t="n">
         <v>3</v>
       </c>
       <c r="H1324" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1324" t="n">
         <v>4</v>
@@ -44152,10 +44152,10 @@
         <v>52.1</v>
       </c>
       <c r="E1325" t="n">
-        <v>1275.7</v>
+        <v>1317.6</v>
       </c>
       <c r="F1325" t="n">
-        <v>10940.3</v>
+        <v>10982.2</v>
       </c>
       <c r="G1325" t="n">
         <v>8</v>
@@ -44185,10 +44185,10 @@
         <v>79.7</v>
       </c>
       <c r="E1326" t="n">
-        <v>1413.3</v>
+        <v>1482.4</v>
       </c>
       <c r="F1326" t="n">
-        <v>12348.1</v>
+        <v>12417.2</v>
       </c>
       <c r="G1326" t="n">
         <v>1</v>
@@ -44218,10 +44218,10 @@
         <v>58</v>
       </c>
       <c r="E1327" t="n">
-        <v>1081.6</v>
+        <v>1154.2</v>
       </c>
       <c r="F1327" t="n">
-        <v>9915.5</v>
+        <v>9988.1</v>
       </c>
       <c r="G1327" t="n">
         <v>7</v>
@@ -44251,16 +44251,16 @@
         <v>59.5</v>
       </c>
       <c r="E1328" t="n">
-        <v>1278.4</v>
+        <v>1339.4</v>
       </c>
       <c r="F1328" t="n">
-        <v>10882.5</v>
+        <v>10943.5</v>
       </c>
       <c r="G1328" t="n">
         <v>6</v>
       </c>
       <c r="H1328" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1328" t="n">
         <v>6</v>
@@ -44284,16 +44284,16 @@
         <v>68.10000000000001</v>
       </c>
       <c r="E1329" t="n">
-        <v>1282.9</v>
+        <v>1334.9</v>
       </c>
       <c r="F1329" t="n">
-        <v>8817.9</v>
+        <v>8869.9</v>
       </c>
       <c r="G1329" t="n">
         <v>4</v>
       </c>
       <c r="H1329" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1329" t="n">
         <v>8</v>
@@ -44317,10 +44317,10 @@
         <v>58.6</v>
       </c>
       <c r="E1330" t="n">
-        <v>1219.5</v>
+        <v>1277.7</v>
       </c>
       <c r="F1330" t="n">
-        <v>11930.6</v>
+        <v>11988.8</v>
       </c>
       <c r="G1330" t="n">
         <v>6</v>
@@ -44350,10 +44350,10 @@
         <v>105.7</v>
       </c>
       <c r="E1331" t="n">
-        <v>1422.1</v>
+        <v>1485.9</v>
       </c>
       <c r="F1331" t="n">
-        <v>12113.1</v>
+        <v>12176.9</v>
       </c>
       <c r="G1331" t="n">
         <v>1</v>
@@ -44383,16 +44383,16 @@
         <v>58.4</v>
       </c>
       <c r="E1332" t="n">
-        <v>1377.7</v>
+        <v>1412.4</v>
       </c>
       <c r="F1332" t="n">
-        <v>11242.8</v>
+        <v>11277.5</v>
       </c>
       <c r="G1332" t="n">
         <v>7</v>
       </c>
       <c r="H1332" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1332" t="n">
         <v>4</v>
@@ -44416,10 +44416,10 @@
         <v>57.4</v>
       </c>
       <c r="E1333" t="n">
-        <v>1333.1</v>
+        <v>1375</v>
       </c>
       <c r="F1333" t="n">
-        <v>10997.7</v>
+        <v>11039.6</v>
       </c>
       <c r="G1333" t="n">
         <v>8</v>
@@ -44449,10 +44449,10 @@
         <v>83.40000000000001</v>
       </c>
       <c r="E1334" t="n">
-        <v>1496.7</v>
+        <v>1565.8</v>
       </c>
       <c r="F1334" t="n">
-        <v>12431.5</v>
+        <v>12500.6</v>
       </c>
       <c r="G1334" t="n">
         <v>3</v>
@@ -44482,10 +44482,10 @@
         <v>74.3</v>
       </c>
       <c r="E1335" t="n">
-        <v>1155.9</v>
+        <v>1228.5</v>
       </c>
       <c r="F1335" t="n">
-        <v>9989.799999999999</v>
+        <v>10062.4</v>
       </c>
       <c r="G1335" t="n">
         <v>4</v>
@@ -44515,10 +44515,10 @@
         <v>72</v>
       </c>
       <c r="E1336" t="n">
-        <v>1350.4</v>
+        <v>1411.4</v>
       </c>
       <c r="F1336" t="n">
-        <v>10954.5</v>
+        <v>11015.5</v>
       </c>
       <c r="G1336" t="n">
         <v>5</v>
@@ -44548,16 +44548,16 @@
         <v>87.09999999999999</v>
       </c>
       <c r="E1337" t="n">
-        <v>1370</v>
+        <v>1422</v>
       </c>
       <c r="F1337" t="n">
-        <v>8905</v>
+        <v>8957</v>
       </c>
       <c r="G1337" t="n">
         <v>2</v>
       </c>
       <c r="H1337" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1337" t="n">
         <v>8</v>
@@ -44581,10 +44581,10 @@
         <v>61.2</v>
       </c>
       <c r="E1338" t="n">
-        <v>1280.7</v>
+        <v>1338.9</v>
       </c>
       <c r="F1338" t="n">
-        <v>11991.8</v>
+        <v>12050</v>
       </c>
       <c r="G1338" t="n">
         <v>5</v>
@@ -44614,10 +44614,10 @@
         <v>55.59999999999999</v>
       </c>
       <c r="E1339" t="n">
-        <v>1477.7</v>
+        <v>1541.5</v>
       </c>
       <c r="F1339" t="n">
-        <v>12168.7</v>
+        <v>12232.5</v>
       </c>
       <c r="G1339" t="n">
         <v>7</v>
@@ -44647,16 +44647,16 @@
         <v>50.59999999999999</v>
       </c>
       <c r="E1340" t="n">
-        <v>1428.3</v>
+        <v>1463</v>
       </c>
       <c r="F1340" t="n">
-        <v>11293.4</v>
+        <v>11328.1</v>
       </c>
       <c r="G1340" t="n">
         <v>8</v>
       </c>
       <c r="H1340" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1340" t="n">
         <v>4</v>
@@ -44680,10 +44680,10 @@
         <v>62.40000000000001</v>
       </c>
       <c r="E1341" t="n">
-        <v>1395.5</v>
+        <v>1437.4</v>
       </c>
       <c r="F1341" t="n">
-        <v>11060.1</v>
+        <v>11102</v>
       </c>
       <c r="G1341" t="n">
         <v>4</v>
@@ -44713,10 +44713,10 @@
         <v>81.90000000000001</v>
       </c>
       <c r="E1342" t="n">
-        <v>1578.6</v>
+        <v>1647.7</v>
       </c>
       <c r="F1342" t="n">
-        <v>12513.4</v>
+        <v>12582.5</v>
       </c>
       <c r="G1342" t="n">
         <v>2</v>
@@ -44746,10 +44746,10 @@
         <v>63.3</v>
       </c>
       <c r="E1343" t="n">
-        <v>1219.2</v>
+        <v>1291.8</v>
       </c>
       <c r="F1343" t="n">
-        <v>10053.1</v>
+        <v>10125.7</v>
       </c>
       <c r="G1343" t="n">
         <v>3</v>
@@ -44779,10 +44779,10 @@
         <v>86</v>
       </c>
       <c r="E1344" t="n">
-        <v>1436.4</v>
+        <v>1497.4</v>
       </c>
       <c r="F1344" t="n">
-        <v>11040.5</v>
+        <v>11101.5</v>
       </c>
       <c r="G1344" t="n">
         <v>1</v>
@@ -44812,16 +44812,16 @@
         <v>58.1</v>
       </c>
       <c r="E1345" t="n">
-        <v>1428.1</v>
+        <v>1480.1</v>
       </c>
       <c r="F1345" t="n">
-        <v>8963.1</v>
+        <v>9015.1</v>
       </c>
       <c r="G1345" t="n">
         <v>6</v>
       </c>
       <c r="H1345" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1345" t="n">
         <v>8</v>
@@ -44845,10 +44845,10 @@
         <v>64.2</v>
       </c>
       <c r="E1346" t="n">
-        <v>1344.9</v>
+        <v>1403.1</v>
       </c>
       <c r="F1346" t="n">
-        <v>12056</v>
+        <v>12114.2</v>
       </c>
       <c r="G1346" t="n">
         <v>5</v>
@@ -44878,10 +44878,10 @@
         <v>88.7</v>
       </c>
       <c r="E1347" t="n">
-        <v>1566.4</v>
+        <v>1630.2</v>
       </c>
       <c r="F1347" t="n">
-        <v>12257.4</v>
+        <v>12321.2</v>
       </c>
       <c r="G1347" t="n">
         <v>1</v>
@@ -44911,16 +44911,16 @@
         <v>76.8</v>
       </c>
       <c r="E1348" t="n">
-        <v>1505.1</v>
+        <v>1539.8</v>
       </c>
       <c r="F1348" t="n">
-        <v>11370.2</v>
+        <v>11404.9</v>
       </c>
       <c r="G1348" t="n">
         <v>3</v>
       </c>
       <c r="H1348" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I1348" t="n">
         <v>4</v>
@@ -44944,10 +44944,10 @@
         <v>45</v>
       </c>
       <c r="E1349" t="n">
-        <v>1440.5</v>
+        <v>1482.4</v>
       </c>
       <c r="F1349" t="n">
-        <v>11105.1</v>
+        <v>11147</v>
       </c>
       <c r="G1349" t="n">
         <v>8</v>
@@ -44977,10 +44977,10 @@
         <v>81.2</v>
       </c>
       <c r="E1350" t="n">
-        <v>1659.8</v>
+        <v>1728.9</v>
       </c>
       <c r="F1350" t="n">
-        <v>12594.6</v>
+        <v>12663.7</v>
       </c>
       <c r="G1350" t="n">
         <v>2</v>
@@ -45010,10 +45010,10 @@
         <v>63.7</v>
       </c>
       <c r="E1351" t="n">
-        <v>1282.9</v>
+        <v>1355.5</v>
       </c>
       <c r="F1351" t="n">
-        <v>10116.8</v>
+        <v>10189.4</v>
       </c>
       <c r="G1351" t="n">
         <v>6</v>
@@ -45043,16 +45043,16 @@
         <v>67.7</v>
       </c>
       <c r="E1352" t="n">
-        <v>1504.1</v>
+        <v>1565.1</v>
       </c>
       <c r="F1352" t="n">
-        <v>11108.2</v>
+        <v>11169.2</v>
       </c>
       <c r="G1352" t="n">
         <v>4</v>
       </c>
       <c r="H1352" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1352" t="n">
         <v>5</v>
@@ -45076,16 +45076,16 @@
         <v>60.2</v>
       </c>
       <c r="E1353" t="n">
-        <v>1488.3</v>
+        <v>1540.3</v>
       </c>
       <c r="F1353" t="n">
-        <v>9023.299999999999</v>
+        <v>9075.299999999999</v>
       </c>
       <c r="G1353" t="n">
         <v>7</v>
       </c>
       <c r="H1353" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1353" t="n">
         <v>8</v>
@@ -45109,16 +45109,16 @@
         <v>88.09999999999999</v>
       </c>
       <c r="E1354" t="n">
-        <v>1433</v>
+        <v>1491.2</v>
       </c>
       <c r="F1354" t="n">
-        <v>12144.1</v>
+        <v>12202.3</v>
       </c>
       <c r="G1354" t="n">
         <v>3</v>
       </c>
       <c r="H1354" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I1354" t="n">
         <v>3</v>
@@ -45142,10 +45142,10 @@
         <v>59.9</v>
       </c>
       <c r="E1355" t="n">
-        <v>1626.3</v>
+        <v>1690.1</v>
       </c>
       <c r="F1355" t="n">
-        <v>12317.3</v>
+        <v>12381.1</v>
       </c>
       <c r="G1355" t="n">
         <v>6</v>
@@ -45175,16 +45175,16 @@
         <v>70.2</v>
       </c>
       <c r="E1356" t="n">
-        <v>1575.3</v>
+        <v>1610</v>
       </c>
       <c r="F1356" t="n">
-        <v>11440.4</v>
+        <v>11475.1</v>
       </c>
       <c r="G1356" t="n">
         <v>4</v>
       </c>
       <c r="H1356" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1356" t="n">
         <v>4</v>
@@ -45208,16 +45208,16 @@
         <v>0</v>
       </c>
       <c r="E1357" t="n">
-        <v>1440.5</v>
+        <v>1482.4</v>
       </c>
       <c r="F1357" t="n">
-        <v>11105.1</v>
+        <v>11147</v>
       </c>
       <c r="G1357" t="n">
         <v>8</v>
       </c>
       <c r="H1357" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1357" t="n">
         <v>6</v>
@@ -45241,10 +45241,10 @@
         <v>94</v>
       </c>
       <c r="E1358" t="n">
-        <v>1753.8</v>
+        <v>1822.9</v>
       </c>
       <c r="F1358" t="n">
-        <v>12688.6</v>
+        <v>12757.7</v>
       </c>
       <c r="G1358" t="n">
         <v>1</v>
@@ -45274,10 +45274,10 @@
         <v>61.6</v>
       </c>
       <c r="E1359" t="n">
-        <v>1344.5</v>
+        <v>1417.1</v>
       </c>
       <c r="F1359" t="n">
-        <v>10178.4</v>
+        <v>10251</v>
       </c>
       <c r="G1359" t="n">
         <v>5</v>
@@ -45307,16 +45307,16 @@
         <v>58.6</v>
       </c>
       <c r="E1360" t="n">
-        <v>1562.7</v>
+        <v>1623.7</v>
       </c>
       <c r="F1360" t="n">
-        <v>11166.8</v>
+        <v>11227.8</v>
       </c>
       <c r="G1360" t="n">
         <v>7</v>
       </c>
       <c r="H1360" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1360" t="n">
         <v>5</v>
@@ -45340,10 +45340,10 @@
         <v>89.5</v>
       </c>
       <c r="E1361" t="n">
-        <v>1577.8</v>
+        <v>1629.8</v>
       </c>
       <c r="F1361" t="n">
-        <v>9112.799999999999</v>
+        <v>9164.799999999999</v>
       </c>
       <c r="G1361" t="n">
         <v>2</v>
@@ -45373,10 +45373,10 @@
         <v>66.7</v>
       </c>
       <c r="E1362" t="n">
-        <v>1499.7</v>
+        <v>1557.9</v>
       </c>
       <c r="F1362" t="n">
-        <v>12210.8</v>
+        <v>12269</v>
       </c>
       <c r="G1362" t="n">
         <v>4</v>
@@ -45406,16 +45406,16 @@
         <v>35.8</v>
       </c>
       <c r="E1363" t="n">
-        <v>1662.1</v>
+        <v>1725.9</v>
       </c>
       <c r="F1363" t="n">
-        <v>12353.1</v>
+        <v>12416.9</v>
       </c>
       <c r="G1363" t="n">
         <v>8</v>
       </c>
       <c r="H1363" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1363" t="n">
         <v>2</v>
@@ -45439,10 +45439,10 @@
         <v>59.2</v>
       </c>
       <c r="E1364" t="n">
-        <v>1634.5</v>
+        <v>1669.2</v>
       </c>
       <c r="F1364" t="n">
-        <v>11499.6</v>
+        <v>11534.3</v>
       </c>
       <c r="G1364" t="n">
         <v>6</v>
@@ -45472,10 +45472,10 @@
         <v>82.2</v>
       </c>
       <c r="E1365" t="n">
-        <v>1522.7</v>
+        <v>1564.6</v>
       </c>
       <c r="F1365" t="n">
-        <v>11187.3</v>
+        <v>11229.2</v>
       </c>
       <c r="G1365" t="n">
         <v>2</v>
@@ -45505,10 +45505,10 @@
         <v>63</v>
       </c>
       <c r="E1366" t="n">
-        <v>1816.8</v>
+        <v>1885.9</v>
       </c>
       <c r="F1366" t="n">
-        <v>12751.6</v>
+        <v>12820.7</v>
       </c>
       <c r="G1366" t="n">
         <v>5</v>
@@ -45538,10 +45538,10 @@
         <v>56.6</v>
       </c>
       <c r="E1367" t="n">
-        <v>1401.1</v>
+        <v>1473.7</v>
       </c>
       <c r="F1367" t="n">
-        <v>10235</v>
+        <v>10307.6</v>
       </c>
       <c r="G1367" t="n">
         <v>7</v>
@@ -45571,10 +45571,10 @@
         <v>78.59999999999999</v>
       </c>
       <c r="E1368" t="n">
-        <v>1641.3</v>
+        <v>1702.3</v>
       </c>
       <c r="F1368" t="n">
-        <v>11245.4</v>
+        <v>11306.4</v>
       </c>
       <c r="G1368" t="n">
         <v>3</v>
@@ -45604,16 +45604,16 @@
         <v>87.3</v>
       </c>
       <c r="E1369" t="n">
-        <v>1665.1</v>
+        <v>1717.1</v>
       </c>
       <c r="F1369" t="n">
-        <v>9200.1</v>
+        <v>9252.1</v>
       </c>
       <c r="G1369" t="n">
         <v>1</v>
       </c>
       <c r="H1369" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1369" t="n">
         <v>8</v>
@@ -45637,10 +45637,10 @@
         <v>70.8</v>
       </c>
       <c r="E1370" t="n">
-        <v>1570.5</v>
+        <v>1628.7</v>
       </c>
       <c r="F1370" t="n">
-        <v>12281.6</v>
+        <v>12339.8</v>
       </c>
       <c r="G1370" t="n">
         <v>4</v>
@@ -45670,10 +45670,10 @@
         <v>76.5</v>
       </c>
       <c r="E1371" t="n">
-        <v>1738.6</v>
+        <v>1802.4</v>
       </c>
       <c r="F1371" t="n">
-        <v>12429.6</v>
+        <v>12493.4</v>
       </c>
       <c r="G1371" t="n">
         <v>2</v>
@@ -45703,16 +45703,16 @@
         <v>75.2</v>
       </c>
       <c r="E1372" t="n">
-        <v>1709.7</v>
+        <v>1744.4</v>
       </c>
       <c r="F1372" t="n">
-        <v>11574.8</v>
+        <v>11609.5</v>
       </c>
       <c r="G1372" t="n">
         <v>3</v>
       </c>
       <c r="H1372" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1372" t="n">
         <v>4</v>
@@ -45736,10 +45736,10 @@
         <v>46.7</v>
       </c>
       <c r="E1373" t="n">
-        <v>1569.4</v>
+        <v>1611.3</v>
       </c>
       <c r="F1373" t="n">
-        <v>11234</v>
+        <v>11275.9</v>
       </c>
       <c r="G1373" t="n">
         <v>8</v>
@@ -45769,10 +45769,10 @@
         <v>79.40000000000001</v>
       </c>
       <c r="E1374" t="n">
-        <v>1896.2</v>
+        <v>1965.3</v>
       </c>
       <c r="F1374" t="n">
-        <v>12831</v>
+        <v>12900.1</v>
       </c>
       <c r="G1374" t="n">
         <v>1</v>
@@ -45802,10 +45802,10 @@
         <v>56.59999999999999</v>
       </c>
       <c r="E1375" t="n">
-        <v>1457.7</v>
+        <v>1530.3</v>
       </c>
       <c r="F1375" t="n">
-        <v>10291.6</v>
+        <v>10364.2</v>
       </c>
       <c r="G1375" t="n">
         <v>6</v>
@@ -45835,16 +45835,16 @@
         <v>65.2</v>
       </c>
       <c r="E1376" t="n">
-        <v>1706.5</v>
+        <v>1767.5</v>
       </c>
       <c r="F1376" t="n">
-        <v>11310.6</v>
+        <v>11371.6</v>
       </c>
       <c r="G1376" t="n">
         <v>5</v>
       </c>
       <c r="H1376" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1376" t="n">
         <v>5</v>
@@ -45868,10 +45868,10 @@
         <v>54.8</v>
       </c>
       <c r="E1377" t="n">
-        <v>1719.9</v>
+        <v>1771.9</v>
       </c>
       <c r="F1377" t="n">
-        <v>9254.9</v>
+        <v>9306.9</v>
       </c>
       <c r="G1377" t="n">
         <v>7</v>
@@ -45901,10 +45901,10 @@
         <v>93.8</v>
       </c>
       <c r="E1378" t="n">
-        <v>1664.3</v>
+        <v>1722.5</v>
       </c>
       <c r="F1378" t="n">
-        <v>12375.4</v>
+        <v>12433.6</v>
       </c>
       <c r="G1378" t="n">
         <v>2</v>
@@ -45934,16 +45934,16 @@
         <v>65.2</v>
       </c>
       <c r="E1379" t="n">
-        <v>1803.8</v>
+        <v>1867.6</v>
       </c>
       <c r="F1379" t="n">
-        <v>12494.8</v>
+        <v>12558.6</v>
       </c>
       <c r="G1379" t="n">
         <v>7</v>
       </c>
       <c r="H1379" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1379" t="n">
         <v>2</v>
@@ -45967,16 +45967,16 @@
         <v>97.59999999999999</v>
       </c>
       <c r="E1380" t="n">
-        <v>1807.3</v>
+        <v>1842</v>
       </c>
       <c r="F1380" t="n">
-        <v>11672.4</v>
+        <v>11707.1</v>
       </c>
       <c r="G1380" t="n">
         <v>1</v>
       </c>
       <c r="H1380" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1380" t="n">
         <v>4</v>
@@ -46000,10 +46000,10 @@
         <v>63.3</v>
       </c>
       <c r="E1381" t="n">
-        <v>1632.7</v>
+        <v>1674.6</v>
       </c>
       <c r="F1381" t="n">
-        <v>11297.3</v>
+        <v>11339.2</v>
       </c>
       <c r="G1381" t="n">
         <v>8</v>
@@ -46033,10 +46033,10 @@
         <v>79.3</v>
       </c>
       <c r="E1382" t="n">
-        <v>1975.5</v>
+        <v>2044.6</v>
       </c>
       <c r="F1382" t="n">
-        <v>12910.3</v>
+        <v>12979.4</v>
       </c>
       <c r="G1382" t="n">
         <v>5</v>
@@ -46066,10 +46066,10 @@
         <v>81.7</v>
       </c>
       <c r="E1383" t="n">
-        <v>1539.4</v>
+        <v>1612</v>
       </c>
       <c r="F1383" t="n">
-        <v>10373.3</v>
+        <v>10445.9</v>
       </c>
       <c r="G1383" t="n">
         <v>4</v>
@@ -46099,10 +46099,10 @@
         <v>67.40000000000001</v>
       </c>
       <c r="E1384" t="n">
-        <v>1773.9</v>
+        <v>1834.9</v>
       </c>
       <c r="F1384" t="n">
-        <v>11378</v>
+        <v>11439</v>
       </c>
       <c r="G1384" t="n">
         <v>6</v>
@@ -46132,16 +46132,16 @@
         <v>82.59999999999999</v>
       </c>
       <c r="E1385" t="n">
-        <v>1802.5</v>
+        <v>1854.5</v>
       </c>
       <c r="F1385" t="n">
-        <v>9337.5</v>
+        <v>9389.5</v>
       </c>
       <c r="G1385" t="n">
         <v>3</v>
       </c>
       <c r="H1385" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1385" t="n">
         <v>8</v>
@@ -46165,10 +46165,10 @@
         <v>100.5</v>
       </c>
       <c r="E1386" t="n">
-        <v>1764.8</v>
+        <v>1823</v>
       </c>
       <c r="F1386" t="n">
-        <v>12475.9</v>
+        <v>12534.1</v>
       </c>
       <c r="G1386" t="n">
         <v>1</v>
@@ -46198,10 +46198,10 @@
         <v>80.3</v>
       </c>
       <c r="E1387" t="n">
-        <v>1884.1</v>
+        <v>1947.9</v>
       </c>
       <c r="F1387" t="n">
-        <v>12575.1</v>
+        <v>12638.9</v>
       </c>
       <c r="G1387" t="n">
         <v>2</v>
@@ -46231,16 +46231,16 @@
         <v>60.3</v>
       </c>
       <c r="E1388" t="n">
-        <v>1867.6</v>
+        <v>1902.3</v>
       </c>
       <c r="F1388" t="n">
-        <v>11732.7</v>
+        <v>11767.4</v>
       </c>
       <c r="G1388" t="n">
         <v>6</v>
       </c>
       <c r="H1388" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1388" t="n">
         <v>4</v>
@@ -46264,10 +46264,10 @@
         <v>67.59999999999999</v>
       </c>
       <c r="E1389" t="n">
-        <v>1700.3</v>
+        <v>1742.2</v>
       </c>
       <c r="F1389" t="n">
-        <v>11364.9</v>
+        <v>11406.8</v>
       </c>
       <c r="G1389" t="n">
         <v>4</v>
@@ -46297,10 +46297,10 @@
         <v>70.2</v>
       </c>
       <c r="E1390" t="n">
-        <v>2045.7</v>
+        <v>2114.8</v>
       </c>
       <c r="F1390" t="n">
-        <v>12980.5</v>
+        <v>13049.6</v>
       </c>
       <c r="G1390" t="n">
         <v>3</v>
@@ -46330,10 +46330,10 @@
         <v>61.2</v>
       </c>
       <c r="E1391" t="n">
-        <v>1600.6</v>
+        <v>1673.2</v>
       </c>
       <c r="F1391" t="n">
-        <v>10434.5</v>
+        <v>10507.1</v>
       </c>
       <c r="G1391" t="n">
         <v>5</v>
@@ -46363,10 +46363,10 @@
         <v>50.8</v>
       </c>
       <c r="E1392" t="n">
-        <v>1824.7</v>
+        <v>1885.7</v>
       </c>
       <c r="F1392" t="n">
-        <v>11428.8</v>
+        <v>11489.8</v>
       </c>
       <c r="G1392" t="n">
         <v>8</v>
@@ -46396,16 +46396,16 @@
         <v>58.9</v>
       </c>
       <c r="E1393" t="n">
-        <v>1861.4</v>
+        <v>1913.4</v>
       </c>
       <c r="F1393" t="n">
-        <v>9396.4</v>
+        <v>9448.4</v>
       </c>
       <c r="G1393" t="n">
         <v>7</v>
       </c>
       <c r="H1393" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1393" t="n">
         <v>8</v>
@@ -46429,10 +46429,10 @@
         <v>92</v>
       </c>
       <c r="E1394" t="n">
-        <v>1856.8</v>
+        <v>1915</v>
       </c>
       <c r="F1394" t="n">
-        <v>12567.9</v>
+        <v>12626.1</v>
       </c>
       <c r="G1394" t="n">
         <v>2</v>
@@ -46462,10 +46462,10 @@
         <v>77.2</v>
       </c>
       <c r="E1395" t="n">
-        <v>1961.3</v>
+        <v>2025.1</v>
       </c>
       <c r="F1395" t="n">
-        <v>12652.3</v>
+        <v>12716.1</v>
       </c>
       <c r="G1395" t="n">
         <v>4</v>
@@ -46495,16 +46495,16 @@
         <v>80.3</v>
       </c>
       <c r="E1396" t="n">
-        <v>1947.9</v>
+        <v>1982.6</v>
       </c>
       <c r="F1396" t="n">
-        <v>11813</v>
+        <v>11847.7</v>
       </c>
       <c r="G1396" t="n">
         <v>3</v>
       </c>
       <c r="H1396" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1396" t="n">
         <v>4</v>
@@ -46528,10 +46528,10 @@
         <v>50.6</v>
       </c>
       <c r="E1397" t="n">
-        <v>1750.9</v>
+        <v>1792.8</v>
       </c>
       <c r="F1397" t="n">
-        <v>11415.5</v>
+        <v>11457.4</v>
       </c>
       <c r="G1397" t="n">
         <v>7</v>
@@ -46561,10 +46561,10 @@
         <v>76.7</v>
       </c>
       <c r="E1398" t="n">
-        <v>2122.4</v>
+        <v>2191.5</v>
       </c>
       <c r="F1398" t="n">
-        <v>13057.2</v>
+        <v>13126.3</v>
       </c>
       <c r="G1398" t="n">
         <v>5</v>
@@ -46594,10 +46594,10 @@
         <v>48.7</v>
       </c>
       <c r="E1399" t="n">
-        <v>1649.3</v>
+        <v>1721.9</v>
       </c>
       <c r="F1399" t="n">
-        <v>10483.2</v>
+        <v>10555.8</v>
       </c>
       <c r="G1399" t="n">
         <v>8</v>
@@ -46627,10 +46627,10 @@
         <v>92.5</v>
       </c>
       <c r="E1400" t="n">
-        <v>1917.2</v>
+        <v>1978.2</v>
       </c>
       <c r="F1400" t="n">
-        <v>11521.3</v>
+        <v>11582.3</v>
       </c>
       <c r="G1400" t="n">
         <v>1</v>
@@ -46660,16 +46660,16 @@
         <v>73.10000000000001</v>
       </c>
       <c r="E1401" t="n">
-        <v>1934.5</v>
+        <v>1986.5</v>
       </c>
       <c r="F1401" t="n">
-        <v>9469.5</v>
+        <v>9521.5</v>
       </c>
       <c r="G1401" t="n">
         <v>6</v>
       </c>
       <c r="H1401" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1401" t="n">
         <v>8</v>
@@ -46693,10 +46693,10 @@
         <v>75.59999999999999</v>
       </c>
       <c r="E1402" t="n">
-        <v>1932.4</v>
+        <v>1990.6</v>
       </c>
       <c r="F1402" t="n">
-        <v>12643.5</v>
+        <v>12701.7</v>
       </c>
       <c r="G1402" t="n">
         <v>3</v>
@@ -46726,10 +46726,10 @@
         <v>84.09999999999999</v>
       </c>
       <c r="E1403" t="n">
-        <v>2045.4</v>
+        <v>2109.2</v>
       </c>
       <c r="F1403" t="n">
-        <v>12736.4</v>
+        <v>12800.2</v>
       </c>
       <c r="G1403" t="n">
         <v>1</v>
@@ -46759,16 +46759,16 @@
         <v>59.3</v>
       </c>
       <c r="E1404" t="n">
-        <v>2007.2</v>
+        <v>2041.9</v>
       </c>
       <c r="F1404" t="n">
-        <v>11872.3</v>
+        <v>11907</v>
       </c>
       <c r="G1404" t="n">
         <v>8</v>
       </c>
       <c r="H1404" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1404" t="n">
         <v>4</v>
@@ -46792,10 +46792,10 @@
         <v>71.5</v>
       </c>
       <c r="E1405" t="n">
-        <v>1822.4</v>
+        <v>1864.3</v>
       </c>
       <c r="F1405" t="n">
-        <v>11487</v>
+        <v>11528.9</v>
       </c>
       <c r="G1405" t="n">
         <v>6</v>
@@ -46825,10 +46825,10 @@
         <v>75.39999999999999</v>
       </c>
       <c r="E1406" t="n">
-        <v>2197.8</v>
+        <v>2266.9</v>
       </c>
       <c r="F1406" t="n">
-        <v>13132.6</v>
+        <v>13201.7</v>
       </c>
       <c r="G1406" t="n">
         <v>4</v>
@@ -46858,10 +46858,10 @@
         <v>62.7</v>
       </c>
       <c r="E1407" t="n">
-        <v>1712</v>
+        <v>1784.6</v>
       </c>
       <c r="F1407" t="n">
-        <v>10545.9</v>
+        <v>10618.5</v>
       </c>
       <c r="G1407" t="n">
         <v>7</v>
@@ -46891,16 +46891,16 @@
         <v>72</v>
       </c>
       <c r="E1408" t="n">
-        <v>1989.2</v>
+        <v>2050.2</v>
       </c>
       <c r="F1408" t="n">
-        <v>11593.3</v>
+        <v>11654.3</v>
       </c>
       <c r="G1408" t="n">
         <v>5</v>
       </c>
       <c r="H1408" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1408" t="n">
         <v>5</v>
@@ -46924,10 +46924,10 @@
         <v>79.09999999999999</v>
       </c>
       <c r="E1409" t="n">
-        <v>2013.6</v>
+        <v>2065.6</v>
       </c>
       <c r="F1409" t="n">
-        <v>9548.6</v>
+        <v>9600.6</v>
       </c>
       <c r="G1409" t="n">
         <v>2</v>
@@ -46957,10 +46957,10 @@
         <v>73.2</v>
       </c>
       <c r="E1410" t="n">
-        <v>2005.6</v>
+        <v>2063.8</v>
       </c>
       <c r="F1410" t="n">
-        <v>12716.7</v>
+        <v>12774.9</v>
       </c>
       <c r="G1410" t="n">
         <v>2</v>
@@ -46990,10 +46990,10 @@
         <v>62.7</v>
       </c>
       <c r="E1411" t="n">
-        <v>2108.1</v>
+        <v>2171.9</v>
       </c>
       <c r="F1411" t="n">
-        <v>12799.1</v>
+        <v>12862.9</v>
       </c>
       <c r="G1411" t="n">
         <v>5</v>
@@ -47023,16 +47023,16 @@
         <v>49.2</v>
       </c>
       <c r="E1412" t="n">
-        <v>2056.4</v>
+        <v>2091.1</v>
       </c>
       <c r="F1412" t="n">
-        <v>11921.5</v>
+        <v>11956.2</v>
       </c>
       <c r="G1412" t="n">
         <v>6</v>
       </c>
       <c r="H1412" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1412" t="n">
         <v>4</v>
@@ -47056,10 +47056,10 @@
         <v>43.9</v>
       </c>
       <c r="E1413" t="n">
-        <v>1866.3</v>
+        <v>1908.2</v>
       </c>
       <c r="F1413" t="n">
-        <v>11530.9</v>
+        <v>11572.8</v>
       </c>
       <c r="G1413" t="n">
         <v>7</v>
@@ -47089,10 +47089,10 @@
         <v>71.2</v>
       </c>
       <c r="E1414" t="n">
-        <v>2269</v>
+        <v>2338.1</v>
       </c>
       <c r="F1414" t="n">
-        <v>13203.8</v>
+        <v>13272.9</v>
       </c>
       <c r="G1414" t="n">
         <v>3</v>
@@ -47122,10 +47122,10 @@
         <v>64.09999999999999</v>
       </c>
       <c r="E1415" t="n">
-        <v>1776.1</v>
+        <v>1848.7</v>
       </c>
       <c r="F1415" t="n">
-        <v>10610</v>
+        <v>10682.6</v>
       </c>
       <c r="G1415" t="n">
         <v>4</v>
@@ -47155,16 +47155,16 @@
         <v>42.9</v>
       </c>
       <c r="E1416" t="n">
-        <v>2032.1</v>
+        <v>2093.1</v>
       </c>
       <c r="F1416" t="n">
-        <v>11636.2</v>
+        <v>11697.2</v>
       </c>
       <c r="G1416" t="n">
         <v>8</v>
       </c>
       <c r="H1416" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1416" t="n">
         <v>5</v>
@@ -47188,10 +47188,10 @@
         <v>73.8</v>
       </c>
       <c r="E1417" t="n">
-        <v>2087.4</v>
+        <v>2139.4</v>
       </c>
       <c r="F1417" t="n">
-        <v>9622.4</v>
+        <v>9674.4</v>
       </c>
       <c r="G1417" t="n">
         <v>1</v>
@@ -47221,16 +47221,16 @@
         <v>79.3</v>
       </c>
       <c r="E1418" t="n">
-        <v>2084.9</v>
+        <v>2143.1</v>
       </c>
       <c r="F1418" t="n">
-        <v>12796</v>
+        <v>12854.2</v>
       </c>
       <c r="G1418" t="n">
         <v>1</v>
       </c>
       <c r="H1418" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1418" t="n">
         <v>3</v>
@@ -47254,10 +47254,10 @@
         <v>62.3</v>
       </c>
       <c r="E1419" t="n">
-        <v>2170.4</v>
+        <v>2234.2</v>
       </c>
       <c r="F1419" t="n">
-        <v>12861.4</v>
+        <v>12925.2</v>
       </c>
       <c r="G1419" t="n">
         <v>4</v>
@@ -47287,16 +47287,16 @@
         <v>50.4</v>
       </c>
       <c r="E1420" t="n">
-        <v>2106.8</v>
+        <v>2141.5</v>
       </c>
       <c r="F1420" t="n">
-        <v>11971.9</v>
+        <v>12006.6</v>
       </c>
       <c r="G1420" t="n">
         <v>7</v>
       </c>
       <c r="H1420" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I1420" t="n">
         <v>4</v>
@@ -47320,10 +47320,10 @@
         <v>48.8</v>
       </c>
       <c r="E1421" t="n">
-        <v>1915.1</v>
+        <v>1957</v>
       </c>
       <c r="F1421" t="n">
-        <v>11579.7</v>
+        <v>11621.6</v>
       </c>
       <c r="G1421" t="n">
         <v>8</v>
@@ -47353,10 +47353,10 @@
         <v>75</v>
       </c>
       <c r="E1422" t="n">
-        <v>2344</v>
+        <v>2413.1</v>
       </c>
       <c r="F1422" t="n">
-        <v>13278.8</v>
+        <v>13347.9</v>
       </c>
       <c r="G1422" t="n">
         <v>2</v>
@@ -47386,10 +47386,10 @@
         <v>64.5</v>
       </c>
       <c r="E1423" t="n">
-        <v>1840.6</v>
+        <v>1913.2</v>
       </c>
       <c r="F1423" t="n">
-        <v>10674.5</v>
+        <v>10747.1</v>
       </c>
       <c r="G1423" t="n">
         <v>3</v>
@@ -47419,16 +47419,16 @@
         <v>59.7</v>
       </c>
       <c r="E1424" t="n">
-        <v>2091.8</v>
+        <v>2152.8</v>
       </c>
       <c r="F1424" t="n">
-        <v>11695.9</v>
+        <v>11756.9</v>
       </c>
       <c r="G1424" t="n">
         <v>5</v>
       </c>
       <c r="H1424" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1424" t="n">
         <v>5</v>
@@ -47452,10 +47452,10 @@
         <v>57.7</v>
       </c>
       <c r="E1425" t="n">
-        <v>2145.1</v>
+        <v>2197.1</v>
       </c>
       <c r="F1425" t="n">
-        <v>9680.1</v>
+        <v>9732.1</v>
       </c>
       <c r="G1425" t="n">
         <v>6</v>
@@ -47485,10 +47485,10 @@
         <v>86.3</v>
       </c>
       <c r="E1426" t="n">
-        <v>2171.2</v>
+        <v>2229.4</v>
       </c>
       <c r="F1426" t="n">
-        <v>12882.3</v>
+        <v>12940.5</v>
       </c>
       <c r="G1426" t="n">
         <v>2</v>
@@ -47518,10 +47518,10 @@
         <v>75.59999999999999</v>
       </c>
       <c r="E1427" t="n">
-        <v>2246</v>
+        <v>2309.8</v>
       </c>
       <c r="F1427" t="n">
-        <v>12937</v>
+        <v>13000.8</v>
       </c>
       <c r="G1427" t="n">
         <v>3</v>
@@ -47551,16 +47551,16 @@
         <v>50.9</v>
       </c>
       <c r="E1428" t="n">
-        <v>2157.7</v>
+        <v>2192.4</v>
       </c>
       <c r="F1428" t="n">
-        <v>12022.8</v>
+        <v>12057.5</v>
       </c>
       <c r="G1428" t="n">
         <v>8</v>
       </c>
       <c r="H1428" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1428" t="n">
         <v>4</v>
@@ -47584,10 +47584,10 @@
         <v>65.3</v>
       </c>
       <c r="E1429" t="n">
-        <v>1980.4</v>
+        <v>2022.3</v>
       </c>
       <c r="F1429" t="n">
-        <v>11645</v>
+        <v>11686.9</v>
       </c>
       <c r="G1429" t="n">
         <v>4</v>
@@ -47617,10 +47617,10 @@
         <v>58.4</v>
       </c>
       <c r="E1430" t="n">
-        <v>2402.4</v>
+        <v>2471.5</v>
       </c>
       <c r="F1430" t="n">
-        <v>13337.2</v>
+        <v>13406.3</v>
       </c>
       <c r="G1430" t="n">
         <v>6</v>
@@ -47650,10 +47650,10 @@
         <v>58.6</v>
       </c>
       <c r="E1431" t="n">
-        <v>1899.2</v>
+        <v>1971.8</v>
       </c>
       <c r="F1431" t="n">
-        <v>10733.1</v>
+        <v>10805.7</v>
       </c>
       <c r="G1431" t="n">
         <v>5</v>
@@ -47683,16 +47683,16 @@
         <v>55.3</v>
       </c>
       <c r="E1432" t="n">
-        <v>2147.1</v>
+        <v>2208.1</v>
       </c>
       <c r="F1432" t="n">
-        <v>11751.2</v>
+        <v>11812.2</v>
       </c>
       <c r="G1432" t="n">
         <v>7</v>
       </c>
       <c r="H1432" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1432" t="n">
         <v>5</v>
@@ -47716,10 +47716,10 @@
         <v>96</v>
       </c>
       <c r="E1433" t="n">
-        <v>2241.1</v>
+        <v>2293.1</v>
       </c>
       <c r="F1433" t="n">
-        <v>9776.1</v>
+        <v>9828.1</v>
       </c>
       <c r="G1433" t="n">
         <v>1</v>
@@ -47749,10 +47749,10 @@
         <v>84.5</v>
       </c>
       <c r="E1434" t="n">
-        <v>2255.7</v>
+        <v>2313.9</v>
       </c>
       <c r="F1434" t="n">
-        <v>12966.8</v>
+        <v>13025</v>
       </c>
       <c r="G1434" t="n">
         <v>1</v>
@@ -47782,16 +47782,16 @@
         <v>66.59999999999999</v>
       </c>
       <c r="E1435" t="n">
-        <v>2312.6</v>
+        <v>2376.4</v>
       </c>
       <c r="F1435" t="n">
-        <v>13003.6</v>
+        <v>13067.4</v>
       </c>
       <c r="G1435" t="n">
         <v>4</v>
       </c>
       <c r="H1435" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1435" t="n">
         <v>2</v>
@@ -47815,16 +47815,16 @@
         <v>60.1</v>
       </c>
       <c r="E1436" t="n">
-        <v>2217.8</v>
+        <v>2252.5</v>
       </c>
       <c r="F1436" t="n">
-        <v>12082.9</v>
+        <v>12117.6</v>
       </c>
       <c r="G1436" t="n">
         <v>6</v>
       </c>
       <c r="H1436" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1436" t="n">
         <v>4</v>
@@ -47848,10 +47848,10 @@
         <v>74.09999999999999</v>
       </c>
       <c r="E1437" t="n">
-        <v>2054.5</v>
+        <v>2096.4</v>
       </c>
       <c r="F1437" t="n">
-        <v>11719.1</v>
+        <v>11761</v>
       </c>
       <c r="G1437" t="n">
         <v>3</v>
@@ -47881,10 +47881,10 @@
         <v>57.4</v>
       </c>
       <c r="E1438" t="n">
-        <v>2459.8</v>
+        <v>2528.9</v>
       </c>
       <c r="F1438" t="n">
-        <v>13394.6</v>
+        <v>13463.7</v>
       </c>
       <c r="G1438" t="n">
         <v>7</v>
@@ -47914,10 +47914,10 @@
         <v>0</v>
       </c>
       <c r="E1439" t="n">
-        <v>1899.2</v>
+        <v>1971.8</v>
       </c>
       <c r="F1439" t="n">
-        <v>10733.1</v>
+        <v>10805.7</v>
       </c>
       <c r="G1439" t="n">
         <v>8</v>
@@ -47947,16 +47947,16 @@
         <v>65.90000000000001</v>
       </c>
       <c r="E1440" t="n">
-        <v>2213</v>
+        <v>2274</v>
       </c>
       <c r="F1440" t="n">
-        <v>11817.1</v>
+        <v>11878.1</v>
       </c>
       <c r="G1440" t="n">
         <v>5</v>
       </c>
       <c r="H1440" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I1440" t="n">
         <v>5</v>
@@ -47980,16 +47980,16 @@
         <v>76</v>
       </c>
       <c r="E1441" t="n">
-        <v>2317.1</v>
+        <v>2369.1</v>
       </c>
       <c r="F1441" t="n">
-        <v>9852.1</v>
+        <v>9904.1</v>
       </c>
       <c r="G1441" t="n">
         <v>2</v>
       </c>
       <c r="H1441" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1441" t="n">
         <v>8</v>
@@ -48013,10 +48013,10 @@
         <v>73.09999999999999</v>
       </c>
       <c r="E1442" t="n">
-        <v>2328.8</v>
+        <v>2387</v>
       </c>
       <c r="F1442" t="n">
-        <v>13039.9</v>
+        <v>13098.1</v>
       </c>
       <c r="G1442" t="n">
         <v>6</v>
@@ -48046,10 +48046,10 @@
         <v>92.90000000000001</v>
       </c>
       <c r="E1443" t="n">
-        <v>2405.5</v>
+        <v>2469.3</v>
       </c>
       <c r="F1443" t="n">
-        <v>13096.5</v>
+        <v>13160.3</v>
       </c>
       <c r="G1443" t="n">
         <v>2</v>
@@ -48079,10 +48079,10 @@
         <v>51.6</v>
       </c>
       <c r="E1444" t="n">
-        <v>2269.4</v>
+        <v>2304.1</v>
       </c>
       <c r="F1444" t="n">
-        <v>12134.5</v>
+        <v>12169.2</v>
       </c>
       <c r="G1444" t="n">
         <v>8</v>
@@ -48112,10 +48112,10 @@
         <v>62.1</v>
       </c>
       <c r="E1445" t="n">
-        <v>2116.6</v>
+        <v>2158.5</v>
       </c>
       <c r="F1445" t="n">
-        <v>11781.2</v>
+        <v>11823.1</v>
       </c>
       <c r="G1445" t="n">
         <v>7</v>
@@ -48145,10 +48145,10 @@
         <v>86.7</v>
       </c>
       <c r="E1446" t="n">
-        <v>2546.5</v>
+        <v>2615.6</v>
       </c>
       <c r="F1446" t="n">
-        <v>13481.3</v>
+        <v>13550.4</v>
       </c>
       <c r="G1446" t="n">
         <v>4</v>
@@ -48178,10 +48178,10 @@
         <v>88.2</v>
       </c>
       <c r="E1447" t="n">
-        <v>1987.4</v>
+        <v>2060</v>
       </c>
       <c r="F1447" t="n">
-        <v>10821.3</v>
+        <v>10893.9</v>
       </c>
       <c r="G1447" t="n">
         <v>3</v>
@@ -48211,10 +48211,10 @@
         <v>73.3</v>
       </c>
       <c r="E1448" t="n">
-        <v>2286.3</v>
+        <v>2347.3</v>
       </c>
       <c r="F1448" t="n">
-        <v>11890.4</v>
+        <v>11951.4</v>
       </c>
       <c r="G1448" t="n">
         <v>5</v>
@@ -48244,10 +48244,10 @@
         <v>100.9</v>
       </c>
       <c r="E1449" t="n">
-        <v>2418</v>
+        <v>2470</v>
       </c>
       <c r="F1449" t="n">
-        <v>9953</v>
+        <v>10005</v>
       </c>
       <c r="G1449" t="n">
         <v>1</v>
@@ -48277,10 +48277,10 @@
         <v>82.5</v>
       </c>
       <c r="E1450" t="n">
-        <v>2411.3</v>
+        <v>2469.5</v>
       </c>
       <c r="F1450" t="n">
-        <v>13122.4</v>
+        <v>13180.6</v>
       </c>
       <c r="G1450" t="n">
         <v>3</v>
@@ -48310,10 +48310,10 @@
         <v>73.5</v>
       </c>
       <c r="E1451" t="n">
-        <v>2479</v>
+        <v>2542.8</v>
       </c>
       <c r="F1451" t="n">
-        <v>13170</v>
+        <v>13233.8</v>
       </c>
       <c r="G1451" t="n">
         <v>4</v>
@@ -48343,10 +48343,10 @@
         <v>114.5</v>
       </c>
       <c r="E1452" t="n">
-        <v>2383.9</v>
+        <v>2418.6</v>
       </c>
       <c r="F1452" t="n">
-        <v>12249</v>
+        <v>12283.7</v>
       </c>
       <c r="G1452" t="n">
         <v>1</v>
@@ -48376,10 +48376,10 @@
         <v>85.90000000000001</v>
       </c>
       <c r="E1453" t="n">
-        <v>2202.5</v>
+        <v>2244.4</v>
       </c>
       <c r="F1453" t="n">
-        <v>11867.1</v>
+        <v>11909</v>
       </c>
       <c r="G1453" t="n">
         <v>2</v>
@@ -48409,10 +48409,10 @@
         <v>48.6</v>
       </c>
       <c r="E1454" t="n">
-        <v>2595.1</v>
+        <v>2664.2</v>
       </c>
       <c r="F1454" t="n">
-        <v>13529.9</v>
+        <v>13599</v>
       </c>
       <c r="G1454" t="n">
         <v>6</v>
@@ -48442,10 +48442,10 @@
         <v>52.8</v>
       </c>
       <c r="E1455" t="n">
-        <v>2040.2</v>
+        <v>2112.8</v>
       </c>
       <c r="F1455" t="n">
-        <v>10874.1</v>
+        <v>10946.7</v>
       </c>
       <c r="G1455" t="n">
         <v>5</v>
@@ -48475,10 +48475,10 @@
         <v>47.9</v>
       </c>
       <c r="E1456" t="n">
-        <v>2334.2</v>
+        <v>2395.2</v>
       </c>
       <c r="F1456" t="n">
-        <v>11938.3</v>
+        <v>11999.3</v>
       </c>
       <c r="G1456" t="n">
         <v>7</v>
@@ -48508,10 +48508,10 @@
         <v>43.3</v>
       </c>
       <c r="E1457" t="n">
-        <v>2461.3</v>
+        <v>2513.3</v>
       </c>
       <c r="F1457" t="n">
-        <v>9996.299999999999</v>
+        <v>10048.3</v>
       </c>
       <c r="G1457" t="n">
         <v>8</v>
@@ -48541,10 +48541,10 @@
         <v>66.5</v>
       </c>
       <c r="E1458" t="n">
-        <v>2477.8</v>
+        <v>2536</v>
       </c>
       <c r="F1458" t="n">
-        <v>13188.9</v>
+        <v>13247.1</v>
       </c>
       <c r="G1458" t="n">
         <v>5</v>
@@ -48574,16 +48574,16 @@
         <v>65.5</v>
       </c>
       <c r="E1459" t="n">
-        <v>2544.5</v>
+        <v>2608.3</v>
       </c>
       <c r="F1459" t="n">
-        <v>13235.5</v>
+        <v>13299.3</v>
       </c>
       <c r="G1459" t="n">
         <v>7</v>
       </c>
       <c r="H1459" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1459" t="n">
         <v>2</v>
@@ -48607,10 +48607,10 @@
         <v>83.90000000000001</v>
       </c>
       <c r="E1460" t="n">
-        <v>2467.8</v>
+        <v>2502.5</v>
       </c>
       <c r="F1460" t="n">
-        <v>12332.9</v>
+        <v>12367.6</v>
       </c>
       <c r="G1460" t="n">
         <v>3</v>
@@ -48640,10 +48640,10 @@
         <v>66.40000000000001</v>
       </c>
       <c r="E1461" t="n">
-        <v>2268.9</v>
+        <v>2310.8</v>
       </c>
       <c r="F1461" t="n">
-        <v>11933.5</v>
+        <v>11975.4</v>
       </c>
       <c r="G1461" t="n">
         <v>6</v>
@@ -48673,10 +48673,10 @@
         <v>107</v>
       </c>
       <c r="E1462" t="n">
-        <v>2702.1</v>
+        <v>2771.2</v>
       </c>
       <c r="F1462" t="n">
-        <v>13636.9</v>
+        <v>13706</v>
       </c>
       <c r="G1462" t="n">
         <v>1</v>
@@ -48706,10 +48706,10 @@
         <v>46.5</v>
       </c>
       <c r="E1463" t="n">
-        <v>2086.7</v>
+        <v>2159.3</v>
       </c>
       <c r="F1463" t="n">
-        <v>10920.6</v>
+        <v>10993.2</v>
       </c>
       <c r="G1463" t="n">
         <v>8</v>
@@ -48739,10 +48739,10 @@
         <v>67.40000000000001</v>
       </c>
       <c r="E1464" t="n">
-        <v>2401.6</v>
+        <v>2462.6</v>
       </c>
       <c r="F1464" t="n">
-        <v>12005.7</v>
+        <v>12066.7</v>
       </c>
       <c r="G1464" t="n">
         <v>4</v>
@@ -48772,16 +48772,16 @@
         <v>85.59999999999999</v>
       </c>
       <c r="E1465" t="n">
-        <v>2546.9</v>
+        <v>2598.9</v>
       </c>
       <c r="F1465" t="n">
-        <v>10081.9</v>
+        <v>10133.9</v>
       </c>
       <c r="G1465" t="n">
         <v>2</v>
       </c>
       <c r="H1465" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1465" t="n">
         <v>8</v>
@@ -48805,10 +48805,10 @@
         <v>100.6</v>
       </c>
       <c r="E1466" t="n">
-        <v>2578.4</v>
+        <v>2636.6</v>
       </c>
       <c r="F1466" t="n">
-        <v>13289.5</v>
+        <v>13347.7</v>
       </c>
       <c r="G1466" t="n">
         <v>1</v>
@@ -48838,10 +48838,10 @@
         <v>65.90000000000001</v>
       </c>
       <c r="E1467" t="n">
-        <v>2610.4</v>
+        <v>2674.2</v>
       </c>
       <c r="F1467" t="n">
-        <v>13301.4</v>
+        <v>13365.2</v>
       </c>
       <c r="G1467" t="n">
         <v>5</v>
@@ -48871,10 +48871,10 @@
         <v>70.8</v>
       </c>
       <c r="E1468" t="n">
-        <v>2538.6</v>
+        <v>2573.3</v>
       </c>
       <c r="F1468" t="n">
-        <v>12403.7</v>
+        <v>12438.4</v>
       </c>
       <c r="G1468" t="n">
         <v>4</v>
@@ -48904,10 +48904,10 @@
         <v>60.5</v>
       </c>
       <c r="E1469" t="n">
-        <v>2329.4</v>
+        <v>2371.3</v>
       </c>
       <c r="F1469" t="n">
-        <v>11994</v>
+        <v>12035.9</v>
       </c>
       <c r="G1469" t="n">
         <v>7</v>
@@ -48937,10 +48937,10 @@
         <v>64.59999999999999</v>
       </c>
       <c r="E1470" t="n">
-        <v>2766.7</v>
+        <v>2835.8</v>
       </c>
       <c r="F1470" t="n">
-        <v>13701.5</v>
+        <v>13770.6</v>
       </c>
       <c r="G1470" t="n">
         <v>6</v>
@@ -48970,10 +48970,10 @@
         <v>73.7</v>
       </c>
       <c r="E1471" t="n">
-        <v>2160.4</v>
+        <v>2233</v>
       </c>
       <c r="F1471" t="n">
-        <v>10994.3</v>
+        <v>11066.9</v>
       </c>
       <c r="G1471" t="n">
         <v>3</v>
@@ -49003,10 +49003,10 @@
         <v>55.2</v>
       </c>
       <c r="E1472" t="n">
-        <v>2456.8</v>
+        <v>2517.8</v>
       </c>
       <c r="F1472" t="n">
-        <v>12060.9</v>
+        <v>12121.9</v>
       </c>
       <c r="G1472" t="n">
         <v>8</v>
@@ -49036,10 +49036,10 @@
         <v>88</v>
       </c>
       <c r="E1473" t="n">
-        <v>2634.9</v>
+        <v>2686.9</v>
       </c>
       <c r="F1473" t="n">
-        <v>10169.9</v>
+        <v>10221.9</v>
       </c>
       <c r="G1473" t="n">
         <v>2</v>
@@ -49069,10 +49069,10 @@
         <v>70.09999999999999</v>
       </c>
       <c r="E1474" t="n">
-        <v>2648.5</v>
+        <v>2706.7</v>
       </c>
       <c r="F1474" t="n">
-        <v>13359.6</v>
+        <v>13417.8</v>
       </c>
       <c r="G1474" t="n">
         <v>4</v>
@@ -49102,10 +49102,10 @@
         <v>77.90000000000001</v>
       </c>
       <c r="E1475" t="n">
-        <v>2688.3</v>
+        <v>2752.1</v>
       </c>
       <c r="F1475" t="n">
-        <v>13379.3</v>
+        <v>13443.1</v>
       </c>
       <c r="G1475" t="n">
         <v>3</v>
@@ -49135,10 +49135,10 @@
         <v>80.8</v>
       </c>
       <c r="E1476" t="n">
-        <v>2619.4</v>
+        <v>2654.1</v>
       </c>
       <c r="F1476" t="n">
-        <v>12484.5</v>
+        <v>12519.2</v>
       </c>
       <c r="G1476" t="n">
         <v>2</v>
@@ -49168,10 +49168,10 @@
         <v>53</v>
       </c>
       <c r="E1477" t="n">
-        <v>2382.4</v>
+        <v>2424.3</v>
       </c>
       <c r="F1477" t="n">
-        <v>12047</v>
+        <v>12088.9</v>
       </c>
       <c r="G1477" t="n">
         <v>7</v>
@@ -49201,10 +49201,10 @@
         <v>59.8</v>
       </c>
       <c r="E1478" t="n">
-        <v>2826.5</v>
+        <v>2895.6</v>
       </c>
       <c r="F1478" t="n">
-        <v>13761.3</v>
+        <v>13830.4</v>
       </c>
       <c r="G1478" t="n">
         <v>6</v>
@@ -49234,10 +49234,10 @@
         <v>68.39999999999999</v>
       </c>
       <c r="E1479" t="n">
-        <v>2228.8</v>
+        <v>2301.4</v>
       </c>
       <c r="F1479" t="n">
-        <v>11062.7</v>
+        <v>11135.3</v>
       </c>
       <c r="G1479" t="n">
         <v>5</v>
@@ -49267,10 +49267,10 @@
         <v>48.4</v>
       </c>
       <c r="E1480" t="n">
-        <v>2505.2</v>
+        <v>2566.2</v>
       </c>
       <c r="F1480" t="n">
-        <v>12109.3</v>
+        <v>12170.3</v>
       </c>
       <c r="G1480" t="n">
         <v>8</v>
@@ -49300,10 +49300,10 @@
         <v>104.8</v>
       </c>
       <c r="E1481" t="n">
-        <v>2739.7</v>
+        <v>2791.7</v>
       </c>
       <c r="F1481" t="n">
-        <v>10274.7</v>
+        <v>10326.7</v>
       </c>
       <c r="G1481" t="n">
         <v>1</v>
@@ -49333,10 +49333,10 @@
         <v>76.3</v>
       </c>
       <c r="E1482" t="n">
-        <v>2724.8</v>
+        <v>2783</v>
       </c>
       <c r="F1482" t="n">
-        <v>13435.9</v>
+        <v>13494.1</v>
       </c>
       <c r="G1482" t="n">
         <v>3</v>
@@ -49366,10 +49366,10 @@
         <v>73.3</v>
       </c>
       <c r="E1483" t="n">
-        <v>2761.6</v>
+        <v>2825.4</v>
       </c>
       <c r="F1483" t="n">
-        <v>13452.6</v>
+        <v>13516.4</v>
       </c>
       <c r="G1483" t="n">
         <v>5</v>
@@ -49399,10 +49399,10 @@
         <v>56.5</v>
       </c>
       <c r="E1484" t="n">
-        <v>2675.9</v>
+        <v>2710.6</v>
       </c>
       <c r="F1484" t="n">
-        <v>12541</v>
+        <v>12575.7</v>
       </c>
       <c r="G1484" t="n">
         <v>7</v>
@@ -49432,10 +49432,10 @@
         <v>75.09999999999999</v>
       </c>
       <c r="E1485" t="n">
-        <v>2457.5</v>
+        <v>2499.4</v>
       </c>
       <c r="F1485" t="n">
-        <v>12122.1</v>
+        <v>12164</v>
       </c>
       <c r="G1485" t="n">
         <v>4</v>
@@ -49465,10 +49465,10 @@
         <v>69.7</v>
       </c>
       <c r="E1486" t="n">
-        <v>2896.2</v>
+        <v>2965.3</v>
       </c>
       <c r="F1486" t="n">
-        <v>13831</v>
+        <v>13900.1</v>
       </c>
       <c r="G1486" t="n">
         <v>6</v>
@@ -49498,10 +49498,10 @@
         <v>80.09999999999999</v>
       </c>
       <c r="E1487" t="n">
-        <v>2308.9</v>
+        <v>2381.5</v>
       </c>
       <c r="F1487" t="n">
-        <v>11142.8</v>
+        <v>11215.4</v>
       </c>
       <c r="G1487" t="n">
         <v>2</v>
@@ -49531,10 +49531,10 @@
         <v>44.90000000000001</v>
       </c>
       <c r="E1488" t="n">
-        <v>2550.1</v>
+        <v>2611.1</v>
       </c>
       <c r="F1488" t="n">
-        <v>12154.2</v>
+        <v>12215.2</v>
       </c>
       <c r="G1488" t="n">
         <v>8</v>
@@ -49564,10 +49564,10 @@
         <v>82.40000000000001</v>
       </c>
       <c r="E1489" t="n">
-        <v>2822.1</v>
+        <v>2874.1</v>
       </c>
       <c r="F1489" t="n">
-        <v>10357.1</v>
+        <v>10409.1</v>
       </c>
       <c r="G1489" t="n">
         <v>1</v>
@@ -49597,10 +49597,10 @@
         <v>94.09999999999999</v>
       </c>
       <c r="E1490" t="n">
-        <v>2818.9</v>
+        <v>2877.1</v>
       </c>
       <c r="F1490" t="n">
-        <v>13530</v>
+        <v>13588.2</v>
       </c>
       <c r="G1490" t="n">
         <v>3</v>
@@ -49630,10 +49630,10 @@
         <v>94.90000000000001</v>
       </c>
       <c r="E1491" t="n">
-        <v>2856.5</v>
+        <v>2920.3</v>
       </c>
       <c r="F1491" t="n">
-        <v>13547.5</v>
+        <v>13611.3</v>
       </c>
       <c r="G1491" t="n">
         <v>2</v>
@@ -49663,10 +49663,10 @@
         <v>75.2</v>
       </c>
       <c r="E1492" t="n">
-        <v>2751.1</v>
+        <v>2785.8</v>
       </c>
       <c r="F1492" t="n">
-        <v>12616.2</v>
+        <v>12650.9</v>
       </c>
       <c r="G1492" t="n">
         <v>5</v>
@@ -49696,10 +49696,10 @@
         <v>38.3</v>
       </c>
       <c r="E1493" t="n">
-        <v>2495.8</v>
+        <v>2537.7</v>
       </c>
       <c r="F1493" t="n">
-        <v>12160.4</v>
+        <v>12202.3</v>
       </c>
       <c r="G1493" t="n">
         <v>8</v>
@@ -49729,10 +49729,10 @@
         <v>52.9</v>
       </c>
       <c r="E1494" t="n">
-        <v>2949.1</v>
+        <v>3018.2</v>
       </c>
       <c r="F1494" t="n">
-        <v>13883.9</v>
+        <v>13953</v>
       </c>
       <c r="G1494" t="n">
         <v>6</v>
@@ -49762,10 +49762,10 @@
         <v>78.7</v>
       </c>
       <c r="E1495" t="n">
-        <v>2387.6</v>
+        <v>2460.2</v>
       </c>
       <c r="F1495" t="n">
-        <v>11221.5</v>
+        <v>11294.1</v>
       </c>
       <c r="G1495" t="n">
         <v>4</v>
@@ -49795,10 +49795,10 @@
         <v>44.4</v>
       </c>
       <c r="E1496" t="n">
-        <v>2594.5</v>
+        <v>2655.5</v>
       </c>
       <c r="F1496" t="n">
-        <v>12198.6</v>
+        <v>12259.6</v>
       </c>
       <c r="G1496" t="n">
         <v>7</v>
@@ -49828,10 +49828,10 @@
         <v>95.3</v>
       </c>
       <c r="E1497" t="n">
-        <v>2917.4</v>
+        <v>2969.4</v>
       </c>
       <c r="F1497" t="n">
-        <v>10452.4</v>
+        <v>10504.4</v>
       </c>
       <c r="G1497" t="n">
         <v>1</v>
@@ -49861,10 +49861,10 @@
         <v>72.8</v>
       </c>
       <c r="E1498" t="n">
-        <v>2891.7</v>
+        <v>2949.9</v>
       </c>
       <c r="F1498" t="n">
-        <v>13602.8</v>
+        <v>13661</v>
       </c>
       <c r="G1498" t="n">
         <v>2</v>
@@ -49894,10 +49894,10 @@
         <v>42</v>
       </c>
       <c r="E1499" t="n">
-        <v>2898.5</v>
+        <v>2962.3</v>
       </c>
       <c r="F1499" t="n">
-        <v>13589.5</v>
+        <v>13653.3</v>
       </c>
       <c r="G1499" t="n">
         <v>7</v>
@@ -49927,10 +49927,10 @@
         <v>65.10000000000001</v>
       </c>
       <c r="E1500" t="n">
-        <v>2816.2</v>
+        <v>2850.9</v>
       </c>
       <c r="F1500" t="n">
-        <v>12681.3</v>
+        <v>12716</v>
       </c>
       <c r="G1500" t="n">
         <v>5</v>
@@ -49960,10 +49960,10 @@
         <v>39.8</v>
       </c>
       <c r="E1501" t="n">
-        <v>2535.6</v>
+        <v>2577.5</v>
       </c>
       <c r="F1501" t="n">
-        <v>12200.2</v>
+        <v>12242.1</v>
       </c>
       <c r="G1501" t="n">
         <v>8</v>
@@ -49993,10 +49993,10 @@
         <v>65.8</v>
       </c>
       <c r="E1502" t="n">
-        <v>3014.9</v>
+        <v>3084</v>
       </c>
       <c r="F1502" t="n">
-        <v>13949.7</v>
+        <v>14018.8</v>
       </c>
       <c r="G1502" t="n">
         <v>4</v>
@@ -50026,10 +50026,10 @@
         <v>66.40000000000001</v>
       </c>
       <c r="E1503" t="n">
-        <v>2454</v>
+        <v>2526.6</v>
       </c>
       <c r="F1503" t="n">
-        <v>11287.9</v>
+        <v>11360.5</v>
       </c>
       <c r="G1503" t="n">
         <v>3</v>
@@ -50059,10 +50059,10 @@
         <v>52.7</v>
       </c>
       <c r="E1504" t="n">
-        <v>2647.2</v>
+        <v>2708.2</v>
       </c>
       <c r="F1504" t="n">
-        <v>12251.3</v>
+        <v>12312.3</v>
       </c>
       <c r="G1504" t="n">
         <v>6</v>
@@ -50092,10 +50092,10 @@
         <v>81.3</v>
       </c>
       <c r="E1505" t="n">
-        <v>2998.7</v>
+        <v>3050.7</v>
       </c>
       <c r="F1505" t="n">
-        <v>10533.7</v>
+        <v>10585.7</v>
       </c>
       <c r="G1505" t="n">
         <v>1</v>
@@ -50125,10 +50125,10 @@
         <v>70.59999999999999</v>
       </c>
       <c r="E1506" t="n">
-        <v>2962.3</v>
+        <v>3020.5</v>
       </c>
       <c r="F1506" t="n">
-        <v>13673.4</v>
+        <v>13731.6</v>
       </c>
       <c r="G1506" t="n">
         <v>4</v>
@@ -50158,10 +50158,10 @@
         <v>76.40000000000001</v>
       </c>
       <c r="E1507" t="n">
-        <v>2974.9</v>
+        <v>3038.7</v>
       </c>
       <c r="F1507" t="n">
-        <v>13665.9</v>
+        <v>13729.7</v>
       </c>
       <c r="G1507" t="n">
         <v>2</v>
@@ -50191,10 +50191,10 @@
         <v>60.3</v>
       </c>
       <c r="E1508" t="n">
-        <v>2876.5</v>
+        <v>2911.2</v>
       </c>
       <c r="F1508" t="n">
-        <v>12741.6</v>
+        <v>12776.3</v>
       </c>
       <c r="G1508" t="n">
         <v>6</v>
@@ -50224,10 +50224,10 @@
         <v>60.4</v>
       </c>
       <c r="E1509" t="n">
-        <v>2596</v>
+        <v>2637.9</v>
       </c>
       <c r="F1509" t="n">
-        <v>12260.6</v>
+        <v>12302.5</v>
       </c>
       <c r="G1509" t="n">
         <v>5</v>
@@ -50257,10 +50257,10 @@
         <v>53.9</v>
       </c>
       <c r="E1510" t="n">
-        <v>3068.8</v>
+        <v>3137.9</v>
       </c>
       <c r="F1510" t="n">
-        <v>14003.6</v>
+        <v>14072.7</v>
       </c>
       <c r="G1510" t="n">
         <v>7</v>
@@ -50290,10 +50290,10 @@
         <v>75.80000000000001</v>
       </c>
       <c r="E1511" t="n">
-        <v>2529.8</v>
+        <v>2602.4</v>
       </c>
       <c r="F1511" t="n">
-        <v>11363.7</v>
+        <v>11436.3</v>
       </c>
       <c r="G1511" t="n">
         <v>3</v>
@@ -50323,10 +50323,10 @@
         <v>53.2</v>
       </c>
       <c r="E1512" t="n">
-        <v>2700.4</v>
+        <v>2761.4</v>
       </c>
       <c r="F1512" t="n">
-        <v>12304.5</v>
+        <v>12365.5</v>
       </c>
       <c r="G1512" t="n">
         <v>8</v>
@@ -50356,10 +50356,10 @@
         <v>87.59999999999999</v>
       </c>
       <c r="E1513" t="n">
-        <v>3086.3</v>
+        <v>3138.3</v>
       </c>
       <c r="F1513" t="n">
-        <v>10621.3</v>
+        <v>10673.3</v>
       </c>
       <c r="G1513" t="n">
         <v>1</v>
@@ -50389,10 +50389,10 @@
         <v>58.2</v>
       </c>
       <c r="E1514" t="n">
-        <v>3020.5</v>
+        <v>3078.7</v>
       </c>
       <c r="F1514" t="n">
-        <v>13731.6</v>
+        <v>13789.8</v>
       </c>
       <c r="G1514" t="n">
         <v>4</v>
@@ -50422,10 +50422,10 @@
         <v>49.3</v>
       </c>
       <c r="E1515" t="n">
-        <v>3024.2</v>
+        <v>3088</v>
       </c>
       <c r="F1515" t="n">
-        <v>13715.2</v>
+        <v>13779</v>
       </c>
       <c r="G1515" t="n">
         <v>5</v>
@@ -50455,10 +50455,10 @@
         <v>69.09999999999999</v>
       </c>
       <c r="E1516" t="n">
-        <v>2945.6</v>
+        <v>2980.3</v>
       </c>
       <c r="F1516" t="n">
-        <v>12810.7</v>
+        <v>12845.4</v>
       </c>
       <c r="G1516" t="n">
         <v>3</v>
@@ -50488,10 +50488,10 @@
         <v>48.4</v>
       </c>
       <c r="E1517" t="n">
-        <v>2644.4</v>
+        <v>2686.3</v>
       </c>
       <c r="F1517" t="n">
-        <v>12309</v>
+        <v>12350.9</v>
       </c>
       <c r="G1517" t="n">
         <v>6</v>
@@ -50521,10 +50521,10 @@
         <v>47.6</v>
       </c>
       <c r="E1518" t="n">
-        <v>3116.4</v>
+        <v>3185.5</v>
       </c>
       <c r="F1518" t="n">
-        <v>14051.2</v>
+        <v>14120.3</v>
       </c>
       <c r="G1518" t="n">
         <v>7</v>
@@ -50554,10 +50554,10 @@
         <v>34.8</v>
       </c>
       <c r="E1519" t="n">
-        <v>2564.6</v>
+        <v>2637.2</v>
       </c>
       <c r="F1519" t="n">
-        <v>11398.5</v>
+        <v>11471.1</v>
       </c>
       <c r="G1519" t="n">
         <v>8</v>
@@ -50587,10 +50587,10 @@
         <v>73.3</v>
       </c>
       <c r="E1520" t="n">
-        <v>2773.7</v>
+        <v>2834.7</v>
       </c>
       <c r="F1520" t="n">
-        <v>12377.8</v>
+        <v>12438.8</v>
       </c>
       <c r="G1520" t="n">
         <v>2</v>
@@ -50620,10 +50620,10 @@
         <v>97.7</v>
       </c>
       <c r="E1521" t="n">
-        <v>3184</v>
+        <v>3236</v>
       </c>
       <c r="F1521" t="n">
-        <v>10719</v>
+        <v>10771</v>
       </c>
       <c r="G1521" t="n">
         <v>1</v>
@@ -50653,10 +50653,10 @@
         <v>95.7</v>
       </c>
       <c r="E1522" t="n">
-        <v>3116.2</v>
+        <v>3174.4</v>
       </c>
       <c r="F1522" t="n">
-        <v>13827.3</v>
+        <v>13885.5</v>
       </c>
       <c r="G1522" t="n">
         <v>1</v>
@@ -50686,10 +50686,10 @@
         <v>0</v>
       </c>
       <c r="E1523" t="n">
-        <v>3024.2</v>
+        <v>3088</v>
       </c>
       <c r="F1523" t="n">
-        <v>13715.2</v>
+        <v>13779</v>
       </c>
       <c r="G1523" t="n">
         <v>8</v>
@@ -50719,10 +50719,10 @@
         <v>40.7</v>
       </c>
       <c r="E1524" t="n">
-        <v>2986.3</v>
+        <v>3021</v>
       </c>
       <c r="F1524" t="n">
-        <v>12851.4</v>
+        <v>12886.1</v>
       </c>
       <c r="G1524" t="n">
         <v>7</v>
@@ -50752,10 +50752,10 @@
         <v>68.2</v>
       </c>
       <c r="E1525" t="n">
-        <v>2712.6</v>
+        <v>2754.5</v>
       </c>
       <c r="F1525" t="n">
-        <v>12377.2</v>
+        <v>12419.1</v>
       </c>
       <c r="G1525" t="n">
         <v>4</v>
@@ -50785,10 +50785,10 @@
         <v>66.59999999999999</v>
       </c>
       <c r="E1526" t="n">
-        <v>3183</v>
+        <v>3252.1</v>
       </c>
       <c r="F1526" t="n">
-        <v>14117.8</v>
+        <v>14186.9</v>
       </c>
       <c r="G1526" t="n">
         <v>5</v>
@@ -50818,10 +50818,10 @@
         <v>80.59999999999999</v>
       </c>
       <c r="E1527" t="n">
-        <v>2645.2</v>
+        <v>2717.8</v>
       </c>
       <c r="F1527" t="n">
-        <v>11479.1</v>
+        <v>11551.7</v>
       </c>
       <c r="G1527" t="n">
         <v>2</v>
@@ -50851,10 +50851,10 @@
         <v>46.4</v>
       </c>
       <c r="E1528" t="n">
-        <v>2820.1</v>
+        <v>2881.1</v>
       </c>
       <c r="F1528" t="n">
-        <v>12424.2</v>
+        <v>12485.2</v>
       </c>
       <c r="G1528" t="n">
         <v>6</v>
@@ -50884,10 +50884,10 @@
         <v>80.40000000000001</v>
       </c>
       <c r="E1529" t="n">
-        <v>3264.4</v>
+        <v>3316.4</v>
       </c>
       <c r="F1529" t="n">
-        <v>10799.4</v>
+        <v>10851.4</v>
       </c>
       <c r="G1529" t="n">
         <v>3</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -42172,7 +42172,7 @@
         <v>114.8</v>
       </c>
       <c r="E1265" t="n">
-        <v>551.6</v>
+        <v>551.5999999999999</v>
       </c>
       <c r="F1265" t="n">
         <v>8086.6</v>
@@ -42436,7 +42436,7 @@
         <v>98.09999999999999</v>
       </c>
       <c r="E1273" t="n">
-        <v>649.7</v>
+        <v>649.6999999999999</v>
       </c>
       <c r="F1273" t="n">
         <v>8184.7</v>
@@ -42733,7 +42733,7 @@
         <v>116.1</v>
       </c>
       <c r="E1282" t="n">
-        <v>781.7</v>
+        <v>781.6999999999999</v>
       </c>
       <c r="F1282" t="n">
         <v>11492.8</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -42172,7 +42172,7 @@
         <v>114.8</v>
       </c>
       <c r="E1265" t="n">
-        <v>551.5999999999999</v>
+        <v>551.6</v>
       </c>
       <c r="F1265" t="n">
         <v>8086.6</v>
@@ -42202,16 +42202,16 @@
         </is>
       </c>
       <c r="D1266" t="n">
-        <v>68.90000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="E1266" t="n">
-        <v>553</v>
+        <v>565.4</v>
       </c>
       <c r="F1266" t="n">
-        <v>11264.1</v>
+        <v>11276.5</v>
       </c>
       <c r="G1266" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H1266" t="n">
         <v>8</v>
@@ -42301,16 +42301,16 @@
         </is>
       </c>
       <c r="D1269" t="n">
-        <v>91.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="E1269" t="n">
-        <v>748.2</v>
+        <v>745.8000000000001</v>
       </c>
       <c r="F1269" t="n">
-        <v>10412.8</v>
+        <v>10410.4</v>
       </c>
       <c r="G1269" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1269" t="n">
         <v>2</v>
@@ -42334,13 +42334,13 @@
         </is>
       </c>
       <c r="D1270" t="n">
-        <v>135.1</v>
+        <v>140.1</v>
       </c>
       <c r="E1270" t="n">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="F1270" t="n">
-        <v>11738.8</v>
+        <v>11743.8</v>
       </c>
       <c r="G1270" t="n">
         <v>1</v>
@@ -42376,7 +42376,7 @@
         <v>9425.1</v>
       </c>
       <c r="G1271" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H1271" t="n">
         <v>7</v>
@@ -42400,16 +42400,16 @@
         </is>
       </c>
       <c r="D1272" t="n">
-        <v>81.3</v>
+        <v>93.7</v>
       </c>
       <c r="E1272" t="n">
-        <v>652.1</v>
+        <v>664.5</v>
       </c>
       <c r="F1272" t="n">
-        <v>10256.2</v>
+        <v>10268.6</v>
       </c>
       <c r="G1272" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1272" t="n">
         <v>5</v>
@@ -42433,13 +42433,13 @@
         </is>
       </c>
       <c r="D1273" t="n">
-        <v>98.09999999999999</v>
+        <v>100.2</v>
       </c>
       <c r="E1273" t="n">
-        <v>649.6999999999999</v>
+        <v>651.8</v>
       </c>
       <c r="F1273" t="n">
-        <v>8184.7</v>
+        <v>8186.8</v>
       </c>
       <c r="G1273" t="n">
         <v>4</v>
@@ -42469,10 +42469,10 @@
         <v>112.6</v>
       </c>
       <c r="E1274" t="n">
-        <v>665.6</v>
+        <v>678</v>
       </c>
       <c r="F1274" t="n">
-        <v>11376.7</v>
+        <v>11389.1</v>
       </c>
       <c r="G1274" t="n">
         <v>8</v>
@@ -42568,10 +42568,10 @@
         <v>127.6</v>
       </c>
       <c r="E1277" t="n">
-        <v>875.8</v>
+        <v>873.4</v>
       </c>
       <c r="F1277" t="n">
-        <v>10540.4</v>
+        <v>10538</v>
       </c>
       <c r="G1277" t="n">
         <v>4</v>
@@ -42601,10 +42601,10 @@
         <v>136.5</v>
       </c>
       <c r="E1278" t="n">
-        <v>940.5</v>
+        <v>945.5</v>
       </c>
       <c r="F1278" t="n">
-        <v>11875.3</v>
+        <v>11880.3</v>
       </c>
       <c r="G1278" t="n">
         <v>3</v>
@@ -42667,10 +42667,10 @@
         <v>154.1</v>
       </c>
       <c r="E1280" t="n">
-        <v>806.2</v>
+        <v>818.5999999999999</v>
       </c>
       <c r="F1280" t="n">
-        <v>10410.3</v>
+        <v>10422.7</v>
       </c>
       <c r="G1280" t="n">
         <v>1</v>
@@ -42700,10 +42700,10 @@
         <v>121.1</v>
       </c>
       <c r="E1281" t="n">
-        <v>770.8</v>
+        <v>772.9</v>
       </c>
       <c r="F1281" t="n">
-        <v>8305.799999999999</v>
+        <v>8307.9</v>
       </c>
       <c r="G1281" t="n">
         <v>6</v>
@@ -42733,10 +42733,10 @@
         <v>116.1</v>
       </c>
       <c r="E1282" t="n">
-        <v>781.6999999999999</v>
+        <v>794.1</v>
       </c>
       <c r="F1282" t="n">
-        <v>11492.8</v>
+        <v>11505.2</v>
       </c>
       <c r="G1282" t="n">
         <v>7</v>
@@ -42832,10 +42832,10 @@
         <v>120.6</v>
       </c>
       <c r="E1285" t="n">
-        <v>996.4</v>
+        <v>994</v>
       </c>
       <c r="F1285" t="n">
-        <v>10661</v>
+        <v>10658.6</v>
       </c>
       <c r="G1285" t="n">
         <v>6</v>
@@ -42865,10 +42865,10 @@
         <v>139</v>
       </c>
       <c r="E1286" t="n">
-        <v>1079.5</v>
+        <v>1084.5</v>
       </c>
       <c r="F1286" t="n">
-        <v>12014.3</v>
+        <v>12019.3</v>
       </c>
       <c r="G1286" t="n">
         <v>1</v>
@@ -42931,10 +42931,10 @@
         <v>123.6</v>
       </c>
       <c r="E1288" t="n">
-        <v>929.8</v>
+        <v>942.1999999999999</v>
       </c>
       <c r="F1288" t="n">
-        <v>10533.9</v>
+        <v>10546.3</v>
       </c>
       <c r="G1288" t="n">
         <v>5</v>
@@ -42964,10 +42964,10 @@
         <v>124</v>
       </c>
       <c r="E1289" t="n">
-        <v>894.8</v>
+        <v>896.9</v>
       </c>
       <c r="F1289" t="n">
-        <v>8429.799999999999</v>
+        <v>8431.9</v>
       </c>
       <c r="G1289" t="n">
         <v>4</v>
@@ -42997,10 +42997,10 @@
         <v>146</v>
       </c>
       <c r="E1290" t="n">
-        <v>927.7</v>
+        <v>940.0999999999999</v>
       </c>
       <c r="F1290" t="n">
-        <v>11638.8</v>
+        <v>11651.2</v>
       </c>
       <c r="G1290" t="n">
         <v>1</v>
@@ -43096,10 +43096,10 @@
         <v>99.5</v>
       </c>
       <c r="E1293" t="n">
-        <v>1095.9</v>
+        <v>1093.5</v>
       </c>
       <c r="F1293" t="n">
-        <v>10760.5</v>
+        <v>10758.1</v>
       </c>
       <c r="G1293" t="n">
         <v>7</v>
@@ -43129,10 +43129,10 @@
         <v>135.4</v>
       </c>
       <c r="E1294" t="n">
-        <v>1214.9</v>
+        <v>1219.9</v>
       </c>
       <c r="F1294" t="n">
-        <v>12149.7</v>
+        <v>12154.7</v>
       </c>
       <c r="G1294" t="n">
         <v>3</v>
@@ -43195,10 +43195,10 @@
         <v>142.1</v>
       </c>
       <c r="E1296" t="n">
-        <v>1071.9</v>
+        <v>1084.3</v>
       </c>
       <c r="F1296" t="n">
-        <v>10676</v>
+        <v>10688.4</v>
       </c>
       <c r="G1296" t="n">
         <v>2</v>
@@ -43228,10 +43228,10 @@
         <v>128.9</v>
       </c>
       <c r="E1297" t="n">
-        <v>1023.7</v>
+        <v>1025.8</v>
       </c>
       <c r="F1297" t="n">
-        <v>8558.700000000001</v>
+        <v>8560.799999999999</v>
       </c>
       <c r="G1297" t="n">
         <v>5</v>
@@ -43261,10 +43261,10 @@
         <v>77.90000000000001</v>
       </c>
       <c r="E1298" t="n">
-        <v>1005.6</v>
+        <v>1018</v>
       </c>
       <c r="F1298" t="n">
-        <v>11716.7</v>
+        <v>11729.1</v>
       </c>
       <c r="G1298" t="n">
         <v>1</v>
@@ -43303,7 +43303,7 @@
         <v>7</v>
       </c>
       <c r="H1299" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1299" t="n">
         <v>2</v>
@@ -43360,10 +43360,10 @@
         <v>60.2</v>
       </c>
       <c r="E1301" t="n">
-        <v>1156.1</v>
+        <v>1153.7</v>
       </c>
       <c r="F1301" t="n">
-        <v>10820.7</v>
+        <v>10818.3</v>
       </c>
       <c r="G1301" t="n">
         <v>6</v>
@@ -43393,10 +43393,10 @@
         <v>62.8</v>
       </c>
       <c r="E1302" t="n">
-        <v>1277.7</v>
+        <v>1282.7</v>
       </c>
       <c r="F1302" t="n">
-        <v>12212.5</v>
+        <v>12217.5</v>
       </c>
       <c r="G1302" t="n">
         <v>5</v>
@@ -43459,16 +43459,16 @@
         <v>69.40000000000001</v>
       </c>
       <c r="E1304" t="n">
-        <v>1141.3</v>
+        <v>1153.7</v>
       </c>
       <c r="F1304" t="n">
-        <v>10745.4</v>
+        <v>10757.8</v>
       </c>
       <c r="G1304" t="n">
         <v>2</v>
       </c>
       <c r="H1304" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I1304" t="n">
         <v>6</v>
@@ -43492,10 +43492,10 @@
         <v>66.3</v>
       </c>
       <c r="E1305" t="n">
-        <v>1090</v>
+        <v>1092.1</v>
       </c>
       <c r="F1305" t="n">
-        <v>8625</v>
+        <v>8627.1</v>
       </c>
       <c r="G1305" t="n">
         <v>4</v>
@@ -43525,10 +43525,10 @@
         <v>68</v>
       </c>
       <c r="E1306" t="n">
-        <v>1073.6</v>
+        <v>1086</v>
       </c>
       <c r="F1306" t="n">
-        <v>11784.7</v>
+        <v>11797.1</v>
       </c>
       <c r="G1306" t="n">
         <v>5</v>
@@ -43624,10 +43624,10 @@
         <v>61</v>
       </c>
       <c r="E1309" t="n">
-        <v>1217.1</v>
+        <v>1214.7</v>
       </c>
       <c r="F1309" t="n">
-        <v>10881.7</v>
+        <v>10879.3</v>
       </c>
       <c r="G1309" t="n">
         <v>6</v>
@@ -43657,10 +43657,10 @@
         <v>57.4</v>
       </c>
       <c r="E1310" t="n">
-        <v>1335.1</v>
+        <v>1340.1</v>
       </c>
       <c r="F1310" t="n">
-        <v>12269.9</v>
+        <v>12274.9</v>
       </c>
       <c r="G1310" t="n">
         <v>7</v>
@@ -43723,10 +43723,10 @@
         <v>77.2</v>
       </c>
       <c r="E1312" t="n">
-        <v>1218.5</v>
+        <v>1230.9</v>
       </c>
       <c r="F1312" t="n">
-        <v>10822.6</v>
+        <v>10835</v>
       </c>
       <c r="G1312" t="n">
         <v>4</v>
@@ -43756,10 +43756,10 @@
         <v>95.2</v>
       </c>
       <c r="E1313" t="n">
-        <v>1185.2</v>
+        <v>1187.3</v>
       </c>
       <c r="F1313" t="n">
-        <v>8720.200000000001</v>
+        <v>8722.299999999999</v>
       </c>
       <c r="G1313" t="n">
         <v>1</v>
@@ -43789,10 +43789,10 @@
         <v>78</v>
       </c>
       <c r="E1314" t="n">
-        <v>1151.6</v>
+        <v>1164</v>
       </c>
       <c r="F1314" t="n">
-        <v>11862.7</v>
+        <v>11875.1</v>
       </c>
       <c r="G1314" t="n">
         <v>3</v>
@@ -43864,7 +43864,7 @@
         <v>4</v>
       </c>
       <c r="H1316" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1316" t="n">
         <v>4</v>
@@ -43888,10 +43888,10 @@
         <v>48.4</v>
       </c>
       <c r="E1317" t="n">
-        <v>1265.5</v>
+        <v>1263.1</v>
       </c>
       <c r="F1317" t="n">
-        <v>10930.1</v>
+        <v>10927.7</v>
       </c>
       <c r="G1317" t="n">
         <v>8</v>
@@ -43921,10 +43921,10 @@
         <v>67.59999999999999</v>
       </c>
       <c r="E1318" t="n">
-        <v>1402.7</v>
+        <v>1407.7</v>
       </c>
       <c r="F1318" t="n">
-        <v>12337.5</v>
+        <v>12342.5</v>
       </c>
       <c r="G1318" t="n">
         <v>5</v>
@@ -43987,16 +43987,16 @@
         <v>61.4</v>
       </c>
       <c r="E1320" t="n">
-        <v>1279.9</v>
+        <v>1292.3</v>
       </c>
       <c r="F1320" t="n">
-        <v>10884</v>
+        <v>10896.4</v>
       </c>
       <c r="G1320" t="n">
         <v>6</v>
       </c>
       <c r="H1320" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1320" t="n">
         <v>6</v>
@@ -44020,10 +44020,10 @@
         <v>81.59999999999999</v>
       </c>
       <c r="E1321" t="n">
-        <v>1266.8</v>
+        <v>1268.9</v>
       </c>
       <c r="F1321" t="n">
-        <v>8801.799999999999</v>
+        <v>8803.9</v>
       </c>
       <c r="G1321" t="n">
         <v>1</v>
@@ -44053,10 +44053,10 @@
         <v>67.5</v>
       </c>
       <c r="E1322" t="n">
-        <v>1219.1</v>
+        <v>1231.5</v>
       </c>
       <c r="F1322" t="n">
-        <v>11930.2</v>
+        <v>11942.6</v>
       </c>
       <c r="G1322" t="n">
         <v>5</v>
@@ -44152,10 +44152,10 @@
         <v>52.1</v>
       </c>
       <c r="E1325" t="n">
-        <v>1317.6</v>
+        <v>1315.2</v>
       </c>
       <c r="F1325" t="n">
-        <v>10982.2</v>
+        <v>10979.8</v>
       </c>
       <c r="G1325" t="n">
         <v>8</v>
@@ -44185,10 +44185,10 @@
         <v>79.7</v>
       </c>
       <c r="E1326" t="n">
-        <v>1482.4</v>
+        <v>1487.4</v>
       </c>
       <c r="F1326" t="n">
-        <v>12417.2</v>
+        <v>12422.2</v>
       </c>
       <c r="G1326" t="n">
         <v>1</v>
@@ -44251,10 +44251,10 @@
         <v>59.5</v>
       </c>
       <c r="E1328" t="n">
-        <v>1339.4</v>
+        <v>1351.8</v>
       </c>
       <c r="F1328" t="n">
-        <v>10943.5</v>
+        <v>10955.9</v>
       </c>
       <c r="G1328" t="n">
         <v>6</v>
@@ -44284,10 +44284,10 @@
         <v>68.10000000000001</v>
       </c>
       <c r="E1329" t="n">
-        <v>1334.9</v>
+        <v>1337</v>
       </c>
       <c r="F1329" t="n">
-        <v>8869.9</v>
+        <v>8872</v>
       </c>
       <c r="G1329" t="n">
         <v>4</v>
@@ -44317,10 +44317,10 @@
         <v>58.6</v>
       </c>
       <c r="E1330" t="n">
-        <v>1277.7</v>
+        <v>1290.1</v>
       </c>
       <c r="F1330" t="n">
-        <v>11988.8</v>
+        <v>12001.2</v>
       </c>
       <c r="G1330" t="n">
         <v>6</v>
@@ -44392,7 +44392,7 @@
         <v>7</v>
       </c>
       <c r="H1332" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1332" t="n">
         <v>4</v>
@@ -44416,10 +44416,10 @@
         <v>57.4</v>
       </c>
       <c r="E1333" t="n">
-        <v>1375</v>
+        <v>1372.6</v>
       </c>
       <c r="F1333" t="n">
-        <v>11039.6</v>
+        <v>11037.2</v>
       </c>
       <c r="G1333" t="n">
         <v>8</v>
@@ -44449,10 +44449,10 @@
         <v>83.40000000000001</v>
       </c>
       <c r="E1334" t="n">
-        <v>1565.8</v>
+        <v>1570.8</v>
       </c>
       <c r="F1334" t="n">
-        <v>12500.6</v>
+        <v>12505.6</v>
       </c>
       <c r="G1334" t="n">
         <v>3</v>
@@ -44515,16 +44515,16 @@
         <v>72</v>
       </c>
       <c r="E1336" t="n">
-        <v>1411.4</v>
+        <v>1423.8</v>
       </c>
       <c r="F1336" t="n">
-        <v>11015.5</v>
+        <v>11027.9</v>
       </c>
       <c r="G1336" t="n">
         <v>5</v>
       </c>
       <c r="H1336" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1336" t="n">
         <v>6</v>
@@ -44548,10 +44548,10 @@
         <v>87.09999999999999</v>
       </c>
       <c r="E1337" t="n">
-        <v>1422</v>
+        <v>1424.1</v>
       </c>
       <c r="F1337" t="n">
-        <v>8957</v>
+        <v>8959.1</v>
       </c>
       <c r="G1337" t="n">
         <v>2</v>
@@ -44581,10 +44581,10 @@
         <v>61.2</v>
       </c>
       <c r="E1338" t="n">
-        <v>1338.9</v>
+        <v>1351.3</v>
       </c>
       <c r="F1338" t="n">
-        <v>12050</v>
+        <v>12062.4</v>
       </c>
       <c r="G1338" t="n">
         <v>5</v>
@@ -44680,10 +44680,10 @@
         <v>62.40000000000001</v>
       </c>
       <c r="E1341" t="n">
-        <v>1437.4</v>
+        <v>1435</v>
       </c>
       <c r="F1341" t="n">
-        <v>11102</v>
+        <v>11099.6</v>
       </c>
       <c r="G1341" t="n">
         <v>4</v>
@@ -44692,7 +44692,7 @@
         <v>6</v>
       </c>
       <c r="I1341" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1342">
@@ -44713,10 +44713,10 @@
         <v>81.90000000000001</v>
       </c>
       <c r="E1342" t="n">
-        <v>1647.7</v>
+        <v>1652.7</v>
       </c>
       <c r="F1342" t="n">
-        <v>12582.5</v>
+        <v>12587.5</v>
       </c>
       <c r="G1342" t="n">
         <v>2</v>
@@ -44779,10 +44779,10 @@
         <v>86</v>
       </c>
       <c r="E1344" t="n">
-        <v>1497.4</v>
+        <v>1509.8</v>
       </c>
       <c r="F1344" t="n">
-        <v>11101.5</v>
+        <v>11113.9</v>
       </c>
       <c r="G1344" t="n">
         <v>1</v>
@@ -44791,7 +44791,7 @@
         <v>3</v>
       </c>
       <c r="I1344" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1345">
@@ -44812,10 +44812,10 @@
         <v>58.1</v>
       </c>
       <c r="E1345" t="n">
-        <v>1480.1</v>
+        <v>1482.2</v>
       </c>
       <c r="F1345" t="n">
-        <v>9015.1</v>
+        <v>9017.200000000001</v>
       </c>
       <c r="G1345" t="n">
         <v>6</v>
@@ -44845,10 +44845,10 @@
         <v>64.2</v>
       </c>
       <c r="E1346" t="n">
-        <v>1403.1</v>
+        <v>1415.5</v>
       </c>
       <c r="F1346" t="n">
-        <v>12114.2</v>
+        <v>12126.6</v>
       </c>
       <c r="G1346" t="n">
         <v>5</v>
@@ -44944,10 +44944,10 @@
         <v>45</v>
       </c>
       <c r="E1349" t="n">
-        <v>1482.4</v>
+        <v>1480</v>
       </c>
       <c r="F1349" t="n">
-        <v>11147</v>
+        <v>11144.6</v>
       </c>
       <c r="G1349" t="n">
         <v>8</v>
@@ -44977,10 +44977,10 @@
         <v>81.2</v>
       </c>
       <c r="E1350" t="n">
-        <v>1728.9</v>
+        <v>1733.9</v>
       </c>
       <c r="F1350" t="n">
-        <v>12663.7</v>
+        <v>12668.7</v>
       </c>
       <c r="G1350" t="n">
         <v>2</v>
@@ -45043,10 +45043,10 @@
         <v>67.7</v>
       </c>
       <c r="E1352" t="n">
-        <v>1565.1</v>
+        <v>1577.5</v>
       </c>
       <c r="F1352" t="n">
-        <v>11169.2</v>
+        <v>11181.6</v>
       </c>
       <c r="G1352" t="n">
         <v>4</v>
@@ -45076,10 +45076,10 @@
         <v>60.2</v>
       </c>
       <c r="E1353" t="n">
-        <v>1540.3</v>
+        <v>1542.4</v>
       </c>
       <c r="F1353" t="n">
-        <v>9075.299999999999</v>
+        <v>9077.4</v>
       </c>
       <c r="G1353" t="n">
         <v>7</v>
@@ -45109,10 +45109,10 @@
         <v>88.09999999999999</v>
       </c>
       <c r="E1354" t="n">
-        <v>1491.2</v>
+        <v>1503.6</v>
       </c>
       <c r="F1354" t="n">
-        <v>12202.3</v>
+        <v>12214.7</v>
       </c>
       <c r="G1354" t="n">
         <v>3</v>
@@ -45208,10 +45208,10 @@
         <v>0</v>
       </c>
       <c r="E1357" t="n">
-        <v>1482.4</v>
+        <v>1480</v>
       </c>
       <c r="F1357" t="n">
-        <v>11147</v>
+        <v>11144.6</v>
       </c>
       <c r="G1357" t="n">
         <v>8</v>
@@ -45241,10 +45241,10 @@
         <v>94</v>
       </c>
       <c r="E1358" t="n">
-        <v>1822.9</v>
+        <v>1827.9</v>
       </c>
       <c r="F1358" t="n">
-        <v>12757.7</v>
+        <v>12762.7</v>
       </c>
       <c r="G1358" t="n">
         <v>1</v>
@@ -45307,16 +45307,16 @@
         <v>58.6</v>
       </c>
       <c r="E1360" t="n">
-        <v>1623.7</v>
+        <v>1636.1</v>
       </c>
       <c r="F1360" t="n">
-        <v>11227.8</v>
+        <v>11240.2</v>
       </c>
       <c r="G1360" t="n">
         <v>7</v>
       </c>
       <c r="H1360" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1360" t="n">
         <v>5</v>
@@ -45340,16 +45340,16 @@
         <v>89.5</v>
       </c>
       <c r="E1361" t="n">
-        <v>1629.8</v>
+        <v>1631.9</v>
       </c>
       <c r="F1361" t="n">
-        <v>9164.799999999999</v>
+        <v>9166.9</v>
       </c>
       <c r="G1361" t="n">
         <v>2</v>
       </c>
       <c r="H1361" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1361" t="n">
         <v>8</v>
@@ -45373,16 +45373,16 @@
         <v>66.7</v>
       </c>
       <c r="E1362" t="n">
-        <v>1557.9</v>
+        <v>1570.3</v>
       </c>
       <c r="F1362" t="n">
-        <v>12269</v>
+        <v>12281.4</v>
       </c>
       <c r="G1362" t="n">
         <v>4</v>
       </c>
       <c r="H1362" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I1362" t="n">
         <v>3</v>
@@ -45472,16 +45472,16 @@
         <v>82.2</v>
       </c>
       <c r="E1365" t="n">
-        <v>1564.6</v>
+        <v>1562.2</v>
       </c>
       <c r="F1365" t="n">
-        <v>11229.2</v>
+        <v>11226.8</v>
       </c>
       <c r="G1365" t="n">
         <v>2</v>
       </c>
       <c r="H1365" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1365" t="n">
         <v>6</v>
@@ -45505,10 +45505,10 @@
         <v>63</v>
       </c>
       <c r="E1366" t="n">
-        <v>1885.9</v>
+        <v>1890.9</v>
       </c>
       <c r="F1366" t="n">
-        <v>12820.7</v>
+        <v>12825.7</v>
       </c>
       <c r="G1366" t="n">
         <v>5</v>
@@ -45571,10 +45571,10 @@
         <v>78.59999999999999</v>
       </c>
       <c r="E1368" t="n">
-        <v>1702.3</v>
+        <v>1714.7</v>
       </c>
       <c r="F1368" t="n">
-        <v>11306.4</v>
+        <v>11318.8</v>
       </c>
       <c r="G1368" t="n">
         <v>3</v>
@@ -45604,10 +45604,10 @@
         <v>87.3</v>
       </c>
       <c r="E1369" t="n">
-        <v>1717.1</v>
+        <v>1719.2</v>
       </c>
       <c r="F1369" t="n">
-        <v>9252.1</v>
+        <v>9254.200000000001</v>
       </c>
       <c r="G1369" t="n">
         <v>1</v>
@@ -45637,10 +45637,10 @@
         <v>70.8</v>
       </c>
       <c r="E1370" t="n">
-        <v>1628.7</v>
+        <v>1641.1</v>
       </c>
       <c r="F1370" t="n">
-        <v>12339.8</v>
+        <v>12352.2</v>
       </c>
       <c r="G1370" t="n">
         <v>4</v>
@@ -45736,10 +45736,10 @@
         <v>46.7</v>
       </c>
       <c r="E1373" t="n">
-        <v>1611.3</v>
+        <v>1608.9</v>
       </c>
       <c r="F1373" t="n">
-        <v>11275.9</v>
+        <v>11273.5</v>
       </c>
       <c r="G1373" t="n">
         <v>8</v>
@@ -45769,10 +45769,10 @@
         <v>79.40000000000001</v>
       </c>
       <c r="E1374" t="n">
-        <v>1965.3</v>
+        <v>1970.3</v>
       </c>
       <c r="F1374" t="n">
-        <v>12900.1</v>
+        <v>12905.1</v>
       </c>
       <c r="G1374" t="n">
         <v>1</v>
@@ -45835,16 +45835,16 @@
         <v>65.2</v>
       </c>
       <c r="E1376" t="n">
-        <v>1767.5</v>
+        <v>1779.9</v>
       </c>
       <c r="F1376" t="n">
-        <v>11371.6</v>
+        <v>11384</v>
       </c>
       <c r="G1376" t="n">
         <v>5</v>
       </c>
       <c r="H1376" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1376" t="n">
         <v>5</v>
@@ -45868,16 +45868,16 @@
         <v>54.8</v>
       </c>
       <c r="E1377" t="n">
-        <v>1771.9</v>
+        <v>1774</v>
       </c>
       <c r="F1377" t="n">
-        <v>9306.9</v>
+        <v>9309</v>
       </c>
       <c r="G1377" t="n">
         <v>7</v>
       </c>
       <c r="H1377" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1377" t="n">
         <v>8</v>
@@ -45901,10 +45901,10 @@
         <v>93.8</v>
       </c>
       <c r="E1378" t="n">
-        <v>1722.5</v>
+        <v>1734.9</v>
       </c>
       <c r="F1378" t="n">
-        <v>12433.6</v>
+        <v>12446</v>
       </c>
       <c r="G1378" t="n">
         <v>2</v>
@@ -45976,7 +45976,7 @@
         <v>1</v>
       </c>
       <c r="H1380" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1380" t="n">
         <v>4</v>
@@ -46000,10 +46000,10 @@
         <v>63.3</v>
       </c>
       <c r="E1381" t="n">
-        <v>1674.6</v>
+        <v>1672.2</v>
       </c>
       <c r="F1381" t="n">
-        <v>11339.2</v>
+        <v>11336.8</v>
       </c>
       <c r="G1381" t="n">
         <v>8</v>
@@ -46033,10 +46033,10 @@
         <v>79.3</v>
       </c>
       <c r="E1382" t="n">
-        <v>2044.6</v>
+        <v>2049.6</v>
       </c>
       <c r="F1382" t="n">
-        <v>12979.4</v>
+        <v>12984.4</v>
       </c>
       <c r="G1382" t="n">
         <v>5</v>
@@ -46099,16 +46099,16 @@
         <v>67.40000000000001</v>
       </c>
       <c r="E1384" t="n">
-        <v>1834.9</v>
+        <v>1847.3</v>
       </c>
       <c r="F1384" t="n">
-        <v>11439</v>
+        <v>11451.4</v>
       </c>
       <c r="G1384" t="n">
         <v>6</v>
       </c>
       <c r="H1384" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1384" t="n">
         <v>5</v>
@@ -46132,10 +46132,10 @@
         <v>82.59999999999999</v>
       </c>
       <c r="E1385" t="n">
-        <v>1854.5</v>
+        <v>1856.6</v>
       </c>
       <c r="F1385" t="n">
-        <v>9389.5</v>
+        <v>9391.6</v>
       </c>
       <c r="G1385" t="n">
         <v>3</v>
@@ -46165,10 +46165,10 @@
         <v>100.5</v>
       </c>
       <c r="E1386" t="n">
-        <v>1823</v>
+        <v>1835.4</v>
       </c>
       <c r="F1386" t="n">
-        <v>12534.1</v>
+        <v>12546.5</v>
       </c>
       <c r="G1386" t="n">
         <v>1</v>
@@ -46264,10 +46264,10 @@
         <v>67.59999999999999</v>
       </c>
       <c r="E1389" t="n">
-        <v>1742.2</v>
+        <v>1739.8</v>
       </c>
       <c r="F1389" t="n">
-        <v>11406.8</v>
+        <v>11404.4</v>
       </c>
       <c r="G1389" t="n">
         <v>4</v>
@@ -46297,10 +46297,10 @@
         <v>70.2</v>
       </c>
       <c r="E1390" t="n">
-        <v>2114.8</v>
+        <v>2119.8</v>
       </c>
       <c r="F1390" t="n">
-        <v>13049.6</v>
+        <v>13054.6</v>
       </c>
       <c r="G1390" t="n">
         <v>3</v>
@@ -46363,10 +46363,10 @@
         <v>50.8</v>
       </c>
       <c r="E1392" t="n">
-        <v>1885.7</v>
+        <v>1898.1</v>
       </c>
       <c r="F1392" t="n">
-        <v>11489.8</v>
+        <v>11502.2</v>
       </c>
       <c r="G1392" t="n">
         <v>8</v>
@@ -46396,10 +46396,10 @@
         <v>58.9</v>
       </c>
       <c r="E1393" t="n">
-        <v>1913.4</v>
+        <v>1915.5</v>
       </c>
       <c r="F1393" t="n">
-        <v>9448.4</v>
+        <v>9450.5</v>
       </c>
       <c r="G1393" t="n">
         <v>7</v>
@@ -46429,10 +46429,10 @@
         <v>92</v>
       </c>
       <c r="E1394" t="n">
-        <v>1915</v>
+        <v>1927.4</v>
       </c>
       <c r="F1394" t="n">
-        <v>12626.1</v>
+        <v>12638.5</v>
       </c>
       <c r="G1394" t="n">
         <v>2</v>
@@ -46504,7 +46504,7 @@
         <v>3</v>
       </c>
       <c r="H1396" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1396" t="n">
         <v>4</v>
@@ -46528,10 +46528,10 @@
         <v>50.6</v>
       </c>
       <c r="E1397" t="n">
-        <v>1792.8</v>
+        <v>1790.4</v>
       </c>
       <c r="F1397" t="n">
-        <v>11457.4</v>
+        <v>11455</v>
       </c>
       <c r="G1397" t="n">
         <v>7</v>
@@ -46561,10 +46561,10 @@
         <v>76.7</v>
       </c>
       <c r="E1398" t="n">
-        <v>2191.5</v>
+        <v>2196.5</v>
       </c>
       <c r="F1398" t="n">
-        <v>13126.3</v>
+        <v>13131.3</v>
       </c>
       <c r="G1398" t="n">
         <v>5</v>
@@ -46627,16 +46627,16 @@
         <v>92.5</v>
       </c>
       <c r="E1400" t="n">
-        <v>1978.2</v>
+        <v>1990.6</v>
       </c>
       <c r="F1400" t="n">
-        <v>11582.3</v>
+        <v>11594.7</v>
       </c>
       <c r="G1400" t="n">
         <v>1</v>
       </c>
       <c r="H1400" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I1400" t="n">
         <v>5</v>
@@ -46660,16 +46660,16 @@
         <v>73.10000000000001</v>
       </c>
       <c r="E1401" t="n">
-        <v>1986.5</v>
+        <v>1988.6</v>
       </c>
       <c r="F1401" t="n">
-        <v>9521.5</v>
+        <v>9523.6</v>
       </c>
       <c r="G1401" t="n">
         <v>6</v>
       </c>
       <c r="H1401" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1401" t="n">
         <v>8</v>
@@ -46693,10 +46693,10 @@
         <v>75.59999999999999</v>
       </c>
       <c r="E1402" t="n">
-        <v>1990.6</v>
+        <v>2003</v>
       </c>
       <c r="F1402" t="n">
-        <v>12701.7</v>
+        <v>12714.1</v>
       </c>
       <c r="G1402" t="n">
         <v>3</v>
@@ -46792,10 +46792,10 @@
         <v>71.5</v>
       </c>
       <c r="E1405" t="n">
-        <v>1864.3</v>
+        <v>1861.9</v>
       </c>
       <c r="F1405" t="n">
-        <v>11528.9</v>
+        <v>11526.5</v>
       </c>
       <c r="G1405" t="n">
         <v>6</v>
@@ -46825,10 +46825,10 @@
         <v>75.39999999999999</v>
       </c>
       <c r="E1406" t="n">
-        <v>2266.9</v>
+        <v>2271.9</v>
       </c>
       <c r="F1406" t="n">
-        <v>13201.7</v>
+        <v>13206.7</v>
       </c>
       <c r="G1406" t="n">
         <v>4</v>
@@ -46891,10 +46891,10 @@
         <v>72</v>
       </c>
       <c r="E1408" t="n">
-        <v>2050.2</v>
+        <v>2062.6</v>
       </c>
       <c r="F1408" t="n">
-        <v>11654.3</v>
+        <v>11666.7</v>
       </c>
       <c r="G1408" t="n">
         <v>5</v>
@@ -46924,10 +46924,10 @@
         <v>79.09999999999999</v>
       </c>
       <c r="E1409" t="n">
-        <v>2065.6</v>
+        <v>2067.7</v>
       </c>
       <c r="F1409" t="n">
-        <v>9600.6</v>
+        <v>9602.700000000001</v>
       </c>
       <c r="G1409" t="n">
         <v>2</v>
@@ -46957,10 +46957,10 @@
         <v>73.2</v>
       </c>
       <c r="E1410" t="n">
-        <v>2063.8</v>
+        <v>2076.2</v>
       </c>
       <c r="F1410" t="n">
-        <v>12774.9</v>
+        <v>12787.3</v>
       </c>
       <c r="G1410" t="n">
         <v>2</v>
@@ -47056,10 +47056,10 @@
         <v>43.9</v>
       </c>
       <c r="E1413" t="n">
-        <v>1908.2</v>
+        <v>1905.8</v>
       </c>
       <c r="F1413" t="n">
-        <v>11572.8</v>
+        <v>11570.4</v>
       </c>
       <c r="G1413" t="n">
         <v>7</v>
@@ -47089,10 +47089,10 @@
         <v>71.2</v>
       </c>
       <c r="E1414" t="n">
-        <v>2338.1</v>
+        <v>2343.1</v>
       </c>
       <c r="F1414" t="n">
-        <v>13272.9</v>
+        <v>13277.9</v>
       </c>
       <c r="G1414" t="n">
         <v>3</v>
@@ -47155,10 +47155,10 @@
         <v>42.9</v>
       </c>
       <c r="E1416" t="n">
-        <v>2093.1</v>
+        <v>2105.5</v>
       </c>
       <c r="F1416" t="n">
-        <v>11697.2</v>
+        <v>11709.6</v>
       </c>
       <c r="G1416" t="n">
         <v>8</v>
@@ -47188,10 +47188,10 @@
         <v>73.8</v>
       </c>
       <c r="E1417" t="n">
-        <v>2139.4</v>
+        <v>2141.5</v>
       </c>
       <c r="F1417" t="n">
-        <v>9674.4</v>
+        <v>9676.5</v>
       </c>
       <c r="G1417" t="n">
         <v>1</v>
@@ -47221,10 +47221,10 @@
         <v>79.3</v>
       </c>
       <c r="E1418" t="n">
-        <v>2143.1</v>
+        <v>2155.5</v>
       </c>
       <c r="F1418" t="n">
-        <v>12854.2</v>
+        <v>12866.6</v>
       </c>
       <c r="G1418" t="n">
         <v>1</v>
@@ -47320,10 +47320,10 @@
         <v>48.8</v>
       </c>
       <c r="E1421" t="n">
-        <v>1957</v>
+        <v>1954.6</v>
       </c>
       <c r="F1421" t="n">
-        <v>11621.6</v>
+        <v>11619.2</v>
       </c>
       <c r="G1421" t="n">
         <v>8</v>
@@ -47353,10 +47353,10 @@
         <v>75</v>
       </c>
       <c r="E1422" t="n">
-        <v>2413.1</v>
+        <v>2418.1</v>
       </c>
       <c r="F1422" t="n">
-        <v>13347.9</v>
+        <v>13352.9</v>
       </c>
       <c r="G1422" t="n">
         <v>2</v>
@@ -47419,10 +47419,10 @@
         <v>59.7</v>
       </c>
       <c r="E1424" t="n">
-        <v>2152.8</v>
+        <v>2165.2</v>
       </c>
       <c r="F1424" t="n">
-        <v>11756.9</v>
+        <v>11769.3</v>
       </c>
       <c r="G1424" t="n">
         <v>5</v>
@@ -47452,10 +47452,10 @@
         <v>57.7</v>
       </c>
       <c r="E1425" t="n">
-        <v>2197.1</v>
+        <v>2199.2</v>
       </c>
       <c r="F1425" t="n">
-        <v>9732.1</v>
+        <v>9734.200000000001</v>
       </c>
       <c r="G1425" t="n">
         <v>6</v>
@@ -47485,10 +47485,10 @@
         <v>86.3</v>
       </c>
       <c r="E1426" t="n">
-        <v>2229.4</v>
+        <v>2241.8</v>
       </c>
       <c r="F1426" t="n">
-        <v>12940.5</v>
+        <v>12952.9</v>
       </c>
       <c r="G1426" t="n">
         <v>2</v>
@@ -47584,10 +47584,10 @@
         <v>65.3</v>
       </c>
       <c r="E1429" t="n">
-        <v>2022.3</v>
+        <v>2019.9</v>
       </c>
       <c r="F1429" t="n">
-        <v>11686.9</v>
+        <v>11684.5</v>
       </c>
       <c r="G1429" t="n">
         <v>4</v>
@@ -47617,10 +47617,10 @@
         <v>58.4</v>
       </c>
       <c r="E1430" t="n">
-        <v>2471.5</v>
+        <v>2476.5</v>
       </c>
       <c r="F1430" t="n">
-        <v>13406.3</v>
+        <v>13411.3</v>
       </c>
       <c r="G1430" t="n">
         <v>6</v>
@@ -47683,10 +47683,10 @@
         <v>55.3</v>
       </c>
       <c r="E1432" t="n">
-        <v>2208.1</v>
+        <v>2220.5</v>
       </c>
       <c r="F1432" t="n">
-        <v>11812.2</v>
+        <v>11824.6</v>
       </c>
       <c r="G1432" t="n">
         <v>7</v>
@@ -47716,10 +47716,10 @@
         <v>96</v>
       </c>
       <c r="E1433" t="n">
-        <v>2293.1</v>
+        <v>2295.2</v>
       </c>
       <c r="F1433" t="n">
-        <v>9828.1</v>
+        <v>9830.200000000001</v>
       </c>
       <c r="G1433" t="n">
         <v>1</v>
@@ -47749,10 +47749,10 @@
         <v>84.5</v>
       </c>
       <c r="E1434" t="n">
-        <v>2313.9</v>
+        <v>2326.3</v>
       </c>
       <c r="F1434" t="n">
-        <v>13025</v>
+        <v>13037.4</v>
       </c>
       <c r="G1434" t="n">
         <v>1</v>
@@ -47848,10 +47848,10 @@
         <v>74.09999999999999</v>
       </c>
       <c r="E1437" t="n">
-        <v>2096.4</v>
+        <v>2094</v>
       </c>
       <c r="F1437" t="n">
-        <v>11761</v>
+        <v>11758.6</v>
       </c>
       <c r="G1437" t="n">
         <v>3</v>
@@ -47881,10 +47881,10 @@
         <v>57.4</v>
       </c>
       <c r="E1438" t="n">
-        <v>2528.9</v>
+        <v>2533.9</v>
       </c>
       <c r="F1438" t="n">
-        <v>13463.7</v>
+        <v>13468.7</v>
       </c>
       <c r="G1438" t="n">
         <v>7</v>
@@ -47947,10 +47947,10 @@
         <v>65.90000000000001</v>
       </c>
       <c r="E1440" t="n">
-        <v>2274</v>
+        <v>2286.4</v>
       </c>
       <c r="F1440" t="n">
-        <v>11878.1</v>
+        <v>11890.5</v>
       </c>
       <c r="G1440" t="n">
         <v>5</v>
@@ -47980,10 +47980,10 @@
         <v>76</v>
       </c>
       <c r="E1441" t="n">
-        <v>2369.1</v>
+        <v>2371.2</v>
       </c>
       <c r="F1441" t="n">
-        <v>9904.1</v>
+        <v>9906.200000000001</v>
       </c>
       <c r="G1441" t="n">
         <v>2</v>
@@ -48013,10 +48013,10 @@
         <v>73.09999999999999</v>
       </c>
       <c r="E1442" t="n">
-        <v>2387</v>
+        <v>2399.4</v>
       </c>
       <c r="F1442" t="n">
-        <v>13098.1</v>
+        <v>13110.5</v>
       </c>
       <c r="G1442" t="n">
         <v>6</v>
@@ -48112,10 +48112,10 @@
         <v>62.1</v>
       </c>
       <c r="E1445" t="n">
-        <v>2158.5</v>
+        <v>2156.1</v>
       </c>
       <c r="F1445" t="n">
-        <v>11823.1</v>
+        <v>11820.7</v>
       </c>
       <c r="G1445" t="n">
         <v>7</v>
@@ -48145,10 +48145,10 @@
         <v>86.7</v>
       </c>
       <c r="E1446" t="n">
-        <v>2615.6</v>
+        <v>2620.6</v>
       </c>
       <c r="F1446" t="n">
-        <v>13550.4</v>
+        <v>13555.4</v>
       </c>
       <c r="G1446" t="n">
         <v>4</v>
@@ -48211,10 +48211,10 @@
         <v>73.3</v>
       </c>
       <c r="E1448" t="n">
-        <v>2347.3</v>
+        <v>2359.7</v>
       </c>
       <c r="F1448" t="n">
-        <v>11951.4</v>
+        <v>11963.8</v>
       </c>
       <c r="G1448" t="n">
         <v>5</v>
@@ -48244,10 +48244,10 @@
         <v>100.9</v>
       </c>
       <c r="E1449" t="n">
-        <v>2470</v>
+        <v>2472.1</v>
       </c>
       <c r="F1449" t="n">
-        <v>10005</v>
+        <v>10007.1</v>
       </c>
       <c r="G1449" t="n">
         <v>1</v>
@@ -48277,10 +48277,10 @@
         <v>82.5</v>
       </c>
       <c r="E1450" t="n">
-        <v>2469.5</v>
+        <v>2481.9</v>
       </c>
       <c r="F1450" t="n">
-        <v>13180.6</v>
+        <v>13193</v>
       </c>
       <c r="G1450" t="n">
         <v>3</v>
@@ -48376,10 +48376,10 @@
         <v>85.90000000000001</v>
       </c>
       <c r="E1453" t="n">
-        <v>2244.4</v>
+        <v>2242</v>
       </c>
       <c r="F1453" t="n">
-        <v>11909</v>
+        <v>11906.6</v>
       </c>
       <c r="G1453" t="n">
         <v>2</v>
@@ -48409,10 +48409,10 @@
         <v>48.6</v>
       </c>
       <c r="E1454" t="n">
-        <v>2664.2</v>
+        <v>2669.2</v>
       </c>
       <c r="F1454" t="n">
-        <v>13599</v>
+        <v>13604</v>
       </c>
       <c r="G1454" t="n">
         <v>6</v>
@@ -48475,10 +48475,10 @@
         <v>47.9</v>
       </c>
       <c r="E1456" t="n">
-        <v>2395.2</v>
+        <v>2407.6</v>
       </c>
       <c r="F1456" t="n">
-        <v>11999.3</v>
+        <v>12011.7</v>
       </c>
       <c r="G1456" t="n">
         <v>7</v>
@@ -48508,10 +48508,10 @@
         <v>43.3</v>
       </c>
       <c r="E1457" t="n">
-        <v>2513.3</v>
+        <v>2515.4</v>
       </c>
       <c r="F1457" t="n">
-        <v>10048.3</v>
+        <v>10050.4</v>
       </c>
       <c r="G1457" t="n">
         <v>8</v>
@@ -48541,10 +48541,10 @@
         <v>66.5</v>
       </c>
       <c r="E1458" t="n">
-        <v>2536</v>
+        <v>2548.4</v>
       </c>
       <c r="F1458" t="n">
-        <v>13247.1</v>
+        <v>13259.5</v>
       </c>
       <c r="G1458" t="n">
         <v>5</v>
@@ -48640,10 +48640,10 @@
         <v>66.40000000000001</v>
       </c>
       <c r="E1461" t="n">
-        <v>2310.8</v>
+        <v>2308.4</v>
       </c>
       <c r="F1461" t="n">
-        <v>11975.4</v>
+        <v>11973</v>
       </c>
       <c r="G1461" t="n">
         <v>6</v>
@@ -48673,10 +48673,10 @@
         <v>107</v>
       </c>
       <c r="E1462" t="n">
-        <v>2771.2</v>
+        <v>2776.2</v>
       </c>
       <c r="F1462" t="n">
-        <v>13706</v>
+        <v>13711</v>
       </c>
       <c r="G1462" t="n">
         <v>1</v>
@@ -48739,10 +48739,10 @@
         <v>67.40000000000001</v>
       </c>
       <c r="E1464" t="n">
-        <v>2462.6</v>
+        <v>2475</v>
       </c>
       <c r="F1464" t="n">
-        <v>12066.7</v>
+        <v>12079.1</v>
       </c>
       <c r="G1464" t="n">
         <v>4</v>
@@ -48772,10 +48772,10 @@
         <v>85.59999999999999</v>
       </c>
       <c r="E1465" t="n">
-        <v>2598.9</v>
+        <v>2601</v>
       </c>
       <c r="F1465" t="n">
-        <v>10133.9</v>
+        <v>10136</v>
       </c>
       <c r="G1465" t="n">
         <v>2</v>
@@ -48805,10 +48805,10 @@
         <v>100.6</v>
       </c>
       <c r="E1466" t="n">
-        <v>2636.6</v>
+        <v>2649</v>
       </c>
       <c r="F1466" t="n">
-        <v>13347.7</v>
+        <v>13360.1</v>
       </c>
       <c r="G1466" t="n">
         <v>1</v>
@@ -48904,10 +48904,10 @@
         <v>60.5</v>
       </c>
       <c r="E1469" t="n">
-        <v>2371.3</v>
+        <v>2368.9</v>
       </c>
       <c r="F1469" t="n">
-        <v>12035.9</v>
+        <v>12033.5</v>
       </c>
       <c r="G1469" t="n">
         <v>7</v>
@@ -48937,10 +48937,10 @@
         <v>64.59999999999999</v>
       </c>
       <c r="E1470" t="n">
-        <v>2835.8</v>
+        <v>2840.8</v>
       </c>
       <c r="F1470" t="n">
-        <v>13770.6</v>
+        <v>13775.6</v>
       </c>
       <c r="G1470" t="n">
         <v>6</v>
@@ -49003,10 +49003,10 @@
         <v>55.2</v>
       </c>
       <c r="E1472" t="n">
-        <v>2517.8</v>
+        <v>2530.2</v>
       </c>
       <c r="F1472" t="n">
-        <v>12121.9</v>
+        <v>12134.3</v>
       </c>
       <c r="G1472" t="n">
         <v>8</v>
@@ -49036,10 +49036,10 @@
         <v>88</v>
       </c>
       <c r="E1473" t="n">
-        <v>2686.9</v>
+        <v>2689</v>
       </c>
       <c r="F1473" t="n">
-        <v>10221.9</v>
+        <v>10224</v>
       </c>
       <c r="G1473" t="n">
         <v>2</v>
@@ -49069,10 +49069,10 @@
         <v>70.09999999999999</v>
       </c>
       <c r="E1474" t="n">
-        <v>2706.7</v>
+        <v>2719.1</v>
       </c>
       <c r="F1474" t="n">
-        <v>13417.8</v>
+        <v>13430.2</v>
       </c>
       <c r="G1474" t="n">
         <v>4</v>
@@ -49168,10 +49168,10 @@
         <v>53</v>
       </c>
       <c r="E1477" t="n">
-        <v>2424.3</v>
+        <v>2421.9</v>
       </c>
       <c r="F1477" t="n">
-        <v>12088.9</v>
+        <v>12086.5</v>
       </c>
       <c r="G1477" t="n">
         <v>7</v>
@@ -49201,10 +49201,10 @@
         <v>59.8</v>
       </c>
       <c r="E1478" t="n">
-        <v>2895.6</v>
+        <v>2900.6</v>
       </c>
       <c r="F1478" t="n">
-        <v>13830.4</v>
+        <v>13835.4</v>
       </c>
       <c r="G1478" t="n">
         <v>6</v>
@@ -49267,10 +49267,10 @@
         <v>48.4</v>
       </c>
       <c r="E1480" t="n">
-        <v>2566.2</v>
+        <v>2578.6</v>
       </c>
       <c r="F1480" t="n">
-        <v>12170.3</v>
+        <v>12182.7</v>
       </c>
       <c r="G1480" t="n">
         <v>8</v>
@@ -49300,10 +49300,10 @@
         <v>104.8</v>
       </c>
       <c r="E1481" t="n">
-        <v>2791.7</v>
+        <v>2793.8</v>
       </c>
       <c r="F1481" t="n">
-        <v>10326.7</v>
+        <v>10328.8</v>
       </c>
       <c r="G1481" t="n">
         <v>1</v>
@@ -49333,10 +49333,10 @@
         <v>76.3</v>
       </c>
       <c r="E1482" t="n">
-        <v>2783</v>
+        <v>2795.4</v>
       </c>
       <c r="F1482" t="n">
-        <v>13494.1</v>
+        <v>13506.5</v>
       </c>
       <c r="G1482" t="n">
         <v>3</v>
@@ -49432,10 +49432,10 @@
         <v>75.09999999999999</v>
       </c>
       <c r="E1485" t="n">
-        <v>2499.4</v>
+        <v>2497</v>
       </c>
       <c r="F1485" t="n">
-        <v>12164</v>
+        <v>12161.6</v>
       </c>
       <c r="G1485" t="n">
         <v>4</v>
@@ -49465,10 +49465,10 @@
         <v>69.7</v>
       </c>
       <c r="E1486" t="n">
-        <v>2965.3</v>
+        <v>2970.3</v>
       </c>
       <c r="F1486" t="n">
-        <v>13900.1</v>
+        <v>13905.1</v>
       </c>
       <c r="G1486" t="n">
         <v>6</v>
@@ -49531,10 +49531,10 @@
         <v>44.90000000000001</v>
       </c>
       <c r="E1488" t="n">
-        <v>2611.1</v>
+        <v>2623.5</v>
       </c>
       <c r="F1488" t="n">
-        <v>12215.2</v>
+        <v>12227.6</v>
       </c>
       <c r="G1488" t="n">
         <v>8</v>
@@ -49564,10 +49564,10 @@
         <v>82.40000000000001</v>
       </c>
       <c r="E1489" t="n">
-        <v>2874.1</v>
+        <v>2876.2</v>
       </c>
       <c r="F1489" t="n">
-        <v>10409.1</v>
+        <v>10411.2</v>
       </c>
       <c r="G1489" t="n">
         <v>1</v>
@@ -49597,10 +49597,10 @@
         <v>94.09999999999999</v>
       </c>
       <c r="E1490" t="n">
-        <v>2877.1</v>
+        <v>2889.5</v>
       </c>
       <c r="F1490" t="n">
-        <v>13588.2</v>
+        <v>13600.6</v>
       </c>
       <c r="G1490" t="n">
         <v>3</v>
@@ -49696,10 +49696,10 @@
         <v>38.3</v>
       </c>
       <c r="E1493" t="n">
-        <v>2537.7</v>
+        <v>2535.3</v>
       </c>
       <c r="F1493" t="n">
-        <v>12202.3</v>
+        <v>12199.9</v>
       </c>
       <c r="G1493" t="n">
         <v>8</v>
@@ -49729,10 +49729,10 @@
         <v>52.9</v>
       </c>
       <c r="E1494" t="n">
-        <v>3018.2</v>
+        <v>3023.2</v>
       </c>
       <c r="F1494" t="n">
-        <v>13953</v>
+        <v>13958</v>
       </c>
       <c r="G1494" t="n">
         <v>6</v>
@@ -49795,10 +49795,10 @@
         <v>44.4</v>
       </c>
       <c r="E1496" t="n">
-        <v>2655.5</v>
+        <v>2667.9</v>
       </c>
       <c r="F1496" t="n">
-        <v>12259.6</v>
+        <v>12272</v>
       </c>
       <c r="G1496" t="n">
         <v>7</v>
@@ -49828,10 +49828,10 @@
         <v>95.3</v>
       </c>
       <c r="E1497" t="n">
-        <v>2969.4</v>
+        <v>2971.5</v>
       </c>
       <c r="F1497" t="n">
-        <v>10504.4</v>
+        <v>10506.5</v>
       </c>
       <c r="G1497" t="n">
         <v>1</v>
@@ -49861,10 +49861,10 @@
         <v>72.8</v>
       </c>
       <c r="E1498" t="n">
-        <v>2949.9</v>
+        <v>2962.3</v>
       </c>
       <c r="F1498" t="n">
-        <v>13661</v>
+        <v>13673.4</v>
       </c>
       <c r="G1498" t="n">
         <v>2</v>
@@ -49960,10 +49960,10 @@
         <v>39.8</v>
       </c>
       <c r="E1501" t="n">
-        <v>2577.5</v>
+        <v>2575.1</v>
       </c>
       <c r="F1501" t="n">
-        <v>12242.1</v>
+        <v>12239.7</v>
       </c>
       <c r="G1501" t="n">
         <v>8</v>
@@ -49993,10 +49993,10 @@
         <v>65.8</v>
       </c>
       <c r="E1502" t="n">
-        <v>3084</v>
+        <v>3089</v>
       </c>
       <c r="F1502" t="n">
-        <v>14018.8</v>
+        <v>14023.8</v>
       </c>
       <c r="G1502" t="n">
         <v>4</v>
@@ -50059,10 +50059,10 @@
         <v>52.7</v>
       </c>
       <c r="E1504" t="n">
-        <v>2708.2</v>
+        <v>2720.6</v>
       </c>
       <c r="F1504" t="n">
-        <v>12312.3</v>
+        <v>12324.7</v>
       </c>
       <c r="G1504" t="n">
         <v>6</v>
@@ -50092,10 +50092,10 @@
         <v>81.3</v>
       </c>
       <c r="E1505" t="n">
-        <v>3050.7</v>
+        <v>3052.8</v>
       </c>
       <c r="F1505" t="n">
-        <v>10585.7</v>
+        <v>10587.8</v>
       </c>
       <c r="G1505" t="n">
         <v>1</v>
@@ -50125,10 +50125,10 @@
         <v>70.59999999999999</v>
       </c>
       <c r="E1506" t="n">
-        <v>3020.5</v>
+        <v>3032.9</v>
       </c>
       <c r="F1506" t="n">
-        <v>13731.6</v>
+        <v>13744</v>
       </c>
       <c r="G1506" t="n">
         <v>4</v>
@@ -50224,10 +50224,10 @@
         <v>60.4</v>
       </c>
       <c r="E1509" t="n">
-        <v>2637.9</v>
+        <v>2635.5</v>
       </c>
       <c r="F1509" t="n">
-        <v>12302.5</v>
+        <v>12300.1</v>
       </c>
       <c r="G1509" t="n">
         <v>5</v>
@@ -50257,16 +50257,16 @@
         <v>53.9</v>
       </c>
       <c r="E1510" t="n">
-        <v>3137.9</v>
+        <v>3142.9</v>
       </c>
       <c r="F1510" t="n">
-        <v>14072.7</v>
+        <v>14077.7</v>
       </c>
       <c r="G1510" t="n">
         <v>7</v>
       </c>
       <c r="H1510" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I1510" t="n">
         <v>1</v>
@@ -50323,10 +50323,10 @@
         <v>53.2</v>
       </c>
       <c r="E1512" t="n">
-        <v>2761.4</v>
+        <v>2773.8</v>
       </c>
       <c r="F1512" t="n">
-        <v>12365.5</v>
+        <v>12377.9</v>
       </c>
       <c r="G1512" t="n">
         <v>8</v>
@@ -50356,16 +50356,16 @@
         <v>87.59999999999999</v>
       </c>
       <c r="E1513" t="n">
-        <v>3138.3</v>
+        <v>3140.4</v>
       </c>
       <c r="F1513" t="n">
-        <v>10673.3</v>
+        <v>10675.4</v>
       </c>
       <c r="G1513" t="n">
         <v>1</v>
       </c>
       <c r="H1513" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I1513" t="n">
         <v>8</v>
@@ -50389,16 +50389,16 @@
         <v>58.2</v>
       </c>
       <c r="E1514" t="n">
-        <v>3078.7</v>
+        <v>3091.1</v>
       </c>
       <c r="F1514" t="n">
-        <v>13789.8</v>
+        <v>13802.2</v>
       </c>
       <c r="G1514" t="n">
         <v>4</v>
       </c>
       <c r="H1514" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1514" t="n">
         <v>2</v>
@@ -50431,7 +50431,7 @@
         <v>5</v>
       </c>
       <c r="H1515" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1515" t="n">
         <v>3</v>
@@ -50488,10 +50488,10 @@
         <v>48.4</v>
       </c>
       <c r="E1517" t="n">
-        <v>2686.3</v>
+        <v>2683.9</v>
       </c>
       <c r="F1517" t="n">
-        <v>12350.9</v>
+        <v>12348.5</v>
       </c>
       <c r="G1517" t="n">
         <v>6</v>
@@ -50521,10 +50521,10 @@
         <v>47.6</v>
       </c>
       <c r="E1518" t="n">
-        <v>3185.5</v>
+        <v>3190.5</v>
       </c>
       <c r="F1518" t="n">
-        <v>14120.3</v>
+        <v>14125.3</v>
       </c>
       <c r="G1518" t="n">
         <v>7</v>
@@ -50587,10 +50587,10 @@
         <v>73.3</v>
       </c>
       <c r="E1520" t="n">
-        <v>2834.7</v>
+        <v>2847.1</v>
       </c>
       <c r="F1520" t="n">
-        <v>12438.8</v>
+        <v>12451.2</v>
       </c>
       <c r="G1520" t="n">
         <v>2</v>
@@ -50620,10 +50620,10 @@
         <v>97.7</v>
       </c>
       <c r="E1521" t="n">
-        <v>3236</v>
+        <v>3238.1</v>
       </c>
       <c r="F1521" t="n">
-        <v>10771</v>
+        <v>10773.1</v>
       </c>
       <c r="G1521" t="n">
         <v>1</v>
@@ -50653,10 +50653,10 @@
         <v>95.7</v>
       </c>
       <c r="E1522" t="n">
-        <v>3174.4</v>
+        <v>3186.8</v>
       </c>
       <c r="F1522" t="n">
-        <v>13885.5</v>
+        <v>13897.9</v>
       </c>
       <c r="G1522" t="n">
         <v>1</v>
@@ -50752,10 +50752,10 @@
         <v>68.2</v>
       </c>
       <c r="E1525" t="n">
-        <v>2754.5</v>
+        <v>2752.1</v>
       </c>
       <c r="F1525" t="n">
-        <v>12419.1</v>
+        <v>12416.7</v>
       </c>
       <c r="G1525" t="n">
         <v>4</v>
@@ -50785,10 +50785,10 @@
         <v>66.59999999999999</v>
       </c>
       <c r="E1526" t="n">
-        <v>3252.1</v>
+        <v>3257.1</v>
       </c>
       <c r="F1526" t="n">
-        <v>14186.9</v>
+        <v>14191.9</v>
       </c>
       <c r="G1526" t="n">
         <v>5</v>
@@ -50851,10 +50851,10 @@
         <v>46.4</v>
       </c>
       <c r="E1528" t="n">
-        <v>2881.1</v>
+        <v>2893.5</v>
       </c>
       <c r="F1528" t="n">
-        <v>12485.2</v>
+        <v>12497.6</v>
       </c>
       <c r="G1528" t="n">
         <v>6</v>
@@ -50884,10 +50884,10 @@
         <v>80.40000000000001</v>
       </c>
       <c r="E1529" t="n">
-        <v>3316.4</v>
+        <v>3318.5</v>
       </c>
       <c r="F1529" t="n">
-        <v>10851.4</v>
+        <v>10853.5</v>
       </c>
       <c r="G1529" t="n">
         <v>3</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -42733,7 +42733,7 @@
         <v>116.1</v>
       </c>
       <c r="E1282" t="n">
-        <v>794.1</v>
+        <v>794.0999999999999</v>
       </c>
       <c r="F1282" t="n">
         <v>11505.2</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -42733,7 +42733,7 @@
         <v>116.1</v>
       </c>
       <c r="E1282" t="n">
-        <v>794.0999999999999</v>
+        <v>794.1</v>
       </c>
       <c r="F1282" t="n">
         <v>11505.2</v>

--- a/datos/vistas_negocio/Fact_Global_Master.xlsx
+++ b/datos/vistas_negocio/Fact_Global_Master.xlsx
@@ -43258,16 +43258,16 @@
         </is>
       </c>
       <c r="D1298" t="n">
-        <v>77.90000000000001</v>
+        <v>151.9</v>
       </c>
       <c r="E1298" t="n">
-        <v>1018</v>
+        <v>1092</v>
       </c>
       <c r="F1298" t="n">
-        <v>11729.1</v>
+        <v>11803.1</v>
       </c>
       <c r="G1298" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1298" t="n">
         <v>7</v>
@@ -43291,19 +43291,19 @@
         </is>
       </c>
       <c r="D1299" t="n">
-        <v>54.8</v>
+        <v>149.1</v>
       </c>
       <c r="E1299" t="n">
-        <v>1142.6</v>
+        <v>1236.9</v>
       </c>
       <c r="F1299" t="n">
-        <v>11833.6</v>
+        <v>11927.9</v>
       </c>
       <c r="G1299" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H1299" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I1299" t="n">
         <v>2</v>
@@ -43324,16 +43324,16 @@
         </is>
       </c>
       <c r="D1300" t="n">
-        <v>68.8</v>
+        <v>128.3</v>
       </c>
       <c r="E1300" t="n">
-        <v>1129.5</v>
+        <v>1189</v>
       </c>
       <c r="F1300" t="n">
-        <v>10994.6</v>
+        <v>11054.1</v>
       </c>
       <c r="G1300" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1300" t="n">
         <v>5</v>
@@ -43357,19 +43357,19 @@
         </is>
       </c>
       <c r="D1301" t="n">
-        <v>60.2</v>
+        <v>108.2</v>
       </c>
       <c r="E1301" t="n">
-        <v>1153.7</v>
+        <v>1201.7</v>
       </c>
       <c r="F1301" t="n">
-        <v>10818.3</v>
+        <v>10866.3</v>
       </c>
       <c r="G1301" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H1301" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I1301" t="n">
         <v>5</v>
@@ -43390,16 +43390,16 @@
         </is>
       </c>
       <c r="D1302" t="n">
-        <v>62.8</v>
+        <v>163.7</v>
       </c>
       <c r="E1302" t="n">
-        <v>1282.7</v>
+        <v>1383.6</v>
       </c>
       <c r="F1302" t="n">
-        <v>12217.5</v>
+        <v>12318.4</v>
       </c>
       <c r="G1302" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H1302" t="n">
         <v>1</v>
@@ -43423,16 +43423,16 @@
         </is>
       </c>
       <c r="D1303" t="n">
-        <v>50.9</v>
+        <v>118.3</v>
       </c>
       <c r="E1303" t="n">
-        <v>991.7</v>
+        <v>1059.1</v>
       </c>
       <c r="F1303" t="n">
-        <v>9825.6</v>
+        <v>9893</v>
       </c>
       <c r="G1303" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H1303" t="n">
         <v>8</v>
@@ -43456,19 +43456,19 @@
         </is>
       </c>
       <c r="D1304" t="n">
-        <v>69.40000000000001</v>
+        <v>138.8</v>
       </c>
       <c r="E1304" t="n">
-        <v>1153.7</v>
+        <v>1223.1</v>
       </c>
       <c r="F1304" t="n">
-        <v>10757.8</v>
+        <v>10827.2</v>
       </c>
       <c r="G1304" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1304" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1304" t="n">
         <v>6</v>
@@ -43489,16 +43489,16 @@
         </is>
       </c>
       <c r="D1305" t="n">
-        <v>66.3</v>
+        <v>122.4</v>
       </c>
       <c r="E1305" t="n">
-        <v>1092.1</v>
+        <v>1148.2</v>
       </c>
       <c r="F1305" t="n">
-        <v>8627.1</v>
+        <v>8683.200000000001</v>
       </c>
       <c r="G1305" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1305" t="n">
         <v>6</v>
@@ -43525,10 +43525,10 @@
         <v>68</v>
       </c>
       <c r="E1306" t="n">
-        <v>1086</v>
+        <v>1160</v>
       </c>
       <c r="F1306" t="n">
-        <v>11797.1</v>
+        <v>11871.1</v>
       </c>
       <c r="G1306" t="n">
         <v>5</v>
@@ -43558,10 +43558,10 @@
         <v>89.2</v>
       </c>
       <c r="E1307" t="n">
-        <v>1231.8</v>
+        <v>1326.1</v>
       </c>
       <c r="F1307" t="n">
-        <v>11922.8</v>
+        <v>12017.1</v>
       </c>
       <c r="G1307" t="n">
         <v>2</v>
@@ -43591,16 +43591,16 @@
         <v>79.3</v>
       </c>
       <c r="E1308" t="n">
-        <v>1208.8</v>
+        <v>1268.3</v>
       </c>
       <c r="F1308" t="n">
-        <v>11073.9</v>
+        <v>11133.4</v>
       </c>
       <c r="G1308" t="n">
         <v>3</v>
       </c>
       <c r="H1308" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1308" t="n">
         <v>4</v>
@@ -43624,16 +43624,16 @@
         <v>61</v>
       </c>
       <c r="E1309" t="n">
-        <v>1214.7</v>
+        <v>1262.7</v>
       </c>
       <c r="F1309" t="n">
-        <v>10879.3</v>
+        <v>10927.3</v>
       </c>
       <c r="G1309" t="n">
         <v>6</v>
       </c>
       <c r="H1309" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1309" t="n">
         <v>5</v>
@@ -43657,10 +43657,10 @@
         <v>57.4</v>
       </c>
       <c r="E1310" t="n">
-        <v>1340.1</v>
+        <v>1441</v>
       </c>
       <c r="F1310" t="n">
-        <v>12274.9</v>
+        <v>12375.8</v>
       </c>
       <c r="G1310" t="n">
         <v>7</v>
@@ -43690,10 +43690,10 @@
         <v>46.4</v>
       </c>
       <c r="E1311" t="n">
-        <v>1038.1</v>
+        <v>1105.5</v>
       </c>
       <c r="F1311" t="n">
-        <v>9872</v>
+        <v>9939.4</v>
       </c>
       <c r="G1311" t="n">
         <v>8</v>
@@ -43723,10 +43723,10 @@
         <v>77.2</v>
       </c>
       <c r="E1312" t="n">
-        <v>1230.9</v>
+        <v>1300.3</v>
       </c>
       <c r="F1312" t="n">
-        <v>10835</v>
+        <v>10904.4</v>
       </c>
       <c r="G1312" t="n">
         <v>4</v>
@@ -43756,10 +43756,10 @@
         <v>95.2</v>
       </c>
       <c r="E1313" t="n">
-        <v>1187.3</v>
+        <v>1243.4</v>
       </c>
       <c r="F1313" t="n">
-        <v>8722.299999999999</v>
+        <v>8778.4</v>
       </c>
       <c r="G1313" t="n">
         <v>1</v>
@@ -43789,10 +43789,10 @@
         <v>78</v>
       </c>
       <c r="E1314" t="n">
-        <v>1164</v>
+        <v>1238</v>
       </c>
       <c r="F1314" t="n">
-        <v>11875.1</v>
+        <v>11949.1</v>
       </c>
       <c r="G1314" t="n">
         <v>3</v>
@@ -43822,10 +43822,10 @@
         <v>78.59999999999999</v>
       </c>
       <c r="E1315" t="n">
-        <v>1310.4</v>
+        <v>1404.7</v>
       </c>
       <c r="F1315" t="n">
-        <v>12001.4</v>
+        <v>12095.7</v>
       </c>
       <c r="G1315" t="n">
         <v>2</v>
@@ -43855,10 +43855,10 @@
         <v>76.90000000000001</v>
       </c>
       <c r="E1316" t="n">
-        <v>1285.7</v>
+        <v>1345.2</v>
       </c>
       <c r="F1316" t="n">
-        <v>11150.8</v>
+        <v>11210.3</v>
       </c>
       <c r="G1316" t="n">
         <v>4</v>
@@ -43888,10 +43888,10 @@
         <v>48.4</v>
       </c>
       <c r="E1317" t="n">
-        <v>1263.1</v>
+        <v>1311.1</v>
       </c>
       <c r="F1317" t="n">
-        <v>10927.7</v>
+        <v>10975.7</v>
       </c>
       <c r="G1317" t="n">
         <v>8</v>
@@ -43921,10 +43921,10 @@
         <v>67.59999999999999</v>
       </c>
       <c r="E1318" t="n">
-        <v>1407.7</v>
+        <v>1508.6</v>
       </c>
       <c r="F1318" t="n">
-        <v>12342.5</v>
+        <v>12443.4</v>
       </c>
       <c r="G1318" t="n">
         <v>5</v>
@@ -43954,10 +43954,10 @@
         <v>58.1</v>
       </c>
       <c r="E1319" t="n">
-        <v>1096.2</v>
+        <v>1163.6</v>
       </c>
       <c r="F1319" t="n">
-        <v>9930.1</v>
+        <v>9997.5</v>
       </c>
       <c r="G1319" t="n">
         <v>7</v>
@@ -43987,10 +43987,10 @@
         <v>61.4</v>
       </c>
       <c r="E1320" t="n">
-        <v>1292.3</v>
+        <v>1361.7</v>
       </c>
       <c r="F1320" t="n">
-        <v>10896.4</v>
+        <v>10965.8</v>
       </c>
       <c r="G1320" t="n">
         <v>6</v>
@@ -44020,10 +44020,10 @@
         <v>81.59999999999999</v>
       </c>
       <c r="E1321" t="n">
-        <v>1268.9</v>
+        <v>1325</v>
       </c>
       <c r="F1321" t="n">
-        <v>8803.9</v>
+        <v>8860</v>
       </c>
       <c r="G1321" t="n">
         <v>1</v>
@@ -44053,10 +44053,10 @@
         <v>67.5</v>
       </c>
       <c r="E1322" t="n">
-        <v>1231.5</v>
+        <v>1305.5</v>
       </c>
       <c r="F1322" t="n">
-        <v>11942.6</v>
+        <v>12016.6</v>
       </c>
       <c r="G1322" t="n">
         <v>5</v>
@@ -44086,10 +44086,10 @@
         <v>69.8</v>
       </c>
       <c r="E1323" t="n">
-        <v>1380.2</v>
+        <v>1474.5</v>
       </c>
       <c r="F1323" t="n">
-        <v>12071.2</v>
+        <v>12165.5</v>
       </c>
       <c r="G1323" t="n">
         <v>2</v>
@@ -44119,16 +44119,16 @@
         <v>68.3</v>
       </c>
       <c r="E1324" t="n">
-        <v>1354</v>
+        <v>1413.5</v>
       </c>
       <c r="F1324" t="n">
-        <v>11219.1</v>
+        <v>11278.6</v>
       </c>
       <c r="G1324" t="n">
         <v>3</v>
       </c>
       <c r="H1324" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1324" t="n">
         <v>4</v>
@@ -44152,10 +44152,10 @@
         <v>52.1</v>
       </c>
       <c r="E1325" t="n">
-        <v>1315.2</v>
+        <v>1363.2</v>
       </c>
       <c r="F1325" t="n">
-        <v>10979.8</v>
+        <v>11027.8</v>
       </c>
       <c r="G1325" t="n">
         <v>8</v>
@@ -44185,10 +44185,10 @@
         <v>79.7</v>
       </c>
       <c r="E1326" t="n">
-        <v>1487.4</v>
+        <v>1588.3</v>
       </c>
       <c r="F1326" t="n">
-        <v>12422.2</v>
+        <v>12523.1</v>
       </c>
       <c r="G1326" t="n">
         <v>1</v>
@@ -44218,10 +44218,10 @@
         <v>58</v>
       </c>
       <c r="E1327" t="n">
-        <v>1154.2</v>
+        <v>1221.6</v>
       </c>
       <c r="F1327" t="n">
-        <v>9988.1</v>
+        <v>10055.5</v>
       </c>
       <c r="G1327" t="n">
         <v>7</v>
@@ -44251,16 +44251,16 @@
         <v>59.5</v>
       </c>
       <c r="E1328" t="n">
-        <v>1351.8</v>
+        <v>1421.2</v>
       </c>
       <c r="F1328" t="n">
-        <v>10955.9</v>
+        <v>11025.3</v>
       </c>
       <c r="G1328" t="n">
         <v>6</v>
       </c>
       <c r="H1328" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1328" t="n">
         <v>6</v>
@@ -44284,10 +44284,10 @@
         <v>68.10000000000001</v>
       </c>
       <c r="E1329" t="n">
-        <v>1337</v>
+        <v>1393.1</v>
       </c>
       <c r="F1329" t="n">
-        <v>8872</v>
+        <v>8928.1</v>
       </c>
       <c r="G1329" t="n">
         <v>4</v>
@@ -44317,10 +44317,10 @@
         <v>58.6</v>
       </c>
       <c r="E1330" t="n">
-        <v>1290.1</v>
+        <v>1364.1</v>
       </c>
       <c r="F1330" t="n">
-        <v>12001.2</v>
+        <v>12075.2</v>
       </c>
       <c r="G1330" t="n">
         <v>6</v>
@@ -44350,10 +44350,10 @@
         <v>105.7</v>
       </c>
       <c r="E1331" t="n">
-        <v>1485.9</v>
+        <v>1580.2</v>
       </c>
       <c r="F1331" t="n">
-        <v>12176.9</v>
+        <v>12271.2</v>
       </c>
       <c r="G1331" t="n">
         <v>1</v>
@@ -44383,10 +44383,10 @@
         <v>58.4</v>
       </c>
       <c r="E1332" t="n">
-        <v>1412.4</v>
+        <v>1471.9</v>
       </c>
       <c r="F1332" t="n">
-        <v>11277.5</v>
+        <v>11337</v>
       </c>
       <c r="G1332" t="n">
         <v>7</v>
@@ -44416,10 +44416,10 @@
         <v>57.4</v>
       </c>
       <c r="E1333" t="n">
-        <v>1372.6</v>
+        <v>1420.6</v>
       </c>
       <c r="F1333" t="n">
-        <v>11037.2</v>
+        <v>11085.2</v>
       </c>
       <c r="G1333" t="n">
         <v>8</v>
@@ -44428,7 +44428,7 @@
         <v>6</v>
       </c>
       <c r="I1333" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1334">
@@ -44449,10 +44449,10 @@
         <v>83.40000000000001</v>
       </c>
       <c r="E1334" t="n">
-        <v>1570.8</v>
+        <v>1671.7</v>
       </c>
       <c r="F1334" t="n">
-        <v>12505.6</v>
+        <v>12606.5</v>
       </c>
       <c r="G1334" t="n">
         <v>3</v>
@@ -44482,10 +44482,10 @@
         <v>74.3</v>
       </c>
       <c r="E1335" t="n">
-        <v>1228.5</v>
+        <v>1295.9</v>
       </c>
       <c r="F1335" t="n">
-        <v>10062.4</v>
+        <v>10129.8</v>
       </c>
       <c r="G1335" t="n">
         <v>4</v>
@@ -44515,19 +44515,19 @@
         <v>72</v>
       </c>
       <c r="E1336" t="n">
-        <v>1423.8</v>
+        <v>1493.2</v>
       </c>
       <c r="F1336" t="n">
-        <v>11027.9</v>
+        <v>11097.3</v>
       </c>
       <c r="G1336" t="n">
         <v>5</v>
       </c>
       <c r="H1336" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1336" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1337">
@@ -44548,16 +44548,16 @@
         <v>87.09999999999999</v>
       </c>
       <c r="E1337" t="n">
-        <v>1424.1</v>
+        <v>1480.2</v>
       </c>
       <c r="F1337" t="n">
-        <v>8959.1</v>
+        <v>9015.200000000001</v>
       </c>
       <c r="G1337" t="n">
         <v>2</v>
       </c>
       <c r="H1337" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1337" t="n">
         <v>8</v>
@@ -44581,10 +44581,10 @@
         <v>61.2</v>
       </c>
       <c r="E1338" t="n">
-        <v>1351.3</v>
+        <v>1425.3</v>
       </c>
       <c r="F1338" t="n">
-        <v>12062.4</v>
+        <v>12136.4</v>
       </c>
       <c r="G1338" t="n">
         <v>5</v>
@@ -44614,10 +44614,10 @@
         <v>55.59999999999999</v>
       </c>
       <c r="E1339" t="n">
-        <v>1541.5</v>
+        <v>1635.8</v>
       </c>
       <c r="F1339" t="n">
-        <v>12232.5</v>
+        <v>12326.8</v>
       </c>
       <c r="G1339" t="n">
         <v>7</v>
@@ -44647,10 +44647,10 @@
         <v>50.59999999999999</v>
       </c>
       <c r="E1340" t="n">
-        <v>1463</v>
+        <v>1522.5</v>
       </c>
       <c r="F1340" t="n">
-        <v>11328.1</v>
+        <v>11387.6</v>
       </c>
       <c r="G1340" t="n">
         <v>8</v>
@@ -44680,10 +44680,10 @@
         <v>62.40000000000001</v>
       </c>
       <c r="E1341" t="n">
-        <v>1435</v>
+        <v>1483</v>
       </c>
       <c r="F1341" t="n">
-        <v>11099.6</v>
+        <v>11147.6</v>
       </c>
       <c r="G1341" t="n">
         <v>4</v>
@@ -44713,10 +44713,10 @@
         <v>81.90000000000001</v>
       </c>
       <c r="E1342" t="n">
-        <v>1652.7</v>
+        <v>1753.6</v>
       </c>
       <c r="F1342" t="n">
-        <v>12587.5</v>
+        <v>12688.4</v>
       </c>
       <c r="G1342" t="n">
         <v>2</v>
@@ -44746,10 +44746,10 @@
         <v>63.3</v>
       </c>
       <c r="E1343" t="n">
-        <v>1291.8</v>
+        <v>1359.2</v>
       </c>
       <c r="F1343" t="n">
-        <v>10125.7</v>
+        <v>10193.1</v>
       </c>
       <c r="G1343" t="n">
         <v>3</v>
@@ -44779,10 +44779,10 @@
         <v>86</v>
       </c>
       <c r="E1344" t="n">
-        <v>1509.8</v>
+        <v>1579.2</v>
       </c>
       <c r="F1344" t="n">
-        <v>11113.9</v>
+        <v>11183.3</v>
       </c>
       <c r="G1344" t="n">
         <v>1</v>
@@ -44812,10 +44812,10 @@
         <v>58.1</v>
       </c>
       <c r="E1345" t="n">
-        <v>1482.2</v>
+        <v>1538.3</v>
       </c>
       <c r="F1345" t="n">
-        <v>9017.200000000001</v>
+        <v>9073.299999999999</v>
       </c>
       <c r="G1345" t="n">
         <v>6</v>
@@ -44845,10 +44845,10 @@
         <v>64.2</v>
       </c>
       <c r="E1346" t="n">
-        <v>1415.5</v>
+        <v>1489.5</v>
       </c>
       <c r="F1346" t="n">
-        <v>12126.6</v>
+        <v>12200.6</v>
       </c>
       <c r="G1346" t="n">
         <v>5</v>
@@ -44878,10 +44878,10 @@
         <v>88.7</v>
       </c>
       <c r="E1347" t="n">
-        <v>1630.2</v>
+        <v>1724.5</v>
       </c>
       <c r="F1347" t="n">
-        <v>12321.2</v>
+        <v>12415.5</v>
       </c>
       <c r="G1347" t="n">
         <v>1</v>
@@ -44911,16 +44911,16 @@
         <v>76.8</v>
       </c>
       <c r="E1348" t="n">
-        <v>1539.8</v>
+        <v>1599.3</v>
       </c>
       <c r="F1348" t="n">
-        <v>11404.9</v>
+        <v>11464.4</v>
       </c>
       <c r="G1348" t="n">
         <v>3</v>
       </c>
       <c r="H1348" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1348" t="n">
         <v>4</v>
@@ -44944,10 +44944,10 @@
         <v>45</v>
       </c>
       <c r="E1349" t="n">
-        <v>1480</v>
+        <v>1528</v>
       </c>
       <c r="F1349" t="n">
-        <v>11144.6</v>
+        <v>11192.6</v>
       </c>
       <c r="G1349" t="n">
         <v>8</v>
@@ -44977,10 +44977,10 @@
         <v>81.2</v>
       </c>
       <c r="E1350" t="n">
-        <v>1733.9</v>
+        <v>1834.8</v>
       </c>
       <c r="F1350" t="n">
-        <v>12668.7</v>
+        <v>12769.6</v>
       </c>
       <c r="G1350" t="n">
         <v>2</v>
@@ -45010,10 +45010,10 @@
         <v>63.7</v>
       </c>
       <c r="E1351" t="n">
-        <v>1355.5</v>
+        <v>1422.9</v>
       </c>
       <c r="F1351" t="n">
-        <v>10189.4</v>
+        <v>10256.8</v>
       </c>
       <c r="G1351" t="n">
         <v>6</v>
@@ -45043,10 +45043,10 @@
         <v>67.7</v>
       </c>
       <c r="E1352" t="n">
-        <v>1577.5</v>
+        <v>1646.9</v>
       </c>
       <c r="F1352" t="n">
-        <v>11181.6</v>
+        <v>11251</v>
       </c>
       <c r="G1352" t="n">
         <v>4</v>
@@ -45076,16 +45076,16 @@
         <v>60.2</v>
       </c>
       <c r="E1353" t="n">
-        <v>1542.4</v>
+        <v>1598.5</v>
       </c>
       <c r="F1353" t="n">
-        <v>9077.4</v>
+        <v>9133.5</v>
       </c>
       <c r="G1353" t="n">
         <v>7</v>
       </c>
       <c r="H1353" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1353" t="n">
         <v>8</v>
@@ -45109,10 +45109,10 @@
         <v>88.09999999999999</v>
       </c>
       <c r="E1354" t="n">
-        <v>1503.6</v>
+        <v>1577.6</v>
       </c>
       <c r="F1354" t="n">
-        <v>12214.7</v>
+        <v>12288.7</v>
       </c>
       <c r="G1354" t="n">
         <v>3</v>
@@ -45142,10 +45142,10 @@
         <v>59.9</v>
       </c>
       <c r="E1355" t="n">
-        <v>1690.1</v>
+        <v>1784.4</v>
       </c>
       <c r="F1355" t="n">
-        <v>12381.1</v>
+        <v>12475.4</v>
       </c>
       <c r="G1355" t="n">
         <v>6</v>
@@ -45175,10 +45175,10 @@
         <v>70.2</v>
       </c>
       <c r="E1356" t="n">
-        <v>1610</v>
+        <v>1669.5</v>
       </c>
       <c r="F1356" t="n">
-        <v>11475.1</v>
+        <v>11534.6</v>
       </c>
       <c r="G1356" t="n">
         <v>4</v>
@@ -45208,10 +45208,10 @@
         <v>0</v>
       </c>
       <c r="E1357" t="n">
-        <v>1480</v>
+        <v>1528</v>
       </c>
       <c r="F1357" t="n">
-        <v>11144.6</v>
+        <v>11192.6</v>
       </c>
       <c r="G1357" t="n">
         <v>8</v>
@@ -45241,10 +45241,10 @@
         <v>94</v>
       </c>
       <c r="E1358" t="n">
-        <v>1827.9</v>
+        <v>1928.8</v>
       </c>
       <c r="F1358" t="n">
-        <v>12762.7</v>
+        <v>12863.6</v>
       </c>
       <c r="G1358" t="n">
         <v>1</v>
@@ -45274,10 +45274,10 @@
         <v>61.6</v>
       </c>
       <c r="E1359" t="n">
-        <v>1417.1</v>
+        <v>1484.5</v>
       </c>
       <c r="F1359" t="n">
-        <v>10251</v>
+        <v>10318.4</v>
       </c>
       <c r="G1359" t="n">
         <v>5</v>
@@ -45307,10 +45307,10 @@
         <v>58.6</v>
       </c>
       <c r="E1360" t="n">
-        <v>1636.1</v>
+        <v>1705.5</v>
       </c>
       <c r="F1360" t="n">
-        <v>11240.2</v>
+        <v>11309.6</v>
       </c>
       <c r="G1360" t="n">
         <v>7</v>
@@ -45340,10 +45340,10 @@
         <v>89.5</v>
       </c>
       <c r="E1361" t="n">
-        <v>1631.9</v>
+        <v>1688</v>
       </c>
       <c r="F1361" t="n">
-        <v>9166.9</v>
+        <v>9223</v>
       </c>
       <c r="G1361" t="n">
         <v>2</v>
@@ -45373,10 +45373,10 @@
         <v>66.7</v>
       </c>
       <c r="E1362" t="n">
-        <v>1570.3</v>
+        <v>1644.3</v>
       </c>
       <c r="F1362" t="n">
-        <v>12281.4</v>
+        <v>12355.4</v>
       </c>
       <c r="G1362" t="n">
         <v>4</v>
@@ -45406,10 +45406,10 @@
         <v>35.8</v>
       </c>
       <c r="E1363" t="n">
-        <v>1725.9</v>
+        <v>1820.2</v>
       </c>
       <c r="F1363" t="n">
-        <v>12416.9</v>
+        <v>12511.2</v>
       </c>
       <c r="G1363" t="n">
         <v>8</v>
@@ -45439,10 +45439,10 @@
         <v>59.2</v>
       </c>
       <c r="E1364" t="n">
-        <v>1669.2</v>
+        <v>1728.7</v>
       </c>
       <c r="F1364" t="n">
-        <v>11534.3</v>
+        <v>11593.8</v>
       </c>
       <c r="G1364" t="n">
         <v>6</v>
@@ -45472,10 +45472,10 @@
         <v>82.2</v>
       </c>
       <c r="E1365" t="n">
-        <v>1562.2</v>
+        <v>1610.2</v>
       </c>
       <c r="F1365" t="n">
-        <v>11226.8</v>
+        <v>11274.8</v>
       </c>
       <c r="G1365" t="n">
         <v>2</v>
@@ -45505,10 +45505,10 @@
         <v>63</v>
       </c>
       <c r="E1366" t="n">
-        <v>1890.9</v>
+        <v>1991.8</v>
       </c>
       <c r="F1366" t="n">
-        <v>12825.7</v>
+        <v>12926.6</v>
       </c>
       <c r="G1366" t="n">
         <v>5</v>
@@ -45538,10 +45538,10 @@
         <v>56.6</v>
       </c>
       <c r="E1367" t="n">
-        <v>1473.7</v>
+        <v>1541.1</v>
       </c>
       <c r="F1367" t="n">
-        <v>10307.6</v>
+        <v>10375</v>
       </c>
       <c r="G1367" t="n">
         <v>7</v>
@@ -45571,16 +45571,16 @@
         <v>78.59999999999999</v>
       </c>
       <c r="E1368" t="n">
-        <v>1714.7</v>
+        <v>1784.1</v>
       </c>
       <c r="F1368" t="n">
-        <v>11318.8</v>
+        <v>11388.2</v>
       </c>
       <c r="G1368" t="n">
         <v>3</v>
       </c>
       <c r="H1368" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1368" t="n">
         <v>5</v>
@@ -45604,16 +45604,16 @@
         <v>87.3</v>
       </c>
       <c r="E1369" t="n">
-        <v>1719.2</v>
+        <v>1775.3</v>
       </c>
       <c r="F1369" t="n">
-        <v>9254.200000000001</v>
+        <v>9310.299999999999</v>
       </c>
       <c r="G1369" t="n">
         <v>1</v>
       </c>
       <c r="H1369" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1369" t="n">
         <v>8</v>
@@ -45637,10 +45637,10 @@
         <v>70.8</v>
       </c>
       <c r="E1370" t="n">
-        <v>1641.1</v>
+        <v>1715.1</v>
       </c>
       <c r="F1370" t="n">
-        <v>12352.2</v>
+        <v>12426.2</v>
       </c>
       <c r="G1370" t="n">
         <v>4</v>
@@ -45670,10 +45670,10 @@
         <v>76.5</v>
       </c>
       <c r="E1371" t="n">
-        <v>1802.4</v>
+        <v>1896.7</v>
       </c>
       <c r="F1371" t="n">
-        <v>12493.4</v>
+        <v>12587.7</v>
       </c>
       <c r="G1371" t="n">
         <v>2</v>
@@ -45703,10 +45703,10 @@
         <v>75.2</v>
       </c>
       <c r="E1372" t="n">
-        <v>1744.4</v>
+        <v>1803.9</v>
       </c>
       <c r="F1372" t="n">
-        <v>11609.5</v>
+        <v>11669</v>
       </c>
       <c r="G1372" t="n">
         <v>3</v>
@@ -45736,10 +45736,10 @@
         <v>46.7</v>
       </c>
       <c r="E1373" t="n">
-        <v>1608.9</v>
+        <v>1656.9</v>
       </c>
       <c r="F1373" t="n">
-        <v>11273.5</v>
+        <v>11321.5</v>
       </c>
       <c r="G1373" t="n">
         <v>8</v>
@@ -45769,10 +45769,10 @@
         <v>79.40000000000001</v>
       </c>
       <c r="E1374" t="n">
-        <v>1970.3</v>
+        <v>2071.2</v>
       </c>
       <c r="F1374" t="n">
-        <v>12905.1</v>
+        <v>13006</v>
       </c>
       <c r="G1374" t="n">
         <v>1</v>
@@ -45802,10 +45802,10 @@
         <v>56.59999999999999</v>
       </c>
       <c r="E1375" t="n">
-        <v>1530.3</v>
+        <v>1597.7</v>
       </c>
       <c r="F1375" t="n">
-        <v>10364.2</v>
+        <v>10431.6</v>
       </c>
       <c r="G1375" t="n">
         <v>6</v>
@@ -45835,10 +45835,10 @@
         <v>65.2</v>
       </c>
       <c r="E1376" t="n">
-        <v>1779.9</v>
+        <v>1849.3</v>
       </c>
       <c r="F1376" t="n">
-        <v>11384</v>
+        <v>11453.4</v>
       </c>
       <c r="G1376" t="n">
         <v>5</v>
@@ -45868,10 +45868,10 @@
         <v>54.8</v>
       </c>
       <c r="E1377" t="n">
-        <v>1774</v>
+        <v>1830.1</v>
       </c>
       <c r="F1377" t="n">
-        <v>9309</v>
+        <v>9365.1</v>
       </c>
       <c r="G1377" t="n">
         <v>7</v>
@@ -45901,10 +45901,10 @@
         <v>93.8</v>
       </c>
       <c r="E1378" t="n">
-        <v>1734.9</v>
+        <v>1808.9</v>
       </c>
       <c r="F1378" t="n">
-        <v>12446</v>
+        <v>12520</v>
       </c>
       <c r="G1378" t="n">
         <v>2</v>
@@ -45934,10 +45934,10 @@
         <v>65.2</v>
       </c>
       <c r="E1379" t="n">
-        <v>1867.6</v>
+        <v>1961.9</v>
       </c>
       <c r="F1379" t="n">
-        <v>12558.6</v>
+        <v>12652.9</v>
       </c>
       <c r="G1379" t="n">
         <v>7</v>
@@ -45967,10 +45967,10 @@
         <v>97.59999999999999</v>
       </c>
       <c r="E1380" t="n">
-        <v>1842</v>
+        <v>1901.5</v>
       </c>
       <c r="F1380" t="n">
-        <v>11707.1</v>
+        <v>11766.6</v>
       </c>
       <c r="G1380" t="n">
         <v>1</v>
@@ -46000,10 +46000,10 @@
         <v>63.3</v>
       </c>
       <c r="E1381" t="n">
-        <v>1672.2</v>
+        <v>1720.2</v>
       </c>
       <c r="F1381" t="n">
-        <v>11336.8</v>
+        <v>11384.8</v>
       </c>
       <c r="G1381" t="n">
         <v>8</v>
@@ -46033,10 +46033,10 @@
         <v>79.3</v>
       </c>
       <c r="E1382" t="n">
-        <v>2049.6</v>
+        <v>2150.5</v>
       </c>
       <c r="F1382" t="n">
-        <v>12984.4</v>
+        <v>13085.3</v>
       </c>
       <c r="G1382" t="n">
         <v>5</v>
@@ -46066,10 +46066,10 @@
         <v>81.7</v>
       </c>
       <c r="E1383" t="n">
-        <v>1612</v>
+        <v>1679.4</v>
       </c>
       <c r="F1383" t="n">
-        <v>10445.9</v>
+        <v>10513.3</v>
       </c>
       <c r="G1383" t="n">
         <v>4</v>
@@ -46099,16 +46099,16 @@
         <v>67.40000000000001</v>
       </c>
       <c r="E1384" t="n">
-        <v>1847.3</v>
+        <v>1916.7</v>
       </c>
       <c r="F1384" t="n">
-        <v>11451.4</v>
+        <v>11520.8</v>
       </c>
       <c r="G1384" t="n">
         <v>6</v>
       </c>
       <c r="H1384" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1384" t="n">
         <v>5</v>
@@ -46132,16 +46132,16 @@
         <v>82.59999999999999</v>
       </c>
       <c r="E1385" t="n">
-        <v>1856.6</v>
+        <v>1912.7</v>
       </c>
       <c r="F1385" t="n">
-        <v>9391.6</v>
+        <v>9447.700000000001</v>
       </c>
       <c r="G1385" t="n">
         <v>3</v>
       </c>
       <c r="H1385" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1385" t="n">
         <v>8</v>
@@ -46165,10 +46165,10 @@
         <v>100.5</v>
       </c>
       <c r="E1386" t="n">
-        <v>1835.4</v>
+        <v>1909.4</v>
       </c>
       <c r="F1386" t="n">
-        <v>12546.5</v>
+        <v>12620.5</v>
       </c>
       <c r="G1386" t="n">
         <v>1</v>
@@ -46198,10 +46198,10 @@
         <v>80.3</v>
       </c>
       <c r="E1387" t="n">
-        <v>1947.9</v>
+        <v>2042.2</v>
       </c>
       <c r="F1387" t="n">
-        <v>12638.9</v>
+        <v>12733.2</v>
       </c>
       <c r="G1387" t="n">
         <v>2</v>
@@ -46231,16 +46231,16 @@
         <v>60.3</v>
       </c>
       <c r="E1388" t="n">
-        <v>1902.3</v>
+        <v>1961.8</v>
       </c>
       <c r="F1388" t="n">
-        <v>11767.4</v>
+        <v>11826.9</v>
       </c>
       <c r="G1388" t="n">
         <v>6</v>
       </c>
       <c r="H1388" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1388" t="n">
         <v>4</v>
@@ -46264,10 +46264,10 @@
         <v>67.59999999999999</v>
       </c>
       <c r="E1389" t="n">
-        <v>1739.8</v>
+        <v>1787.8</v>
       </c>
       <c r="F1389" t="n">
-        <v>11404.4</v>
+        <v>11452.4</v>
       </c>
       <c r="G1389" t="n">
         <v>4</v>
@@ -46297,10 +46297,10 @@
         <v>70.2</v>
       </c>
       <c r="E1390" t="n">
-        <v>2119.8</v>
+        <v>2220.7</v>
       </c>
       <c r="F1390" t="n">
-        <v>13054.6</v>
+        <v>13155.5</v>
       </c>
       <c r="G1390" t="n">
         <v>3</v>
@@ -46330,10 +46330,10 @@
         <v>61.2</v>
       </c>
       <c r="E1391" t="n">
-        <v>1673.2</v>
+        <v>1740.6</v>
       </c>
       <c r="F1391" t="n">
-        <v>10507.1</v>
+        <v>10574.5</v>
       </c>
       <c r="G1391" t="n">
         <v>5</v>
@@ -46363,16 +46363,16 @@
         <v>50.8</v>
       </c>
       <c r="E1392" t="n">
-        <v>1898.1</v>
+        <v>1967.5</v>
       </c>
       <c r="F1392" t="n">
-        <v>11502.2</v>
+        <v>11571.6</v>
       </c>
       <c r="G1392" t="n">
         <v>8</v>
       </c>
       <c r="H1392" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I1392" t="n">
         <v>5</v>
@@ -46396,10 +46396,10 @@
         <v>58.9</v>
       </c>
       <c r="E1393" t="n">
-        <v>1915.5</v>
+        <v>1971.6</v>
       </c>
       <c r="F1393" t="n">
-        <v>9450.5</v>
+        <v>9506.6</v>
       </c>
       <c r="G1393" t="n">
         <v>7</v>
@@ -46429,10 +46429,10 @@
         <v>92</v>
       </c>
       <c r="E1394" t="n">
-        <v>1927.4</v>
+        <v>2001.4</v>
       </c>
       <c r="F1394" t="n">
-        <v>12638.5</v>
+        <v>12712.5</v>
       </c>
       <c r="G1394" t="n">
         <v>2</v>
@@ -46462,10 +46462,10 @@
         <v>77.2</v>
       </c>
       <c r="E1395" t="n">
-        <v>2025.1</v>
+        <v>2119.4</v>
       </c>
       <c r="F1395" t="n">
-        <v>12716.1</v>
+        <v>12810.4</v>
       </c>
       <c r="G1395" t="n">
         <v>4</v>
@@ -46495,10 +46495,10 @@
         <v>80.3</v>
       </c>
       <c r="E1396" t="n">
-        <v>1982.6</v>
+        <v>2042.1</v>
       </c>
       <c r="F1396" t="n">
-        <v>11847.7</v>
+        <v>11907.2</v>
       </c>
       <c r="G1396" t="n">
         <v>3</v>
@@ -46528,10 +46528,10 @@
         <v>50.6</v>
       </c>
       <c r="E1397" t="n">
-        <v>1790.4</v>
+        <v>1838.4</v>
       </c>
       <c r="F1397" t="n">
-        <v>11455</v>
+        <v>11503</v>
       </c>
       <c r="G1397" t="n">
         <v>7</v>
@@ -46561,10 +46561,10 @@
         <v>76.7</v>
       </c>
       <c r="E1398" t="n">
-        <v>2196.5</v>
+        <v>2297.4</v>
       </c>
       <c r="F1398" t="n">
-        <v>13131.3</v>
+        <v>13232.2</v>
       </c>
       <c r="G1398" t="n">
         <v>5</v>
@@ -46594,10 +46594,10 @@
         <v>48.7</v>
       </c>
       <c r="E1399" t="n">
-        <v>1721.9</v>
+        <v>1789.3</v>
       </c>
       <c r="F1399" t="n">
-        <v>10555.8</v>
+        <v>10623.2</v>
       </c>
       <c r="G1399" t="n">
         <v>8</v>
@@ -46627,10 +46627,10 @@
         <v>92.5</v>
       </c>
       <c r="E1400" t="n">
-        <v>1990.6</v>
+        <v>2060</v>
       </c>
       <c r="F1400" t="n">
-        <v>11594.7</v>
+        <v>11664.1</v>
       </c>
       <c r="G1400" t="n">
         <v>1</v>
@@ -46660,10 +46660,10 @@
         <v>73.10000000000001</v>
       </c>
       <c r="E1401" t="n">
-        <v>1988.6</v>
+        <v>2044.7</v>
       </c>
       <c r="F1401" t="n">
-        <v>9523.6</v>
+        <v>9579.700000000001</v>
       </c>
       <c r="G1401" t="n">
         <v>6</v>
@@ -46693,10 +46693,10 @@
         <v>75.59999999999999</v>
       </c>
       <c r="E1402" t="n">
-        <v>2003</v>
+        <v>2077</v>
       </c>
       <c r="F1402" t="n">
-        <v>12714.1</v>
+        <v>12788.1</v>
       </c>
       <c r="G1402" t="n">
         <v>3</v>
@@ -46726,10 +46726,10 @@
         <v>84.09999999999999</v>
       </c>
       <c r="E1403" t="n">
-        <v>2109.2</v>
+        <v>2203.5</v>
       </c>
       <c r="F1403" t="n">
-        <v>12800.2</v>
+        <v>12894.5</v>
       </c>
       <c r="G1403" t="n">
         <v>1</v>
@@ -46759,10 +46759,10 @@
         <v>59.3</v>
       </c>
       <c r="E1404" t="n">
-        <v>2041.9</v>
+        <v>2101.4</v>
       </c>
       <c r="F1404" t="n">
-        <v>11907</v>
+        <v>11966.5</v>
       </c>
       <c r="G1404" t="n">
         <v>8</v>
@@ -46792,10 +46792,10 @@
         <v>71.5</v>
       </c>
       <c r="E1405" t="n">
-        <v>1861.9</v>
+        <v>1909.9</v>
       </c>
       <c r="F1405" t="n">
-        <v>11526.5</v>
+        <v>11574.5</v>
       </c>
       <c r="G1405" t="n">
         <v>6</v>
@@ -46825,10 +46825,10 @@
         <v>75.39999999999999</v>
       </c>
       <c r="E1406" t="n">
-        <v>2271.9</v>
+        <v>2372.8</v>
       </c>
       <c r="F1406" t="n">
-        <v>13206.7</v>
+        <v>13307.6</v>
       </c>
       <c r="G1406" t="n">
         <v>4</v>
@@ -46858,10 +46858,10 @@
         <v>62.7</v>
       </c>
       <c r="E1407" t="n">
-        <v>1784.6</v>
+        <v>1852</v>
       </c>
       <c r="F1407" t="n">
-        <v>10618.5</v>
+        <v>10685.9</v>
       </c>
       <c r="G1407" t="n">
         <v>7</v>
@@ -46891,16 +46891,16 @@
         <v>72</v>
       </c>
       <c r="E1408" t="n">
-        <v>2062.6</v>
+        <v>2132</v>
       </c>
       <c r="F1408" t="n">
-        <v>11666.7</v>
+        <v>11736.1</v>
       </c>
       <c r="G1408" t="n">
         <v>5</v>
       </c>
       <c r="H1408" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1408" t="n">
         <v>5</v>
@@ -46924,16 +46924,16 @@
         <v>79.09999999999999</v>
       </c>
       <c r="E1409" t="n">
-        <v>2067.7</v>
+        <v>2123.8</v>
       </c>
       <c r="F1409" t="n">
-        <v>9602.700000000001</v>
+        <v>9658.799999999999</v>
       </c>
       <c r="G1409" t="n">
         <v>2</v>
       </c>
       <c r="H1409" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1409" t="n">
         <v>8</v>
@@ -46957,10 +46957,10 @@
         <v>73.2</v>
       </c>
       <c r="E1410" t="n">
-        <v>2076.2</v>
+        <v>2150.2</v>
       </c>
       <c r="F1410" t="n">
-        <v>12787.3</v>
+        <v>12861.3</v>
       </c>
       <c r="G1410" t="n">
         <v>2</v>
@@ -46990,10 +46990,10 @@
         <v>62.7</v>
       </c>
       <c r="E1411" t="n">
-        <v>2171.9</v>
+        <v>2266.2</v>
       </c>
       <c r="F1411" t="n">
-        <v>12862.9</v>
+        <v>12957.2</v>
       </c>
       <c r="G1411" t="n">
         <v>5</v>
@@ -47023,10 +47023,10 @@
         <v>49.2</v>
       </c>
       <c r="E1412" t="n">
-        <v>2091.1</v>
+        <v>2150.6</v>
       </c>
       <c r="F1412" t="n">
-        <v>11956.2</v>
+        <v>12015.7</v>
       </c>
       <c r="G1412" t="n">
         <v>6</v>
@@ -47056,10 +47056,10 @@
         <v>43.9</v>
       </c>
       <c r="E1413" t="n">
-        <v>1905.8</v>
+        <v>1953.8</v>
       </c>
       <c r="F1413" t="n">
-        <v>11570.4</v>
+        <v>11618.4</v>
       </c>
       <c r="G1413" t="n">
         <v>7</v>
@@ -47089,10 +47089,10 @@
         <v>71.2</v>
       </c>
       <c r="E1414" t="n">
-        <v>2343.1</v>
+        <v>2444</v>
       </c>
       <c r="F1414" t="n">
-        <v>13277.9</v>
+        <v>13378.8</v>
       </c>
       <c r="G1414" t="n">
         <v>3</v>
@@ -47122,10 +47122,10 @@
         <v>64.09999999999999</v>
       </c>
       <c r="E1415" t="n">
-        <v>1848.7</v>
+        <v>1916.1</v>
       </c>
       <c r="F1415" t="n">
-        <v>10682.6</v>
+        <v>10750</v>
       </c>
       <c r="G1415" t="n">
         <v>4</v>
@@ -47155,10 +47155,10 @@
         <v>42.9</v>
       </c>
       <c r="E1416" t="n">
-        <v>2105.5</v>
+        <v>2174.9</v>
       </c>
       <c r="F1416" t="n">
-        <v>11709.6</v>
+        <v>11779</v>
       </c>
       <c r="G1416" t="n">
         <v>8</v>
@@ -47188,10 +47188,10 @@
         <v>73.8</v>
       </c>
       <c r="E1417" t="n">
-        <v>2141.5</v>
+        <v>2197.6</v>
       </c>
       <c r="F1417" t="n">
-        <v>9676.5</v>
+        <v>9732.6</v>
       </c>
       <c r="G1417" t="n">
         <v>1</v>
@@ -47221,10 +47221,10 @@
         <v>79.3</v>
       </c>
       <c r="E1418" t="n">
-        <v>2155.5</v>
+        <v>2229.5</v>
       </c>
       <c r="F1418" t="n">
-        <v>12866.6</v>
+        <v>12940.6</v>
       </c>
       <c r="G1418" t="n">
         <v>1</v>
@@ -47254,10 +47254,10 @@
         <v>62.3</v>
       </c>
       <c r="E1419" t="n">
-        <v>2234.2</v>
+        <v>2328.5</v>
       </c>
       <c r="F1419" t="n">
-        <v>12925.2</v>
+        <v>13019.5</v>
       </c>
       <c r="G1419" t="n">
         <v>4</v>
@@ -47287,10 +47287,10 @@
         <v>50.4</v>
       </c>
       <c r="E1420" t="n">
-        <v>2141.5</v>
+        <v>2201</v>
       </c>
       <c r="F1420" t="n">
-        <v>12006.6</v>
+        <v>12066.1</v>
       </c>
       <c r="G1420" t="n">
         <v>7</v>
@@ -47320,10 +47320,10 @@
         <v>48.8</v>
       </c>
       <c r="E1421" t="n">
-        <v>1954.6</v>
+        <v>2002.6</v>
       </c>
       <c r="F1421" t="n">
-        <v>11619.2</v>
+        <v>11667.2</v>
       </c>
       <c r="G1421" t="n">
         <v>8</v>
@@ -47353,10 +47353,10 @@
         <v>75</v>
       </c>
       <c r="E1422" t="n">
-        <v>2418.1</v>
+        <v>2519</v>
       </c>
       <c r="F1422" t="n">
-        <v>13352.9</v>
+        <v>13453.8</v>
       </c>
       <c r="G1422" t="n">
         <v>2</v>
@@ -47386,10 +47386,10 @@
         <v>64.5</v>
       </c>
       <c r="E1423" t="n">
-        <v>1913.2</v>
+        <v>1980.6</v>
       </c>
       <c r="F1423" t="n">
-        <v>10747.1</v>
+        <v>10814.5</v>
       </c>
       <c r="G1423" t="n">
         <v>3</v>
@@ -47419,10 +47419,10 @@
         <v>59.7</v>
       </c>
       <c r="E1424" t="n">
-        <v>2165.2</v>
+        <v>2234.6</v>
       </c>
       <c r="F1424" t="n">
-        <v>11769.3</v>
+        <v>11838.7</v>
       </c>
       <c r="G1424" t="n">
         <v>5</v>
@@ -47452,10 +47452,10 @@
         <v>57.7</v>
       </c>
       <c r="E1425" t="n">
-        <v>2199.2</v>
+        <v>2255.3</v>
       </c>
       <c r="F1425" t="n">
-        <v>9734.200000000001</v>
+        <v>9790.299999999999</v>
       </c>
       <c r="G1425" t="n">
         <v>6</v>
@@ -47485,10 +47485,10 @@
         <v>86.3</v>
       </c>
       <c r="E1426" t="n">
-        <v>2241.8</v>
+        <v>2315.8</v>
       </c>
       <c r="F1426" t="n">
-        <v>12952.9</v>
+        <v>13026.9</v>
       </c>
       <c r="G1426" t="n">
         <v>2</v>
@@ -47518,10 +47518,10 @@
         <v>75.59999999999999</v>
       </c>
       <c r="E1427" t="n">
-        <v>2309.8</v>
+        <v>2404.1</v>
       </c>
       <c r="F1427" t="n">
-        <v>13000.8</v>
+        <v>13095.1</v>
       </c>
       <c r="G1427" t="n">
         <v>3</v>
@@ -47551,10 +47551,10 @@
         <v>50.9</v>
       </c>
       <c r="E1428" t="n">
-        <v>2192.4</v>
+        <v>2251.9</v>
       </c>
       <c r="F1428" t="n">
-        <v>12057.5</v>
+        <v>12117</v>
       </c>
       <c r="G1428" t="n">
         <v>8</v>
@@ -47584,10 +47584,10 @@
         <v>65.3</v>
       </c>
       <c r="E1429" t="n">
-        <v>2019.9</v>
+        <v>2067.9</v>
       </c>
       <c r="F1429" t="n">
-        <v>11684.5</v>
+        <v>11732.5</v>
       </c>
       <c r="G1429" t="n">
         <v>4</v>
@@ -47617,10 +47617,10 @@
         <v>58.4</v>
       </c>
       <c r="E1430" t="n">
-        <v>2476.5</v>
+        <v>2577.4</v>
       </c>
       <c r="F1430" t="n">
-        <v>13411.3</v>
+        <v>13512.2</v>
       </c>
       <c r="G1430" t="n">
         <v>6</v>
@@ -47650,10 +47650,10 @@
         <v>58.6</v>
       </c>
       <c r="E1431" t="n">
-        <v>1971.8</v>
+        <v>2039.2</v>
       </c>
       <c r="F1431" t="n">
-        <v>10805.7</v>
+        <v>10873.1</v>
       </c>
       <c r="G1431" t="n">
         <v>5</v>
@@ -47683,10 +47683,10 @@
         <v>55.3</v>
       </c>
       <c r="E1432" t="n">
-        <v>2220.5</v>
+        <v>2289.9</v>
       </c>
       <c r="F1432" t="n">
-        <v>11824.6</v>
+        <v>11894</v>
       </c>
       <c r="G1432" t="n">
         <v>7</v>
@@ -47716,10 +47716,10 @@
         <v>96</v>
       </c>
       <c r="E1433" t="n">
-        <v>2295.2</v>
+        <v>2351.3</v>
       </c>
       <c r="F1433" t="n">
-        <v>9830.200000000001</v>
+        <v>9886.299999999999</v>
       </c>
       <c r="G1433" t="n">
         <v>1</v>
@@ -47749,10 +47749,10 @@
         <v>84.5</v>
       </c>
       <c r="E1434" t="n">
-        <v>2326.3</v>
+        <v>2400.3</v>
       </c>
       <c r="F1434" t="n">
-        <v>13037.4</v>
+        <v>13111.4</v>
       </c>
       <c r="G1434" t="n">
         <v>1</v>
@@ -47782,10 +47782,10 @@
         <v>66.59999999999999</v>
       </c>
       <c r="E1435" t="n">
-        <v>2376.4</v>
+        <v>2470.7</v>
       </c>
       <c r="F1435" t="n">
-        <v>13067.4</v>
+        <v>13161.7</v>
       </c>
       <c r="G1435" t="n">
         <v>4</v>
@@ -47815,10 +47815,10 @@
         <v>60.1</v>
       </c>
       <c r="E1436" t="n">
-        <v>2252.5</v>
+        <v>2312</v>
       </c>
       <c r="F1436" t="n">
-        <v>12117.6</v>
+        <v>12177.1</v>
       </c>
       <c r="G1436" t="n">
         <v>6</v>
@@ -47848,10 +47848,10 @@
         <v>74.09999999999999</v>
       </c>
       <c r="E1437" t="n">
-        <v>2094</v>
+        <v>2142</v>
       </c>
       <c r="F1437" t="n">
-        <v>11758.6</v>
+        <v>11806.6</v>
       </c>
       <c r="G1437" t="n">
         <v>3</v>
@@ -47881,10 +47881,10 @@
         <v>57.4</v>
       </c>
       <c r="E1438" t="n">
-        <v>2533.9</v>
+        <v>2634.8</v>
       </c>
       <c r="F1438" t="n">
-        <v>13468.7</v>
+        <v>13569.6</v>
       </c>
       <c r="G1438" t="n">
         <v>7</v>
@@ -47914,10 +47914,10 @@
         <v>0</v>
       </c>
       <c r="E1439" t="n">
-        <v>1971.8</v>
+        <v>2039.2</v>
       </c>
       <c r="F1439" t="n">
-        <v>10805.7</v>
+        <v>10873.1</v>
       </c>
       <c r="G1439" t="n">
         <v>8</v>
@@ -47947,10 +47947,10 @@
         <v>65.90000000000001</v>
       </c>
       <c r="E1440" t="n">
-        <v>2286.4</v>
+        <v>2355.8</v>
       </c>
       <c r="F1440" t="n">
-        <v>11890.5</v>
+        <v>11959.9</v>
       </c>
       <c r="G1440" t="n">
         <v>5</v>
@@ -47980,10 +47980,10 @@
         <v>76</v>
       </c>
       <c r="E1441" t="n">
-        <v>2371.2</v>
+        <v>2427.3</v>
       </c>
       <c r="F1441" t="n">
-        <v>9906.200000000001</v>
+        <v>9962.299999999999</v>
       </c>
       <c r="G1441" t="n">
         <v>2</v>
@@ -48013,10 +48013,10 @@
         <v>73.09999999999999</v>
       </c>
       <c r="E1442" t="n">
-        <v>2399.4</v>
+        <v>2473.4</v>
       </c>
       <c r="F1442" t="n">
-        <v>13110.5</v>
+        <v>13184.5</v>
       </c>
       <c r="G1442" t="n">
         <v>6</v>
@@ -48046,16 +48046,16 @@
         <v>92.90000000000001</v>
       </c>
       <c r="E1443" t="n">
-        <v>2469.3</v>
+        <v>2563.6</v>
       </c>
       <c r="F1443" t="n">
-        <v>13160.3</v>
+        <v>13254.6</v>
       </c>
       <c r="G1443" t="n">
         <v>2</v>
       </c>
       <c r="H1443" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1443" t="n">
         <v>2</v>
@@ -48079,10 +48079,10 @@
         <v>51.6</v>
       </c>
       <c r="E1444" t="n">
-        <v>2304.1</v>
+        <v>2363.6</v>
       </c>
       <c r="F1444" t="n">
-        <v>12169.2</v>
+        <v>12228.7</v>
       </c>
       <c r="G1444" t="n">
         <v>8</v>
@@ -48112,10 +48112,10 @@
         <v>62.1</v>
       </c>
       <c r="E1445" t="n">
-        <v>2156.1</v>
+        <v>2204.1</v>
       </c>
       <c r="F1445" t="n">
-        <v>11820.7</v>
+        <v>11868.7</v>
       </c>
       <c r="G1445" t="n">
         <v>7</v>
@@ -48145,10 +48145,10 @@
         <v>86.7</v>
       </c>
       <c r="E1446" t="n">
-        <v>2620.6</v>
+        <v>2721.5</v>
       </c>
       <c r="F1446" t="n">
-        <v>13555.4</v>
+        <v>13656.3</v>
       </c>
       <c r="G1446" t="n">
         <v>4</v>
@@ -48178,10 +48178,10 @@
         <v>88.2</v>
       </c>
       <c r="E1447" t="n">
-        <v>2060</v>
+        <v>2127.4</v>
       </c>
       <c r="F1447" t="n">
-        <v>10893.9</v>
+        <v>10961.3</v>
       </c>
       <c r="G1447" t="n">
         <v>3</v>
@@ -48211,10 +48211,10 @@
         <v>73.3</v>
       </c>
       <c r="E1448" t="n">
-        <v>2359.7</v>
+        <v>2429.1</v>
       </c>
       <c r="F1448" t="n">
-        <v>11963.8</v>
+        <v>12033.2</v>
       </c>
       <c r="G1448" t="n">
         <v>5</v>
@@ -48244,16 +48244,16 @@
         <v>100.9</v>
       </c>
       <c r="E1449" t="n">
-        <v>2472.1</v>
+        <v>2528.2</v>
       </c>
       <c r="F1449" t="n">
-        <v>10007.1</v>
+        <v>10063.2</v>
       </c>
       <c r="G1449" t="n">
         <v>1</v>
       </c>
       <c r="H1449" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1449" t="n">
         <v>8</v>
@@ -48277,10 +48277,10 @@
         <v>82.5</v>
       </c>
       <c r="E1450" t="n">
-        <v>2481.9</v>
+        <v>2555.9</v>
       </c>
       <c r="F1450" t="n">
-        <v>13193</v>
+        <v>13267</v>
       </c>
       <c r="G1450" t="n">
         <v>3</v>
@@ -48310,10 +48310,10 @@
         <v>73.5</v>
       </c>
       <c r="E1451" t="n">
-        <v>2542.8</v>
+        <v>2637.1</v>
       </c>
       <c r="F1451" t="n">
-        <v>13233.8</v>
+        <v>13328.1</v>
       </c>
       <c r="G1451" t="n">
         <v>4</v>
@@ -48343,10 +48343,10 @@
         <v>114.5</v>
       </c>
       <c r="E1452" t="n">
-        <v>2418.6</v>
+        <v>2478.1</v>
       </c>
       <c r="F1452" t="n">
-        <v>12283.7</v>
+        <v>12343.2</v>
       </c>
       <c r="G1452" t="n">
         <v>1</v>
@@ -48376,10 +48376,10 @@
         <v>85.90000000000001</v>
       </c>
       <c r="E1453" t="n">
-        <v>2242</v>
+        <v>2290</v>
       </c>
       <c r="F1453" t="n">
-        <v>11906.6</v>
+        <v>11954.6</v>
       </c>
       <c r="G1453" t="n">
         <v>2</v>
@@ -48409,10 +48409,10 @@
         <v>48.6</v>
       </c>
       <c r="E1454" t="n">
-        <v>2669.2</v>
+        <v>2770.1</v>
       </c>
       <c r="F1454" t="n">
-        <v>13604</v>
+        <v>13704.9</v>
       </c>
       <c r="G1454" t="n">
         <v>6</v>
@@ -48442,10 +48442,10 @@
         <v>52.8</v>
       </c>
       <c r="E1455" t="n">
-        <v>2112.8</v>
+        <v>2180.2</v>
       </c>
       <c r="F1455" t="n">
-        <v>10946.7</v>
+        <v>11014.1</v>
       </c>
       <c r="G1455" t="n">
         <v>5</v>
@@ -48475,10 +48475,10 @@
         <v>47.9</v>
       </c>
       <c r="E1456" t="n">
-        <v>2407.6</v>
+        <v>2477</v>
       </c>
       <c r="F1456" t="n">
-        <v>12011.7</v>
+        <v>12081.1</v>
       </c>
       <c r="G1456" t="n">
         <v>7</v>
@@ -48508,10 +48508,10 @@
         <v>43.3</v>
       </c>
       <c r="E1457" t="n">
-        <v>2515.4</v>
+        <v>2571.5</v>
       </c>
       <c r="F1457" t="n">
-        <v>10050.4</v>
+        <v>10106.5</v>
       </c>
       <c r="G1457" t="n">
         <v>8</v>
@@ -48541,10 +48541,10 @@
         <v>66.5</v>
       </c>
       <c r="E1458" t="n">
-        <v>2548.4</v>
+        <v>2622.4</v>
       </c>
       <c r="F1458" t="n">
-        <v>13259.5</v>
+        <v>13333.5</v>
       </c>
       <c r="G1458" t="n">
         <v>5</v>
@@ -48574,10 +48574,10 @@
         <v>65.5</v>
       </c>
       <c r="E1459" t="n">
-        <v>2608.3</v>
+        <v>2702.6</v>
       </c>
       <c r="F1459" t="n">
-        <v>13299.3</v>
+        <v>13393.6</v>
       </c>
       <c r="G1459" t="n">
         <v>7</v>
@@ -48607,10 +48607,10 @@
         <v>83.90000000000001</v>
       </c>
       <c r="E1460" t="n">
-        <v>2502.5</v>
+        <v>2562</v>
       </c>
       <c r="F1460" t="n">
-        <v>12367.6</v>
+        <v>12427.1</v>
       </c>
       <c r="G1460" t="n">
         <v>3</v>
@@ -48640,10 +48640,10 @@
         <v>66.40000000000001</v>
       </c>
       <c r="E1461" t="n">
-        <v>2308.4</v>
+        <v>2356.4</v>
       </c>
       <c r="F1461" t="n">
-        <v>11973</v>
+        <v>12021</v>
       </c>
       <c r="G1461" t="n">
         <v>6</v>
@@ -48673,10 +48673,10 @@
         <v>107</v>
       </c>
       <c r="E1462" t="n">
-        <v>2776.2</v>
+        <v>2877.1</v>
       </c>
       <c r="F1462" t="n">
-        <v>13711</v>
+        <v>13811.9</v>
       </c>
       <c r="G1462" t="n">
         <v>1</v>
@@ -48706,10 +48706,10 @@
         <v>46.5</v>
       </c>
       <c r="E1463" t="n">
-        <v>2159.3</v>
+        <v>2226.7</v>
       </c>
       <c r="F1463" t="n">
-        <v>10993.2</v>
+        <v>11060.6</v>
       </c>
       <c r="G1463" t="n">
         <v>8</v>
@@ -48739,10 +48739,10 @@
         <v>67.40000000000001</v>
       </c>
       <c r="E1464" t="n">
-        <v>2475</v>
+        <v>2544.4</v>
       </c>
       <c r="F1464" t="n">
-        <v>12079.1</v>
+        <v>12148.5</v>
       </c>
       <c r="G1464" t="n">
         <v>4</v>
@@ -48772,10 +48772,10 @@
         <v>85.59999999999999</v>
       </c>
       <c r="E1465" t="n">
-        <v>2601</v>
+        <v>2657.1</v>
       </c>
       <c r="F1465" t="n">
-        <v>10136</v>
+        <v>10192.1</v>
       </c>
       <c r="G1465" t="n">
         <v>2</v>
@@ -48805,10 +48805,10 @@
         <v>100.6</v>
       </c>
       <c r="E1466" t="n">
-        <v>2649</v>
+        <v>2723</v>
       </c>
       <c r="F1466" t="n">
-        <v>13360.1</v>
+        <v>13434.1</v>
       </c>
       <c r="G1466" t="n">
         <v>1</v>
@@ -48838,16 +48838,16 @@
         <v>65.90000000000001</v>
       </c>
       <c r="E1467" t="n">
-        <v>2674.2</v>
+        <v>2768.5</v>
       </c>
       <c r="F1467" t="n">
-        <v>13365.2</v>
+        <v>13459.5</v>
       </c>
       <c r="G1467" t="n">
         <v>5</v>
       </c>
       <c r="H1467" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1467" t="n">
         <v>2</v>
@@ -48871,10 +48871,10 @@
         <v>70.8</v>
       </c>
       <c r="E1468" t="n">
-        <v>2573.3</v>
+        <v>2632.8</v>
       </c>
       <c r="F1468" t="n">
-        <v>12438.4</v>
+        <v>12497.9</v>
       </c>
       <c r="G1468" t="n">
         <v>4</v>
@@ -48904,10 +48904,10 @@
         <v>60.5</v>
       </c>
       <c r="E1469" t="n">
-        <v>2368.9</v>
+        <v>2416.9</v>
       </c>
       <c r="F1469" t="n">
-        <v>12033.5</v>
+        <v>12081.5</v>
       </c>
       <c r="G1469" t="n">
         <v>7</v>
@@ -48937,10 +48937,10 @@
         <v>64.59999999999999</v>
       </c>
       <c r="E1470" t="n">
-        <v>2840.8</v>
+        <v>2941.7</v>
       </c>
       <c r="F1470" t="n">
-        <v>13775.6</v>
+        <v>13876.5</v>
       </c>
       <c r="G1470" t="n">
         <v>6</v>
@@ -48970,10 +48970,10 @@
         <v>73.7</v>
       </c>
       <c r="E1471" t="n">
-        <v>2233</v>
+        <v>2300.4</v>
       </c>
       <c r="F1471" t="n">
-        <v>11066.9</v>
+        <v>11134.3</v>
       </c>
       <c r="G1471" t="n">
         <v>3</v>
@@ -49003,10 +49003,10 @@
         <v>55.2</v>
       </c>
       <c r="E1472" t="n">
-        <v>2530.2</v>
+        <v>2599.6</v>
       </c>
       <c r="F1472" t="n">
-        <v>12134.3</v>
+        <v>12203.7</v>
       </c>
       <c r="G1472" t="n">
         <v>8</v>
@@ -49036,16 +49036,16 @@
         <v>88</v>
       </c>
       <c r="E1473" t="n">
-        <v>2689</v>
+        <v>2745.1</v>
       </c>
       <c r="F1473" t="n">
-        <v>10224</v>
+        <v>10280.1</v>
       </c>
       <c r="G1473" t="n">
         <v>2</v>
       </c>
       <c r="H1473" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I1473" t="n">
         <v>8</v>
@@ -49069,10 +49069,10 @@
         <v>70.09999999999999</v>
       </c>
       <c r="E1474" t="n">
-        <v>2719.1</v>
+        <v>2793.1</v>
       </c>
       <c r="F1474" t="n">
-        <v>13430.2</v>
+        <v>13504.2</v>
       </c>
       <c r="G1474" t="n">
         <v>4</v>
@@ -49102,10 +49102,10 @@
         <v>77.90000000000001</v>
       </c>
       <c r="E1475" t="n">
-        <v>2752.1</v>
+        <v>2846.4</v>
       </c>
       <c r="F1475" t="n">
-        <v>13443.1</v>
+        <v>13537.4</v>
       </c>
       <c r="G1475" t="n">
         <v>3</v>
@@ -49135,10 +49135,10 @@
         <v>80.8</v>
       </c>
       <c r="E1476" t="n">
-        <v>2654.1</v>
+        <v>2713.6</v>
       </c>
       <c r="F1476" t="n">
-        <v>12519.2</v>
+        <v>12578.7</v>
       </c>
       <c r="G1476" t="n">
         <v>2</v>
@@ -49168,10 +49168,10 @@
         <v>53</v>
       </c>
       <c r="E1477" t="n">
-        <v>2421.9</v>
+        <v>2469.9</v>
       </c>
       <c r="F1477" t="n">
-        <v>12086.5</v>
+        <v>12134.5</v>
       </c>
       <c r="G1477" t="n">
         <v>7</v>
@@ -49201,10 +49201,10 @@
         <v>59.8</v>
       </c>
       <c r="E1478" t="n">
-        <v>2900.6</v>
+        <v>3001.5</v>
       </c>
       <c r="F1478" t="n">
-        <v>13835.4</v>
+        <v>13936.3</v>
       </c>
       <c r="G1478" t="n">
         <v>6</v>
@@ -49234,10 +49234,10 @@
         <v>68.39999999999999</v>
       </c>
       <c r="E1479" t="n">
-        <v>2301.4</v>
+        <v>2368.8</v>
       </c>
       <c r="F1479" t="n">
-        <v>11135.3</v>
+        <v>11202.7</v>
       </c>
       <c r="G1479" t="n">
         <v>5</v>
@@ -49267,10 +49267,10 @@
         <v>48.4</v>
       </c>
       <c r="E1480" t="n">
-        <v>2578.6</v>
+        <v>2648</v>
       </c>
       <c r="F1480" t="n">
-        <v>12182.7</v>
+        <v>12252.1</v>
       </c>
       <c r="G1480" t="n">
         <v>8</v>
@@ -49300,10 +49300,10 @@
         <v>104.8</v>
       </c>
       <c r="E1481" t="n">
-        <v>2793.8</v>
+        <v>2849.9</v>
       </c>
       <c r="F1481" t="n">
-        <v>10328.8</v>
+        <v>10384.9</v>
       </c>
       <c r="G1481" t="n">
         <v>1</v>
@@ -49333,10 +49333,10 @@
         <v>76.3</v>
       </c>
       <c r="E1482" t="n">
-        <v>2795.4</v>
+        <v>2869.4</v>
       </c>
       <c r="F1482" t="n">
-        <v>13506.5</v>
+        <v>13580.5</v>
       </c>
       <c r="G1482" t="n">
         <v>3</v>
@@ -49366,10 +49366,10 @@
         <v>73.3</v>
       </c>
       <c r="E1483" t="n">
-        <v>2825.4</v>
+        <v>2919.7</v>
       </c>
       <c r="F1483" t="n">
-        <v>13516.4</v>
+        <v>13610.7</v>
       </c>
       <c r="G1483" t="n">
         <v>5</v>
@@ -49399,10 +49399,10 @@
         <v>56.5</v>
       </c>
       <c r="E1484" t="n">
-        <v>2710.6</v>
+        <v>2770.1</v>
       </c>
       <c r="F1484" t="n">
-        <v>12575.7</v>
+        <v>12635.2</v>
       </c>
       <c r="G1484" t="n">
         <v>7</v>
@@ -49432,10 +49432,10 @@
         <v>75.09999999999999</v>
       </c>
       <c r="E1485" t="n">
-        <v>2497</v>
+        <v>2545</v>
       </c>
       <c r="F1485" t="n">
-        <v>12161.6</v>
+        <v>12209.6</v>
       </c>
       <c r="G1485" t="n">
         <v>4</v>
@@ -49465,10 +49465,10 @@
         <v>69.7</v>
       </c>
       <c r="E1486" t="n">
-        <v>2970.3</v>
+        <v>3071.2</v>
       </c>
       <c r="F1486" t="n">
-        <v>13905.1</v>
+        <v>14006</v>
       </c>
       <c r="G1486" t="n">
         <v>6</v>
@@ -49498,10 +49498,10 @@
         <v>80.09999999999999</v>
       </c>
       <c r="E1487" t="n">
-        <v>2381.5</v>
+        <v>2448.9</v>
       </c>
       <c r="F1487" t="n">
-        <v>11215.4</v>
+        <v>11282.8</v>
       </c>
       <c r="G1487" t="n">
         <v>2</v>
@@ -49531,10 +49531,10 @@
         <v>44.90000000000001</v>
       </c>
       <c r="E1488" t="n">
-        <v>2623.5</v>
+        <v>2692.9</v>
       </c>
       <c r="F1488" t="n">
-        <v>12227.6</v>
+        <v>12297</v>
       </c>
       <c r="G1488" t="n">
         <v>8</v>
@@ -49564,10 +49564,10 @@
         <v>82.40000000000001</v>
       </c>
       <c r="E1489" t="n">
-        <v>2876.2</v>
+        <v>2932.3</v>
       </c>
       <c r="F1489" t="n">
-        <v>10411.2</v>
+        <v>10467.3</v>
       </c>
       <c r="G1489" t="n">
         <v>1</v>
@@ -49597,10 +49597,10 @@
         <v>94.09999999999999</v>
       </c>
       <c r="E1490" t="n">
-        <v>2889.5</v>
+        <v>2963.5</v>
       </c>
       <c r="F1490" t="n">
-        <v>13600.6</v>
+        <v>13674.6</v>
       </c>
       <c r="G1490" t="n">
         <v>3</v>
@@ -49630,10 +49630,10 @@
         <v>94.90000000000001</v>
       </c>
       <c r="E1491" t="n">
-        <v>2920.3</v>
+        <v>3014.6</v>
       </c>
       <c r="F1491" t="n">
-        <v>13611.3</v>
+        <v>13705.6</v>
       </c>
       <c r="G1491" t="n">
         <v>2</v>
@@ -49663,10 +49663,10 @@
         <v>75.2</v>
       </c>
       <c r="E1492" t="n">
-        <v>2785.8</v>
+        <v>2845.3</v>
       </c>
       <c r="F1492" t="n">
-        <v>12650.9</v>
+        <v>12710.4</v>
       </c>
       <c r="G1492" t="n">
         <v>5</v>
@@ -49696,10 +49696,10 @@
         <v>38.3</v>
       </c>
       <c r="E1493" t="n">
-        <v>2535.3</v>
+        <v>2583.3</v>
       </c>
       <c r="F1493" t="n">
-        <v>12199.9</v>
+        <v>12247.9</v>
       </c>
       <c r="G1493" t="n">
         <v>8</v>
@@ -49729,10 +49729,10 @@
         <v>52.9</v>
       </c>
       <c r="E1494" t="n">
-        <v>3023.2</v>
+        <v>3124.1</v>
       </c>
       <c r="F1494" t="n">
-        <v>13958</v>
+        <v>14058.9</v>
       </c>
       <c r="G1494" t="n">
         <v>6</v>
@@ -49762,10 +49762,10 @@
         <v>78.7</v>
       </c>
       <c r="E1495" t="n">
-        <v>2460.2</v>
+        <v>2527.6</v>
       </c>
       <c r="F1495" t="n">
-        <v>11294.1</v>
+        <v>11361.5</v>
       </c>
       <c r="G1495" t="n">
         <v>4</v>
@@ -49795,10 +49795,10 @@
         <v>44.4</v>
       </c>
       <c r="E1496" t="n">
-        <v>2667.9</v>
+        <v>2737.3</v>
       </c>
       <c r="F1496" t="n">
-        <v>12272</v>
+        <v>12341.4</v>
       </c>
       <c r="G1496" t="n">
         <v>7</v>
@@ -49828,10 +49828,10 @@
         <v>95.3</v>
       </c>
       <c r="E1497" t="n">
-        <v>2971.5</v>
+        <v>3027.6</v>
       </c>
       <c r="F1497" t="n">
-        <v>10506.5</v>
+        <v>10562.6</v>
       </c>
       <c r="G1497" t="n">
         <v>1</v>
@@ -49861,10 +49861,10 @@
         <v>72.8</v>
       </c>
       <c r="E1498" t="n">
-        <v>2962.3</v>
+        <v>3036.3</v>
       </c>
       <c r="F1498" t="n">
-        <v>13673.4</v>
+        <v>13747.4</v>
       </c>
       <c r="G1498" t="n">
         <v>2</v>
@@ -49873,7 +49873,7 @@
         <v>4</v>
       </c>
       <c r="I1498" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1499">
@@ -49894,10 +49894,10 @@
         <v>42</v>
       </c>
       <c r="E1499" t="n">
-        <v>2962.3</v>
+        <v>3056.6</v>
       </c>
       <c r="F1499" t="n">
-        <v>13653.3</v>
+        <v>13747.6</v>
       </c>
       <c r="G1499" t="n">
         <v>7</v>
@@ -49906,7 +49906,7 @@
         <v>3</v>
       </c>
       <c r="I1499" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1500">
@@ -49927,10 +49927,10 @@
         <v>65.10000000000001</v>
       </c>
       <c r="E1500" t="n">
-        <v>2850.9</v>
+        <v>2910.4</v>
       </c>
       <c r="F1500" t="n">
-        <v>12716</v>
+        <v>12775.5</v>
       </c>
       <c r="G1500" t="n">
         <v>5</v>
@@ -49960,10 +49960,10 @@
         <v>39.8</v>
       </c>
       <c r="E1501" t="n">
-        <v>2575.1</v>
+        <v>2623.1</v>
       </c>
       <c r="F1501" t="n">
-        <v>12239.7</v>
+        <v>12287.7</v>
       </c>
       <c r="G1501" t="n">
         <v>8</v>
@@ -49993,10 +49993,10 @@
         <v>65.8</v>
       </c>
       <c r="E1502" t="n">
-        <v>3089</v>
+        <v>3189.9</v>
       </c>
       <c r="F1502" t="n">
-        <v>14023.8</v>
+        <v>14124.7</v>
       </c>
       <c r="G1502" t="n">
         <v>4</v>
@@ -50026,10 +50026,10 @@
         <v>66.40000000000001</v>
       </c>
       <c r="E1503" t="n">
-        <v>2526.6</v>
+        <v>2594</v>
       </c>
       <c r="F1503" t="n">
-        <v>11360.5</v>
+        <v>11427.9</v>
       </c>
       <c r="G1503" t="n">
         <v>3</v>
@@ -50059,10 +50059,10 @@
         <v>52.7</v>
       </c>
       <c r="E1504" t="n">
-        <v>2720.6</v>
+        <v>2790</v>
       </c>
       <c r="F1504" t="n">
-        <v>12324.7</v>
+        <v>12394.1</v>
       </c>
       <c r="G1504" t="n">
         <v>6</v>
@@ -50092,10 +50092,10 @@
         <v>81.3</v>
       </c>
       <c r="E1505" t="n">
-        <v>3052.8</v>
+        <v>3108.9</v>
       </c>
       <c r="F1505" t="n">
-        <v>10587.8</v>
+        <v>10643.9</v>
       </c>
       <c r="G1505" t="n">
         <v>1</v>
@@ -50125,10 +50125,10 @@
         <v>70.59999999999999</v>
       </c>
       <c r="E1506" t="n">
-        <v>3032.9</v>
+        <v>3106.9</v>
       </c>
       <c r="F1506" t="n">
-        <v>13744</v>
+        <v>13818</v>
       </c>
       <c r="G1506" t="n">
         <v>4</v>
@@ -50137,7 +50137,7 @@
         <v>4</v>
       </c>
       <c r="I1506" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1507">
@@ -50158,10 +50158,10 @@
         <v>76.40000000000001</v>
       </c>
       <c r="E1507" t="n">
-        <v>3038.7</v>
+        <v>3133</v>
       </c>
       <c r="F1507" t="n">
-        <v>13729.7</v>
+        <v>13824</v>
       </c>
       <c r="G1507" t="n">
         <v>2</v>
@@ -50170,7 +50170,7 @@
         <v>3</v>
       </c>
       <c r="I1507" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1508">
@@ -50191,10 +50191,10 @@
         <v>60.3</v>
       </c>
       <c r="E1508" t="n">
-        <v>2911.2</v>
+        <v>2970.7</v>
       </c>
       <c r="F1508" t="n">
-        <v>12776.3</v>
+        <v>12835.8</v>
       </c>
       <c r="G1508" t="n">
         <v>6</v>
@@ -50224,10 +50224,10 @@
         <v>60.4</v>
       </c>
       <c r="E1509" t="n">
-        <v>2635.5</v>
+        <v>2683.5</v>
       </c>
       <c r="F1509" t="n">
-        <v>12300.1</v>
+        <v>12348.1</v>
       </c>
       <c r="G1509" t="n">
         <v>5</v>
@@ -50257,10 +50257,10 @@
         <v>53.9</v>
       </c>
       <c r="E1510" t="n">
-        <v>3142.9</v>
+        <v>3243.8</v>
       </c>
       <c r="F1510" t="n">
-        <v>14077.7</v>
+        <v>14178.6</v>
       </c>
       <c r="G1510" t="n">
         <v>7</v>
@@ -50290,10 +50290,10 @@
         <v>75.80000000000001</v>
       </c>
       <c r="E1511" t="n">
-        <v>2602.4</v>
+        <v>2669.8</v>
       </c>
       <c r="F1511" t="n">
-        <v>11436.3</v>
+        <v>11503.7</v>
       </c>
       <c r="G1511" t="n">
         <v>3</v>
@@ -50323,10 +50323,10 @@
         <v>53.2</v>
       </c>
       <c r="E1512" t="n">
-        <v>2773.8</v>
+        <v>2843.2</v>
       </c>
       <c r="F1512" t="n">
-        <v>12377.9</v>
+        <v>12447.3</v>
       </c>
       <c r="G1512" t="n">
         <v>8</v>
@@ -50356,10 +50356,10 @@
         <v>87.59999999999999</v>
       </c>
       <c r="E1513" t="n">
-        <v>3140.4</v>
+        <v>3196.5</v>
       </c>
       <c r="F1513" t="n">
-        <v>10675.4</v>
+        <v>10731.5</v>
       </c>
       <c r="G1513" t="n">
         <v>1</v>
@@ -50389,16 +50389,16 @@
         <v>58.2</v>
       </c>
       <c r="E1514" t="n">
-        <v>3091.1</v>
+        <v>3165.1</v>
       </c>
       <c r="F1514" t="n">
-        <v>13802.2</v>
+        <v>13876.2</v>
       </c>
       <c r="G1514" t="n">
         <v>4</v>
       </c>
       <c r="H1514" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I1514" t="n">
         <v>2</v>
@@ -50422,16 +50422,16 @@
         <v>49.3</v>
       </c>
       <c r="E1515" t="n">
-        <v>3088</v>
+        <v>3182.3</v>
       </c>
       <c r="F1515" t="n">
-        <v>13779</v>
+        <v>13873.3</v>
       </c>
       <c r="G1515" t="n">
         <v>5</v>
       </c>
       <c r="H1515" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1515" t="n">
         <v>3</v>
@@ -50455,10 +50455,10 @@
         <v>69.09999999999999</v>
       </c>
       <c r="E1516" t="n">
-        <v>2980.3</v>
+        <v>3039.8</v>
       </c>
       <c r="F1516" t="n">
-        <v>12845.4</v>
+        <v>12904.9</v>
       </c>
       <c r="G1516" t="n">
         <v>3</v>
@@ -50488,10 +50488,10 @@
         <v>48.4</v>
       </c>
       <c r="E1517" t="n">
-        <v>2683.9</v>
+        <v>2731.9</v>
       </c>
       <c r="F1517" t="n">
-        <v>12348.5</v>
+        <v>12396.5</v>
       </c>
       <c r="G1517" t="n">
         <v>6</v>
@@ -50521,10 +50521,10 @@
         <v>47.6</v>
       </c>
       <c r="E1518" t="n">
-        <v>3190.5</v>
+        <v>3291.4</v>
       </c>
       <c r="F1518" t="n">
-        <v>14125.3</v>
+        <v>14226.2</v>
       </c>
       <c r="G1518" t="n">
         <v>7</v>
@@ -50554,10 +50554,10 @@
         <v>34.8</v>
       </c>
       <c r="E1519" t="n">
-        <v>2637.2</v>
+        <v>2704.6</v>
       </c>
       <c r="F1519" t="n">
-        <v>11471.1</v>
+        <v>11538.5</v>
       </c>
       <c r="G1519" t="n">
         <v>8</v>
@@ -50587,10 +50587,10 @@
         <v>73.3</v>
       </c>
       <c r="E1520" t="n">
-        <v>2847.1</v>
+        <v>2916.5</v>
       </c>
       <c r="F1520" t="n">
-        <v>12451.2</v>
+        <v>12520.6</v>
       </c>
       <c r="G1520" t="n">
         <v>2</v>
@@ -50620,10 +50620,10 @@
         <v>97.7</v>
       </c>
       <c r="E1521" t="n">
-        <v>3238.1</v>
+        <v>3294.2</v>
       </c>
       <c r="F1521" t="n">
-        <v>10773.1</v>
+        <v>10829.2</v>
       </c>
       <c r="G1521" t="n">
         <v>1</v>
@@ -50653,10 +50653,10 @@
         <v>95.7</v>
       </c>
       <c r="E1522" t="n">
-        <v>3186.8</v>
+        <v>3260.8</v>
       </c>
       <c r="F1522" t="n">
-        <v>13897.9</v>
+        <v>13971.9</v>
       </c>
       <c r="G1522" t="n">
         <v>1</v>
@@ -50686,10 +50686,10 @@
         <v>0</v>
       </c>
       <c r="E1523" t="n">
-        <v>3088</v>
+        <v>3182.3</v>
       </c>
       <c r="F1523" t="n">
-        <v>13779</v>
+        <v>13873.3</v>
       </c>
       <c r="G1523" t="n">
         <v>8</v>
@@ -50719,10 +50719,10 @@
         <v>40.7</v>
       </c>
       <c r="E1524" t="n">
-        <v>3021</v>
+        <v>3080.5</v>
       </c>
       <c r="F1524" t="n">
-        <v>12886.1</v>
+        <v>12945.6</v>
       </c>
       <c r="G1524" t="n">
         <v>7</v>
@@ -50752,10 +50752,10 @@
         <v>68.2</v>
       </c>
       <c r="E1525" t="n">
-        <v>2752.1</v>
+        <v>2800.1</v>
       </c>
       <c r="F1525" t="n">
-        <v>12416.7</v>
+        <v>12464.7</v>
       </c>
       <c r="G1525" t="n">
         <v>4</v>
@@ -50785,10 +50785,10 @@
         <v>66.59999999999999</v>
       </c>
       <c r="E1526" t="n">
-        <v>3257.1</v>
+        <v>3358</v>
       </c>
       <c r="F1526" t="n">
-        <v>14191.9</v>
+        <v>14292.8</v>
       </c>
       <c r="G1526" t="n">
         <v>5</v>
@@ -50818,10 +50818,10 @@
         <v>80.59999999999999</v>
       </c>
       <c r="E1527" t="n">
-        <v>2717.8</v>
+        <v>2785.2</v>
       </c>
       <c r="F1527" t="n">
-        <v>11551.7</v>
+        <v>11619.1</v>
       </c>
       <c r="G1527" t="n">
         <v>2</v>
@@ -50851,10 +50851,10 @@
         <v>46.4</v>
       </c>
       <c r="E1528" t="n">
-        <v>2893.5</v>
+        <v>2962.9</v>
       </c>
       <c r="F1528" t="n">
-        <v>12497.6</v>
+        <v>12567</v>
       </c>
       <c r="G1528" t="n">
         <v>6</v>
@@ -50884,10 +50884,10 @@
         <v>80.40000000000001</v>
       </c>
       <c r="E1529" t="n">
-        <v>3318.5</v>
+        <v>3374.6</v>
       </c>
       <c r="F1529" t="n">
-        <v>10853.5</v>
+        <v>10909.6</v>
       </c>
       <c r="G1529" t="n">
         <v>3</v>
